--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894D563C-62FC-4E2F-B0CE-6B02FF836B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935188A9-9026-449F-94BB-9F218D846742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" xr2:uid="{5152B028-5D8D-40E5-B01B-F055ABF9B154}"/>
+    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5" xr2:uid="{5152B028-5D8D-40E5-B01B-F055ABF9B154}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -140,11 +140,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
+    <numFmt numFmtId="174" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,8 +178,120 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="19"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="62"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -188,8 +304,141 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="56"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="54"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -270,14 +519,941 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="56"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="27"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="27"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="56"/>
+      </top>
+      <bottom style="double">
+        <color indexed="56"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="809">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -317,17 +1493,827 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="809">
+    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{4C1F6AF9-C2C6-4D4F-BDB4-24A84AC67864}"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{64F93E83-777D-42DA-BFB9-80EEB14E8A5C}"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{E36321BB-21BF-4833-A71B-6D02629D246A}"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{08A9312D-2785-494C-808A-016B96F64A71}"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{46EA7CBA-1313-428F-9EFA-37411A38FB3D}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{39CA57F4-2D9B-4BA2-92CD-29D379BDB0BE}"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{E27AE825-F08E-446E-8991-5A448447C099}"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{3F837449-132E-443E-84D8-0A4F1DE34552}"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{58213CE0-28DB-41FB-B176-C8B4D885ECD3}"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{AE866907-F8D6-4CCA-8DC9-EC63D679D7E4}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{1B47D904-B8A6-4D17-96B0-F9E58A45A12B}"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{E6338C18-6F5B-4352-8362-5A39C1FE6122}"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{5BCBD1D0-CD8B-40C7-8D13-9C2E1D684B75}"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{6E19A926-B979-4345-8CC2-05CB97AC6C26}"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{E6018A2A-00F8-4BA3-A660-693A91C5EA89}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{ADB4197C-A1E6-46CC-BAEE-E5D85A9A1EF8}"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{958198DC-62D7-45BF-8D5E-451B493AFEF9}"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{3A3351FF-CEA8-4388-98F1-00C83913E871}"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{92DBF5E1-63CA-42F0-9919-E89CF7F2DEC5}"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{A5656AF4-B335-4F4F-AC61-7B837FA39A82}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{57FC36DE-8AE6-42BD-BC5C-9ABEDD700664}"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{94707772-64DC-44F0-B5D7-10AD6C2888C5}"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{BA4D69A1-82F1-429B-826D-0929E6741888}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{3EDB7517-6444-4DCE-816F-2C3EDE1CB35C}"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{B1A7AE61-86F6-48EF-9712-BA0DA1995554}"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{02E4BB81-7B26-4238-AD73-7E2533BFCF0F}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{5ADAFF5F-98E7-495B-8C8A-7987827B8563}"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{BD7E5BF3-E7B8-4882-8689-2E3EF2107A67}"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{3AF3C8A6-695B-4BA1-9F00-256CE2262AF4}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{FB869613-E827-46DA-8398-1E071E0552FC}"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{0DBF0DDE-06CF-492B-848C-81A56BDC8392}"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{8EB7DD2F-4736-41F9-86CB-5F8DA3721093}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{5A392FDF-B39D-4412-A269-F9CF0175F0E5}"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{6C7FD24B-CD26-4573-AF9F-C64763526438}"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{BF78EFDC-3ED5-488F-8410-EBAB5F7D5BBF}"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{2B3C0D7A-12B7-4FD8-972C-E4E86F420E11}"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{09836EBF-E128-4D11-99A9-4E8BEA5DDDE1}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{E4C5116E-06C2-4A98-B678-FF67121A1BD8}"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{5435718B-E367-4201-A107-CAD4ABED7B1C}"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{14D63FEA-2BDE-4617-94EF-96B423EF934B}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{8DC0406C-3861-45A5-9C89-4B22A1A0D3E5}"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{D595AD87-442A-4548-8427-DC15086AB880}"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{A5024469-DE0A-47B4-9D7B-E809AE6C0316}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{07E6E230-7601-43DC-B3A5-9126F578829B}"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{C5BD5A08-BC63-4B9E-819A-B72989AA4519}"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{01A20566-4462-4525-84CD-C1B7DB84A321}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{830BBF0A-F7C3-426D-954D-355A488A307A}"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{42335429-F6A4-4FD9-9F31-EDEB1EA21138}"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{736AC983-BE17-49BD-A12A-742BCF069FBC}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{0663239A-2F3A-4BA7-B4DC-5DD43EA736D2}"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{EA737BB3-C572-4941-B32E-28D22AEFE44E}"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{C38F7C0E-0678-456F-8671-863DA416F341}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{4BC2A840-7D8F-446D-A905-C6797B56CF14}"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{0AFE8E0F-9E1D-4A07-9285-2AD53A844797}"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{621FEE32-5965-43ED-93C8-D86BFFD5ACC7}"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{21C07476-710F-4EE4-BB5C-E7B3CEDA86A6}"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{F80B5B4E-63D6-4E9E-AC89-97610DACB31D}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{6479AA33-C55F-4C1F-9720-EA0C57B2F598}"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{4B4D600F-7116-4E24-AE4C-E4BD283484E8}"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{02A3FDE7-2491-41F7-BC1C-BF8C787623CE}"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{9C77428A-727A-484D-8D0E-32110E465DE6}"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{6AF969A7-E456-4400-A469-0141AFC94902}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{C7929753-A670-46D2-9D90-03B09C2D8AFE}"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{CB71EA2B-2CC3-4C39-B9FE-77961338725B}"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{D20514AF-549A-4BA1-9419-1BF2EA054412}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{22E9D53F-DBED-4E3B-9FE8-7AB03CD42B4B}"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{A5487202-3560-4049-AC12-945905769309}"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{6D5785B7-0A92-4A58-A869-3DE648F4E961}"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{11CF140A-A59B-44C3-9AC9-02708B562B0F}"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{4EA8705F-F732-45E0-9811-E3F6DDB76FCE}"/>
+    <cellStyle name="Buena 2" xfId="74" xr:uid="{FF140419-618D-4E1B-BE0A-46976549ABCC}"/>
+    <cellStyle name="Buena 3" xfId="75" xr:uid="{F8F9A4DC-EAC0-40C2-9CA5-A3A5466BAD1D}"/>
+    <cellStyle name="Buena 4" xfId="76" xr:uid="{91957E4D-896B-4FF2-90B8-B85EEE661892}"/>
+    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{C1D869BA-C367-41F5-A48E-08E72380BBCE}"/>
+    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{75A43D64-1D57-4621-A528-E6BA3B2817F6}"/>
+    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{1D4247DB-53A7-4FA6-88D2-14F5E05FF0CA}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{350163C5-0B5A-4211-AAB1-4486FF9997A4}"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{151B7195-2E52-451D-A2BC-2853F2C59FBC}"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{60AAD422-9116-4F63-80F9-CF1214148415}"/>
+    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{BEB8387D-972B-4978-80D6-C03EED4AD3CF}"/>
+    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{F0C8C395-9EDB-4A9F-8BB5-B4A36B59B8B4}"/>
+    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{FCCF11B4-8081-43F5-B331-E07578D8D4A6}"/>
+    <cellStyle name="Comma 2" xfId="121" xr:uid="{B1620963-1B87-4652-962B-182547FD4800}"/>
+    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{05F7F6A8-1080-4AF8-96D3-C9F32B1D1494}"/>
+    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{39B45B43-1908-4748-B21B-AA40BA00CBFC}"/>
+    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{DF5C0EA4-F1F6-4EEE-B90C-6A74642C2024}"/>
+    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{35C38597-1885-445B-9069-08C79EB1EA70}"/>
+    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{76754287-4BD0-494C-BA3A-AFCFF7A1BFD0}"/>
+    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{4A29A633-E092-4D5A-A2F2-C4BBF48E3175}"/>
+    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{B85ECD18-A060-4BC7-AE21-2E7CD492D787}"/>
+    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{2F90C461-1E95-4FD4-B057-7936BAF461E6}"/>
+    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{64EA65E7-CCB3-4FEC-854A-845E5867FA32}"/>
+    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{CECE3725-A2D4-4548-92AA-72BF57CA2078}"/>
+    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{E8C1293C-BF12-4477-A57B-5872F3011B52}"/>
+    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{4264603B-E6CC-42DD-AF7F-E6A886288DC4}"/>
+    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{BDE600DC-9AC4-485F-81B0-1D8FD2BE23A8}"/>
+    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{C409837C-8AF4-4F19-9D33-E3A3FFBDBFB8}"/>
+    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{5BD8E991-FA77-4CF6-8D8B-02A86647217C}"/>
+    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{551C7CF7-54B4-4252-8E14-2C711D66FCF4}"/>
+    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{DC4F5A4F-9FC4-4A7A-A197-334350D552BA}"/>
+    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{F60AF022-23DF-4A48-8AA4-54F52B62DF79}"/>
+    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{1438A5E6-E6E4-4B11-BC87-6FE42B7E59AE}"/>
+    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{6F6B8DDD-6812-424F-B06E-5AB96CFBEF45}"/>
+    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{93162E2C-1B15-46D7-A3BA-5008A77EE925}"/>
+    <cellStyle name="Entrada 2" xfId="107" xr:uid="{D837E91D-FD62-4874-84A4-051A3CED421C}"/>
+    <cellStyle name="Entrada 3" xfId="108" xr:uid="{79766B91-3506-4E6E-AF39-F62FE9A62207}"/>
+    <cellStyle name="Entrada 4" xfId="109" xr:uid="{8E24CBBE-F4AB-44D1-90EA-D475CB72366F}"/>
+    <cellStyle name="Euro" xfId="110" xr:uid="{4EF04BF9-476A-4265-A865-8F0362D2F03E}"/>
+    <cellStyle name="Euro 2" xfId="111" xr:uid="{4F4737C1-A55F-4F56-8207-851C7F517620}"/>
+    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{F18FEE46-7005-47E5-83A1-56709FDA314D}"/>
+    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{73ABB318-225A-411C-B3B5-51C2CCF5AB84}"/>
+    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{A68739EE-332B-4E10-8A66-4F329926ACE6}"/>
+    <cellStyle name="Euro 3" xfId="115" xr:uid="{5451A2DF-3D31-4937-B347-FC5BB2070DEF}"/>
+    <cellStyle name="Euro 4" xfId="116" xr:uid="{E03885F9-6D5F-4D2B-8107-6FCF6A77ED5D}"/>
+    <cellStyle name="Euro 5" xfId="117" xr:uid="{726DABEA-1C31-4A8C-A372-8B6C7D8D8947}"/>
+    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{2E4ECB7A-9A20-4123-8A1A-E68A2975F4BF}"/>
+    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{F765C2D9-6D6E-4E4F-A4E5-5F9D83DD22FC}"/>
+    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{3A4BA0CD-3632-4147-92E6-C00FDE319801}"/>
+    <cellStyle name="Millares 10" xfId="122" xr:uid="{1817CCC0-A5DF-490C-B7E8-37CA196AF2C3}"/>
+    <cellStyle name="Millares 2" xfId="123" xr:uid="{CFCE98DB-C2A2-4A9E-A3DD-87C77AFE8B06}"/>
+    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{4F28587A-3DF7-47BC-9B74-992E8C1790FE}"/>
+    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{13EF1C90-E81E-4228-8256-897F5E00B5CB}"/>
+    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{2C2787B5-5AEC-4121-B515-BC8FC037A8C3}"/>
+    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{25E4379B-A901-4123-89FE-B54B3C3615A3}"/>
+    <cellStyle name="Millares 3" xfId="128" xr:uid="{DD5D3D04-F867-40D3-BD10-99968662EB9C}"/>
+    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{F1C54CCB-80C3-4913-BF2A-591DEE30F38D}"/>
+    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{C5DC4B5E-B1F4-4889-B2CF-137AB786A2FD}"/>
+    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{8D4C6E37-08FB-42E2-AA7A-F06234C2A674}"/>
+    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{ADAB9156-DAC4-47C4-86EE-9413845B18AE}"/>
+    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{DFE0DF33-9AF4-4E69-BC9E-16E5E2A29520}"/>
+    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{DD319EF0-5752-4653-9EDF-181136F66F6F}"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{AD957B70-C67D-4AED-B999-1D0C3995BAF7}"/>
+    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{0BFA2798-C382-460E-95A6-2E8F78498681}"/>
+    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{227B2093-C360-4A95-A7C3-BA7428AE1659}"/>
+    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{3E64C706-678E-4A51-AFA5-84365BAF48D7}"/>
+    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{CFBFB42E-95E8-4F51-BFA4-38586F1EA1F5}"/>
+    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{7EF8B100-CA5C-4805-9177-135693BE6DEA}"/>
+    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{3776CFEA-A36C-4D56-9044-3780FCFF2208}"/>
+    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{7E43FC61-F1F9-4193-95C3-03B995F593CD}"/>
+    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{7D86599A-56DA-4202-9C1D-CB6EAD9FD0BF}"/>
+    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{240EF294-8376-478C-80A0-D07F27415DCB}"/>
+    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{D0D79BD7-97C9-453E-AE73-745633CC3C09}"/>
+    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{A3DB116A-8988-4E7A-8AE2-F9A2609ECE7C}"/>
+    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{A33B7E3F-41BA-4A52-A555-AD9113B41B09}"/>
+    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{C1D287EE-C9F7-4184-9D1D-190C0C00B2E4}"/>
+    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{9BCBAC7A-55F8-4975-9F2E-D3889C6B63E8}"/>
+    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{018F1313-CE01-41CB-AF6A-4C7C0664DC0C}"/>
+    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{C9083562-B880-4366-A5AE-4F0EE4EE573F}"/>
+    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{1F177D85-B66D-4DFF-834C-ABABCAF3809D}"/>
+    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{EC4B0EBA-E19D-4F46-93D5-3A67CE53B841}"/>
+    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{229A3773-87F3-40A2-97D2-FAD26D50B6DE}"/>
+    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{D80C6905-CC5F-402C-9CA5-3DF354B79D56}"/>
+    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{18A21EC0-EB1E-453F-A7B5-EB523BB1E606}"/>
+    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{B331BE05-204C-484C-9518-6EF6CEFAC03B}"/>
+    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{CF22DC8C-32D1-4B54-A224-1E072C29CA3C}"/>
+    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{A0EAC1B7-6EF3-4522-86A8-D0066AB9EB52}"/>
+    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{EEA5ED24-12AD-4FC9-81B3-3C9399CF2F36}"/>
+    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{64CE7214-5829-4507-A01D-089CD02DF77B}"/>
+    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{C719E815-0848-4707-A294-9D13C8749B1D}"/>
+    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{B89652BA-5842-4FE2-8299-0FE1E93D9272}"/>
+    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{B06AEE7D-51DC-4601-B831-B8CBEF10F989}"/>
+    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{B8D34674-6497-463A-936F-FDC2EF3164B7}"/>
+    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{EA74AFA9-56FC-41E6-AB24-97703A6330FC}"/>
+    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{D44D2937-F162-4AC0-8A66-0386C03F23E4}"/>
+    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{D158EFAA-FE9F-4937-B140-2128BC0779C5}"/>
+    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{DECDA3CE-A776-41FF-8DE3-3B07DEFD5308}"/>
+    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{7DB9DDDE-98F2-4EE8-BBE7-90BF165CB4A0}"/>
+    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{3F2F2FD2-C396-4CD3-BD40-C4FBCFD7BD3A}"/>
+    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{2A268F30-126D-4FDF-B3B0-1EB18F7CACBD}"/>
+    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{CFB606EE-AB1E-42F8-9A27-912B712819FD}"/>
+    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{0FA35113-8984-482D-9088-72B23E04AB2F}"/>
+    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{30195EDF-FA3A-4E45-BF0F-65C5B5A997EC}"/>
+    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{34F620EC-E647-4E1C-B55F-229A358B2A28}"/>
+    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{CBBAE46D-5489-4F4D-ACB2-82ADB81CF9E5}"/>
+    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{7C980247-3E74-4686-9186-BE7884FBB0E7}"/>
+    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{9C6AD0FC-8632-48D7-B619-DCC5CAA18A2E}"/>
+    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{044C4797-148A-4205-A4B1-11CC78F02BAC}"/>
+    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{D6DA5EFF-63A1-4408-849E-C875F2759508}"/>
+    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{0C5C0789-D5FB-4BC5-8877-E3F03C3B4A42}"/>
+    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{799D618F-1648-4D7B-8515-32753398D539}"/>
+    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{6772F29D-6756-4E61-9FDA-953A3E7F03DF}"/>
+    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{FC1F24BF-3CFC-4F1A-9916-66E530EFE6AC}"/>
+    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{2A063913-C25B-4CC0-BB55-6D538056CC19}"/>
+    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{7B8998D3-3C78-4F54-8AD5-E1B33BAB7F46}"/>
+    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{E624F533-75D6-4626-ADD7-47EEAAE5DA5A}"/>
+    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{A8E4A561-032D-4866-BE2D-E6BB0BCCD27E}"/>
+    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{667E44E6-3393-4F2B-9D54-759A7E83A720}"/>
+    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{1703FF1F-1324-463A-AB03-1013AA2183F1}"/>
+    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{45CAC9F3-71CC-49DF-9B15-A04C2B56B913}"/>
+    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{C3309B8D-8C4D-49A3-988D-9C0B1F1D2648}"/>
+    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{27FB2678-338B-4D5D-8799-4DEFCB83C356}"/>
+    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{CE282ABB-B9E1-41B3-A32E-4B7F0F7C3FFE}"/>
+    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{F06B659F-2BFE-4AB9-9BE5-8C8A7CB6227B}"/>
+    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{1217E3F5-4665-45F3-A0E7-9C813F9589E8}"/>
+    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{BA4BAA26-D20A-41EC-A6E2-785549FA95B1}"/>
+    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{247DD842-196E-4A7A-BE54-C80AF88E9EA5}"/>
+    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{908A662C-40B2-44A0-AC17-91034BCA627D}"/>
+    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{1BA93D64-D51D-4DCE-A873-5195E36FCB9A}"/>
+    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{784E3B02-A759-4F40-ADAE-33E3556E769D}"/>
+    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{F4731554-C373-4637-8C49-4F244653C18D}"/>
+    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{817D6995-D3E8-4E49-A866-8BFFD40E8850}"/>
+    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{FBBF7C33-114D-45A5-9B21-C29577DC293D}"/>
+    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{39A808ED-CC60-4993-AE68-19953630FD03}"/>
+    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{6D626AB2-8DEE-472B-997B-4A21AC2E594A}"/>
+    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{181C5B34-0B22-4C23-910C-8B9FB82459AE}"/>
+    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{DD8942EF-BFE4-49EA-8F1B-E182ECBAE57B}"/>
+    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{67B684D4-508F-4881-9057-3EFC6FC45934}"/>
+    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{C6D3E8A0-80A2-4473-96BE-33DA8AE2CB50}"/>
+    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{30D50C7F-D93C-4048-95E6-1AD0AC2EEA52}"/>
+    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{5B1F7586-3D29-4ABB-B5D2-C8829271876A}"/>
+    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{B1CCA735-4249-4950-9EA9-B3999772C4DB}"/>
+    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{2F0DB9C7-295A-4B2A-BEE8-8E95E5F0E1A0}"/>
+    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{DE3A04D1-85BF-4744-B457-75850CB76E36}"/>
+    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{337951BD-FEB7-42C2-AC4D-B02A408AD202}"/>
+    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{8C1437F3-AD0D-4C73-8993-00B11B36204C}"/>
+    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{22C1BA57-5416-44A2-AD49-3EA198165C3A}"/>
+    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{2E4505F7-B623-4C74-A663-862716621A74}"/>
+    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{3EC65A6B-782B-4A85-9965-88A7F027F788}"/>
+    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{C99B938F-9A37-4258-BE46-825000F2F266}"/>
+    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{E1B61DDA-AABD-4EF6-90E4-825D39C44033}"/>
+    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{931D844C-031B-4800-ABBD-EBAA9F560741}"/>
+    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{2F9CE121-57E9-4E1C-B1E4-6EA22B06DCCE}"/>
+    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{6F14D8CD-43D4-46B4-B4EC-EA2AD9530DF6}"/>
+    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{6771ECA7-E22A-4DB2-852F-D79B2E8E1DEB}"/>
+    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{2085CD53-65BA-4021-9E19-DA40B31E9EF2}"/>
+    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{4CDAA3A2-CD73-40E4-B644-7B727F1B7932}"/>
+    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{CCA3E8D2-55A8-4B96-B690-9D625D82A88F}"/>
+    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{73FEEBA4-2CD7-45E7-8ED0-9D8AAAE8AF86}"/>
+    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{50BDDEF5-52DE-4EFE-8696-C27129DE9541}"/>
+    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{60C8AFDB-0EB7-4B66-9EF8-CFFD3F07E375}"/>
+    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{8CDC2C00-427A-4970-84CE-C67393B404D2}"/>
+    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{1AED798E-7A54-4237-A617-87E2A6592C69}"/>
+    <cellStyle name="Millares 4" xfId="236" xr:uid="{BA8288D4-D934-475A-81BE-E2A88B273483}"/>
+    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{BFF80574-B9C9-48F6-B020-9D5CA2A09EF0}"/>
+    <cellStyle name="Millares 5" xfId="238" xr:uid="{C3EA714A-9CE1-461C-87A8-F7C1970F11B6}"/>
+    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{DC42F69F-67AF-4CCC-9C87-987257195845}"/>
+    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{ABBC8BD6-3CA5-4FD1-8A64-B0869523B350}"/>
+    <cellStyle name="Millares 6" xfId="241" xr:uid="{D767DC43-E6B0-4051-A010-1CDF7F69DBFD}"/>
+    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{3C33B28B-050C-44DC-A368-B2D59C71BA4C}"/>
+    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{1A37C586-C353-41F0-912B-A6CBAFF496C6}"/>
+    <cellStyle name="Millares 7" xfId="244" xr:uid="{93D8AD8D-F1FF-430C-A038-1A62E7DD5506}"/>
+    <cellStyle name="Millares 8" xfId="245" xr:uid="{4D0FF579-A0B1-4ED6-A82F-807630017CF5}"/>
+    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{C1121105-1A39-42FD-A66F-0E8A97419FE5}"/>
+    <cellStyle name="Millares 9" xfId="247" xr:uid="{74821AEC-6544-4414-BBB4-7ABFA6D28E3E}"/>
+    <cellStyle name="Neutral 2" xfId="249" xr:uid="{AE50FD0F-34AA-4BD4-95C9-B8E2D8CBCE8E}"/>
+    <cellStyle name="Neutral 3" xfId="250" xr:uid="{F8415CE2-3751-4FA8-8B58-A4526DB0C803}"/>
+    <cellStyle name="Neutral 4" xfId="251" xr:uid="{8CB66ABD-7C12-4B3E-B85E-0347AE9EA8B3}"/>
+    <cellStyle name="Neutral 5" xfId="248" xr:uid="{5F94F30B-879A-4A33-A3D7-B94911CFEA9D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="252" xr:uid="{084EBCA8-0BA0-41FE-9AEE-8DC7BA361460}"/>
+    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{C2C9558A-2B3D-4406-83D0-059E914225AA}"/>
+    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{9CA1290F-CA8E-45B4-95E9-2E24CDDC793D}"/>
+    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{4C55E28F-D046-4B85-9B6D-D75AB72D2C8E}"/>
+    <cellStyle name="Normal 100" xfId="256" xr:uid="{61A73F6D-F81E-42C0-98C1-5B73D097C73B}"/>
+    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{5F7635C1-BEF4-4D9C-924A-FAE15F254CA8}"/>
+    <cellStyle name="Normal 101" xfId="258" xr:uid="{D8078189-B1A2-45B0-8A43-92ACEA2AC42D}"/>
+    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{D85EA871-3511-44A4-9411-D0CF58C6F494}"/>
+    <cellStyle name="Normal 102" xfId="260" xr:uid="{AE4D7422-7E0D-4870-9723-88CD569A7863}"/>
+    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{12A83050-AB19-49EB-89C5-9DADBFDEB8F8}"/>
+    <cellStyle name="Normal 103" xfId="262" xr:uid="{B52740D5-30AA-48DB-BEC5-8CB4FC6D9D1D}"/>
+    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{B648BD3C-F258-43EF-BC17-8B0F6693AE02}"/>
+    <cellStyle name="Normal 104" xfId="264" xr:uid="{0ABDF0C9-05C5-41A3-863E-526D7CFF6368}"/>
+    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{8BD6FE1C-5951-4B61-9E78-2E97ECBBFD77}"/>
+    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{B983A86B-B518-413F-8757-FFC8F17ACE1B}"/>
+    <cellStyle name="Normal 105" xfId="267" xr:uid="{9AA8F441-5CA6-4DDF-9F5C-AC943913608B}"/>
+    <cellStyle name="Normal 106" xfId="268" xr:uid="{C3F91CDD-4C60-478E-A97B-603835C5008A}"/>
+    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{9B96B2E1-ED3E-4681-A7CC-C31261D2BDAA}"/>
+    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{39F36360-6D68-42E8-96D6-C0FBF790B00A}"/>
+    <cellStyle name="Normal 107" xfId="271" xr:uid="{3604C7F0-6C05-4DFF-8D25-24A3332624C3}"/>
+    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{4DDE6BFE-8403-43AF-A16E-36F7286CEDAD}"/>
+    <cellStyle name="Normal 108" xfId="273" xr:uid="{FA3FC4D9-1DD3-496A-9433-70A1FBD15B0C}"/>
+    <cellStyle name="Normal 109" xfId="274" xr:uid="{1B1B7645-D32E-4EC7-8498-48D0EC50BFA5}"/>
+    <cellStyle name="Normal 11" xfId="275" xr:uid="{DDF97C8D-FC4B-4EA9-80FE-86B7FDF283D8}"/>
+    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{040E1D54-9628-4051-A703-F2D4FF7E3160}"/>
+    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{9B7AC5B6-8859-44E4-979B-0843BB462446}"/>
+    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{FB221B44-61F2-4893-B13E-835DF32D2B49}"/>
+    <cellStyle name="Normal 110" xfId="279" xr:uid="{2F26D2EC-8C76-4194-9F0C-145966C7AC1D}"/>
+    <cellStyle name="Normal 111" xfId="280" xr:uid="{5F47D1D7-9E84-47C9-8831-F95B09F8313B}"/>
+    <cellStyle name="Normal 112" xfId="281" xr:uid="{F25C7080-7681-4D09-AB2A-36B62C0885EE}"/>
+    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{52E0B4B7-D4CE-46D1-9F54-162B9E544BD0}"/>
+    <cellStyle name="Normal 113" xfId="283" xr:uid="{97986F54-80E0-49C8-BDDC-BED5201F8073}"/>
+    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{20960359-FA8F-468F-9B3C-8ACC3793442E}"/>
+    <cellStyle name="Normal 114" xfId="285" xr:uid="{F631585A-6727-45B4-8093-AB33284E3114}"/>
+    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{E02C6EAE-2E1E-4D14-A9A8-814449AA6B45}"/>
+    <cellStyle name="Normal 115" xfId="287" xr:uid="{CCF7EB0F-F8D2-4508-8D43-D091DDB2378C}"/>
+    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{E93E5B31-D7B0-4AF3-90E6-8923A679E635}"/>
+    <cellStyle name="Normal 116" xfId="289" xr:uid="{F93F575F-DACF-493C-94C2-C4D8BCCE1D25}"/>
+    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{0C95AFDB-D53A-415F-AE14-8E2005D4B01E}"/>
+    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{85CA3D7B-6300-4D54-BFA0-555B8FA144C0}"/>
+    <cellStyle name="Normal 117" xfId="292" xr:uid="{394DCC4A-25C3-4838-AA70-77A3F855E342}"/>
+    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{A4FB58F4-AF86-4CF9-B8BE-0204E07DA895}"/>
+    <cellStyle name="Normal 118" xfId="294" xr:uid="{0127623A-4881-4F1E-952D-D85F9332A956}"/>
+    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{6CADA8FD-2A17-4F7E-BFBC-E7D7F89A16F4}"/>
+    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{A6A7E842-2CE2-46A2-9BF7-46EFD2D5AA13}"/>
+    <cellStyle name="Normal 119" xfId="297" xr:uid="{0DB93230-6257-4E41-A236-142A8AA7B666}"/>
+    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{CFC1580F-85CE-4F23-A547-B4EECA8BFE5A}"/>
+    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{F1902491-CBCE-4C4F-99E0-A931B8E543CE}"/>
+    <cellStyle name="Normal 12" xfId="300" xr:uid="{58AC8F61-AB96-4B38-AC37-0A9D26BB9CDD}"/>
+    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{EB87F916-6D50-41F4-8E55-27BB933F0537}"/>
+    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{198993C1-E914-4D20-9017-3AA41CC0E475}"/>
+    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{A5FEA652-204F-407D-A634-1C0951A99661}"/>
+    <cellStyle name="Normal 120" xfId="304" xr:uid="{37FE5AAB-4FDF-41ED-89D3-7CAC742E249E}"/>
+    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{E379EA7B-9C0C-4A8E-9454-0A5DB53D3443}"/>
+    <cellStyle name="Normal 121" xfId="306" xr:uid="{39F22EC0-06AC-4362-8489-2708C380CE08}"/>
+    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{29FB3A12-995D-44B3-A516-105E5369AD40}"/>
+    <cellStyle name="Normal 122" xfId="308" xr:uid="{A8F16106-56C3-435F-9FFC-62588A72D60F}"/>
+    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{8B661892-7493-484A-BA77-DEB8DF8CAAF4}"/>
+    <cellStyle name="Normal 123" xfId="310" xr:uid="{692DDE0C-FCC7-428C-975F-6F64C9E51B07}"/>
+    <cellStyle name="Normal 124" xfId="311" xr:uid="{9992C9E9-124A-4642-B1B2-A5832E8FD404}"/>
+    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{9C3C93DF-C216-486E-8258-BA8426333C17}"/>
+    <cellStyle name="Normal 125" xfId="313" xr:uid="{B5C78AF4-39A0-4135-A36E-F3E11E87FD59}"/>
+    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{F25D0D47-98CC-4B1F-8524-EAA69FAA8C61}"/>
+    <cellStyle name="Normal 126" xfId="315" xr:uid="{1400D3E7-9D3B-41B2-99C7-28911E301358}"/>
+    <cellStyle name="Normal 127" xfId="316" xr:uid="{6636678D-7232-48F1-887E-F92010EA99A1}"/>
+    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{EC3F3F83-500E-4FE8-AB75-49E9E793C41A}"/>
+    <cellStyle name="Normal 128" xfId="318" xr:uid="{8B7281F7-0A29-411A-85D4-F2B9D1C69A3E}"/>
+    <cellStyle name="Normal 129" xfId="319" xr:uid="{322672C8-357A-4EDC-A003-C69BFD9BC798}"/>
+    <cellStyle name="Normal 13" xfId="320" xr:uid="{AFDCFA01-015E-4DA3-9CC3-AD7005E926BA}"/>
+    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{DB4E4E57-B0C2-40C2-ABC2-592306897BCD}"/>
+    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{9DCDD1ED-5D4C-44D4-985D-E674B983355D}"/>
+    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00D96212-4968-40E8-9AA9-9D1FB5F9A9B5}"/>
+    <cellStyle name="Normal 130" xfId="324" xr:uid="{3CAA6D22-1AC7-46A0-BB9A-71C8344A2B30}"/>
+    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{FA019089-AD11-449D-8853-AE5C1386F974}"/>
+    <cellStyle name="Normal 131" xfId="326" xr:uid="{90019043-C212-41D3-B271-AF7097CD9CB3}"/>
+    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{C761AC25-8663-4246-BC68-ADCA4BD31529}"/>
+    <cellStyle name="Normal 132" xfId="328" xr:uid="{C081A645-82CF-4A65-BA48-61D535D4CD91}"/>
+    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{7E996725-5A85-4681-9696-57D73CBBE768}"/>
+    <cellStyle name="Normal 133" xfId="330" xr:uid="{DBBCE3BC-4D8D-4165-BCB1-DF23369D2790}"/>
+    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{AB539EE1-B70D-4177-A699-CA9F5F6001CD}"/>
+    <cellStyle name="Normal 134" xfId="332" xr:uid="{610A5923-CCFF-43FE-9D5E-9CDB0F36982B}"/>
+    <cellStyle name="Normal 135" xfId="333" xr:uid="{7D1DA2E4-33BD-4DCF-8698-5792C38FE0E6}"/>
+    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{5AD4EE68-31E7-4E1C-9B51-702BE9406175}"/>
+    <cellStyle name="Normal 136" xfId="335" xr:uid="{1186A786-EF10-49F1-94E0-A4808313E432}"/>
+    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{DEBC06EB-F6B1-4E0B-AD6B-B1BE8CD6A0D6}"/>
+    <cellStyle name="Normal 137" xfId="337" xr:uid="{90158BC5-5B3A-45C3-BE32-8FA196299CED}"/>
+    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{8D5E5FF7-B5A5-4994-A1C6-37A4334E0A92}"/>
+    <cellStyle name="Normal 138" xfId="339" xr:uid="{55CD8AC1-7FC7-4012-9BF5-4D1DBBA5E390}"/>
+    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{AFC1D4DB-9BC3-494B-A298-11AC8565A9EB}"/>
+    <cellStyle name="Normal 139" xfId="341" xr:uid="{D16D13E3-506D-404B-8AFC-EC5FFCCFCB1E}"/>
+    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{FD41F7A8-0539-4F7F-9864-157A4BB5C4E4}"/>
+    <cellStyle name="Normal 14" xfId="343" xr:uid="{0858813F-2F85-4960-81E5-251DEDFE28E9}"/>
+    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{E701FEC9-0FE5-4E7D-9957-B4E895D37515}"/>
+    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{34D04FFD-B2FE-47E8-BD31-99B04195B060}"/>
+    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{1DCB8A28-8EE0-436E-9C83-8860D789505E}"/>
+    <cellStyle name="Normal 140" xfId="347" xr:uid="{2126FB6B-CBFA-4223-A5F1-2E08F3573273}"/>
+    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{3810A04C-AE97-4200-8A4E-B72FB46E1A53}"/>
+    <cellStyle name="Normal 141" xfId="349" xr:uid="{B230D6BE-3D64-476F-A0D6-8242BB651993}"/>
+    <cellStyle name="Normal 142" xfId="350" xr:uid="{546345E2-F248-4198-9215-7DFE6B04D625}"/>
+    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{C92B0FCE-0B15-4AAE-8F59-4211BB119920}"/>
+    <cellStyle name="Normal 143" xfId="352" xr:uid="{A76042E8-8771-45D9-903F-6B5AF81AC84B}"/>
+    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{6CFDAC86-8D5E-46AC-A184-FE1A469062BE}"/>
+    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{718A03B5-3F90-43F4-A958-D8730DC9BAAD}"/>
+    <cellStyle name="Normal 144" xfId="355" xr:uid="{CB9FBE4E-4DFE-450E-BC8B-4E8DD048816E}"/>
+    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{562D1075-0355-4BB4-8AFF-EFE338A9DBC6}"/>
+    <cellStyle name="Normal 145" xfId="357" xr:uid="{7129AA69-B166-4A86-9933-0365FAD61389}"/>
+    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{BF097E1B-B77C-487A-9054-0E75D97B63C7}"/>
+    <cellStyle name="Normal 146" xfId="359" xr:uid="{E0FBB80D-4DE7-4DA4-98D2-20F0119E7AE7}"/>
+    <cellStyle name="Normal 147" xfId="360" xr:uid="{F7F11328-7818-4D3B-ACA8-C57D48F418F5}"/>
+    <cellStyle name="Normal 15" xfId="361" xr:uid="{87CC9222-169A-4762-B2FB-F836258FD265}"/>
+    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{93FE13D7-9F93-4074-8475-242718609C99}"/>
+    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{01902B12-575D-456D-841D-B1E5E369C1F2}"/>
+    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{219BC5BC-1F96-4F35-82EF-A1056AA502FD}"/>
+    <cellStyle name="Normal 16" xfId="365" xr:uid="{433457D5-F9AF-4F87-9CA3-9151760DE6BF}"/>
+    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{96282A7A-F4AC-4EC1-A21C-916DAA6ECA59}"/>
+    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{C5344315-DB7C-4221-875E-D1B1A58E25D0}"/>
+    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{0634B5BE-A680-4343-9316-444C974A5F0E}"/>
+    <cellStyle name="Normal 17" xfId="369" xr:uid="{6AE9A62B-DB29-4D46-99E5-D2ACAC1284E3}"/>
+    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{A6323A19-4C26-4316-A3BE-20145CC6CB40}"/>
+    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{D123A59E-A0BA-4800-A848-D10C0028638C}"/>
+    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{1DF6A807-A08D-4A1E-97A9-FECDFCA7D3F3}"/>
+    <cellStyle name="Normal 18" xfId="373" xr:uid="{9AB0AE66-7739-45BB-8972-F90B7D0A7665}"/>
+    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{B5F81ABE-1007-4A3E-A65C-96A53CBA8EE4}"/>
+    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{7E0DDB6A-E13E-472E-9DAE-F114A6229BCD}"/>
+    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{E174DB80-E50E-4F71-BC6B-9C772776EC22}"/>
+    <cellStyle name="Normal 19" xfId="377" xr:uid="{6E980DA7-A2AC-4671-915D-7BFE10A80835}"/>
+    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{C599F739-99BD-4311-AF6B-A7B7966CA83F}"/>
+    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{23DE42BF-5DEE-4B21-B46A-06B6E5F78AA8}"/>
+    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{02C9A42D-5312-48E2-957A-43769A3D38B4}"/>
+    <cellStyle name="Normal 2" xfId="381" xr:uid="{459495BA-6982-4F5C-BCB4-BD256FBB65BB}"/>
+    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{7F1F8F06-264C-4E87-A856-CE5C6634EB2F}"/>
+    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{5059B14C-2CC7-445F-BDD7-EE623AD12D74}"/>
+    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{F83BBCC1-7291-4648-9B9B-01CF249FFA70}"/>
+    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{C2253001-F1DF-4A91-980C-B5B8DA5862BC}"/>
+    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{B9486AB9-3732-4EAF-9EAE-0A650EE81A2D}"/>
+    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{B93360BC-E4C2-4EB8-892E-8DABE4EAD0D9}"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{D74ACA62-DBC6-4464-8B11-AB2E3AC5702C}"/>
+    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{32574485-CB3E-4075-BB9B-44ECF58D1671}"/>
+    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{BC9266DF-F1FB-4E25-AD96-E077B0ED4EA3}"/>
+    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{65BF6333-E99B-4495-86DE-DAEF01CEAC49}"/>
+    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{61B01230-3C8A-4CBC-996D-29FC265BE993}"/>
+    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{9523EB68-FC3F-43E9-956D-591DCDCC7BA7}"/>
+    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{EBB93D1B-5F95-4DD0-94DB-A27B1E3D01E1}"/>
+    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{2E27D646-D769-47DF-957D-E8DE03AD9343}"/>
+    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{A1A23999-076E-466D-913A-C39E74381D75}"/>
+    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{E2539EA6-93BC-4225-A3B3-07714999F5B7}"/>
+    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{2A99AA66-9720-4929-9EC4-3127BC3E41C2}"/>
+    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{044C11D7-B742-4183-BBF8-B5BE03356AD6}"/>
+    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{5E538B18-B049-4708-9965-5BE9A8EB8310}"/>
+    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{6C529256-5092-48BA-8F7B-3E40A75542B6}"/>
+    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{09DA0D5A-2549-41ED-AE54-4BAA994D7653}"/>
+    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{2DB6593D-7EE3-4909-AB7D-F1F09C0CAE7C}"/>
+    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{EA861B67-7ECC-4369-BAD3-EC4FDBC60656}"/>
+    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{58207C0A-EA2A-47FB-B828-291437CEA170}"/>
+    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{BD61C73D-791F-4263-981F-E70A609525F1}"/>
+    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{D0946525-DD76-4FA1-960A-D336BA60FB4A}"/>
+    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{2770EB8B-6915-438C-98CE-AB55DAB6FCDF}"/>
+    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{EAF3B951-71FC-4D19-AAD6-8646B8086A55}"/>
+    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{668C60F7-AEAD-43BC-8D91-BC636E397794}"/>
+    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{C2BF7D84-DC2D-4D3D-845A-55FE1897B827}"/>
+    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{C91175E2-D6FA-4F7E-B684-DE4DBD974263}"/>
+    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{79C5FD1F-C92B-44B8-82EB-659CF5B9A75C}"/>
+    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{6D70CE10-22FC-4813-AFA8-E013B46F6B14}"/>
+    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{B3F450B0-F1ED-4EE3-8E43-694E44E3920D}"/>
+    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{21497C75-66D1-432F-AFD5-62C747BCC0D4}"/>
+    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{423A0D32-BD99-4676-83F8-3E336705EDF3}"/>
+    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{50012E93-1F43-4DF3-A24C-54F11EAD526E}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{FB8B4FCB-D920-45DB-B82A-8C0BCB1253D2}"/>
+    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{AE360487-041F-46AA-B884-C9D02BA1F110}"/>
+    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{C003D66E-FB20-4661-B4A3-C417F5939706}"/>
+    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{AE7AB400-C95C-48B2-ADD0-9F5783115E86}"/>
+    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{CA1C7703-A97A-40CD-A742-620DF760C965}"/>
+    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{A7031F68-5681-4A5F-9871-88CDDD544C6B}"/>
+    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{ABCCE1B6-A5D8-4C4B-A0A1-C516FD19DD61}"/>
+    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{9237849E-38B0-4270-99E3-D546573F1D7D}"/>
+    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{BCCCB71E-EDD5-42B3-BC11-EB8614D4C85B}"/>
+    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{0F416CFA-E74F-47D0-A333-02C0CA8DD655}"/>
+    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{17BD6D73-5B0C-4AF3-8ECF-633B0463B8DE}"/>
+    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{CDDEBB90-3431-4050-8079-E72C9375610C}"/>
+    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{106B9754-EA0D-4203-B8E5-7C7BA32DEF42}"/>
+    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{CB2AC498-0835-4F7A-93EA-3F74C52EECC9}"/>
+    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{FD2D7FC4-A2D8-408D-8C01-2E9AB2C0370C}"/>
+    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{62224986-BE60-4C42-9EA1-6EB395F164FC}"/>
+    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{BA117E2C-FBAB-4218-A105-8B112F1728D0}"/>
+    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{E3ECB07C-FCCE-4E45-A828-5CFD14E0E3A1}"/>
+    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{485A0937-4412-416E-B3D7-9E404B026064}"/>
+    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{D9404978-0366-4974-948D-7535EAB9E287}"/>
+    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{7D6573DC-AB2C-4A5E-A2F9-5CA147F8FFD6}"/>
+    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{E04188FF-30ED-4A49-906C-8CAEABEA5441}"/>
+    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{7667970D-AD04-40A3-8F04-3DAFAE08B565}"/>
+    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{E6A52649-8440-40A6-ADD2-4C463159DEE4}"/>
+    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{CA883F42-9DC6-4863-AD03-8DE3F8EC623A}"/>
+    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{C26485C8-31DE-494A-8248-A97AEE7CD028}"/>
+    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{15BA2801-5538-431D-AE66-2A4159E0F21F}"/>
+    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{BE264327-139D-4D00-834C-C4FAD193EF33}"/>
+    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{9A61D5E5-3A7E-4376-B08B-738566866469}"/>
+    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{2FF65403-A40E-4A35-9EC3-BC02CC7F4894}"/>
+    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{FBFFD7F6-2DC4-4A1D-A2FB-945AFDF2266D}"/>
+    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{83ECBAE1-A9D8-4E78-A1B3-C076998FC9E9}"/>
+    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{A8C5D06C-697C-4EBB-A6D6-13358A5CBE5B}"/>
+    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{3106C343-9D9E-4F96-8885-229AB7DF7D10}"/>
+    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{18AFF674-7D36-40B4-91B6-E712062B4D6F}"/>
+    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{BA919AC6-9E4C-494E-8829-B53B19FC5769}"/>
+    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{132C7599-867E-4173-999F-7771BA4EC197}"/>
+    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{F4AB1593-3493-439D-A69E-2B5AC1E4597C}"/>
+    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{0AD6CE2C-C27F-4328-95EE-DA6ACC6853C4}"/>
+    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{87B4E720-3475-4AF7-9824-E53CBFCA69FD}"/>
+    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{EFE97F5A-0060-4563-B75D-E98F5C6CA615}"/>
+    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{F18BDAEF-C493-412D-9876-67F17213C2CA}"/>
+    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{484FEE23-2642-481C-848A-2B551C1C3AB0}"/>
+    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{8C4F0C12-BC55-4520-9BEE-FCBF03474712}"/>
+    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{71C83530-075C-47CB-9A06-06FCD1814541}"/>
+    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{382BB28A-5AA6-42DF-AC0F-DEDC4909B01F}"/>
+    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{9A15E26B-F7FE-49B9-8944-ED2181EF80E4}"/>
+    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{4D8718F5-3AE5-4FB5-BADF-7AEF740DDBDE}"/>
+    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{62D139A8-62DD-4FCE-84CA-408AD9B0A82A}"/>
+    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{C51278B5-0079-498F-9B29-9A14D8A42268}"/>
+    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{547112F2-0DEE-4179-A0E9-D806CBCA5240}"/>
+    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{CC40E526-128B-461D-8552-E4DFEBB949D7}"/>
+    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{C3BA539C-008E-40FB-A190-7E76F7FA1F56}"/>
+    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{DDFAD1A7-F40D-4FC8-8138-506242692797}"/>
+    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{4413DF38-D86B-4FDA-B47C-3F75D75F1B35}"/>
+    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{D3B98E95-B160-4C52-A277-3A699D70F7B5}"/>
+    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{656CCD1B-6D83-4B65-86EF-F15E6BBCB455}"/>
+    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{E3E63D19-9F61-4CA8-9E03-24CA6A626F29}"/>
+    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{2DF31EF9-28D6-44D6-8FF1-EF53290F2F60}"/>
+    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{7055F94B-53EE-4794-B8F0-E0B7499A07E9}"/>
+    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{CC2F86B9-CBEA-48BC-8F4C-5514384E12F0}"/>
+    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{AD86E3BF-1617-4C73-ADD7-CA29456B363F}"/>
+    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{1D0CE22F-37B2-4C97-8AA1-479BEEFB0069}"/>
+    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{D38B2065-406E-42CE-ABC8-6B43E8911FCF}"/>
+    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{EBAC9A40-B3EB-448B-978C-5A9B6784E099}"/>
+    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{EF8F73C5-1F9A-4A56-A1C6-E57EDB791267}"/>
+    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{2AB0E11D-0E2D-4C17-B11C-ED3C221412DF}"/>
+    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{9D7BE2A4-7F5C-4282-9550-793B9203B05A}"/>
+    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{61CA0DEC-D1B0-43AD-908B-9A21EA9B59BA}"/>
+    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{5846530A-CEB4-4009-9B74-A7E5950894E8}"/>
+    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{FAC35099-1419-49BF-B920-0365F6F40A93}"/>
+    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{C34EE97B-8AA0-4206-A2EE-076DE4DB72D8}"/>
+    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{4F6136A5-7AF2-45C5-B794-28FC0614BDC2}"/>
+    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{4DE461F1-CFD6-40D6-9FB4-22379162B23A}"/>
+    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{281D8DE3-F066-4365-B129-80EEBC5D0A87}"/>
+    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{75FFFDC6-B1CF-436A-A437-A1EC001D3ACB}"/>
+    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{B39EA674-24BA-4A6C-93FB-D38F16C2AFB3}"/>
+    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{DB639C04-220C-485F-B8F8-F2AB7E4DAF11}"/>
+    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{8F3AE0CA-3824-40AA-B4C8-EB2A5DD49341}"/>
+    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{834D3BDC-1F2A-45A8-9188-4549B278FA67}"/>
+    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{C7A5FA3C-F05B-478D-BFE7-99C340EB9256}"/>
+    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{F426D380-E7F6-4450-9411-C0A5E2C69EBD}"/>
+    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{DE753BFC-2E2A-4288-B5F0-5C005EF6CB95}"/>
+    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{13529469-A397-4051-B6B0-E94110AA034A}"/>
+    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{34EB5D72-5254-43BD-BA18-68AE9299471F}"/>
+    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{A0C7431C-E6BA-434A-85FE-BBD80B6318F2}"/>
+    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{45225194-4A4D-49DC-B2F6-3DC7A27F6720}"/>
+    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{6CB75D43-0978-4641-9A9A-0F404BFB624A}"/>
+    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{1145C56D-7669-4DD3-B030-900FB2FBFA1C}"/>
+    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{29D6CEF5-0950-430F-816C-CE837D13794F}"/>
+    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{680006B8-2755-4CD3-AFB2-1A9F8540B0CE}"/>
+    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{3B3F0856-B160-4C50-A410-27E5AB12852E}"/>
+    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{7DBC7104-D268-450F-9E1A-4714C1E69432}"/>
+    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{D2BB24A8-5DDF-403D-B27A-EA761766D2F1}"/>
+    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{9F034895-5A79-4B63-AAAC-64CEC92C09FE}"/>
+    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{541922D0-3005-44E5-A44F-3DFEFE824AB0}"/>
+    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{D100FB59-0080-4BF6-AA2D-B234A19F75D4}"/>
+    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{9DEB0894-8965-446D-AC98-CF1D19949C7B}"/>
+    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{7C479DCC-25FF-4208-96E5-EC375811158A}"/>
+    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{4F3CDDE3-5A95-4F0E-835E-7CD5AC35973C}"/>
+    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{347268ED-0E8F-4FB6-823D-15DAE6130AE7}"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{B2C0E2B6-F387-4C46-9195-C70021FE11CB}"/>
+    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{68601F51-D380-47BC-A9FA-1DE6BBF3BFA9}"/>
+    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{3B7A85B0-42A3-4999-BC75-BFBDEEF1ABBC}"/>
+    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{CCDE718F-1CDB-40C7-8835-4B9C4155C9E7}"/>
+    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{C7021254-7E03-4CD5-9544-19899DCC3A54}"/>
+    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{650E1F43-8EA9-47AE-9258-9CB925063531}"/>
+    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{1F5DC4B0-1508-4134-A772-B7F014A8F539}"/>
+    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{A8513978-2F8A-4CB8-A553-42789DD2E510}"/>
+    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{7FFD1515-C8C7-4045-A2E6-3505420351C9}"/>
+    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{595A0FEC-F9AB-4398-933B-FF22555F8F56}"/>
+    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{67BF00EB-1AB7-454E-B0B8-2BADFD2DEF75}"/>
+    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{71C3BC9A-5F09-4724-B236-C3AFC6F2C6E6}"/>
+    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{3594554B-CEFC-4C51-AAC6-CFDE152F9362}"/>
+    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{B5485D19-C897-4151-8F35-7CF7FDD9BD25}"/>
+    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{FC753AF5-0FE9-40EC-BAC0-BBFD301A2B33}"/>
+    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{B1069335-3CBC-4532-96A8-C71BA2D81B5E}"/>
+    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{7201245C-8F72-4F6F-ADAB-53708CBA2015}"/>
+    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{0B4018CB-A6ED-4017-85DA-2C20A39B3982}"/>
+    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{51135A3E-B73C-4D3B-87C8-EDD0A60343B5}"/>
+    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{BB7599D1-397F-447C-B460-A93DA4F22B9C}"/>
+    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{93927D0D-BF34-4DC7-85DC-FF86163DD571}"/>
+    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{D741029D-97AC-4326-A040-BF6CDDFD79C2}"/>
+    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{4A358CC2-D4E0-4BCF-9583-DE428AE8A76F}"/>
+    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{9AE3721D-DC8B-4F60-A61C-640226EFE086}"/>
+    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{64838451-5857-4A95-A0BC-0B94E8127FA4}"/>
+    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{3A717A90-C2D4-4051-B5D4-186E263E7EB6}"/>
+    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{D8FD8A7F-5FCE-4DEE-AEC3-0E952BA80F5A}"/>
+    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{219A49BF-3BA9-4C69-96E2-5EAA70FE986B}"/>
+    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{5E57888C-773B-4DDE-BCB4-10444E777200}"/>
+    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{46BDD246-1B57-4421-8781-C2EA32AF7877}"/>
+    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{551936C4-6DC2-4F90-9C19-A7D02BDF73DE}"/>
+    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{1FB0203C-EE2E-43F9-B83B-362EB81FB32B}"/>
+    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{3458BAD9-0514-4012-B6FB-80D5D26AF0A6}"/>
+    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{32CEFF4E-9200-4116-9BA3-B23C55EE1E8A}"/>
+    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{66D4A804-2F9C-444D-A25C-1E20B2B797B7}"/>
+    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{1383939C-E452-472C-9635-9681AC03228D}"/>
+    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{1706A99A-95DD-4870-B7B8-9F4F427440A7}"/>
+    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{4D097D50-C597-4667-B199-5D95787A3E7C}"/>
+    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{0933EEC6-CFAE-4A9A-95AC-623D502EABAC}"/>
+    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{8741F196-8FC6-44D7-A20A-DAE57160A108}"/>
+    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{EFB90566-8629-4F74-BEBE-D2E196788BD9}"/>
+    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{675CD6BA-AA6A-47D8-8F95-6355A7704B2D}"/>
+    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{83734F73-E219-46AC-9D78-AFE3B1B78E0D}"/>
+    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{A56A818D-22B1-4E7C-B375-19826563C134}"/>
+    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{7C6CBCCA-6E3B-445E-9BDE-512AC9A4A894}"/>
+    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{B38B8D26-D8D8-4976-85A1-9A841919FCC7}"/>
+    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{87F1FBA9-4F9F-4C56-A28A-E4E091CDF8D6}"/>
+    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{2149EE71-3C76-4F32-9503-C496E6A14307}"/>
+    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{C95CA3E0-1CD5-4DAA-A451-E7AC7F3E8213}"/>
+    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00F08B53-42C5-4956-9565-A7DEC0574687}"/>
+    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{C55F1E53-A6FF-4123-94F4-FBEFF1B40343}"/>
+    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{E3938777-4141-4D36-BF7E-B3F9963053AF}"/>
+    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{BE821E30-6E4B-41CF-9F16-77F93BF09AEB}"/>
+    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{F891C673-CB7E-4630-825B-70D9A6A9F3DF}"/>
+    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{484F6EEA-5818-4470-82D4-C8E53EE6F0FB}"/>
+    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{CCB6D8F0-3D07-4BD4-A30D-30D2012FEE71}"/>
+    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{7C01C525-835C-4CE4-8AC4-4A5D4916665A}"/>
+    <cellStyle name="Normal 20" xfId="577" xr:uid="{CB6C40B2-188A-40A1-BBBC-776FBB13D68C}"/>
+    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{66975FD2-E358-48A5-8D0F-DDEF580B1CB3}"/>
+    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{FC0FFF92-D6A9-4108-855A-7949F234313B}"/>
+    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{D09A6B3C-180D-4A6E-9BD0-E4F7FC036764}"/>
+    <cellStyle name="Normal 21" xfId="581" xr:uid="{615324CC-C499-4C09-806A-27823D06F668}"/>
+    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{521CB14C-83D4-4692-AECF-21DC73F523D9}"/>
+    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{36207B69-EB61-4560-8FB0-F31F5E90384F}"/>
+    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{CE5A0DFB-F8D1-467E-A00C-A88D8107E0BF}"/>
+    <cellStyle name="Normal 22" xfId="585" xr:uid="{ECF93FF4-FBC4-4D2B-BCF1-49C6B813330F}"/>
+    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{52DFD668-B264-4C5B-AF57-00B504F5CB25}"/>
+    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{E8A9C3CD-A59C-4825-94E1-9BC6FB90D9D1}"/>
+    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{21BA8A34-360F-4A27-9E51-062B2EB1A265}"/>
+    <cellStyle name="Normal 23" xfId="589" xr:uid="{A2319FC8-2E18-464F-B861-C57151D0568D}"/>
+    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{A7981741-F99A-4734-9F3A-7E8D06A10B88}"/>
+    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{2201A317-D72F-4403-8BDC-25EEC7790DFB}"/>
+    <cellStyle name="Normal 24" xfId="592" xr:uid="{20179CDC-9D9C-4C37-8842-BBD443E86343}"/>
+    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{9E18510A-2F52-4BFE-ADA4-83F7CD4F8A01}"/>
+    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{8ED1BDB7-9585-48EA-96FA-18CDF1F1D90E}"/>
+    <cellStyle name="Normal 25" xfId="595" xr:uid="{CCF8ABCC-84D5-4E5F-AAC9-641540BAFDBF}"/>
+    <cellStyle name="Normal 26" xfId="596" xr:uid="{78EE13BD-00E9-4AAD-AC83-E5B069E35F21}"/>
+    <cellStyle name="Normal 27" xfId="597" xr:uid="{4786ADC3-F77D-4688-8E0E-85C4C197DEED}"/>
+    <cellStyle name="Normal 28" xfId="598" xr:uid="{F359F718-A266-4D1D-906E-94D5A9205FB4}"/>
+    <cellStyle name="Normal 29" xfId="599" xr:uid="{65DD99D4-993C-4CA8-BEB6-CD1B5C1EF8E7}"/>
+    <cellStyle name="Normal 3" xfId="600" xr:uid="{DC1D8B4C-CA7E-4CFF-93EF-2A6F5E39390B}"/>
+    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{9075BCCE-6EDB-496D-B51F-E1802708E56C}"/>
+    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{61DB3744-D2FA-43ED-AE0E-92E80D189311}"/>
+    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{1D70D478-C172-4E63-9C99-CB0CE3D1256E}"/>
+    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{FA205D85-4851-49A1-8DEA-2C30238CE1FA}"/>
+    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{02DB2995-744E-4B1C-B3D7-634E7903DBF3}"/>
+    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{9EA73752-25DF-42E9-9D0D-2FB61E76EC5E}"/>
+    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{E66F1E58-E942-4F98-9E9C-2E904F6D4E7A}"/>
+    <cellStyle name="Normal 30" xfId="608" xr:uid="{67135321-20A5-463E-837E-09E66DFDF722}"/>
+    <cellStyle name="Normal 31" xfId="609" xr:uid="{3FDDC6C5-909A-49A5-90E9-5BDF1475FCC5}"/>
+    <cellStyle name="Normal 32" xfId="610" xr:uid="{E486F490-35A1-46EF-B902-8BD8F285F090}"/>
+    <cellStyle name="Normal 33" xfId="611" xr:uid="{2BE1C039-1893-4CC0-8910-B9E9805C86A4}"/>
+    <cellStyle name="Normal 34" xfId="612" xr:uid="{67A17848-1292-487C-BC45-83E4D8C8F2CB}"/>
+    <cellStyle name="Normal 35" xfId="613" xr:uid="{F92040A7-875D-4070-AFDF-CE845C646253}"/>
+    <cellStyle name="Normal 36" xfId="614" xr:uid="{2F5BCA1F-4F75-4756-8FDF-00E0A9591C68}"/>
+    <cellStyle name="Normal 37" xfId="615" xr:uid="{83F80D49-FF7C-4C5A-B30C-5038ED131343}"/>
+    <cellStyle name="Normal 38" xfId="616" xr:uid="{EEBAC40B-98C5-4304-8FD1-29C3366CBA0C}"/>
+    <cellStyle name="Normal 39" xfId="617" xr:uid="{183B55D6-640B-4813-A571-BEDBCB78F031}"/>
+    <cellStyle name="Normal 4" xfId="618" xr:uid="{E9E24CCB-FBF0-4259-ACF5-A7A1C2E0E27F}"/>
+    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{252EF4F6-6E74-478F-896B-283BEBEBCA5B}"/>
+    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{BE7C1520-7DCE-4A35-92A9-6CBC8865D761}"/>
+    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{09C3B765-0878-4F87-B7AD-6BBC3267A0E9}"/>
+    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{9CBE0980-E798-46A5-8697-CAEAFA174844}"/>
+    <cellStyle name="Normal 40" xfId="623" xr:uid="{A3B08754-61EE-409E-951D-183DAEC4A704}"/>
+    <cellStyle name="Normal 41" xfId="624" xr:uid="{4CEBD015-CB24-4B47-95BD-3FD06EB41948}"/>
+    <cellStyle name="Normal 42" xfId="625" xr:uid="{A283B2EC-F7FE-4D2A-A469-CF3A4C0A8285}"/>
+    <cellStyle name="Normal 43" xfId="626" xr:uid="{8C4C7313-305A-4F41-B4BE-B4C4D9578241}"/>
+    <cellStyle name="Normal 44" xfId="627" xr:uid="{0FD6C1D3-6073-4ED4-9B8C-0AD415B29FE4}"/>
+    <cellStyle name="Normal 45" xfId="628" xr:uid="{AEB9347F-883C-4A54-A468-2752E42E2E63}"/>
+    <cellStyle name="Normal 46" xfId="629" xr:uid="{04333C79-C0ED-48C8-B00F-768A6A091C3C}"/>
+    <cellStyle name="Normal 47" xfId="630" xr:uid="{68F1CB37-0895-4BD8-A312-6B790FF6D47A}"/>
+    <cellStyle name="Normal 48" xfId="631" xr:uid="{48455078-FE6D-4D19-85E4-56F371F365A7}"/>
+    <cellStyle name="Normal 49" xfId="632" xr:uid="{28D8B773-3B6B-4E3D-8895-1D5D39C3ABBB}"/>
+    <cellStyle name="Normal 5" xfId="633" xr:uid="{219102FC-1555-4FC3-AE20-F6349C228C25}"/>
+    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{B8A7D67A-0A07-4D1B-966A-8FECAA5BB54E}"/>
+    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{FCEE43D6-B410-4563-8452-A553D3B33E04}"/>
+    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{B61BC7C9-A0DC-4B2F-8099-23147655F75E}"/>
+    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{0DDA601F-0AE4-4C0D-99C7-A977BAFA2DA9}"/>
+    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{3193FC1A-113A-4C91-A02E-253E6E6D7620}"/>
+    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{81568482-8033-485D-A774-D7A577FCE9BA}"/>
+    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{A581DC1D-9346-4977-B0BC-B9914B2134F5}"/>
+    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{8D0673B7-2EFD-4681-8702-3F4014549F97}"/>
+    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{7D352EFF-9443-43E7-B2E1-CEC82406FD62}"/>
+    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{1A644E23-F424-446A-95EF-EC7AB6491C78}"/>
+    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{5648AED7-585A-42BF-A832-46013052F1BB}"/>
+    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{E4DB6445-C64C-45ED-AEF4-C3C45C558E8A}"/>
+    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{D12CEFA3-C21E-4F0F-A756-3B5785C3DCCE}"/>
+    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{7508E18E-74C6-4991-9D6F-27DD16F1FF9B}"/>
+    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{602BBFD0-8DBB-48E0-8478-6D50C2CD8713}"/>
+    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{52BCEC1B-B515-401A-8F85-DC048A7B4A4A}"/>
+    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{6027E096-81EB-4F25-B81E-894D836B196F}"/>
+    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{3552F934-9880-4D65-9915-366C4AEED3E8}"/>
+    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{7C970F93-2186-40A8-83F3-5D6CD4D52DB5}"/>
+    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{303F8099-A611-4301-A46E-64C9C19906D4}"/>
+    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{A7F4C5F6-B2D8-4A84-8D30-1ACB31E34088}"/>
+    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{C5D53BF3-23DB-4760-A911-36E8971D0FD1}"/>
+    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{33BE5FE3-EA5D-4327-B433-4CD22C9AC031}"/>
+    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{082D991B-8B21-4B7A-BA73-E8BD39D4328C}"/>
+    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{EF0AF637-AC93-46A1-A0EB-1E02ED4DBA28}"/>
+    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{81E49D2D-9A6C-4616-94BE-E0D8B0BC8824}"/>
+    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{9966C65F-BE34-42E2-87C9-1DCDF31658FC}"/>
+    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{8CC11D6C-BE50-421B-9524-5BA7C47445AC}"/>
+    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{21CD012C-B6AA-4D9A-BF46-FA3C4D8BE2AE}"/>
+    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{D125C1F4-66A5-4C8B-97B1-0110C5FA85CA}"/>
+    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{129CCE14-7D6E-4BE9-A1B8-2319041BD8C7}"/>
+    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{6FE70AD2-D949-4F6A-B224-70CFB287CF90}"/>
+    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{2F62ED83-17F1-43A7-B0FD-969C48061CDA}"/>
+    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{6E5339F9-411C-41D7-9C97-F121A6F50157}"/>
+    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{D5167A38-BD5B-4F28-BD66-69E20BAF0828}"/>
+    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{DF29436F-5BE4-4E0E-868E-064535ECEDF7}"/>
+    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{5DA40E90-3145-466F-8652-63A22C551398}"/>
+    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{36482820-BA97-466D-80CE-C2298ED84E30}"/>
+    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{B7CA44EE-7C1C-45CB-971B-9F1EFBF59A88}"/>
+    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{43F1078E-9847-4951-A918-786358DCAAFF}"/>
+    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{C8752D87-0561-4CBB-BCB7-67C6CA1F487C}"/>
+    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{9751616F-8F72-4ED7-B26E-B6D36A7F7303}"/>
+    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{9F9C3152-05B9-4AFD-8A8D-52512D3710EC}"/>
+    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{8BC21AF8-93D0-435D-89C2-2B4C88EFD6EC}"/>
+    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{B6AE6F9A-9779-4408-B395-02CA27B89D2D}"/>
+    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{FBB3218C-DD06-425A-BA7A-AC1D8E1F3226}"/>
+    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{B4619193-68B1-4BFC-9DC6-899A7BCC79EC}"/>
+    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{3D40A40F-51D0-4D71-A8DC-0CB7ECA3ED35}"/>
+    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{12F234C9-5CD0-4E52-99F2-71E06DD4FB24}"/>
+    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{14E59730-92F3-4A93-947A-9DA909DC5566}"/>
+    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{C39F8384-03D5-4FC4-A21C-4EF4456ED462}"/>
+    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{B0AD780E-E693-4590-AD1A-5C4D0453E1C2}"/>
+    <cellStyle name="Normal 50" xfId="686" xr:uid="{780E9F4F-FE56-46A0-A1A4-ED18F73D0138}"/>
+    <cellStyle name="Normal 51" xfId="687" xr:uid="{1E338177-AED8-4B59-AF4D-8ECF93BDACCD}"/>
+    <cellStyle name="Normal 52" xfId="688" xr:uid="{CDEBBED1-0530-42A2-B0BC-F600A925E3C6}"/>
+    <cellStyle name="Normal 53" xfId="689" xr:uid="{75038936-1E40-4D2C-AE3F-386183227F3A}"/>
+    <cellStyle name="Normal 54" xfId="690" xr:uid="{16729C09-5D18-4A99-BEEA-56A6949F5EF2}"/>
+    <cellStyle name="Normal 55" xfId="691" xr:uid="{3EAE9C30-34A5-4C37-AEC4-39146506F24F}"/>
     <cellStyle name="Normal 56" xfId="2" xr:uid="{9730C38F-3C43-42D6-94B2-B11839A8846B}"/>
+    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{E6DE8DE4-1087-465A-BF31-995FF04C9B04}"/>
+    <cellStyle name="Normal 57" xfId="693" xr:uid="{B93286D0-6471-4EA0-BC30-4FD068C507DE}"/>
+    <cellStyle name="Normal 58" xfId="694" xr:uid="{9EEA731D-E9DA-4509-9C83-2536B9376D92}"/>
+    <cellStyle name="Normal 59" xfId="695" xr:uid="{593FF683-579A-4A86-A6AB-6F958E9D3DE9}"/>
+    <cellStyle name="Normal 6" xfId="696" xr:uid="{63E50E58-5740-4850-B396-8BE12DF1183A}"/>
+    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{CE81DA93-6F5E-4542-97B3-846406C77B73}"/>
+    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{822F3836-F0CA-48F4-A813-2C1E581F59E1}"/>
+    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{CFCB84E0-AD08-4406-801F-24C5C7CD6930}"/>
+    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{E648884C-0CD9-4EBC-8C29-DA9D3D125388}"/>
+    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{317D1CBA-C96E-456F-82AA-0AB7B83FADBB}"/>
+    <cellStyle name="Normal 60" xfId="702" xr:uid="{0A52F6EA-1CDE-4FC5-85D7-D58B90A1C807}"/>
+    <cellStyle name="Normal 61" xfId="703" xr:uid="{44ABA0C7-F4BC-46D8-814C-1D9F7A160BD2}"/>
+    <cellStyle name="Normal 62" xfId="704" xr:uid="{C530BA90-6A44-4657-9D84-ADAE92CF547D}"/>
+    <cellStyle name="Normal 63" xfId="705" xr:uid="{E7D4AE88-4B1D-4FDB-BF2B-0B8DF2EA3F19}"/>
+    <cellStyle name="Normal 64" xfId="706" xr:uid="{2E5923D0-3E1C-4E3D-8911-9100A17D2242}"/>
+    <cellStyle name="Normal 65" xfId="707" xr:uid="{82600F7D-D7E5-42A3-89E3-813811A2E2FC}"/>
+    <cellStyle name="Normal 66" xfId="708" xr:uid="{F5BE7655-84E0-43AB-B880-CEA9C746D4D9}"/>
+    <cellStyle name="Normal 67" xfId="709" xr:uid="{5903F13F-949C-4542-9BFE-FDDF208FFD8D}"/>
+    <cellStyle name="Normal 68" xfId="710" xr:uid="{91459C12-7A02-4897-9E66-0D631A6F9024}"/>
+    <cellStyle name="Normal 69" xfId="711" xr:uid="{CC68BFE2-8BA9-41E9-9307-9339B0F278ED}"/>
+    <cellStyle name="Normal 7" xfId="712" xr:uid="{A6005739-2B1A-4265-B8FD-0FCF7EDB45BA}"/>
+    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{AB328181-927A-43DE-9A52-AEE3809611F0}"/>
+    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{4C41A2F1-30C6-4DAD-8745-C9D575CA49AD}"/>
+    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{EE1F68C6-B252-41F2-B4D8-D9011E62AFE9}"/>
+    <cellStyle name="Normal 70" xfId="716" xr:uid="{78822FA2-58A5-4767-99FE-5FF922A942E1}"/>
+    <cellStyle name="Normal 71" xfId="717" xr:uid="{472098A9-BB60-48DA-8E26-B26FB98ADF1F}"/>
+    <cellStyle name="Normal 72" xfId="718" xr:uid="{B56DABF2-1F6A-477F-9E1E-1DC2BC347221}"/>
+    <cellStyle name="Normal 73" xfId="719" xr:uid="{F490A527-708C-41C0-B5B5-CEFB458E6938}"/>
+    <cellStyle name="Normal 74" xfId="720" xr:uid="{0D80E111-E78B-4BFB-A8F6-969766D06DA0}"/>
+    <cellStyle name="Normal 75" xfId="721" xr:uid="{D7191799-040E-4DAC-99A3-884F459EBF46}"/>
+    <cellStyle name="Normal 76" xfId="722" xr:uid="{31059DF7-F0F4-48B3-AD39-4CF4AFA6F679}"/>
+    <cellStyle name="Normal 77" xfId="723" xr:uid="{05A30249-0BF3-4D04-9323-C29386D4D36A}"/>
+    <cellStyle name="Normal 78" xfId="724" xr:uid="{200E4D1A-381D-4EC2-994B-2BF6785931A0}"/>
+    <cellStyle name="Normal 79" xfId="725" xr:uid="{E65A4015-1159-49BE-B2B6-2405AAB6D118}"/>
+    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{59AA1ED2-223A-4DE4-A75F-FABE9B805DD1}"/>
+    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{453FAD6F-DF0A-4555-98BF-112DB3B34EB3}"/>
+    <cellStyle name="Normal 8" xfId="728" xr:uid="{E6E51E91-2B50-4869-A34C-69B4A89CFEF8}"/>
+    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{8231493B-3085-4F4B-83CE-FD133A398F86}"/>
+    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{3EC89CF8-5E5E-45F2-9F14-C936E2600F47}"/>
+    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{72BA04F9-1B91-480E-9CE4-CA4B430AD154}"/>
+    <cellStyle name="Normal 80" xfId="732" xr:uid="{70EB5AC9-CE7A-439D-A014-D4BB1C0DB0A8}"/>
+    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{6F63C6CF-184C-4E28-B580-75AB800B12A7}"/>
+    <cellStyle name="Normal 81" xfId="734" xr:uid="{41060087-0F78-4970-A740-8681D453A6F7}"/>
+    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{5F47731D-12E9-4653-B5DC-C29DC3E41BD7}"/>
+    <cellStyle name="Normal 82" xfId="736" xr:uid="{EF4D9537-D708-48BC-BF9A-86853C10EA6C}"/>
+    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{7F98E9CF-5FBA-43C6-835B-7486D27A4C39}"/>
+    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{C4DF2079-83AC-4037-8DC9-0B56697600D0}"/>
+    <cellStyle name="Normal 83" xfId="739" xr:uid="{C5C33BB7-BAD5-4BF5-8376-B605AAAFFFD0}"/>
+    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{F5F7FEF7-F60D-4EAC-AFEA-A9AA727156AC}"/>
+    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{A1FF16E8-05DE-430C-A20F-EF59CA1A9D3D}"/>
+    <cellStyle name="Normal 84" xfId="742" xr:uid="{906FA809-1B94-44D2-8DEC-E38554CFFCA8}"/>
+    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{3349AF23-0053-47A8-B2D1-C38ABEFC2EE3}"/>
+    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{A41E461D-0005-41DD-85A9-689CE82CD270}"/>
+    <cellStyle name="Normal 85" xfId="745" xr:uid="{A8EA39BD-0FBD-4F74-A89A-D444203BEBC5}"/>
+    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{2C1F49E4-1085-4D5F-B435-E9137DECADFA}"/>
+    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{0FEF1941-C37A-47EA-958D-6ABB8A4DD3EA}"/>
+    <cellStyle name="Normal 86" xfId="748" xr:uid="{585B389E-5C37-4F67-9C74-834F55B22F96}"/>
+    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{7BE61E26-4FAC-4546-A692-F8B3DAA15F00}"/>
+    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{97A5D3B0-EFB0-435E-86CB-77696BDDAA6E}"/>
+    <cellStyle name="Normal 87" xfId="751" xr:uid="{70BD093B-63F0-44A4-BB18-21BD5A1FEFAC}"/>
+    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{10EC29DB-CCB1-4596-ABE4-15E7393F5C25}"/>
+    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{C8DCAEC7-993D-41AB-A56E-A5B82ED47127}"/>
+    <cellStyle name="Normal 88" xfId="754" xr:uid="{7E884CA3-1534-49DF-8683-1AB89439E0CA}"/>
+    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{2C3AC846-2360-4E15-AE13-45AB2082A79C}"/>
+    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{50CC4E47-041C-4D63-8234-C4CAA9B40797}"/>
+    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{578DBC71-43A5-4B7C-9B5C-45E1615E1084}"/>
+    <cellStyle name="Normal 89" xfId="758" xr:uid="{B3ED2692-1D33-45F8-B970-F5C743F970F4}"/>
+    <cellStyle name="Normal 9" xfId="759" xr:uid="{E941E19B-E186-426F-A320-7B6D01222BA2}"/>
+    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{564570D7-9A8B-4DCB-91E0-485D48DC05EA}"/>
+    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{FFF9F98C-DA01-4286-83B6-52D8C236B7DC}"/>
+    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{EDF18F4E-E155-43FC-99CD-7EAA60BC1F2E}"/>
+    <cellStyle name="Normal 90" xfId="763" xr:uid="{58BCDA86-96CF-4592-AAFE-73061F133895}"/>
+    <cellStyle name="Normal 91" xfId="764" xr:uid="{25648426-E748-41D1-AE1B-2D45A0900B96}"/>
+    <cellStyle name="Normal 92" xfId="765" xr:uid="{23005439-88B0-44B7-A263-2FC92FA71960}"/>
+    <cellStyle name="Normal 93" xfId="766" xr:uid="{D7255857-1F24-49BA-8AC5-8144FEA87735}"/>
+    <cellStyle name="Normal 94" xfId="767" xr:uid="{FBFCC060-41EE-4E78-B1C7-97B7690BC166}"/>
+    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{23310C5D-B255-4F2B-9220-2B38ED151CDF}"/>
+    <cellStyle name="Normal 95" xfId="769" xr:uid="{3B7D2B12-80B6-4370-9950-7F64CD1BEEA5}"/>
+    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{28765132-1573-4880-8ADD-ED3BDDFDAD31}"/>
+    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{92A03F67-D2BB-471D-A2C8-D81D5F3DDA20}"/>
+    <cellStyle name="Normal 96" xfId="772" xr:uid="{1F3AC05B-4540-42C6-A7D0-F786F8CC4503}"/>
+    <cellStyle name="Normal 97" xfId="773" xr:uid="{2FD84B57-C7C2-46E4-BF60-5B4471CE486F}"/>
+    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{3C1A80B5-EEB6-43B3-A4D1-F3A1C912A352}"/>
+    <cellStyle name="Normal 98" xfId="775" xr:uid="{E495EF88-FACB-4CB9-8DF8-0FCA8AED44CC}"/>
+    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{F0F5082A-1AFA-4FDE-B3E0-8A37A54590B9}"/>
+    <cellStyle name="Normal 99" xfId="777" xr:uid="{652B533F-4E61-4A6F-AE54-D709EFF18F55}"/>
+    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{A0BC0354-EF57-4655-B069-03E2EA8D374F}"/>
     <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{55CE7787-8275-4D8C-9DD8-FBACCA7FE62B}"/>
+    <cellStyle name="Notas 2" xfId="779" xr:uid="{29BEFE6C-C375-4AA0-897B-2FDC1F43FEAB}"/>
+    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{AA3A2B50-6892-419A-B77A-99B4BB44F21D}"/>
+    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{3AF66E0C-23BC-4276-A7DE-F552239D3D5F}"/>
+    <cellStyle name="Notas 3" xfId="782" xr:uid="{0173F74A-C224-4051-819E-3C4A33F56617}"/>
+    <cellStyle name="Notas 4" xfId="783" xr:uid="{DBCB6CAD-7F69-4694-9A0B-9FE76A32E12C}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{0626749F-50D8-480E-8163-9A61FEE8FCAF}"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{27D27D78-B85C-4343-AA40-5B4546337C0E}"/>
+    <cellStyle name="Salida 2" xfId="786" xr:uid="{5F7D66D7-7D0D-44CB-B09D-615B8AA01F34}"/>
+    <cellStyle name="Salida 3" xfId="787" xr:uid="{58C3A535-31B7-4C0A-932B-6CD0E9F72694}"/>
+    <cellStyle name="Salida 4" xfId="788" xr:uid="{64782063-8128-4723-BCA0-1BC503EEA38B}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{EBA980F8-0FD8-4D77-B976-46BB962B9455}"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{DB8B12A9-ABED-4E5F-8D02-3805DA01473F}"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{BAE0ACF2-A32E-44D8-807D-772D523B2B49}"/>
+    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{2239296C-AC91-4C58-B229-71AB7FE71CA1}"/>
+    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{20527625-32A2-4F08-94C9-4A9C796BDF86}"/>
+    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{04172329-BD3F-4EBC-A8A8-9B6F6D1FEAAD}"/>
+    <cellStyle name="Título 1 2" xfId="795" xr:uid="{C1386367-B31C-4208-A56D-CD2C6453D1E2}"/>
+    <cellStyle name="Título 2 2" xfId="796" xr:uid="{85CDB38A-FD67-4B69-BB46-C178E6A69E0A}"/>
+    <cellStyle name="Título 2 3" xfId="797" xr:uid="{6AC02DEA-11BC-49A7-94FC-BD1BC059E97E}"/>
+    <cellStyle name="Título 2 4" xfId="798" xr:uid="{CD27F34B-0125-44BD-9B88-CE653B3E68E1}"/>
+    <cellStyle name="Título 3 2" xfId="799" xr:uid="{699D463B-632F-429F-9205-EC4A14CE361F}"/>
+    <cellStyle name="Título 3 3" xfId="800" xr:uid="{1BC347C2-446A-4928-A609-850766F6DCCB}"/>
+    <cellStyle name="Título 3 4" xfId="801" xr:uid="{5DED24EE-812C-4112-B9E1-4BAA537CA5DA}"/>
+    <cellStyle name="Título 4" xfId="802" xr:uid="{35B8EAE3-61C4-4C7D-A449-65DD0E622C12}"/>
+    <cellStyle name="Título 5" xfId="803" xr:uid="{4CBE3CDB-6D89-42FB-B42D-80476B340520}"/>
+    <cellStyle name="Título 6" xfId="804" xr:uid="{F33F369F-149F-48BD-BF13-4A934B045587}"/>
+    <cellStyle name="Total 2" xfId="806" xr:uid="{6931E99E-87DA-40B6-AF61-693113B3F2F3}"/>
+    <cellStyle name="Total 3" xfId="807" xr:uid="{1F129012-82C8-4F3C-9CDF-462BA1469809}"/>
+    <cellStyle name="Total 4" xfId="808" xr:uid="{F64ADB95-C974-4C1E-A6E2-A48BDFE4DA32}"/>
+    <cellStyle name="Total 5" xfId="805" xr:uid="{65F18EF9-7BC5-4B38-879D-C8CA14AE986E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -659,10 +2645,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12C2188-7ECA-4686-95A1-CA6D9A4276B5}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -1111,6 +3097,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>46140</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>46141</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1118,7 +3138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195F5366-1760-4B97-B100-3707835114CC}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
@@ -1143,171 +3163,187 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>46139</v>
-      </c>
-      <c r="B2">
-        <v>40338.944788629997</v>
-      </c>
-      <c r="D2" s="15" t="s">
+        <v>46141</v>
+      </c>
+      <c r="B2" s="18">
+        <v>28385.438679769999</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <v>42155.425069182624</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
-        <v>46136</v>
-      </c>
-      <c r="B3">
-        <v>60973.651931649998</v>
-      </c>
-      <c r="D3" s="15" t="s">
+        <v>46140</v>
+      </c>
+      <c r="B3" s="18">
+        <v>70324.097718699995</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <v>68497.757342013356</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B4">
-        <v>4652.1817311200002</v>
-      </c>
-      <c r="D4" s="15" t="s">
+        <v>40338.944788629997</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>85928.931135131905</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B5">
-        <v>17251.00486529</v>
+        <v>60973.651931649998</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B6">
-        <v>47981.781644150004</v>
+        <v>4652.1817311200002</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B7">
-        <v>51339.49161813</v>
+        <v>17251.00486529</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B8">
-        <v>17216.492596060001</v>
+        <v>47981.781644150004</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B9">
-        <v>18.890111640000001</v>
+        <v>51339.49161813</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B10">
-        <v>15.79809785</v>
+        <v>17216.492596060001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B11">
-        <v>16.215898760000002</v>
+        <v>18.890111640000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B12">
-        <v>2475.4322626600001</v>
+        <v>15.79809785</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B13">
-        <v>7956.2858669899997</v>
+        <v>16.215898760000002</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B14">
-        <v>41.536584740000002</v>
+        <v>2475.4322626600001</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B15">
-        <v>580.56056466999996</v>
+        <v>7956.2858669899997</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B16">
-        <v>116.97186189</v>
+        <v>41.536584740000002</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B17">
-        <v>6972.36861443</v>
+        <v>580.56056466999996</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="B18">
-        <v>540.00852741999995</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="B19">
-        <v>5262.3389565099997</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B20">
+        <v>540.00852741999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B21">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
         <v>46111</v>
       </c>
-      <c r="B20">
+      <c r="B22">
         <v>22969.58967849</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935188A9-9026-449F-94BB-9F218D846742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5" xr2:uid="{5152B028-5D8D-40E5-B01B-F055ABF9B154}"/>
+    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>DÍA</t>
   </si>
@@ -135,20 +129,26 @@
   <si>
     <t>SEMANAL</t>
   </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>24/04/2026 (*)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
-    <numFmt numFmtId="174" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
+    <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,7 +642,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="809">
+  <cellStyleXfs count="810">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
@@ -753,18 +753,18 @@
     <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -884,9 +884,9 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1452,8 +1452,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1500,820 +1501,831 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="809">
-    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{4C1F6AF9-C2C6-4D4F-BDB4-24A84AC67864}"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{64F93E83-777D-42DA-BFB9-80EEB14E8A5C}"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{E36321BB-21BF-4833-A71B-6D02629D246A}"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{08A9312D-2785-494C-808A-016B96F64A71}"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{46EA7CBA-1313-428F-9EFA-37411A38FB3D}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{39CA57F4-2D9B-4BA2-92CD-29D379BDB0BE}"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{E27AE825-F08E-446E-8991-5A448447C099}"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{3F837449-132E-443E-84D8-0A4F1DE34552}"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{58213CE0-28DB-41FB-B176-C8B4D885ECD3}"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{AE866907-F8D6-4CCA-8DC9-EC63D679D7E4}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{1B47D904-B8A6-4D17-96B0-F9E58A45A12B}"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{E6338C18-6F5B-4352-8362-5A39C1FE6122}"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{5BCBD1D0-CD8B-40C7-8D13-9C2E1D684B75}"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{6E19A926-B979-4345-8CC2-05CB97AC6C26}"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{E6018A2A-00F8-4BA3-A660-693A91C5EA89}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{ADB4197C-A1E6-46CC-BAEE-E5D85A9A1EF8}"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{958198DC-62D7-45BF-8D5E-451B493AFEF9}"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{3A3351FF-CEA8-4388-98F1-00C83913E871}"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{92DBF5E1-63CA-42F0-9919-E89CF7F2DEC5}"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{A5656AF4-B335-4F4F-AC61-7B837FA39A82}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{57FC36DE-8AE6-42BD-BC5C-9ABEDD700664}"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{94707772-64DC-44F0-B5D7-10AD6C2888C5}"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{BA4D69A1-82F1-429B-826D-0929E6741888}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{3EDB7517-6444-4DCE-816F-2C3EDE1CB35C}"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{B1A7AE61-86F6-48EF-9712-BA0DA1995554}"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{02E4BB81-7B26-4238-AD73-7E2533BFCF0F}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{5ADAFF5F-98E7-495B-8C8A-7987827B8563}"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{BD7E5BF3-E7B8-4882-8689-2E3EF2107A67}"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{3AF3C8A6-695B-4BA1-9F00-256CE2262AF4}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{FB869613-E827-46DA-8398-1E071E0552FC}"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{0DBF0DDE-06CF-492B-848C-81A56BDC8392}"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{8EB7DD2F-4736-41F9-86CB-5F8DA3721093}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{5A392FDF-B39D-4412-A269-F9CF0175F0E5}"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{6C7FD24B-CD26-4573-AF9F-C64763526438}"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{BF78EFDC-3ED5-488F-8410-EBAB5F7D5BBF}"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{2B3C0D7A-12B7-4FD8-972C-E4E86F420E11}"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{09836EBF-E128-4D11-99A9-4E8BEA5DDDE1}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{E4C5116E-06C2-4A98-B678-FF67121A1BD8}"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{5435718B-E367-4201-A107-CAD4ABED7B1C}"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{14D63FEA-2BDE-4617-94EF-96B423EF934B}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{8DC0406C-3861-45A5-9C89-4B22A1A0D3E5}"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{D595AD87-442A-4548-8427-DC15086AB880}"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{A5024469-DE0A-47B4-9D7B-E809AE6C0316}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{07E6E230-7601-43DC-B3A5-9126F578829B}"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{C5BD5A08-BC63-4B9E-819A-B72989AA4519}"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{01A20566-4462-4525-84CD-C1B7DB84A321}"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{830BBF0A-F7C3-426D-954D-355A488A307A}"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{42335429-F6A4-4FD9-9F31-EDEB1EA21138}"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{736AC983-BE17-49BD-A12A-742BCF069FBC}"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{0663239A-2F3A-4BA7-B4DC-5DD43EA736D2}"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{EA737BB3-C572-4941-B32E-28D22AEFE44E}"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{C38F7C0E-0678-456F-8671-863DA416F341}"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{4BC2A840-7D8F-446D-A905-C6797B56CF14}"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{0AFE8E0F-9E1D-4A07-9285-2AD53A844797}"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{621FEE32-5965-43ED-93C8-D86BFFD5ACC7}"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{21C07476-710F-4EE4-BB5C-E7B3CEDA86A6}"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{F80B5B4E-63D6-4E9E-AC89-97610DACB31D}"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{6479AA33-C55F-4C1F-9720-EA0C57B2F598}"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{4B4D600F-7116-4E24-AE4C-E4BD283484E8}"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{02A3FDE7-2491-41F7-BC1C-BF8C787623CE}"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{9C77428A-727A-484D-8D0E-32110E465DE6}"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{6AF969A7-E456-4400-A469-0141AFC94902}"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{C7929753-A670-46D2-9D90-03B09C2D8AFE}"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{CB71EA2B-2CC3-4C39-B9FE-77961338725B}"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{D20514AF-549A-4BA1-9419-1BF2EA054412}"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{22E9D53F-DBED-4E3B-9FE8-7AB03CD42B4B}"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{A5487202-3560-4049-AC12-945905769309}"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{6D5785B7-0A92-4A58-A869-3DE648F4E961}"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{11CF140A-A59B-44C3-9AC9-02708B562B0F}"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{4EA8705F-F732-45E0-9811-E3F6DDB76FCE}"/>
-    <cellStyle name="Buena 2" xfId="74" xr:uid="{FF140419-618D-4E1B-BE0A-46976549ABCC}"/>
-    <cellStyle name="Buena 3" xfId="75" xr:uid="{F8F9A4DC-EAC0-40C2-9CA5-A3A5466BAD1D}"/>
-    <cellStyle name="Buena 4" xfId="76" xr:uid="{91957E4D-896B-4FF2-90B8-B85EEE661892}"/>
-    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{C1D869BA-C367-41F5-A48E-08E72380BBCE}"/>
-    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{75A43D64-1D57-4621-A528-E6BA3B2817F6}"/>
-    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{1D4247DB-53A7-4FA6-88D2-14F5E05FF0CA}"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{350163C5-0B5A-4211-AAB1-4486FF9997A4}"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{151B7195-2E52-451D-A2BC-2853F2C59FBC}"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{60AAD422-9116-4F63-80F9-CF1214148415}"/>
-    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{BEB8387D-972B-4978-80D6-C03EED4AD3CF}"/>
-    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{F0C8C395-9EDB-4A9F-8BB5-B4A36B59B8B4}"/>
-    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{FCCF11B4-8081-43F5-B331-E07578D8D4A6}"/>
-    <cellStyle name="Comma 2" xfId="121" xr:uid="{B1620963-1B87-4652-962B-182547FD4800}"/>
-    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{05F7F6A8-1080-4AF8-96D3-C9F32B1D1494}"/>
-    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{39B45B43-1908-4748-B21B-AA40BA00CBFC}"/>
-    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{DF5C0EA4-F1F6-4EEE-B90C-6A74642C2024}"/>
-    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{35C38597-1885-445B-9069-08C79EB1EA70}"/>
-    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{76754287-4BD0-494C-BA3A-AFCFF7A1BFD0}"/>
-    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{4A29A633-E092-4D5A-A2F2-C4BBF48E3175}"/>
-    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{B85ECD18-A060-4BC7-AE21-2E7CD492D787}"/>
-    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{2F90C461-1E95-4FD4-B057-7936BAF461E6}"/>
-    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{64EA65E7-CCB3-4FEC-854A-845E5867FA32}"/>
-    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{CECE3725-A2D4-4548-92AA-72BF57CA2078}"/>
-    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{E8C1293C-BF12-4477-A57B-5872F3011B52}"/>
-    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{4264603B-E6CC-42DD-AF7F-E6A886288DC4}"/>
-    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{BDE600DC-9AC4-485F-81B0-1D8FD2BE23A8}"/>
-    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{C409837C-8AF4-4F19-9D33-E3A3FFBDBFB8}"/>
-    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{5BD8E991-FA77-4CF6-8D8B-02A86647217C}"/>
-    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{551C7CF7-54B4-4252-8E14-2C711D66FCF4}"/>
-    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{DC4F5A4F-9FC4-4A7A-A197-334350D552BA}"/>
-    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{F60AF022-23DF-4A48-8AA4-54F52B62DF79}"/>
-    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{1438A5E6-E6E4-4B11-BC87-6FE42B7E59AE}"/>
-    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{6F6B8DDD-6812-424F-B06E-5AB96CFBEF45}"/>
-    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{93162E2C-1B15-46D7-A3BA-5008A77EE925}"/>
-    <cellStyle name="Entrada 2" xfId="107" xr:uid="{D837E91D-FD62-4874-84A4-051A3CED421C}"/>
-    <cellStyle name="Entrada 3" xfId="108" xr:uid="{79766B91-3506-4E6E-AF39-F62FE9A62207}"/>
-    <cellStyle name="Entrada 4" xfId="109" xr:uid="{8E24CBBE-F4AB-44D1-90EA-D475CB72366F}"/>
-    <cellStyle name="Euro" xfId="110" xr:uid="{4EF04BF9-476A-4265-A865-8F0362D2F03E}"/>
-    <cellStyle name="Euro 2" xfId="111" xr:uid="{4F4737C1-A55F-4F56-8207-851C7F517620}"/>
-    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{F18FEE46-7005-47E5-83A1-56709FDA314D}"/>
-    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{73ABB318-225A-411C-B3B5-51C2CCF5AB84}"/>
-    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{A68739EE-332B-4E10-8A66-4F329926ACE6}"/>
-    <cellStyle name="Euro 3" xfId="115" xr:uid="{5451A2DF-3D31-4937-B347-FC5BB2070DEF}"/>
-    <cellStyle name="Euro 4" xfId="116" xr:uid="{E03885F9-6D5F-4D2B-8107-6FCF6A77ED5D}"/>
-    <cellStyle name="Euro 5" xfId="117" xr:uid="{726DABEA-1C31-4A8C-A372-8B6C7D8D8947}"/>
-    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{2E4ECB7A-9A20-4123-8A1A-E68A2975F4BF}"/>
-    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{F765C2D9-6D6E-4E4F-A4E5-5F9D83DD22FC}"/>
-    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{3A4BA0CD-3632-4147-92E6-C00FDE319801}"/>
-    <cellStyle name="Millares 10" xfId="122" xr:uid="{1817CCC0-A5DF-490C-B7E8-37CA196AF2C3}"/>
-    <cellStyle name="Millares 2" xfId="123" xr:uid="{CFCE98DB-C2A2-4A9E-A3DD-87C77AFE8B06}"/>
-    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{4F28587A-3DF7-47BC-9B74-992E8C1790FE}"/>
-    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{13EF1C90-E81E-4228-8256-897F5E00B5CB}"/>
-    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{2C2787B5-5AEC-4121-B515-BC8FC037A8C3}"/>
-    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{25E4379B-A901-4123-89FE-B54B3C3615A3}"/>
-    <cellStyle name="Millares 3" xfId="128" xr:uid="{DD5D3D04-F867-40D3-BD10-99968662EB9C}"/>
-    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{F1C54CCB-80C3-4913-BF2A-591DEE30F38D}"/>
-    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{C5DC4B5E-B1F4-4889-B2CF-137AB786A2FD}"/>
-    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{8D4C6E37-08FB-42E2-AA7A-F06234C2A674}"/>
-    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{ADAB9156-DAC4-47C4-86EE-9413845B18AE}"/>
-    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{DFE0DF33-9AF4-4E69-BC9E-16E5E2A29520}"/>
-    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{DD319EF0-5752-4653-9EDF-181136F66F6F}"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{AD957B70-C67D-4AED-B999-1D0C3995BAF7}"/>
-    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{0BFA2798-C382-460E-95A6-2E8F78498681}"/>
-    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{227B2093-C360-4A95-A7C3-BA7428AE1659}"/>
-    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{3E64C706-678E-4A51-AFA5-84365BAF48D7}"/>
-    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{CFBFB42E-95E8-4F51-BFA4-38586F1EA1F5}"/>
-    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{7EF8B100-CA5C-4805-9177-135693BE6DEA}"/>
-    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{3776CFEA-A36C-4D56-9044-3780FCFF2208}"/>
-    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{7E43FC61-F1F9-4193-95C3-03B995F593CD}"/>
-    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{7D86599A-56DA-4202-9C1D-CB6EAD9FD0BF}"/>
-    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{240EF294-8376-478C-80A0-D07F27415DCB}"/>
-    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{D0D79BD7-97C9-453E-AE73-745633CC3C09}"/>
-    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{A3DB116A-8988-4E7A-8AE2-F9A2609ECE7C}"/>
-    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{A33B7E3F-41BA-4A52-A555-AD9113B41B09}"/>
-    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{C1D287EE-C9F7-4184-9D1D-190C0C00B2E4}"/>
-    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{9BCBAC7A-55F8-4975-9F2E-D3889C6B63E8}"/>
-    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{018F1313-CE01-41CB-AF6A-4C7C0664DC0C}"/>
-    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{C9083562-B880-4366-A5AE-4F0EE4EE573F}"/>
-    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{1F177D85-B66D-4DFF-834C-ABABCAF3809D}"/>
-    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{EC4B0EBA-E19D-4F46-93D5-3A67CE53B841}"/>
-    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{229A3773-87F3-40A2-97D2-FAD26D50B6DE}"/>
-    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{D80C6905-CC5F-402C-9CA5-3DF354B79D56}"/>
-    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{18A21EC0-EB1E-453F-A7B5-EB523BB1E606}"/>
-    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{B331BE05-204C-484C-9518-6EF6CEFAC03B}"/>
-    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{CF22DC8C-32D1-4B54-A224-1E072C29CA3C}"/>
-    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{A0EAC1B7-6EF3-4522-86A8-D0066AB9EB52}"/>
-    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{EEA5ED24-12AD-4FC9-81B3-3C9399CF2F36}"/>
-    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{64CE7214-5829-4507-A01D-089CD02DF77B}"/>
-    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{C719E815-0848-4707-A294-9D13C8749B1D}"/>
-    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{B89652BA-5842-4FE2-8299-0FE1E93D9272}"/>
-    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{B06AEE7D-51DC-4601-B831-B8CBEF10F989}"/>
-    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{B8D34674-6497-463A-936F-FDC2EF3164B7}"/>
-    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{EA74AFA9-56FC-41E6-AB24-97703A6330FC}"/>
-    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{D44D2937-F162-4AC0-8A66-0386C03F23E4}"/>
-    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{D158EFAA-FE9F-4937-B140-2128BC0779C5}"/>
-    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{DECDA3CE-A776-41FF-8DE3-3B07DEFD5308}"/>
-    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{7DB9DDDE-98F2-4EE8-BBE7-90BF165CB4A0}"/>
-    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{3F2F2FD2-C396-4CD3-BD40-C4FBCFD7BD3A}"/>
-    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{2A268F30-126D-4FDF-B3B0-1EB18F7CACBD}"/>
-    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{CFB606EE-AB1E-42F8-9A27-912B712819FD}"/>
-    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{0FA35113-8984-482D-9088-72B23E04AB2F}"/>
-    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{30195EDF-FA3A-4E45-BF0F-65C5B5A997EC}"/>
-    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{34F620EC-E647-4E1C-B55F-229A358B2A28}"/>
-    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{CBBAE46D-5489-4F4D-ACB2-82ADB81CF9E5}"/>
-    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{7C980247-3E74-4686-9186-BE7884FBB0E7}"/>
-    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{9C6AD0FC-8632-48D7-B619-DCC5CAA18A2E}"/>
-    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{044C4797-148A-4205-A4B1-11CC78F02BAC}"/>
-    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{D6DA5EFF-63A1-4408-849E-C875F2759508}"/>
-    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{0C5C0789-D5FB-4BC5-8877-E3F03C3B4A42}"/>
-    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{799D618F-1648-4D7B-8515-32753398D539}"/>
-    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{6772F29D-6756-4E61-9FDA-953A3E7F03DF}"/>
-    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{FC1F24BF-3CFC-4F1A-9916-66E530EFE6AC}"/>
-    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{2A063913-C25B-4CC0-BB55-6D538056CC19}"/>
-    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{7B8998D3-3C78-4F54-8AD5-E1B33BAB7F46}"/>
-    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{E624F533-75D6-4626-ADD7-47EEAAE5DA5A}"/>
-    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{A8E4A561-032D-4866-BE2D-E6BB0BCCD27E}"/>
-    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{667E44E6-3393-4F2B-9D54-759A7E83A720}"/>
-    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{1703FF1F-1324-463A-AB03-1013AA2183F1}"/>
-    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{45CAC9F3-71CC-49DF-9B15-A04C2B56B913}"/>
-    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{C3309B8D-8C4D-49A3-988D-9C0B1F1D2648}"/>
-    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{27FB2678-338B-4D5D-8799-4DEFCB83C356}"/>
-    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{CE282ABB-B9E1-41B3-A32E-4B7F0F7C3FFE}"/>
-    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{F06B659F-2BFE-4AB9-9BE5-8C8A7CB6227B}"/>
-    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{1217E3F5-4665-45F3-A0E7-9C813F9589E8}"/>
-    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{BA4BAA26-D20A-41EC-A6E2-785549FA95B1}"/>
-    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{247DD842-196E-4A7A-BE54-C80AF88E9EA5}"/>
-    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{908A662C-40B2-44A0-AC17-91034BCA627D}"/>
-    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{1BA93D64-D51D-4DCE-A873-5195E36FCB9A}"/>
-    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{784E3B02-A759-4F40-ADAE-33E3556E769D}"/>
-    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{F4731554-C373-4637-8C49-4F244653C18D}"/>
-    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{817D6995-D3E8-4E49-A866-8BFFD40E8850}"/>
-    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{FBBF7C33-114D-45A5-9B21-C29577DC293D}"/>
-    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{39A808ED-CC60-4993-AE68-19953630FD03}"/>
-    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{6D626AB2-8DEE-472B-997B-4A21AC2E594A}"/>
-    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{181C5B34-0B22-4C23-910C-8B9FB82459AE}"/>
-    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{DD8942EF-BFE4-49EA-8F1B-E182ECBAE57B}"/>
-    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{67B684D4-508F-4881-9057-3EFC6FC45934}"/>
-    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{C6D3E8A0-80A2-4473-96BE-33DA8AE2CB50}"/>
-    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{30D50C7F-D93C-4048-95E6-1AD0AC2EEA52}"/>
-    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{5B1F7586-3D29-4ABB-B5D2-C8829271876A}"/>
-    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{B1CCA735-4249-4950-9EA9-B3999772C4DB}"/>
-    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{2F0DB9C7-295A-4B2A-BEE8-8E95E5F0E1A0}"/>
-    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{DE3A04D1-85BF-4744-B457-75850CB76E36}"/>
-    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{337951BD-FEB7-42C2-AC4D-B02A408AD202}"/>
-    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{8C1437F3-AD0D-4C73-8993-00B11B36204C}"/>
-    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{22C1BA57-5416-44A2-AD49-3EA198165C3A}"/>
-    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{2E4505F7-B623-4C74-A663-862716621A74}"/>
-    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{3EC65A6B-782B-4A85-9965-88A7F027F788}"/>
-    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{C99B938F-9A37-4258-BE46-825000F2F266}"/>
-    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{E1B61DDA-AABD-4EF6-90E4-825D39C44033}"/>
-    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{931D844C-031B-4800-ABBD-EBAA9F560741}"/>
-    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{2F9CE121-57E9-4E1C-B1E4-6EA22B06DCCE}"/>
-    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{6F14D8CD-43D4-46B4-B4EC-EA2AD9530DF6}"/>
-    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{6771ECA7-E22A-4DB2-852F-D79B2E8E1DEB}"/>
-    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{2085CD53-65BA-4021-9E19-DA40B31E9EF2}"/>
-    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{4CDAA3A2-CD73-40E4-B644-7B727F1B7932}"/>
-    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{CCA3E8D2-55A8-4B96-B690-9D625D82A88F}"/>
-    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{73FEEBA4-2CD7-45E7-8ED0-9D8AAAE8AF86}"/>
-    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{50BDDEF5-52DE-4EFE-8696-C27129DE9541}"/>
-    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{60C8AFDB-0EB7-4B66-9EF8-CFFD3F07E375}"/>
-    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{8CDC2C00-427A-4970-84CE-C67393B404D2}"/>
-    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{1AED798E-7A54-4237-A617-87E2A6592C69}"/>
-    <cellStyle name="Millares 4" xfId="236" xr:uid="{BA8288D4-D934-475A-81BE-E2A88B273483}"/>
-    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{BFF80574-B9C9-48F6-B020-9D5CA2A09EF0}"/>
-    <cellStyle name="Millares 5" xfId="238" xr:uid="{C3EA714A-9CE1-461C-87A8-F7C1970F11B6}"/>
-    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{DC42F69F-67AF-4CCC-9C87-987257195845}"/>
-    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{ABBC8BD6-3CA5-4FD1-8A64-B0869523B350}"/>
-    <cellStyle name="Millares 6" xfId="241" xr:uid="{D767DC43-E6B0-4051-A010-1CDF7F69DBFD}"/>
-    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{3C33B28B-050C-44DC-A368-B2D59C71BA4C}"/>
-    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{1A37C586-C353-41F0-912B-A6CBAFF496C6}"/>
-    <cellStyle name="Millares 7" xfId="244" xr:uid="{93D8AD8D-F1FF-430C-A038-1A62E7DD5506}"/>
-    <cellStyle name="Millares 8" xfId="245" xr:uid="{4D0FF579-A0B1-4ED6-A82F-807630017CF5}"/>
-    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{C1121105-1A39-42FD-A66F-0E8A97419FE5}"/>
-    <cellStyle name="Millares 9" xfId="247" xr:uid="{74821AEC-6544-4414-BBB4-7ABFA6D28E3E}"/>
-    <cellStyle name="Neutral 2" xfId="249" xr:uid="{AE50FD0F-34AA-4BD4-95C9-B8E2D8CBCE8E}"/>
-    <cellStyle name="Neutral 3" xfId="250" xr:uid="{F8415CE2-3751-4FA8-8B58-A4526DB0C803}"/>
-    <cellStyle name="Neutral 4" xfId="251" xr:uid="{8CB66ABD-7C12-4B3E-B85E-0347AE9EA8B3}"/>
-    <cellStyle name="Neutral 5" xfId="248" xr:uid="{5F94F30B-879A-4A33-A3D7-B94911CFEA9D}"/>
+  <cellStyles count="810">
+    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
+    <cellStyle name="Buena 2" xfId="74"/>
+    <cellStyle name="Buena 3" xfId="75"/>
+    <cellStyle name="Buena 4" xfId="76"/>
+    <cellStyle name="Cálculo 2" xfId="77"/>
+    <cellStyle name="Cálculo 3" xfId="78"/>
+    <cellStyle name="Cálculo 4" xfId="79"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82"/>
+    <cellStyle name="Celda vinculada 2" xfId="83"/>
+    <cellStyle name="Celda vinculada 3" xfId="84"/>
+    <cellStyle name="Celda vinculada 4" xfId="85"/>
+    <cellStyle name="Comma 2" xfId="121"/>
+    <cellStyle name="Encabezado 4 2" xfId="86"/>
+    <cellStyle name="Encabezado 4 3" xfId="87"/>
+    <cellStyle name="Encabezado 4 4" xfId="88"/>
+    <cellStyle name="Énfasis1 2" xfId="89"/>
+    <cellStyle name="Énfasis1 3" xfId="90"/>
+    <cellStyle name="Énfasis1 4" xfId="91"/>
+    <cellStyle name="Énfasis2 2" xfId="92"/>
+    <cellStyle name="Énfasis2 3" xfId="93"/>
+    <cellStyle name="Énfasis2 4" xfId="94"/>
+    <cellStyle name="Énfasis3 2" xfId="95"/>
+    <cellStyle name="Énfasis3 3" xfId="96"/>
+    <cellStyle name="Énfasis3 4" xfId="97"/>
+    <cellStyle name="Énfasis4 2" xfId="98"/>
+    <cellStyle name="Énfasis4 3" xfId="99"/>
+    <cellStyle name="Énfasis4 4" xfId="100"/>
+    <cellStyle name="Énfasis5 2" xfId="101"/>
+    <cellStyle name="Énfasis5 3" xfId="102"/>
+    <cellStyle name="Énfasis5 4" xfId="103"/>
+    <cellStyle name="Énfasis6 2" xfId="104"/>
+    <cellStyle name="Énfasis6 3" xfId="105"/>
+    <cellStyle name="Énfasis6 4" xfId="106"/>
+    <cellStyle name="Entrada 2" xfId="107"/>
+    <cellStyle name="Entrada 3" xfId="108"/>
+    <cellStyle name="Entrada 4" xfId="109"/>
+    <cellStyle name="Euro" xfId="110"/>
+    <cellStyle name="Euro 2" xfId="111"/>
+    <cellStyle name="Euro 2 2" xfId="112"/>
+    <cellStyle name="Euro 2 3" xfId="113"/>
+    <cellStyle name="Euro 2 4" xfId="114"/>
+    <cellStyle name="Euro 3" xfId="115"/>
+    <cellStyle name="Euro 4" xfId="116"/>
+    <cellStyle name="Euro 5" xfId="117"/>
+    <cellStyle name="Incorrecto 2" xfId="118"/>
+    <cellStyle name="Incorrecto 3" xfId="119"/>
+    <cellStyle name="Incorrecto 4" xfId="120"/>
+    <cellStyle name="Millares 10" xfId="122"/>
+    <cellStyle name="Millares 2" xfId="123"/>
+    <cellStyle name="Millares 2 2" xfId="124"/>
+    <cellStyle name="Millares 2 2 2" xfId="125"/>
+    <cellStyle name="Millares 2 3" xfId="126"/>
+    <cellStyle name="Millares 2 4" xfId="127"/>
+    <cellStyle name="Millares 3" xfId="128"/>
+    <cellStyle name="Millares 3 10" xfId="129"/>
+    <cellStyle name="Millares 3 100" xfId="130"/>
+    <cellStyle name="Millares 3 101" xfId="131"/>
+    <cellStyle name="Millares 3 102" xfId="132"/>
+    <cellStyle name="Millares 3 103" xfId="133"/>
+    <cellStyle name="Millares 3 103 2" xfId="134"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
+    <cellStyle name="Millares 3 104" xfId="136"/>
+    <cellStyle name="Millares 3 11" xfId="137"/>
+    <cellStyle name="Millares 3 12" xfId="138"/>
+    <cellStyle name="Millares 3 13" xfId="139"/>
+    <cellStyle name="Millares 3 14" xfId="140"/>
+    <cellStyle name="Millares 3 15" xfId="141"/>
+    <cellStyle name="Millares 3 16" xfId="142"/>
+    <cellStyle name="Millares 3 17" xfId="143"/>
+    <cellStyle name="Millares 3 18" xfId="144"/>
+    <cellStyle name="Millares 3 19" xfId="145"/>
+    <cellStyle name="Millares 3 2" xfId="146"/>
+    <cellStyle name="Millares 3 2 2" xfId="147"/>
+    <cellStyle name="Millares 3 2 3" xfId="148"/>
+    <cellStyle name="Millares 3 20" xfId="149"/>
+    <cellStyle name="Millares 3 21" xfId="150"/>
+    <cellStyle name="Millares 3 22" xfId="151"/>
+    <cellStyle name="Millares 3 23" xfId="152"/>
+    <cellStyle name="Millares 3 24" xfId="153"/>
+    <cellStyle name="Millares 3 25" xfId="154"/>
+    <cellStyle name="Millares 3 26" xfId="155"/>
+    <cellStyle name="Millares 3 27" xfId="156"/>
+    <cellStyle name="Millares 3 28" xfId="157"/>
+    <cellStyle name="Millares 3 29" xfId="158"/>
+    <cellStyle name="Millares 3 3" xfId="159"/>
+    <cellStyle name="Millares 3 30" xfId="160"/>
+    <cellStyle name="Millares 3 31" xfId="161"/>
+    <cellStyle name="Millares 3 32" xfId="162"/>
+    <cellStyle name="Millares 3 33" xfId="163"/>
+    <cellStyle name="Millares 3 34" xfId="164"/>
+    <cellStyle name="Millares 3 35" xfId="165"/>
+    <cellStyle name="Millares 3 36" xfId="166"/>
+    <cellStyle name="Millares 3 37" xfId="167"/>
+    <cellStyle name="Millares 3 38" xfId="168"/>
+    <cellStyle name="Millares 3 39" xfId="169"/>
+    <cellStyle name="Millares 3 4" xfId="170"/>
+    <cellStyle name="Millares 3 40" xfId="171"/>
+    <cellStyle name="Millares 3 41" xfId="172"/>
+    <cellStyle name="Millares 3 42" xfId="173"/>
+    <cellStyle name="Millares 3 43" xfId="174"/>
+    <cellStyle name="Millares 3 44" xfId="175"/>
+    <cellStyle name="Millares 3 45" xfId="176"/>
+    <cellStyle name="Millares 3 46" xfId="177"/>
+    <cellStyle name="Millares 3 47" xfId="178"/>
+    <cellStyle name="Millares 3 48" xfId="179"/>
+    <cellStyle name="Millares 3 49" xfId="180"/>
+    <cellStyle name="Millares 3 5" xfId="181"/>
+    <cellStyle name="Millares 3 50" xfId="182"/>
+    <cellStyle name="Millares 3 51" xfId="183"/>
+    <cellStyle name="Millares 3 52" xfId="184"/>
+    <cellStyle name="Millares 3 53" xfId="185"/>
+    <cellStyle name="Millares 3 54" xfId="186"/>
+    <cellStyle name="Millares 3 55" xfId="187"/>
+    <cellStyle name="Millares 3 56" xfId="188"/>
+    <cellStyle name="Millares 3 57" xfId="189"/>
+    <cellStyle name="Millares 3 58" xfId="190"/>
+    <cellStyle name="Millares 3 59" xfId="191"/>
+    <cellStyle name="Millares 3 6" xfId="192"/>
+    <cellStyle name="Millares 3 60" xfId="193"/>
+    <cellStyle name="Millares 3 61" xfId="194"/>
+    <cellStyle name="Millares 3 62" xfId="195"/>
+    <cellStyle name="Millares 3 63" xfId="196"/>
+    <cellStyle name="Millares 3 64" xfId="197"/>
+    <cellStyle name="Millares 3 65" xfId="198"/>
+    <cellStyle name="Millares 3 66" xfId="199"/>
+    <cellStyle name="Millares 3 67" xfId="200"/>
+    <cellStyle name="Millares 3 68" xfId="201"/>
+    <cellStyle name="Millares 3 69" xfId="202"/>
+    <cellStyle name="Millares 3 7" xfId="203"/>
+    <cellStyle name="Millares 3 70" xfId="204"/>
+    <cellStyle name="Millares 3 71" xfId="205"/>
+    <cellStyle name="Millares 3 72" xfId="206"/>
+    <cellStyle name="Millares 3 73" xfId="207"/>
+    <cellStyle name="Millares 3 74" xfId="208"/>
+    <cellStyle name="Millares 3 75" xfId="209"/>
+    <cellStyle name="Millares 3 76" xfId="210"/>
+    <cellStyle name="Millares 3 77" xfId="211"/>
+    <cellStyle name="Millares 3 78" xfId="212"/>
+    <cellStyle name="Millares 3 79" xfId="213"/>
+    <cellStyle name="Millares 3 8" xfId="214"/>
+    <cellStyle name="Millares 3 80" xfId="215"/>
+    <cellStyle name="Millares 3 81" xfId="216"/>
+    <cellStyle name="Millares 3 82" xfId="217"/>
+    <cellStyle name="Millares 3 83" xfId="218"/>
+    <cellStyle name="Millares 3 84" xfId="219"/>
+    <cellStyle name="Millares 3 85" xfId="220"/>
+    <cellStyle name="Millares 3 86" xfId="221"/>
+    <cellStyle name="Millares 3 87" xfId="222"/>
+    <cellStyle name="Millares 3 88" xfId="223"/>
+    <cellStyle name="Millares 3 89" xfId="224"/>
+    <cellStyle name="Millares 3 9" xfId="225"/>
+    <cellStyle name="Millares 3 90" xfId="226"/>
+    <cellStyle name="Millares 3 91" xfId="227"/>
+    <cellStyle name="Millares 3 92" xfId="228"/>
+    <cellStyle name="Millares 3 93" xfId="229"/>
+    <cellStyle name="Millares 3 94" xfId="230"/>
+    <cellStyle name="Millares 3 95" xfId="231"/>
+    <cellStyle name="Millares 3 96" xfId="232"/>
+    <cellStyle name="Millares 3 97" xfId="233"/>
+    <cellStyle name="Millares 3 98" xfId="234"/>
+    <cellStyle name="Millares 3 99" xfId="235"/>
+    <cellStyle name="Millares 4" xfId="236"/>
+    <cellStyle name="Millares 4 2" xfId="237"/>
+    <cellStyle name="Millares 5" xfId="238"/>
+    <cellStyle name="Millares 5 2" xfId="239"/>
+    <cellStyle name="Millares 5 3" xfId="240"/>
+    <cellStyle name="Millares 6" xfId="241"/>
+    <cellStyle name="Millares 6 2" xfId="242"/>
+    <cellStyle name="Millares 6 3" xfId="243"/>
+    <cellStyle name="Millares 7" xfId="244"/>
+    <cellStyle name="Millares 8" xfId="245"/>
+    <cellStyle name="Millares 8 2" xfId="246"/>
+    <cellStyle name="Millares 9" xfId="247"/>
+    <cellStyle name="Neutral 2" xfId="249"/>
+    <cellStyle name="Neutral 3" xfId="250"/>
+    <cellStyle name="Neutral 4" xfId="251"/>
+    <cellStyle name="Neutral 5" xfId="248"/>
+    <cellStyle name="NivelFila_3 2" xfId="809"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252" xr:uid="{084EBCA8-0BA0-41FE-9AEE-8DC7BA361460}"/>
-    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{C2C9558A-2B3D-4406-83D0-059E914225AA}"/>
-    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{9CA1290F-CA8E-45B4-95E9-2E24CDDC793D}"/>
-    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{4C55E28F-D046-4B85-9B6D-D75AB72D2C8E}"/>
-    <cellStyle name="Normal 100" xfId="256" xr:uid="{61A73F6D-F81E-42C0-98C1-5B73D097C73B}"/>
-    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{5F7635C1-BEF4-4D9C-924A-FAE15F254CA8}"/>
-    <cellStyle name="Normal 101" xfId="258" xr:uid="{D8078189-B1A2-45B0-8A43-92ACEA2AC42D}"/>
-    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{D85EA871-3511-44A4-9411-D0CF58C6F494}"/>
-    <cellStyle name="Normal 102" xfId="260" xr:uid="{AE4D7422-7E0D-4870-9723-88CD569A7863}"/>
-    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{12A83050-AB19-49EB-89C5-9DADBFDEB8F8}"/>
-    <cellStyle name="Normal 103" xfId="262" xr:uid="{B52740D5-30AA-48DB-BEC5-8CB4FC6D9D1D}"/>
-    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{B648BD3C-F258-43EF-BC17-8B0F6693AE02}"/>
-    <cellStyle name="Normal 104" xfId="264" xr:uid="{0ABDF0C9-05C5-41A3-863E-526D7CFF6368}"/>
-    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{8BD6FE1C-5951-4B61-9E78-2E97ECBBFD77}"/>
-    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{B983A86B-B518-413F-8757-FFC8F17ACE1B}"/>
-    <cellStyle name="Normal 105" xfId="267" xr:uid="{9AA8F441-5CA6-4DDF-9F5C-AC943913608B}"/>
-    <cellStyle name="Normal 106" xfId="268" xr:uid="{C3F91CDD-4C60-478E-A97B-603835C5008A}"/>
-    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{9B96B2E1-ED3E-4681-A7CC-C31261D2BDAA}"/>
-    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{39F36360-6D68-42E8-96D6-C0FBF790B00A}"/>
-    <cellStyle name="Normal 107" xfId="271" xr:uid="{3604C7F0-6C05-4DFF-8D25-24A3332624C3}"/>
-    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{4DDE6BFE-8403-43AF-A16E-36F7286CEDAD}"/>
-    <cellStyle name="Normal 108" xfId="273" xr:uid="{FA3FC4D9-1DD3-496A-9433-70A1FBD15B0C}"/>
-    <cellStyle name="Normal 109" xfId="274" xr:uid="{1B1B7645-D32E-4EC7-8498-48D0EC50BFA5}"/>
-    <cellStyle name="Normal 11" xfId="275" xr:uid="{DDF97C8D-FC4B-4EA9-80FE-86B7FDF283D8}"/>
-    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{040E1D54-9628-4051-A703-F2D4FF7E3160}"/>
-    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{9B7AC5B6-8859-44E4-979B-0843BB462446}"/>
-    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{FB221B44-61F2-4893-B13E-835DF32D2B49}"/>
-    <cellStyle name="Normal 110" xfId="279" xr:uid="{2F26D2EC-8C76-4194-9F0C-145966C7AC1D}"/>
-    <cellStyle name="Normal 111" xfId="280" xr:uid="{5F47D1D7-9E84-47C9-8831-F95B09F8313B}"/>
-    <cellStyle name="Normal 112" xfId="281" xr:uid="{F25C7080-7681-4D09-AB2A-36B62C0885EE}"/>
-    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{52E0B4B7-D4CE-46D1-9F54-162B9E544BD0}"/>
-    <cellStyle name="Normal 113" xfId="283" xr:uid="{97986F54-80E0-49C8-BDDC-BED5201F8073}"/>
-    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{20960359-FA8F-468F-9B3C-8ACC3793442E}"/>
-    <cellStyle name="Normal 114" xfId="285" xr:uid="{F631585A-6727-45B4-8093-AB33284E3114}"/>
-    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{E02C6EAE-2E1E-4D14-A9A8-814449AA6B45}"/>
-    <cellStyle name="Normal 115" xfId="287" xr:uid="{CCF7EB0F-F8D2-4508-8D43-D091DDB2378C}"/>
-    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{E93E5B31-D7B0-4AF3-90E6-8923A679E635}"/>
-    <cellStyle name="Normal 116" xfId="289" xr:uid="{F93F575F-DACF-493C-94C2-C4D8BCCE1D25}"/>
-    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{0C95AFDB-D53A-415F-AE14-8E2005D4B01E}"/>
-    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{85CA3D7B-6300-4D54-BFA0-555B8FA144C0}"/>
-    <cellStyle name="Normal 117" xfId="292" xr:uid="{394DCC4A-25C3-4838-AA70-77A3F855E342}"/>
-    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{A4FB58F4-AF86-4CF9-B8BE-0204E07DA895}"/>
-    <cellStyle name="Normal 118" xfId="294" xr:uid="{0127623A-4881-4F1E-952D-D85F9332A956}"/>
-    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{6CADA8FD-2A17-4F7E-BFBC-E7D7F89A16F4}"/>
-    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{A6A7E842-2CE2-46A2-9BF7-46EFD2D5AA13}"/>
-    <cellStyle name="Normal 119" xfId="297" xr:uid="{0DB93230-6257-4E41-A236-142A8AA7B666}"/>
-    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{CFC1580F-85CE-4F23-A547-B4EECA8BFE5A}"/>
-    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{F1902491-CBCE-4C4F-99E0-A931B8E543CE}"/>
-    <cellStyle name="Normal 12" xfId="300" xr:uid="{58AC8F61-AB96-4B38-AC37-0A9D26BB9CDD}"/>
-    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{EB87F916-6D50-41F4-8E55-27BB933F0537}"/>
-    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{198993C1-E914-4D20-9017-3AA41CC0E475}"/>
-    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{A5FEA652-204F-407D-A634-1C0951A99661}"/>
-    <cellStyle name="Normal 120" xfId="304" xr:uid="{37FE5AAB-4FDF-41ED-89D3-7CAC742E249E}"/>
-    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{E379EA7B-9C0C-4A8E-9454-0A5DB53D3443}"/>
-    <cellStyle name="Normal 121" xfId="306" xr:uid="{39F22EC0-06AC-4362-8489-2708C380CE08}"/>
-    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{29FB3A12-995D-44B3-A516-105E5369AD40}"/>
-    <cellStyle name="Normal 122" xfId="308" xr:uid="{A8F16106-56C3-435F-9FFC-62588A72D60F}"/>
-    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{8B661892-7493-484A-BA77-DEB8DF8CAAF4}"/>
-    <cellStyle name="Normal 123" xfId="310" xr:uid="{692DDE0C-FCC7-428C-975F-6F64C9E51B07}"/>
-    <cellStyle name="Normal 124" xfId="311" xr:uid="{9992C9E9-124A-4642-B1B2-A5832E8FD404}"/>
-    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{9C3C93DF-C216-486E-8258-BA8426333C17}"/>
-    <cellStyle name="Normal 125" xfId="313" xr:uid="{B5C78AF4-39A0-4135-A36E-F3E11E87FD59}"/>
-    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{F25D0D47-98CC-4B1F-8524-EAA69FAA8C61}"/>
-    <cellStyle name="Normal 126" xfId="315" xr:uid="{1400D3E7-9D3B-41B2-99C7-28911E301358}"/>
-    <cellStyle name="Normal 127" xfId="316" xr:uid="{6636678D-7232-48F1-887E-F92010EA99A1}"/>
-    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{EC3F3F83-500E-4FE8-AB75-49E9E793C41A}"/>
-    <cellStyle name="Normal 128" xfId="318" xr:uid="{8B7281F7-0A29-411A-85D4-F2B9D1C69A3E}"/>
-    <cellStyle name="Normal 129" xfId="319" xr:uid="{322672C8-357A-4EDC-A003-C69BFD9BC798}"/>
-    <cellStyle name="Normal 13" xfId="320" xr:uid="{AFDCFA01-015E-4DA3-9CC3-AD7005E926BA}"/>
-    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{DB4E4E57-B0C2-40C2-ABC2-592306897BCD}"/>
-    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{9DCDD1ED-5D4C-44D4-985D-E674B983355D}"/>
-    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00D96212-4968-40E8-9AA9-9D1FB5F9A9B5}"/>
-    <cellStyle name="Normal 130" xfId="324" xr:uid="{3CAA6D22-1AC7-46A0-BB9A-71C8344A2B30}"/>
-    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{FA019089-AD11-449D-8853-AE5C1386F974}"/>
-    <cellStyle name="Normal 131" xfId="326" xr:uid="{90019043-C212-41D3-B271-AF7097CD9CB3}"/>
-    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{C761AC25-8663-4246-BC68-ADCA4BD31529}"/>
-    <cellStyle name="Normal 132" xfId="328" xr:uid="{C081A645-82CF-4A65-BA48-61D535D4CD91}"/>
-    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{7E996725-5A85-4681-9696-57D73CBBE768}"/>
-    <cellStyle name="Normal 133" xfId="330" xr:uid="{DBBCE3BC-4D8D-4165-BCB1-DF23369D2790}"/>
-    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{AB539EE1-B70D-4177-A699-CA9F5F6001CD}"/>
-    <cellStyle name="Normal 134" xfId="332" xr:uid="{610A5923-CCFF-43FE-9D5E-9CDB0F36982B}"/>
-    <cellStyle name="Normal 135" xfId="333" xr:uid="{7D1DA2E4-33BD-4DCF-8698-5792C38FE0E6}"/>
-    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{5AD4EE68-31E7-4E1C-9B51-702BE9406175}"/>
-    <cellStyle name="Normal 136" xfId="335" xr:uid="{1186A786-EF10-49F1-94E0-A4808313E432}"/>
-    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{DEBC06EB-F6B1-4E0B-AD6B-B1BE8CD6A0D6}"/>
-    <cellStyle name="Normal 137" xfId="337" xr:uid="{90158BC5-5B3A-45C3-BE32-8FA196299CED}"/>
-    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{8D5E5FF7-B5A5-4994-A1C6-37A4334E0A92}"/>
-    <cellStyle name="Normal 138" xfId="339" xr:uid="{55CD8AC1-7FC7-4012-9BF5-4D1DBBA5E390}"/>
-    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{AFC1D4DB-9BC3-494B-A298-11AC8565A9EB}"/>
-    <cellStyle name="Normal 139" xfId="341" xr:uid="{D16D13E3-506D-404B-8AFC-EC5FFCCFCB1E}"/>
-    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{FD41F7A8-0539-4F7F-9864-157A4BB5C4E4}"/>
-    <cellStyle name="Normal 14" xfId="343" xr:uid="{0858813F-2F85-4960-81E5-251DEDFE28E9}"/>
-    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{E701FEC9-0FE5-4E7D-9957-B4E895D37515}"/>
-    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{34D04FFD-B2FE-47E8-BD31-99B04195B060}"/>
-    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{1DCB8A28-8EE0-436E-9C83-8860D789505E}"/>
-    <cellStyle name="Normal 140" xfId="347" xr:uid="{2126FB6B-CBFA-4223-A5F1-2E08F3573273}"/>
-    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{3810A04C-AE97-4200-8A4E-B72FB46E1A53}"/>
-    <cellStyle name="Normal 141" xfId="349" xr:uid="{B230D6BE-3D64-476F-A0D6-8242BB651993}"/>
-    <cellStyle name="Normal 142" xfId="350" xr:uid="{546345E2-F248-4198-9215-7DFE6B04D625}"/>
-    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{C92B0FCE-0B15-4AAE-8F59-4211BB119920}"/>
-    <cellStyle name="Normal 143" xfId="352" xr:uid="{A76042E8-8771-45D9-903F-6B5AF81AC84B}"/>
-    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{6CFDAC86-8D5E-46AC-A184-FE1A469062BE}"/>
-    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{718A03B5-3F90-43F4-A958-D8730DC9BAAD}"/>
-    <cellStyle name="Normal 144" xfId="355" xr:uid="{CB9FBE4E-4DFE-450E-BC8B-4E8DD048816E}"/>
-    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{562D1075-0355-4BB4-8AFF-EFE338A9DBC6}"/>
-    <cellStyle name="Normal 145" xfId="357" xr:uid="{7129AA69-B166-4A86-9933-0365FAD61389}"/>
-    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{BF097E1B-B77C-487A-9054-0E75D97B63C7}"/>
-    <cellStyle name="Normal 146" xfId="359" xr:uid="{E0FBB80D-4DE7-4DA4-98D2-20F0119E7AE7}"/>
-    <cellStyle name="Normal 147" xfId="360" xr:uid="{F7F11328-7818-4D3B-ACA8-C57D48F418F5}"/>
-    <cellStyle name="Normal 15" xfId="361" xr:uid="{87CC9222-169A-4762-B2FB-F836258FD265}"/>
-    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{93FE13D7-9F93-4074-8475-242718609C99}"/>
-    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{01902B12-575D-456D-841D-B1E5E369C1F2}"/>
-    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{219BC5BC-1F96-4F35-82EF-A1056AA502FD}"/>
-    <cellStyle name="Normal 16" xfId="365" xr:uid="{433457D5-F9AF-4F87-9CA3-9151760DE6BF}"/>
-    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{96282A7A-F4AC-4EC1-A21C-916DAA6ECA59}"/>
-    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{C5344315-DB7C-4221-875E-D1B1A58E25D0}"/>
-    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{0634B5BE-A680-4343-9316-444C974A5F0E}"/>
-    <cellStyle name="Normal 17" xfId="369" xr:uid="{6AE9A62B-DB29-4D46-99E5-D2ACAC1284E3}"/>
-    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{A6323A19-4C26-4316-A3BE-20145CC6CB40}"/>
-    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{D123A59E-A0BA-4800-A848-D10C0028638C}"/>
-    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{1DF6A807-A08D-4A1E-97A9-FECDFCA7D3F3}"/>
-    <cellStyle name="Normal 18" xfId="373" xr:uid="{9AB0AE66-7739-45BB-8972-F90B7D0A7665}"/>
-    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{B5F81ABE-1007-4A3E-A65C-96A53CBA8EE4}"/>
-    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{7E0DDB6A-E13E-472E-9DAE-F114A6229BCD}"/>
-    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{E174DB80-E50E-4F71-BC6B-9C772776EC22}"/>
-    <cellStyle name="Normal 19" xfId="377" xr:uid="{6E980DA7-A2AC-4671-915D-7BFE10A80835}"/>
-    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{C599F739-99BD-4311-AF6B-A7B7966CA83F}"/>
-    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{23DE42BF-5DEE-4B21-B46A-06B6E5F78AA8}"/>
-    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{02C9A42D-5312-48E2-957A-43769A3D38B4}"/>
-    <cellStyle name="Normal 2" xfId="381" xr:uid="{459495BA-6982-4F5C-BCB4-BD256FBB65BB}"/>
-    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{7F1F8F06-264C-4E87-A856-CE5C6634EB2F}"/>
-    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{5059B14C-2CC7-445F-BDD7-EE623AD12D74}"/>
-    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{F83BBCC1-7291-4648-9B9B-01CF249FFA70}"/>
-    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{C2253001-F1DF-4A91-980C-B5B8DA5862BC}"/>
-    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{B9486AB9-3732-4EAF-9EAE-0A650EE81A2D}"/>
-    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{B93360BC-E4C2-4EB8-892E-8DABE4EAD0D9}"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{D74ACA62-DBC6-4464-8B11-AB2E3AC5702C}"/>
-    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{32574485-CB3E-4075-BB9B-44ECF58D1671}"/>
-    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{BC9266DF-F1FB-4E25-AD96-E077B0ED4EA3}"/>
-    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{65BF6333-E99B-4495-86DE-DAEF01CEAC49}"/>
-    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{61B01230-3C8A-4CBC-996D-29FC265BE993}"/>
-    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{9523EB68-FC3F-43E9-956D-591DCDCC7BA7}"/>
-    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{EBB93D1B-5F95-4DD0-94DB-A27B1E3D01E1}"/>
-    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{2E27D646-D769-47DF-957D-E8DE03AD9343}"/>
-    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{A1A23999-076E-466D-913A-C39E74381D75}"/>
-    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{E2539EA6-93BC-4225-A3B3-07714999F5B7}"/>
-    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{2A99AA66-9720-4929-9EC4-3127BC3E41C2}"/>
-    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{044C11D7-B742-4183-BBF8-B5BE03356AD6}"/>
-    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{5E538B18-B049-4708-9965-5BE9A8EB8310}"/>
-    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{6C529256-5092-48BA-8F7B-3E40A75542B6}"/>
-    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{09DA0D5A-2549-41ED-AE54-4BAA994D7653}"/>
-    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{2DB6593D-7EE3-4909-AB7D-F1F09C0CAE7C}"/>
-    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{EA861B67-7ECC-4369-BAD3-EC4FDBC60656}"/>
-    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{58207C0A-EA2A-47FB-B828-291437CEA170}"/>
-    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{BD61C73D-791F-4263-981F-E70A609525F1}"/>
-    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{D0946525-DD76-4FA1-960A-D336BA60FB4A}"/>
-    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{2770EB8B-6915-438C-98CE-AB55DAB6FCDF}"/>
-    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{EAF3B951-71FC-4D19-AAD6-8646B8086A55}"/>
-    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{668C60F7-AEAD-43BC-8D91-BC636E397794}"/>
-    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{C2BF7D84-DC2D-4D3D-845A-55FE1897B827}"/>
-    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{C91175E2-D6FA-4F7E-B684-DE4DBD974263}"/>
-    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{79C5FD1F-C92B-44B8-82EB-659CF5B9A75C}"/>
-    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{6D70CE10-22FC-4813-AFA8-E013B46F6B14}"/>
-    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{B3F450B0-F1ED-4EE3-8E43-694E44E3920D}"/>
-    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{21497C75-66D1-432F-AFD5-62C747BCC0D4}"/>
-    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{423A0D32-BD99-4676-83F8-3E336705EDF3}"/>
-    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{50012E93-1F43-4DF3-A24C-54F11EAD526E}"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{FB8B4FCB-D920-45DB-B82A-8C0BCB1253D2}"/>
-    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{AE360487-041F-46AA-B884-C9D02BA1F110}"/>
-    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{C003D66E-FB20-4661-B4A3-C417F5939706}"/>
-    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{AE7AB400-C95C-48B2-ADD0-9F5783115E86}"/>
-    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{CA1C7703-A97A-40CD-A742-620DF760C965}"/>
-    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{A7031F68-5681-4A5F-9871-88CDDD544C6B}"/>
-    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{ABCCE1B6-A5D8-4C4B-A0A1-C516FD19DD61}"/>
-    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{9237849E-38B0-4270-99E3-D546573F1D7D}"/>
-    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{BCCCB71E-EDD5-42B3-BC11-EB8614D4C85B}"/>
-    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{0F416CFA-E74F-47D0-A333-02C0CA8DD655}"/>
-    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{17BD6D73-5B0C-4AF3-8ECF-633B0463B8DE}"/>
-    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{CDDEBB90-3431-4050-8079-E72C9375610C}"/>
-    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{106B9754-EA0D-4203-B8E5-7C7BA32DEF42}"/>
-    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{CB2AC498-0835-4F7A-93EA-3F74C52EECC9}"/>
-    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{FD2D7FC4-A2D8-408D-8C01-2E9AB2C0370C}"/>
-    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{62224986-BE60-4C42-9EA1-6EB395F164FC}"/>
-    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{BA117E2C-FBAB-4218-A105-8B112F1728D0}"/>
-    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{E3ECB07C-FCCE-4E45-A828-5CFD14E0E3A1}"/>
-    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{485A0937-4412-416E-B3D7-9E404B026064}"/>
-    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{D9404978-0366-4974-948D-7535EAB9E287}"/>
-    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{7D6573DC-AB2C-4A5E-A2F9-5CA147F8FFD6}"/>
-    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{E04188FF-30ED-4A49-906C-8CAEABEA5441}"/>
-    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{7667970D-AD04-40A3-8F04-3DAFAE08B565}"/>
-    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{E6A52649-8440-40A6-ADD2-4C463159DEE4}"/>
-    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{CA883F42-9DC6-4863-AD03-8DE3F8EC623A}"/>
-    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{C26485C8-31DE-494A-8248-A97AEE7CD028}"/>
-    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{15BA2801-5538-431D-AE66-2A4159E0F21F}"/>
-    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{BE264327-139D-4D00-834C-C4FAD193EF33}"/>
-    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{9A61D5E5-3A7E-4376-B08B-738566866469}"/>
-    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{2FF65403-A40E-4A35-9EC3-BC02CC7F4894}"/>
-    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{FBFFD7F6-2DC4-4A1D-A2FB-945AFDF2266D}"/>
-    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{83ECBAE1-A9D8-4E78-A1B3-C076998FC9E9}"/>
-    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{A8C5D06C-697C-4EBB-A6D6-13358A5CBE5B}"/>
-    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{3106C343-9D9E-4F96-8885-229AB7DF7D10}"/>
-    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{18AFF674-7D36-40B4-91B6-E712062B4D6F}"/>
-    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{BA919AC6-9E4C-494E-8829-B53B19FC5769}"/>
-    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{132C7599-867E-4173-999F-7771BA4EC197}"/>
-    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{F4AB1593-3493-439D-A69E-2B5AC1E4597C}"/>
-    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{0AD6CE2C-C27F-4328-95EE-DA6ACC6853C4}"/>
-    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{87B4E720-3475-4AF7-9824-E53CBFCA69FD}"/>
-    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{EFE97F5A-0060-4563-B75D-E98F5C6CA615}"/>
-    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{F18BDAEF-C493-412D-9876-67F17213C2CA}"/>
-    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{484FEE23-2642-481C-848A-2B551C1C3AB0}"/>
-    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{8C4F0C12-BC55-4520-9BEE-FCBF03474712}"/>
-    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{71C83530-075C-47CB-9A06-06FCD1814541}"/>
-    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{382BB28A-5AA6-42DF-AC0F-DEDC4909B01F}"/>
-    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{9A15E26B-F7FE-49B9-8944-ED2181EF80E4}"/>
-    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{4D8718F5-3AE5-4FB5-BADF-7AEF740DDBDE}"/>
-    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{62D139A8-62DD-4FCE-84CA-408AD9B0A82A}"/>
-    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{C51278B5-0079-498F-9B29-9A14D8A42268}"/>
-    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{547112F2-0DEE-4179-A0E9-D806CBCA5240}"/>
-    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{CC40E526-128B-461D-8552-E4DFEBB949D7}"/>
-    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{C3BA539C-008E-40FB-A190-7E76F7FA1F56}"/>
-    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{DDFAD1A7-F40D-4FC8-8138-506242692797}"/>
-    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{4413DF38-D86B-4FDA-B47C-3F75D75F1B35}"/>
-    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{D3B98E95-B160-4C52-A277-3A699D70F7B5}"/>
-    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{656CCD1B-6D83-4B65-86EF-F15E6BBCB455}"/>
-    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{E3E63D19-9F61-4CA8-9E03-24CA6A626F29}"/>
-    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{2DF31EF9-28D6-44D6-8FF1-EF53290F2F60}"/>
-    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{7055F94B-53EE-4794-B8F0-E0B7499A07E9}"/>
-    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{CC2F86B9-CBEA-48BC-8F4C-5514384E12F0}"/>
-    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{AD86E3BF-1617-4C73-ADD7-CA29456B363F}"/>
-    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{1D0CE22F-37B2-4C97-8AA1-479BEEFB0069}"/>
-    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{D38B2065-406E-42CE-ABC8-6B43E8911FCF}"/>
-    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{EBAC9A40-B3EB-448B-978C-5A9B6784E099}"/>
-    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{EF8F73C5-1F9A-4A56-A1C6-E57EDB791267}"/>
-    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{2AB0E11D-0E2D-4C17-B11C-ED3C221412DF}"/>
-    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{9D7BE2A4-7F5C-4282-9550-793B9203B05A}"/>
-    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{61CA0DEC-D1B0-43AD-908B-9A21EA9B59BA}"/>
-    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{5846530A-CEB4-4009-9B74-A7E5950894E8}"/>
-    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{FAC35099-1419-49BF-B920-0365F6F40A93}"/>
-    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{C34EE97B-8AA0-4206-A2EE-076DE4DB72D8}"/>
-    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{4F6136A5-7AF2-45C5-B794-28FC0614BDC2}"/>
-    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{4DE461F1-CFD6-40D6-9FB4-22379162B23A}"/>
-    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{281D8DE3-F066-4365-B129-80EEBC5D0A87}"/>
-    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{75FFFDC6-B1CF-436A-A437-A1EC001D3ACB}"/>
-    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{B39EA674-24BA-4A6C-93FB-D38F16C2AFB3}"/>
-    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{DB639C04-220C-485F-B8F8-F2AB7E4DAF11}"/>
-    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{8F3AE0CA-3824-40AA-B4C8-EB2A5DD49341}"/>
-    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{834D3BDC-1F2A-45A8-9188-4549B278FA67}"/>
-    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{C7A5FA3C-F05B-478D-BFE7-99C340EB9256}"/>
-    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{F426D380-E7F6-4450-9411-C0A5E2C69EBD}"/>
-    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{DE753BFC-2E2A-4288-B5F0-5C005EF6CB95}"/>
-    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{13529469-A397-4051-B6B0-E94110AA034A}"/>
-    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{34EB5D72-5254-43BD-BA18-68AE9299471F}"/>
-    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{A0C7431C-E6BA-434A-85FE-BBD80B6318F2}"/>
-    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{45225194-4A4D-49DC-B2F6-3DC7A27F6720}"/>
-    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{6CB75D43-0978-4641-9A9A-0F404BFB624A}"/>
-    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{1145C56D-7669-4DD3-B030-900FB2FBFA1C}"/>
-    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{29D6CEF5-0950-430F-816C-CE837D13794F}"/>
-    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{680006B8-2755-4CD3-AFB2-1A9F8540B0CE}"/>
-    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{3B3F0856-B160-4C50-A410-27E5AB12852E}"/>
-    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{7DBC7104-D268-450F-9E1A-4714C1E69432}"/>
-    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{D2BB24A8-5DDF-403D-B27A-EA761766D2F1}"/>
-    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{9F034895-5A79-4B63-AAAC-64CEC92C09FE}"/>
-    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{541922D0-3005-44E5-A44F-3DFEFE824AB0}"/>
-    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{D100FB59-0080-4BF6-AA2D-B234A19F75D4}"/>
-    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{9DEB0894-8965-446D-AC98-CF1D19949C7B}"/>
-    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{7C479DCC-25FF-4208-96E5-EC375811158A}"/>
-    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{4F3CDDE3-5A95-4F0E-835E-7CD5AC35973C}"/>
-    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{347268ED-0E8F-4FB6-823D-15DAE6130AE7}"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{B2C0E2B6-F387-4C46-9195-C70021FE11CB}"/>
-    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{68601F51-D380-47BC-A9FA-1DE6BBF3BFA9}"/>
-    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{3B7A85B0-42A3-4999-BC75-BFBDEEF1ABBC}"/>
-    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{CCDE718F-1CDB-40C7-8835-4B9C4155C9E7}"/>
-    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{C7021254-7E03-4CD5-9544-19899DCC3A54}"/>
-    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{650E1F43-8EA9-47AE-9258-9CB925063531}"/>
-    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{1F5DC4B0-1508-4134-A772-B7F014A8F539}"/>
-    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{A8513978-2F8A-4CB8-A553-42789DD2E510}"/>
-    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{7FFD1515-C8C7-4045-A2E6-3505420351C9}"/>
-    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{595A0FEC-F9AB-4398-933B-FF22555F8F56}"/>
-    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{67BF00EB-1AB7-454E-B0B8-2BADFD2DEF75}"/>
-    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{71C3BC9A-5F09-4724-B236-C3AFC6F2C6E6}"/>
-    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{3594554B-CEFC-4C51-AAC6-CFDE152F9362}"/>
-    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{B5485D19-C897-4151-8F35-7CF7FDD9BD25}"/>
-    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{FC753AF5-0FE9-40EC-BAC0-BBFD301A2B33}"/>
-    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{B1069335-3CBC-4532-96A8-C71BA2D81B5E}"/>
-    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{7201245C-8F72-4F6F-ADAB-53708CBA2015}"/>
-    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{0B4018CB-A6ED-4017-85DA-2C20A39B3982}"/>
-    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{51135A3E-B73C-4D3B-87C8-EDD0A60343B5}"/>
-    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{BB7599D1-397F-447C-B460-A93DA4F22B9C}"/>
-    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{93927D0D-BF34-4DC7-85DC-FF86163DD571}"/>
-    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{D741029D-97AC-4326-A040-BF6CDDFD79C2}"/>
-    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{4A358CC2-D4E0-4BCF-9583-DE428AE8A76F}"/>
-    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{9AE3721D-DC8B-4F60-A61C-640226EFE086}"/>
-    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{64838451-5857-4A95-A0BC-0B94E8127FA4}"/>
-    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{3A717A90-C2D4-4051-B5D4-186E263E7EB6}"/>
-    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{D8FD8A7F-5FCE-4DEE-AEC3-0E952BA80F5A}"/>
-    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{219A49BF-3BA9-4C69-96E2-5EAA70FE986B}"/>
-    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{5E57888C-773B-4DDE-BCB4-10444E777200}"/>
-    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{46BDD246-1B57-4421-8781-C2EA32AF7877}"/>
-    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{551936C4-6DC2-4F90-9C19-A7D02BDF73DE}"/>
-    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{1FB0203C-EE2E-43F9-B83B-362EB81FB32B}"/>
-    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{3458BAD9-0514-4012-B6FB-80D5D26AF0A6}"/>
-    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{32CEFF4E-9200-4116-9BA3-B23C55EE1E8A}"/>
-    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{66D4A804-2F9C-444D-A25C-1E20B2B797B7}"/>
-    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{1383939C-E452-472C-9635-9681AC03228D}"/>
-    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{1706A99A-95DD-4870-B7B8-9F4F427440A7}"/>
-    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{4D097D50-C597-4667-B199-5D95787A3E7C}"/>
-    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{0933EEC6-CFAE-4A9A-95AC-623D502EABAC}"/>
-    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{8741F196-8FC6-44D7-A20A-DAE57160A108}"/>
-    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{EFB90566-8629-4F74-BEBE-D2E196788BD9}"/>
-    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{675CD6BA-AA6A-47D8-8F95-6355A7704B2D}"/>
-    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{83734F73-E219-46AC-9D78-AFE3B1B78E0D}"/>
-    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{A56A818D-22B1-4E7C-B375-19826563C134}"/>
-    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{7C6CBCCA-6E3B-445E-9BDE-512AC9A4A894}"/>
-    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{B38B8D26-D8D8-4976-85A1-9A841919FCC7}"/>
-    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{87F1FBA9-4F9F-4C56-A28A-E4E091CDF8D6}"/>
-    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{2149EE71-3C76-4F32-9503-C496E6A14307}"/>
-    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{C95CA3E0-1CD5-4DAA-A451-E7AC7F3E8213}"/>
-    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00F08B53-42C5-4956-9565-A7DEC0574687}"/>
-    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{C55F1E53-A6FF-4123-94F4-FBEFF1B40343}"/>
-    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{E3938777-4141-4D36-BF7E-B3F9963053AF}"/>
-    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{BE821E30-6E4B-41CF-9F16-77F93BF09AEB}"/>
-    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{F891C673-CB7E-4630-825B-70D9A6A9F3DF}"/>
-    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{484F6EEA-5818-4470-82D4-C8E53EE6F0FB}"/>
-    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{CCB6D8F0-3D07-4BD4-A30D-30D2012FEE71}"/>
-    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{7C01C525-835C-4CE4-8AC4-4A5D4916665A}"/>
-    <cellStyle name="Normal 20" xfId="577" xr:uid="{CB6C40B2-188A-40A1-BBBC-776FBB13D68C}"/>
-    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{66975FD2-E358-48A5-8D0F-DDEF580B1CB3}"/>
-    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{FC0FFF92-D6A9-4108-855A-7949F234313B}"/>
-    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{D09A6B3C-180D-4A6E-9BD0-E4F7FC036764}"/>
-    <cellStyle name="Normal 21" xfId="581" xr:uid="{615324CC-C499-4C09-806A-27823D06F668}"/>
-    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{521CB14C-83D4-4692-AECF-21DC73F523D9}"/>
-    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{36207B69-EB61-4560-8FB0-F31F5E90384F}"/>
-    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{CE5A0DFB-F8D1-467E-A00C-A88D8107E0BF}"/>
-    <cellStyle name="Normal 22" xfId="585" xr:uid="{ECF93FF4-FBC4-4D2B-BCF1-49C6B813330F}"/>
-    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{52DFD668-B264-4C5B-AF57-00B504F5CB25}"/>
-    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{E8A9C3CD-A59C-4825-94E1-9BC6FB90D9D1}"/>
-    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{21BA8A34-360F-4A27-9E51-062B2EB1A265}"/>
-    <cellStyle name="Normal 23" xfId="589" xr:uid="{A2319FC8-2E18-464F-B861-C57151D0568D}"/>
-    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{A7981741-F99A-4734-9F3A-7E8D06A10B88}"/>
-    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{2201A317-D72F-4403-8BDC-25EEC7790DFB}"/>
-    <cellStyle name="Normal 24" xfId="592" xr:uid="{20179CDC-9D9C-4C37-8842-BBD443E86343}"/>
-    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{9E18510A-2F52-4BFE-ADA4-83F7CD4F8A01}"/>
-    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{8ED1BDB7-9585-48EA-96FA-18CDF1F1D90E}"/>
-    <cellStyle name="Normal 25" xfId="595" xr:uid="{CCF8ABCC-84D5-4E5F-AAC9-641540BAFDBF}"/>
-    <cellStyle name="Normal 26" xfId="596" xr:uid="{78EE13BD-00E9-4AAD-AC83-E5B069E35F21}"/>
-    <cellStyle name="Normal 27" xfId="597" xr:uid="{4786ADC3-F77D-4688-8E0E-85C4C197DEED}"/>
-    <cellStyle name="Normal 28" xfId="598" xr:uid="{F359F718-A266-4D1D-906E-94D5A9205FB4}"/>
-    <cellStyle name="Normal 29" xfId="599" xr:uid="{65DD99D4-993C-4CA8-BEB6-CD1B5C1EF8E7}"/>
-    <cellStyle name="Normal 3" xfId="600" xr:uid="{DC1D8B4C-CA7E-4CFF-93EF-2A6F5E39390B}"/>
-    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{9075BCCE-6EDB-496D-B51F-E1802708E56C}"/>
-    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{61DB3744-D2FA-43ED-AE0E-92E80D189311}"/>
-    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{1D70D478-C172-4E63-9C99-CB0CE3D1256E}"/>
-    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{FA205D85-4851-49A1-8DEA-2C30238CE1FA}"/>
-    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{02DB2995-744E-4B1C-B3D7-634E7903DBF3}"/>
-    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{9EA73752-25DF-42E9-9D0D-2FB61E76EC5E}"/>
-    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{E66F1E58-E942-4F98-9E9C-2E904F6D4E7A}"/>
-    <cellStyle name="Normal 30" xfId="608" xr:uid="{67135321-20A5-463E-837E-09E66DFDF722}"/>
-    <cellStyle name="Normal 31" xfId="609" xr:uid="{3FDDC6C5-909A-49A5-90E9-5BDF1475FCC5}"/>
-    <cellStyle name="Normal 32" xfId="610" xr:uid="{E486F490-35A1-46EF-B902-8BD8F285F090}"/>
-    <cellStyle name="Normal 33" xfId="611" xr:uid="{2BE1C039-1893-4CC0-8910-B9E9805C86A4}"/>
-    <cellStyle name="Normal 34" xfId="612" xr:uid="{67A17848-1292-487C-BC45-83E4D8C8F2CB}"/>
-    <cellStyle name="Normal 35" xfId="613" xr:uid="{F92040A7-875D-4070-AFDF-CE845C646253}"/>
-    <cellStyle name="Normal 36" xfId="614" xr:uid="{2F5BCA1F-4F75-4756-8FDF-00E0A9591C68}"/>
-    <cellStyle name="Normal 37" xfId="615" xr:uid="{83F80D49-FF7C-4C5A-B30C-5038ED131343}"/>
-    <cellStyle name="Normal 38" xfId="616" xr:uid="{EEBAC40B-98C5-4304-8FD1-29C3366CBA0C}"/>
-    <cellStyle name="Normal 39" xfId="617" xr:uid="{183B55D6-640B-4813-A571-BEDBCB78F031}"/>
-    <cellStyle name="Normal 4" xfId="618" xr:uid="{E9E24CCB-FBF0-4259-ACF5-A7A1C2E0E27F}"/>
-    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{252EF4F6-6E74-478F-896B-283BEBEBCA5B}"/>
-    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{BE7C1520-7DCE-4A35-92A9-6CBC8865D761}"/>
-    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{09C3B765-0878-4F87-B7AD-6BBC3267A0E9}"/>
-    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{9CBE0980-E798-46A5-8697-CAEAFA174844}"/>
-    <cellStyle name="Normal 40" xfId="623" xr:uid="{A3B08754-61EE-409E-951D-183DAEC4A704}"/>
-    <cellStyle name="Normal 41" xfId="624" xr:uid="{4CEBD015-CB24-4B47-95BD-3FD06EB41948}"/>
-    <cellStyle name="Normal 42" xfId="625" xr:uid="{A283B2EC-F7FE-4D2A-A469-CF3A4C0A8285}"/>
-    <cellStyle name="Normal 43" xfId="626" xr:uid="{8C4C7313-305A-4F41-B4BE-B4C4D9578241}"/>
-    <cellStyle name="Normal 44" xfId="627" xr:uid="{0FD6C1D3-6073-4ED4-9B8C-0AD415B29FE4}"/>
-    <cellStyle name="Normal 45" xfId="628" xr:uid="{AEB9347F-883C-4A54-A468-2752E42E2E63}"/>
-    <cellStyle name="Normal 46" xfId="629" xr:uid="{04333C79-C0ED-48C8-B00F-768A6A091C3C}"/>
-    <cellStyle name="Normal 47" xfId="630" xr:uid="{68F1CB37-0895-4BD8-A312-6B790FF6D47A}"/>
-    <cellStyle name="Normal 48" xfId="631" xr:uid="{48455078-FE6D-4D19-85E4-56F371F365A7}"/>
-    <cellStyle name="Normal 49" xfId="632" xr:uid="{28D8B773-3B6B-4E3D-8895-1D5D39C3ABBB}"/>
-    <cellStyle name="Normal 5" xfId="633" xr:uid="{219102FC-1555-4FC3-AE20-F6349C228C25}"/>
-    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{B8A7D67A-0A07-4D1B-966A-8FECAA5BB54E}"/>
-    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{FCEE43D6-B410-4563-8452-A553D3B33E04}"/>
-    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{B61BC7C9-A0DC-4B2F-8099-23147655F75E}"/>
-    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{0DDA601F-0AE4-4C0D-99C7-A977BAFA2DA9}"/>
-    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{3193FC1A-113A-4C91-A02E-253E6E6D7620}"/>
-    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{81568482-8033-485D-A774-D7A577FCE9BA}"/>
-    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{A581DC1D-9346-4977-B0BC-B9914B2134F5}"/>
-    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{8D0673B7-2EFD-4681-8702-3F4014549F97}"/>
-    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{7D352EFF-9443-43E7-B2E1-CEC82406FD62}"/>
-    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{1A644E23-F424-446A-95EF-EC7AB6491C78}"/>
-    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{5648AED7-585A-42BF-A832-46013052F1BB}"/>
-    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{E4DB6445-C64C-45ED-AEF4-C3C45C558E8A}"/>
-    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{D12CEFA3-C21E-4F0F-A756-3B5785C3DCCE}"/>
-    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{7508E18E-74C6-4991-9D6F-27DD16F1FF9B}"/>
-    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{602BBFD0-8DBB-48E0-8478-6D50C2CD8713}"/>
-    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{52BCEC1B-B515-401A-8F85-DC048A7B4A4A}"/>
-    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{6027E096-81EB-4F25-B81E-894D836B196F}"/>
-    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{3552F934-9880-4D65-9915-366C4AEED3E8}"/>
-    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{7C970F93-2186-40A8-83F3-5D6CD4D52DB5}"/>
-    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{303F8099-A611-4301-A46E-64C9C19906D4}"/>
-    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{A7F4C5F6-B2D8-4A84-8D30-1ACB31E34088}"/>
-    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{C5D53BF3-23DB-4760-A911-36E8971D0FD1}"/>
-    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{33BE5FE3-EA5D-4327-B433-4CD22C9AC031}"/>
-    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{082D991B-8B21-4B7A-BA73-E8BD39D4328C}"/>
-    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{EF0AF637-AC93-46A1-A0EB-1E02ED4DBA28}"/>
-    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{81E49D2D-9A6C-4616-94BE-E0D8B0BC8824}"/>
-    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{9966C65F-BE34-42E2-87C9-1DCDF31658FC}"/>
-    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{8CC11D6C-BE50-421B-9524-5BA7C47445AC}"/>
-    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{21CD012C-B6AA-4D9A-BF46-FA3C4D8BE2AE}"/>
-    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{D125C1F4-66A5-4C8B-97B1-0110C5FA85CA}"/>
-    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{129CCE14-7D6E-4BE9-A1B8-2319041BD8C7}"/>
-    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{6FE70AD2-D949-4F6A-B224-70CFB287CF90}"/>
-    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{2F62ED83-17F1-43A7-B0FD-969C48061CDA}"/>
-    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{6E5339F9-411C-41D7-9C97-F121A6F50157}"/>
-    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{D5167A38-BD5B-4F28-BD66-69E20BAF0828}"/>
-    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{DF29436F-5BE4-4E0E-868E-064535ECEDF7}"/>
-    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{5DA40E90-3145-466F-8652-63A22C551398}"/>
-    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{36482820-BA97-466D-80CE-C2298ED84E30}"/>
-    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{B7CA44EE-7C1C-45CB-971B-9F1EFBF59A88}"/>
-    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{43F1078E-9847-4951-A918-786358DCAAFF}"/>
-    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{C8752D87-0561-4CBB-BCB7-67C6CA1F487C}"/>
-    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{9751616F-8F72-4ED7-B26E-B6D36A7F7303}"/>
-    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{9F9C3152-05B9-4AFD-8A8D-52512D3710EC}"/>
-    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{8BC21AF8-93D0-435D-89C2-2B4C88EFD6EC}"/>
-    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{B6AE6F9A-9779-4408-B395-02CA27B89D2D}"/>
-    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{FBB3218C-DD06-425A-BA7A-AC1D8E1F3226}"/>
-    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{B4619193-68B1-4BFC-9DC6-899A7BCC79EC}"/>
-    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{3D40A40F-51D0-4D71-A8DC-0CB7ECA3ED35}"/>
-    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{12F234C9-5CD0-4E52-99F2-71E06DD4FB24}"/>
-    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{14E59730-92F3-4A93-947A-9DA909DC5566}"/>
-    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{C39F8384-03D5-4FC4-A21C-4EF4456ED462}"/>
-    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{B0AD780E-E693-4590-AD1A-5C4D0453E1C2}"/>
-    <cellStyle name="Normal 50" xfId="686" xr:uid="{780E9F4F-FE56-46A0-A1A4-ED18F73D0138}"/>
-    <cellStyle name="Normal 51" xfId="687" xr:uid="{1E338177-AED8-4B59-AF4D-8ECF93BDACCD}"/>
-    <cellStyle name="Normal 52" xfId="688" xr:uid="{CDEBBED1-0530-42A2-B0BC-F600A925E3C6}"/>
-    <cellStyle name="Normal 53" xfId="689" xr:uid="{75038936-1E40-4D2C-AE3F-386183227F3A}"/>
-    <cellStyle name="Normal 54" xfId="690" xr:uid="{16729C09-5D18-4A99-BEEA-56A6949F5EF2}"/>
-    <cellStyle name="Normal 55" xfId="691" xr:uid="{3EAE9C30-34A5-4C37-AEC4-39146506F24F}"/>
-    <cellStyle name="Normal 56" xfId="2" xr:uid="{9730C38F-3C43-42D6-94B2-B11839A8846B}"/>
-    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{E6DE8DE4-1087-465A-BF31-995FF04C9B04}"/>
-    <cellStyle name="Normal 57" xfId="693" xr:uid="{B93286D0-6471-4EA0-BC30-4FD068C507DE}"/>
-    <cellStyle name="Normal 58" xfId="694" xr:uid="{9EEA731D-E9DA-4509-9C83-2536B9376D92}"/>
-    <cellStyle name="Normal 59" xfId="695" xr:uid="{593FF683-579A-4A86-A6AB-6F958E9D3DE9}"/>
-    <cellStyle name="Normal 6" xfId="696" xr:uid="{63E50E58-5740-4850-B396-8BE12DF1183A}"/>
-    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{CE81DA93-6F5E-4542-97B3-846406C77B73}"/>
-    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{822F3836-F0CA-48F4-A813-2C1E581F59E1}"/>
-    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{CFCB84E0-AD08-4406-801F-24C5C7CD6930}"/>
-    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{E648884C-0CD9-4EBC-8C29-DA9D3D125388}"/>
-    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{317D1CBA-C96E-456F-82AA-0AB7B83FADBB}"/>
-    <cellStyle name="Normal 60" xfId="702" xr:uid="{0A52F6EA-1CDE-4FC5-85D7-D58B90A1C807}"/>
-    <cellStyle name="Normal 61" xfId="703" xr:uid="{44ABA0C7-F4BC-46D8-814C-1D9F7A160BD2}"/>
-    <cellStyle name="Normal 62" xfId="704" xr:uid="{C530BA90-6A44-4657-9D84-ADAE92CF547D}"/>
-    <cellStyle name="Normal 63" xfId="705" xr:uid="{E7D4AE88-4B1D-4FDB-BF2B-0B8DF2EA3F19}"/>
-    <cellStyle name="Normal 64" xfId="706" xr:uid="{2E5923D0-3E1C-4E3D-8911-9100A17D2242}"/>
-    <cellStyle name="Normal 65" xfId="707" xr:uid="{82600F7D-D7E5-42A3-89E3-813811A2E2FC}"/>
-    <cellStyle name="Normal 66" xfId="708" xr:uid="{F5BE7655-84E0-43AB-B880-CEA9C746D4D9}"/>
-    <cellStyle name="Normal 67" xfId="709" xr:uid="{5903F13F-949C-4542-9BFE-FDDF208FFD8D}"/>
-    <cellStyle name="Normal 68" xfId="710" xr:uid="{91459C12-7A02-4897-9E66-0D631A6F9024}"/>
-    <cellStyle name="Normal 69" xfId="711" xr:uid="{CC68BFE2-8BA9-41E9-9307-9339B0F278ED}"/>
-    <cellStyle name="Normal 7" xfId="712" xr:uid="{A6005739-2B1A-4265-B8FD-0FCF7EDB45BA}"/>
-    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{AB328181-927A-43DE-9A52-AEE3809611F0}"/>
-    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{4C41A2F1-30C6-4DAD-8745-C9D575CA49AD}"/>
-    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{EE1F68C6-B252-41F2-B4D8-D9011E62AFE9}"/>
-    <cellStyle name="Normal 70" xfId="716" xr:uid="{78822FA2-58A5-4767-99FE-5FF922A942E1}"/>
-    <cellStyle name="Normal 71" xfId="717" xr:uid="{472098A9-BB60-48DA-8E26-B26FB98ADF1F}"/>
-    <cellStyle name="Normal 72" xfId="718" xr:uid="{B56DABF2-1F6A-477F-9E1E-1DC2BC347221}"/>
-    <cellStyle name="Normal 73" xfId="719" xr:uid="{F490A527-708C-41C0-B5B5-CEFB458E6938}"/>
-    <cellStyle name="Normal 74" xfId="720" xr:uid="{0D80E111-E78B-4BFB-A8F6-969766D06DA0}"/>
-    <cellStyle name="Normal 75" xfId="721" xr:uid="{D7191799-040E-4DAC-99A3-884F459EBF46}"/>
-    <cellStyle name="Normal 76" xfId="722" xr:uid="{31059DF7-F0F4-48B3-AD39-4CF4AFA6F679}"/>
-    <cellStyle name="Normal 77" xfId="723" xr:uid="{05A30249-0BF3-4D04-9323-C29386D4D36A}"/>
-    <cellStyle name="Normal 78" xfId="724" xr:uid="{200E4D1A-381D-4EC2-994B-2BF6785931A0}"/>
-    <cellStyle name="Normal 79" xfId="725" xr:uid="{E65A4015-1159-49BE-B2B6-2405AAB6D118}"/>
-    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{59AA1ED2-223A-4DE4-A75F-FABE9B805DD1}"/>
-    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{453FAD6F-DF0A-4555-98BF-112DB3B34EB3}"/>
-    <cellStyle name="Normal 8" xfId="728" xr:uid="{E6E51E91-2B50-4869-A34C-69B4A89CFEF8}"/>
-    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{8231493B-3085-4F4B-83CE-FD133A398F86}"/>
-    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{3EC89CF8-5E5E-45F2-9F14-C936E2600F47}"/>
-    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{72BA04F9-1B91-480E-9CE4-CA4B430AD154}"/>
-    <cellStyle name="Normal 80" xfId="732" xr:uid="{70EB5AC9-CE7A-439D-A014-D4BB1C0DB0A8}"/>
-    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{6F63C6CF-184C-4E28-B580-75AB800B12A7}"/>
-    <cellStyle name="Normal 81" xfId="734" xr:uid="{41060087-0F78-4970-A740-8681D453A6F7}"/>
-    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{5F47731D-12E9-4653-B5DC-C29DC3E41BD7}"/>
-    <cellStyle name="Normal 82" xfId="736" xr:uid="{EF4D9537-D708-48BC-BF9A-86853C10EA6C}"/>
-    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{7F98E9CF-5FBA-43C6-835B-7486D27A4C39}"/>
-    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{C4DF2079-83AC-4037-8DC9-0B56697600D0}"/>
-    <cellStyle name="Normal 83" xfId="739" xr:uid="{C5C33BB7-BAD5-4BF5-8376-B605AAAFFFD0}"/>
-    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{F5F7FEF7-F60D-4EAC-AFEA-A9AA727156AC}"/>
-    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{A1FF16E8-05DE-430C-A20F-EF59CA1A9D3D}"/>
-    <cellStyle name="Normal 84" xfId="742" xr:uid="{906FA809-1B94-44D2-8DEC-E38554CFFCA8}"/>
-    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{3349AF23-0053-47A8-B2D1-C38ABEFC2EE3}"/>
-    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{A41E461D-0005-41DD-85A9-689CE82CD270}"/>
-    <cellStyle name="Normal 85" xfId="745" xr:uid="{A8EA39BD-0FBD-4F74-A89A-D444203BEBC5}"/>
-    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{2C1F49E4-1085-4D5F-B435-E9137DECADFA}"/>
-    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{0FEF1941-C37A-47EA-958D-6ABB8A4DD3EA}"/>
-    <cellStyle name="Normal 86" xfId="748" xr:uid="{585B389E-5C37-4F67-9C74-834F55B22F96}"/>
-    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{7BE61E26-4FAC-4546-A692-F8B3DAA15F00}"/>
-    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{97A5D3B0-EFB0-435E-86CB-77696BDDAA6E}"/>
-    <cellStyle name="Normal 87" xfId="751" xr:uid="{70BD093B-63F0-44A4-BB18-21BD5A1FEFAC}"/>
-    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{10EC29DB-CCB1-4596-ABE4-15E7393F5C25}"/>
-    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{C8DCAEC7-993D-41AB-A56E-A5B82ED47127}"/>
-    <cellStyle name="Normal 88" xfId="754" xr:uid="{7E884CA3-1534-49DF-8683-1AB89439E0CA}"/>
-    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{2C3AC846-2360-4E15-AE13-45AB2082A79C}"/>
-    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{50CC4E47-041C-4D63-8234-C4CAA9B40797}"/>
-    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{578DBC71-43A5-4B7C-9B5C-45E1615E1084}"/>
-    <cellStyle name="Normal 89" xfId="758" xr:uid="{B3ED2692-1D33-45F8-B970-F5C743F970F4}"/>
-    <cellStyle name="Normal 9" xfId="759" xr:uid="{E941E19B-E186-426F-A320-7B6D01222BA2}"/>
-    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{564570D7-9A8B-4DCB-91E0-485D48DC05EA}"/>
-    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{FFF9F98C-DA01-4286-83B6-52D8C236B7DC}"/>
-    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{EDF18F4E-E155-43FC-99CD-7EAA60BC1F2E}"/>
-    <cellStyle name="Normal 90" xfId="763" xr:uid="{58BCDA86-96CF-4592-AAFE-73061F133895}"/>
-    <cellStyle name="Normal 91" xfId="764" xr:uid="{25648426-E748-41D1-AE1B-2D45A0900B96}"/>
-    <cellStyle name="Normal 92" xfId="765" xr:uid="{23005439-88B0-44B7-A263-2FC92FA71960}"/>
-    <cellStyle name="Normal 93" xfId="766" xr:uid="{D7255857-1F24-49BA-8AC5-8144FEA87735}"/>
-    <cellStyle name="Normal 94" xfId="767" xr:uid="{FBFCC060-41EE-4E78-B1C7-97B7690BC166}"/>
-    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{23310C5D-B255-4F2B-9220-2B38ED151CDF}"/>
-    <cellStyle name="Normal 95" xfId="769" xr:uid="{3B7D2B12-80B6-4370-9950-7F64CD1BEEA5}"/>
-    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{28765132-1573-4880-8ADD-ED3BDDFDAD31}"/>
-    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{92A03F67-D2BB-471D-A2C8-D81D5F3DDA20}"/>
-    <cellStyle name="Normal 96" xfId="772" xr:uid="{1F3AC05B-4540-42C6-A7D0-F786F8CC4503}"/>
-    <cellStyle name="Normal 97" xfId="773" xr:uid="{2FD84B57-C7C2-46E4-BF60-5B4471CE486F}"/>
-    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{3C1A80B5-EEB6-43B3-A4D1-F3A1C912A352}"/>
-    <cellStyle name="Normal 98" xfId="775" xr:uid="{E495EF88-FACB-4CB9-8DF8-0FCA8AED44CC}"/>
-    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{F0F5082A-1AFA-4FDE-B3E0-8A37A54590B9}"/>
-    <cellStyle name="Normal 99" xfId="777" xr:uid="{652B533F-4E61-4A6F-AE54-D709EFF18F55}"/>
-    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{A0BC0354-EF57-4655-B069-03E2EA8D374F}"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{55CE7787-8275-4D8C-9DD8-FBACCA7FE62B}"/>
-    <cellStyle name="Notas 2" xfId="779" xr:uid="{29BEFE6C-C375-4AA0-897B-2FDC1F43FEAB}"/>
-    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{AA3A2B50-6892-419A-B77A-99B4BB44F21D}"/>
-    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{3AF66E0C-23BC-4276-A7DE-F552239D3D5F}"/>
-    <cellStyle name="Notas 3" xfId="782" xr:uid="{0173F74A-C224-4051-819E-3C4A33F56617}"/>
-    <cellStyle name="Notas 4" xfId="783" xr:uid="{DBCB6CAD-7F69-4694-9A0B-9FE76A32E12C}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{0626749F-50D8-480E-8163-9A61FEE8FCAF}"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{27D27D78-B85C-4343-AA40-5B4546337C0E}"/>
-    <cellStyle name="Salida 2" xfId="786" xr:uid="{5F7D66D7-7D0D-44CB-B09D-615B8AA01F34}"/>
-    <cellStyle name="Salida 3" xfId="787" xr:uid="{58C3A535-31B7-4C0A-932B-6CD0E9F72694}"/>
-    <cellStyle name="Salida 4" xfId="788" xr:uid="{64782063-8128-4723-BCA0-1BC503EEA38B}"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{EBA980F8-0FD8-4D77-B976-46BB962B9455}"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{DB8B12A9-ABED-4E5F-8D02-3805DA01473F}"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{BAE0ACF2-A32E-44D8-807D-772D523B2B49}"/>
-    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{2239296C-AC91-4C58-B229-71AB7FE71CA1}"/>
-    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{20527625-32A2-4F08-94C9-4A9C796BDF86}"/>
-    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{04172329-BD3F-4EBC-A8A8-9B6F6D1FEAAD}"/>
-    <cellStyle name="Título 1 2" xfId="795" xr:uid="{C1386367-B31C-4208-A56D-CD2C6453D1E2}"/>
-    <cellStyle name="Título 2 2" xfId="796" xr:uid="{85CDB38A-FD67-4B69-BB46-C178E6A69E0A}"/>
-    <cellStyle name="Título 2 3" xfId="797" xr:uid="{6AC02DEA-11BC-49A7-94FC-BD1BC059E97E}"/>
-    <cellStyle name="Título 2 4" xfId="798" xr:uid="{CD27F34B-0125-44BD-9B88-CE653B3E68E1}"/>
-    <cellStyle name="Título 3 2" xfId="799" xr:uid="{699D463B-632F-429F-9205-EC4A14CE361F}"/>
-    <cellStyle name="Título 3 3" xfId="800" xr:uid="{1BC347C2-446A-4928-A609-850766F6DCCB}"/>
-    <cellStyle name="Título 3 4" xfId="801" xr:uid="{5DED24EE-812C-4112-B9E1-4BAA537CA5DA}"/>
-    <cellStyle name="Título 4" xfId="802" xr:uid="{35B8EAE3-61C4-4C7D-A449-65DD0E622C12}"/>
-    <cellStyle name="Título 5" xfId="803" xr:uid="{4CBE3CDB-6D89-42FB-B42D-80476B340520}"/>
-    <cellStyle name="Título 6" xfId="804" xr:uid="{F33F369F-149F-48BD-BF13-4A934B045587}"/>
-    <cellStyle name="Total 2" xfId="806" xr:uid="{6931E99E-87DA-40B6-AF61-693113B3F2F3}"/>
-    <cellStyle name="Total 3" xfId="807" xr:uid="{1F129012-82C8-4F3C-9CDF-462BA1469809}"/>
-    <cellStyle name="Total 4" xfId="808" xr:uid="{F64ADB95-C974-4C1E-A6E2-A48BDFE4DA32}"/>
-    <cellStyle name="Total 5" xfId="805" xr:uid="{65F18EF9-7BC5-4B38-879D-C8CA14AE986E}"/>
+    <cellStyle name="Normal 10" xfId="252"/>
+    <cellStyle name="Normal 10 2" xfId="253"/>
+    <cellStyle name="Normal 10 3" xfId="254"/>
+    <cellStyle name="Normal 10 4" xfId="255"/>
+    <cellStyle name="Normal 100" xfId="256"/>
+    <cellStyle name="Normal 100 2" xfId="257"/>
+    <cellStyle name="Normal 101" xfId="258"/>
+    <cellStyle name="Normal 101 2" xfId="259"/>
+    <cellStyle name="Normal 102" xfId="260"/>
+    <cellStyle name="Normal 102 2" xfId="261"/>
+    <cellStyle name="Normal 103" xfId="262"/>
+    <cellStyle name="Normal 103 2" xfId="263"/>
+    <cellStyle name="Normal 104" xfId="264"/>
+    <cellStyle name="Normal 104 2" xfId="265"/>
+    <cellStyle name="Normal 104 3" xfId="266"/>
+    <cellStyle name="Normal 105" xfId="267"/>
+    <cellStyle name="Normal 106" xfId="268"/>
+    <cellStyle name="Normal 106 2" xfId="269"/>
+    <cellStyle name="Normal 106 3" xfId="270"/>
+    <cellStyle name="Normal 107" xfId="271"/>
+    <cellStyle name="Normal 107 2" xfId="272"/>
+    <cellStyle name="Normal 108" xfId="273"/>
+    <cellStyle name="Normal 109" xfId="274"/>
+    <cellStyle name="Normal 11" xfId="275"/>
+    <cellStyle name="Normal 11 2" xfId="276"/>
+    <cellStyle name="Normal 11 3" xfId="277"/>
+    <cellStyle name="Normal 11 4" xfId="278"/>
+    <cellStyle name="Normal 110" xfId="279"/>
+    <cellStyle name="Normal 111" xfId="280"/>
+    <cellStyle name="Normal 112" xfId="281"/>
+    <cellStyle name="Normal 112 2" xfId="282"/>
+    <cellStyle name="Normal 113" xfId="283"/>
+    <cellStyle name="Normal 113 2" xfId="284"/>
+    <cellStyle name="Normal 114" xfId="285"/>
+    <cellStyle name="Normal 114 2" xfId="286"/>
+    <cellStyle name="Normal 115" xfId="287"/>
+    <cellStyle name="Normal 115 2" xfId="288"/>
+    <cellStyle name="Normal 116" xfId="289"/>
+    <cellStyle name="Normal 116 2" xfId="290"/>
+    <cellStyle name="Normal 116 3" xfId="291"/>
+    <cellStyle name="Normal 117" xfId="292"/>
+    <cellStyle name="Normal 117 2" xfId="293"/>
+    <cellStyle name="Normal 118" xfId="294"/>
+    <cellStyle name="Normal 118 2" xfId="295"/>
+    <cellStyle name="Normal 118 3" xfId="296"/>
+    <cellStyle name="Normal 119" xfId="297"/>
+    <cellStyle name="Normal 119 2" xfId="298"/>
+    <cellStyle name="Normal 119 3" xfId="299"/>
+    <cellStyle name="Normal 12" xfId="300"/>
+    <cellStyle name="Normal 12 2" xfId="301"/>
+    <cellStyle name="Normal 12 3" xfId="302"/>
+    <cellStyle name="Normal 12 4" xfId="303"/>
+    <cellStyle name="Normal 120" xfId="304"/>
+    <cellStyle name="Normal 120 2" xfId="305"/>
+    <cellStyle name="Normal 121" xfId="306"/>
+    <cellStyle name="Normal 121 2" xfId="307"/>
+    <cellStyle name="Normal 122" xfId="308"/>
+    <cellStyle name="Normal 122 2" xfId="309"/>
+    <cellStyle name="Normal 123" xfId="310"/>
+    <cellStyle name="Normal 124" xfId="311"/>
+    <cellStyle name="Normal 124 2" xfId="312"/>
+    <cellStyle name="Normal 125" xfId="313"/>
+    <cellStyle name="Normal 125 2" xfId="314"/>
+    <cellStyle name="Normal 126" xfId="315"/>
+    <cellStyle name="Normal 127" xfId="316"/>
+    <cellStyle name="Normal 127 2" xfId="317"/>
+    <cellStyle name="Normal 128" xfId="318"/>
+    <cellStyle name="Normal 129" xfId="319"/>
+    <cellStyle name="Normal 13" xfId="320"/>
+    <cellStyle name="Normal 13 2" xfId="321"/>
+    <cellStyle name="Normal 13 3" xfId="322"/>
+    <cellStyle name="Normal 13 4" xfId="323"/>
+    <cellStyle name="Normal 130" xfId="324"/>
+    <cellStyle name="Normal 130 2" xfId="325"/>
+    <cellStyle name="Normal 131" xfId="326"/>
+    <cellStyle name="Normal 131 2" xfId="327"/>
+    <cellStyle name="Normal 132" xfId="328"/>
+    <cellStyle name="Normal 132 2" xfId="329"/>
+    <cellStyle name="Normal 133" xfId="330"/>
+    <cellStyle name="Normal 133 2" xfId="331"/>
+    <cellStyle name="Normal 134" xfId="332"/>
+    <cellStyle name="Normal 135" xfId="333"/>
+    <cellStyle name="Normal 135 2" xfId="334"/>
+    <cellStyle name="Normal 136" xfId="335"/>
+    <cellStyle name="Normal 136 2" xfId="336"/>
+    <cellStyle name="Normal 137" xfId="337"/>
+    <cellStyle name="Normal 137 2" xfId="338"/>
+    <cellStyle name="Normal 138" xfId="339"/>
+    <cellStyle name="Normal 138 2" xfId="340"/>
+    <cellStyle name="Normal 139" xfId="341"/>
+    <cellStyle name="Normal 139 2" xfId="342"/>
+    <cellStyle name="Normal 14" xfId="343"/>
+    <cellStyle name="Normal 14 2" xfId="344"/>
+    <cellStyle name="Normal 14 3" xfId="345"/>
+    <cellStyle name="Normal 14 4" xfId="346"/>
+    <cellStyle name="Normal 140" xfId="347"/>
+    <cellStyle name="Normal 140 2" xfId="348"/>
+    <cellStyle name="Normal 141" xfId="349"/>
+    <cellStyle name="Normal 142" xfId="350"/>
+    <cellStyle name="Normal 142 2" xfId="351"/>
+    <cellStyle name="Normal 143" xfId="352"/>
+    <cellStyle name="Normal 143 2" xfId="353"/>
+    <cellStyle name="Normal 143 3" xfId="354"/>
+    <cellStyle name="Normal 144" xfId="355"/>
+    <cellStyle name="Normal 144 2" xfId="356"/>
+    <cellStyle name="Normal 145" xfId="357"/>
+    <cellStyle name="Normal 145 2" xfId="358"/>
+    <cellStyle name="Normal 146" xfId="359"/>
+    <cellStyle name="Normal 147" xfId="360"/>
+    <cellStyle name="Normal 15" xfId="361"/>
+    <cellStyle name="Normal 15 2" xfId="362"/>
+    <cellStyle name="Normal 15 3" xfId="363"/>
+    <cellStyle name="Normal 15 4" xfId="364"/>
+    <cellStyle name="Normal 16" xfId="365"/>
+    <cellStyle name="Normal 16 2" xfId="366"/>
+    <cellStyle name="Normal 16 3" xfId="367"/>
+    <cellStyle name="Normal 16 4" xfId="368"/>
+    <cellStyle name="Normal 17" xfId="369"/>
+    <cellStyle name="Normal 17 2" xfId="370"/>
+    <cellStyle name="Normal 17 3" xfId="371"/>
+    <cellStyle name="Normal 17 4" xfId="372"/>
+    <cellStyle name="Normal 18" xfId="373"/>
+    <cellStyle name="Normal 18 2" xfId="374"/>
+    <cellStyle name="Normal 18 3" xfId="375"/>
+    <cellStyle name="Normal 18 4" xfId="376"/>
+    <cellStyle name="Normal 19" xfId="377"/>
+    <cellStyle name="Normal 19 2" xfId="378"/>
+    <cellStyle name="Normal 19 3" xfId="379"/>
+    <cellStyle name="Normal 19 4" xfId="380"/>
+    <cellStyle name="Normal 2" xfId="381"/>
+    <cellStyle name="Normal 2 10" xfId="382"/>
+    <cellStyle name="Normal 2 100" xfId="383"/>
+    <cellStyle name="Normal 2 101" xfId="384"/>
+    <cellStyle name="Normal 2 102" xfId="385"/>
+    <cellStyle name="Normal 2 103" xfId="386"/>
+    <cellStyle name="Normal 2 103 2" xfId="387"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
+    <cellStyle name="Normal 2 104" xfId="389"/>
+    <cellStyle name="Normal 2 104 2" xfId="390"/>
+    <cellStyle name="Normal 2 105" xfId="391"/>
+    <cellStyle name="Normal 2 105 2" xfId="392"/>
+    <cellStyle name="Normal 2 106" xfId="393"/>
+    <cellStyle name="Normal 2 106 2" xfId="394"/>
+    <cellStyle name="Normal 2 106 3" xfId="395"/>
+    <cellStyle name="Normal 2 107" xfId="396"/>
+    <cellStyle name="Normal 2 107 2" xfId="397"/>
+    <cellStyle name="Normal 2 108" xfId="398"/>
+    <cellStyle name="Normal 2 108 2" xfId="399"/>
+    <cellStyle name="Normal 2 109" xfId="400"/>
+    <cellStyle name="Normal 2 109 2" xfId="401"/>
+    <cellStyle name="Normal 2 11" xfId="402"/>
+    <cellStyle name="Normal 2 110" xfId="403"/>
+    <cellStyle name="Normal 2 111" xfId="404"/>
+    <cellStyle name="Normal 2 112" xfId="405"/>
+    <cellStyle name="Normal 2 113" xfId="406"/>
+    <cellStyle name="Normal 2 114" xfId="407"/>
+    <cellStyle name="Normal 2 115" xfId="408"/>
+    <cellStyle name="Normal 2 12" xfId="409"/>
+    <cellStyle name="Normal 2 13" xfId="410"/>
+    <cellStyle name="Normal 2 14" xfId="411"/>
+    <cellStyle name="Normal 2 15" xfId="412"/>
+    <cellStyle name="Normal 2 16" xfId="413"/>
+    <cellStyle name="Normal 2 17" xfId="414"/>
+    <cellStyle name="Normal 2 18" xfId="415"/>
+    <cellStyle name="Normal 2 19" xfId="416"/>
+    <cellStyle name="Normal 2 2" xfId="417"/>
+    <cellStyle name="Normal 2 2 2" xfId="418"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
+    <cellStyle name="Normal 2 2 3" xfId="420"/>
+    <cellStyle name="Normal 2 2 4" xfId="421"/>
+    <cellStyle name="Normal 2 20" xfId="422"/>
+    <cellStyle name="Normal 2 21" xfId="423"/>
+    <cellStyle name="Normal 2 22" xfId="424"/>
+    <cellStyle name="Normal 2 23" xfId="425"/>
+    <cellStyle name="Normal 2 24" xfId="426"/>
+    <cellStyle name="Normal 2 25" xfId="427"/>
+    <cellStyle name="Normal 2 26" xfId="428"/>
+    <cellStyle name="Normal 2 27" xfId="429"/>
+    <cellStyle name="Normal 2 28" xfId="430"/>
+    <cellStyle name="Normal 2 29" xfId="431"/>
+    <cellStyle name="Normal 2 3" xfId="432"/>
+    <cellStyle name="Normal 2 3 2" xfId="433"/>
+    <cellStyle name="Normal 2 3 3" xfId="434"/>
+    <cellStyle name="Normal 2 30" xfId="435"/>
+    <cellStyle name="Normal 2 31" xfId="436"/>
+    <cellStyle name="Normal 2 32" xfId="437"/>
+    <cellStyle name="Normal 2 33" xfId="438"/>
+    <cellStyle name="Normal 2 34" xfId="439"/>
+    <cellStyle name="Normal 2 35" xfId="440"/>
+    <cellStyle name="Normal 2 36" xfId="441"/>
+    <cellStyle name="Normal 2 37" xfId="442"/>
+    <cellStyle name="Normal 2 38" xfId="443"/>
+    <cellStyle name="Normal 2 39" xfId="444"/>
+    <cellStyle name="Normal 2 4" xfId="445"/>
+    <cellStyle name="Normal 2 4 2" xfId="446"/>
+    <cellStyle name="Normal 2 4 3" xfId="447"/>
+    <cellStyle name="Normal 2 4 4" xfId="448"/>
+    <cellStyle name="Normal 2 40" xfId="449"/>
+    <cellStyle name="Normal 2 41" xfId="450"/>
+    <cellStyle name="Normal 2 42" xfId="451"/>
+    <cellStyle name="Normal 2 43" xfId="452"/>
+    <cellStyle name="Normal 2 44" xfId="453"/>
+    <cellStyle name="Normal 2 45" xfId="454"/>
+    <cellStyle name="Normal 2 45 10" xfId="455"/>
+    <cellStyle name="Normal 2 45 11" xfId="456"/>
+    <cellStyle name="Normal 2 45 12" xfId="457"/>
+    <cellStyle name="Normal 2 45 13" xfId="458"/>
+    <cellStyle name="Normal 2 45 14" xfId="459"/>
+    <cellStyle name="Normal 2 45 15" xfId="460"/>
+    <cellStyle name="Normal 2 45 16" xfId="461"/>
+    <cellStyle name="Normal 2 45 17" xfId="462"/>
+    <cellStyle name="Normal 2 45 18" xfId="463"/>
+    <cellStyle name="Normal 2 45 19" xfId="464"/>
+    <cellStyle name="Normal 2 45 2" xfId="465"/>
+    <cellStyle name="Normal 2 45 20" xfId="466"/>
+    <cellStyle name="Normal 2 45 21" xfId="467"/>
+    <cellStyle name="Normal 2 45 22" xfId="468"/>
+    <cellStyle name="Normal 2 45 23" xfId="469"/>
+    <cellStyle name="Normal 2 45 24" xfId="470"/>
+    <cellStyle name="Normal 2 45 25" xfId="471"/>
+    <cellStyle name="Normal 2 45 26" xfId="472"/>
+    <cellStyle name="Normal 2 45 27" xfId="473"/>
+    <cellStyle name="Normal 2 45 28" xfId="474"/>
+    <cellStyle name="Normal 2 45 29" xfId="475"/>
+    <cellStyle name="Normal 2 45 3" xfId="476"/>
+    <cellStyle name="Normal 2 45 30" xfId="477"/>
+    <cellStyle name="Normal 2 45 31" xfId="478"/>
+    <cellStyle name="Normal 2 45 32" xfId="479"/>
+    <cellStyle name="Normal 2 45 33" xfId="480"/>
+    <cellStyle name="Normal 2 45 34" xfId="481"/>
+    <cellStyle name="Normal 2 45 35" xfId="482"/>
+    <cellStyle name="Normal 2 45 36" xfId="483"/>
+    <cellStyle name="Normal 2 45 37" xfId="484"/>
+    <cellStyle name="Normal 2 45 38" xfId="485"/>
+    <cellStyle name="Normal 2 45 39" xfId="486"/>
+    <cellStyle name="Normal 2 45 4" xfId="487"/>
+    <cellStyle name="Normal 2 45 40" xfId="488"/>
+    <cellStyle name="Normal 2 45 41" xfId="489"/>
+    <cellStyle name="Normal 2 45 42" xfId="490"/>
+    <cellStyle name="Normal 2 45 43" xfId="491"/>
+    <cellStyle name="Normal 2 45 44" xfId="492"/>
+    <cellStyle name="Normal 2 45 45" xfId="493"/>
+    <cellStyle name="Normal 2 45 46" xfId="494"/>
+    <cellStyle name="Normal 2 45 47" xfId="495"/>
+    <cellStyle name="Normal 2 45 48" xfId="496"/>
+    <cellStyle name="Normal 2 45 49" xfId="497"/>
+    <cellStyle name="Normal 2 45 5" xfId="498"/>
+    <cellStyle name="Normal 2 45 50" xfId="499"/>
+    <cellStyle name="Normal 2 45 51" xfId="500"/>
+    <cellStyle name="Normal 2 45 52" xfId="501"/>
+    <cellStyle name="Normal 2 45 53" xfId="502"/>
+    <cellStyle name="Normal 2 45 54" xfId="503"/>
+    <cellStyle name="Normal 2 45 55" xfId="504"/>
+    <cellStyle name="Normal 2 45 56" xfId="505"/>
+    <cellStyle name="Normal 2 45 57" xfId="506"/>
+    <cellStyle name="Normal 2 45 58" xfId="507"/>
+    <cellStyle name="Normal 2 45 59" xfId="508"/>
+    <cellStyle name="Normal 2 45 6" xfId="509"/>
+    <cellStyle name="Normal 2 45 7" xfId="510"/>
+    <cellStyle name="Normal 2 45 8" xfId="511"/>
+    <cellStyle name="Normal 2 45 9" xfId="512"/>
+    <cellStyle name="Normal 2 46" xfId="513"/>
+    <cellStyle name="Normal 2 47" xfId="514"/>
+    <cellStyle name="Normal 2 48" xfId="515"/>
+    <cellStyle name="Normal 2 49" xfId="516"/>
+    <cellStyle name="Normal 2 5" xfId="517"/>
+    <cellStyle name="Normal 2 5 2" xfId="518"/>
+    <cellStyle name="Normal 2 5 3" xfId="519"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
+    <cellStyle name="Normal 2 5 4" xfId="521"/>
+    <cellStyle name="Normal 2 50" xfId="522"/>
+    <cellStyle name="Normal 2 51" xfId="523"/>
+    <cellStyle name="Normal 2 52" xfId="524"/>
+    <cellStyle name="Normal 2 53" xfId="525"/>
+    <cellStyle name="Normal 2 54" xfId="526"/>
+    <cellStyle name="Normal 2 55" xfId="527"/>
+    <cellStyle name="Normal 2 56" xfId="528"/>
+    <cellStyle name="Normal 2 57" xfId="529"/>
+    <cellStyle name="Normal 2 58" xfId="530"/>
+    <cellStyle name="Normal 2 59" xfId="531"/>
+    <cellStyle name="Normal 2 6" xfId="532"/>
+    <cellStyle name="Normal 2 6 2" xfId="533"/>
+    <cellStyle name="Normal 2 60" xfId="534"/>
+    <cellStyle name="Normal 2 61" xfId="535"/>
+    <cellStyle name="Normal 2 62" xfId="536"/>
+    <cellStyle name="Normal 2 63" xfId="537"/>
+    <cellStyle name="Normal 2 64" xfId="538"/>
+    <cellStyle name="Normal 2 65" xfId="539"/>
+    <cellStyle name="Normal 2 66" xfId="540"/>
+    <cellStyle name="Normal 2 67" xfId="541"/>
+    <cellStyle name="Normal 2 68" xfId="542"/>
+    <cellStyle name="Normal 2 69" xfId="543"/>
+    <cellStyle name="Normal 2 7" xfId="544"/>
+    <cellStyle name="Normal 2 70" xfId="545"/>
+    <cellStyle name="Normal 2 71" xfId="546"/>
+    <cellStyle name="Normal 2 72" xfId="547"/>
+    <cellStyle name="Normal 2 73" xfId="548"/>
+    <cellStyle name="Normal 2 74" xfId="549"/>
+    <cellStyle name="Normal 2 75" xfId="550"/>
+    <cellStyle name="Normal 2 76" xfId="551"/>
+    <cellStyle name="Normal 2 77" xfId="552"/>
+    <cellStyle name="Normal 2 78" xfId="553"/>
+    <cellStyle name="Normal 2 79" xfId="554"/>
+    <cellStyle name="Normal 2 8" xfId="555"/>
+    <cellStyle name="Normal 2 80" xfId="556"/>
+    <cellStyle name="Normal 2 81" xfId="557"/>
+    <cellStyle name="Normal 2 82" xfId="558"/>
+    <cellStyle name="Normal 2 83" xfId="559"/>
+    <cellStyle name="Normal 2 84" xfId="560"/>
+    <cellStyle name="Normal 2 85" xfId="561"/>
+    <cellStyle name="Normal 2 86" xfId="562"/>
+    <cellStyle name="Normal 2 87" xfId="563"/>
+    <cellStyle name="Normal 2 88" xfId="564"/>
+    <cellStyle name="Normal 2 89" xfId="565"/>
+    <cellStyle name="Normal 2 9" xfId="566"/>
+    <cellStyle name="Normal 2 90" xfId="567"/>
+    <cellStyle name="Normal 2 91" xfId="568"/>
+    <cellStyle name="Normal 2 92" xfId="569"/>
+    <cellStyle name="Normal 2 93" xfId="570"/>
+    <cellStyle name="Normal 2 94" xfId="571"/>
+    <cellStyle name="Normal 2 95" xfId="572"/>
+    <cellStyle name="Normal 2 96" xfId="573"/>
+    <cellStyle name="Normal 2 97" xfId="574"/>
+    <cellStyle name="Normal 2 98" xfId="575"/>
+    <cellStyle name="Normal 2 99" xfId="576"/>
+    <cellStyle name="Normal 20" xfId="577"/>
+    <cellStyle name="Normal 20 2" xfId="578"/>
+    <cellStyle name="Normal 20 3" xfId="579"/>
+    <cellStyle name="Normal 20 4" xfId="580"/>
+    <cellStyle name="Normal 21" xfId="581"/>
+    <cellStyle name="Normal 21 2" xfId="582"/>
+    <cellStyle name="Normal 21 3" xfId="583"/>
+    <cellStyle name="Normal 21 4" xfId="584"/>
+    <cellStyle name="Normal 22" xfId="585"/>
+    <cellStyle name="Normal 22 2" xfId="586"/>
+    <cellStyle name="Normal 22 3" xfId="587"/>
+    <cellStyle name="Normal 22 4" xfId="588"/>
+    <cellStyle name="Normal 23" xfId="589"/>
+    <cellStyle name="Normal 23 2" xfId="590"/>
+    <cellStyle name="Normal 23 3" xfId="591"/>
+    <cellStyle name="Normal 24" xfId="592"/>
+    <cellStyle name="Normal 24 2" xfId="593"/>
+    <cellStyle name="Normal 24 3" xfId="594"/>
+    <cellStyle name="Normal 25" xfId="595"/>
+    <cellStyle name="Normal 26" xfId="596"/>
+    <cellStyle name="Normal 27" xfId="597"/>
+    <cellStyle name="Normal 28" xfId="598"/>
+    <cellStyle name="Normal 29" xfId="599"/>
+    <cellStyle name="Normal 3" xfId="600"/>
+    <cellStyle name="Normal 3 2" xfId="601"/>
+    <cellStyle name="Normal 3 2 2" xfId="602"/>
+    <cellStyle name="Normal 3 3" xfId="603"/>
+    <cellStyle name="Normal 3 3 2" xfId="604"/>
+    <cellStyle name="Normal 3 3 3" xfId="605"/>
+    <cellStyle name="Normal 3 4" xfId="606"/>
+    <cellStyle name="Normal 3 5" xfId="607"/>
+    <cellStyle name="Normal 30" xfId="608"/>
+    <cellStyle name="Normal 31" xfId="609"/>
+    <cellStyle name="Normal 32" xfId="610"/>
+    <cellStyle name="Normal 33" xfId="611"/>
+    <cellStyle name="Normal 34" xfId="612"/>
+    <cellStyle name="Normal 35" xfId="613"/>
+    <cellStyle name="Normal 36" xfId="614"/>
+    <cellStyle name="Normal 37" xfId="615"/>
+    <cellStyle name="Normal 38" xfId="616"/>
+    <cellStyle name="Normal 39" xfId="617"/>
+    <cellStyle name="Normal 4" xfId="618"/>
+    <cellStyle name="Normal 4 2" xfId="619"/>
+    <cellStyle name="Normal 4 2 2" xfId="620"/>
+    <cellStyle name="Normal 4 3" xfId="621"/>
+    <cellStyle name="Normal 4 4" xfId="622"/>
+    <cellStyle name="Normal 40" xfId="623"/>
+    <cellStyle name="Normal 41" xfId="624"/>
+    <cellStyle name="Normal 42" xfId="625"/>
+    <cellStyle name="Normal 43" xfId="626"/>
+    <cellStyle name="Normal 44" xfId="627"/>
+    <cellStyle name="Normal 45" xfId="628"/>
+    <cellStyle name="Normal 46" xfId="629"/>
+    <cellStyle name="Normal 47" xfId="630"/>
+    <cellStyle name="Normal 48" xfId="631"/>
+    <cellStyle name="Normal 49" xfId="632"/>
+    <cellStyle name="Normal 5" xfId="633"/>
+    <cellStyle name="Normal 5 10" xfId="634"/>
+    <cellStyle name="Normal 5 11" xfId="635"/>
+    <cellStyle name="Normal 5 12" xfId="636"/>
+    <cellStyle name="Normal 5 13" xfId="637"/>
+    <cellStyle name="Normal 5 14" xfId="638"/>
+    <cellStyle name="Normal 5 15" xfId="639"/>
+    <cellStyle name="Normal 5 16" xfId="640"/>
+    <cellStyle name="Normal 5 17" xfId="641"/>
+    <cellStyle name="Normal 5 18" xfId="642"/>
+    <cellStyle name="Normal 5 19" xfId="643"/>
+    <cellStyle name="Normal 5 2" xfId="644"/>
+    <cellStyle name="Normal 5 20" xfId="645"/>
+    <cellStyle name="Normal 5 21" xfId="646"/>
+    <cellStyle name="Normal 5 22" xfId="647"/>
+    <cellStyle name="Normal 5 23" xfId="648"/>
+    <cellStyle name="Normal 5 24" xfId="649"/>
+    <cellStyle name="Normal 5 25" xfId="650"/>
+    <cellStyle name="Normal 5 26" xfId="651"/>
+    <cellStyle name="Normal 5 27" xfId="652"/>
+    <cellStyle name="Normal 5 28" xfId="653"/>
+    <cellStyle name="Normal 5 28 10" xfId="654"/>
+    <cellStyle name="Normal 5 28 11" xfId="655"/>
+    <cellStyle name="Normal 5 28 12" xfId="656"/>
+    <cellStyle name="Normal 5 28 13" xfId="657"/>
+    <cellStyle name="Normal 5 28 14" xfId="658"/>
+    <cellStyle name="Normal 5 28 15" xfId="659"/>
+    <cellStyle name="Normal 5 28 16" xfId="660"/>
+    <cellStyle name="Normal 5 28 17" xfId="661"/>
+    <cellStyle name="Normal 5 28 18" xfId="662"/>
+    <cellStyle name="Normal 5 28 19" xfId="663"/>
+    <cellStyle name="Normal 5 28 2" xfId="664"/>
+    <cellStyle name="Normal 5 28 20" xfId="665"/>
+    <cellStyle name="Normal 5 28 21" xfId="666"/>
+    <cellStyle name="Normal 5 28 22" xfId="667"/>
+    <cellStyle name="Normal 5 28 23" xfId="668"/>
+    <cellStyle name="Normal 5 28 24" xfId="669"/>
+    <cellStyle name="Normal 5 28 25" xfId="670"/>
+    <cellStyle name="Normal 5 28 3" xfId="671"/>
+    <cellStyle name="Normal 5 28 4" xfId="672"/>
+    <cellStyle name="Normal 5 28 5" xfId="673"/>
+    <cellStyle name="Normal 5 28 6" xfId="674"/>
+    <cellStyle name="Normal 5 28 7" xfId="675"/>
+    <cellStyle name="Normal 5 28 8" xfId="676"/>
+    <cellStyle name="Normal 5 28 9" xfId="677"/>
+    <cellStyle name="Normal 5 29" xfId="678"/>
+    <cellStyle name="Normal 5 3" xfId="679"/>
+    <cellStyle name="Normal 5 4" xfId="680"/>
+    <cellStyle name="Normal 5 5" xfId="681"/>
+    <cellStyle name="Normal 5 6" xfId="682"/>
+    <cellStyle name="Normal 5 7" xfId="683"/>
+    <cellStyle name="Normal 5 8" xfId="684"/>
+    <cellStyle name="Normal 5 9" xfId="685"/>
+    <cellStyle name="Normal 50" xfId="686"/>
+    <cellStyle name="Normal 51" xfId="687"/>
+    <cellStyle name="Normal 52" xfId="688"/>
+    <cellStyle name="Normal 53" xfId="689"/>
+    <cellStyle name="Normal 54" xfId="690"/>
+    <cellStyle name="Normal 55" xfId="691"/>
+    <cellStyle name="Normal 56" xfId="2"/>
+    <cellStyle name="Normal 56 2" xfId="692"/>
+    <cellStyle name="Normal 57" xfId="693"/>
+    <cellStyle name="Normal 58" xfId="694"/>
+    <cellStyle name="Normal 59" xfId="695"/>
+    <cellStyle name="Normal 6" xfId="696"/>
+    <cellStyle name="Normal 6 2" xfId="697"/>
+    <cellStyle name="Normal 6 2 2" xfId="698"/>
+    <cellStyle name="Normal 6 2 3" xfId="699"/>
+    <cellStyle name="Normal 6 3" xfId="700"/>
+    <cellStyle name="Normal 6 4" xfId="701"/>
+    <cellStyle name="Normal 60" xfId="702"/>
+    <cellStyle name="Normal 61" xfId="703"/>
+    <cellStyle name="Normal 62" xfId="704"/>
+    <cellStyle name="Normal 63" xfId="705"/>
+    <cellStyle name="Normal 64" xfId="706"/>
+    <cellStyle name="Normal 65" xfId="707"/>
+    <cellStyle name="Normal 66" xfId="708"/>
+    <cellStyle name="Normal 67" xfId="709"/>
+    <cellStyle name="Normal 68" xfId="710"/>
+    <cellStyle name="Normal 69" xfId="711"/>
+    <cellStyle name="Normal 7" xfId="712"/>
+    <cellStyle name="Normal 7 2" xfId="713"/>
+    <cellStyle name="Normal 7 3" xfId="714"/>
+    <cellStyle name="Normal 7 4" xfId="715"/>
+    <cellStyle name="Normal 70" xfId="716"/>
+    <cellStyle name="Normal 71" xfId="717"/>
+    <cellStyle name="Normal 72" xfId="718"/>
+    <cellStyle name="Normal 73" xfId="719"/>
+    <cellStyle name="Normal 74" xfId="720"/>
+    <cellStyle name="Normal 75" xfId="721"/>
+    <cellStyle name="Normal 76" xfId="722"/>
+    <cellStyle name="Normal 77" xfId="723"/>
+    <cellStyle name="Normal 78" xfId="724"/>
+    <cellStyle name="Normal 79" xfId="725"/>
+    <cellStyle name="Normal 79 2" xfId="726"/>
+    <cellStyle name="Normal 79 3" xfId="727"/>
+    <cellStyle name="Normal 8" xfId="728"/>
+    <cellStyle name="Normal 8 2" xfId="729"/>
+    <cellStyle name="Normal 8 3" xfId="730"/>
+    <cellStyle name="Normal 8 4" xfId="731"/>
+    <cellStyle name="Normal 80" xfId="732"/>
+    <cellStyle name="Normal 80 2" xfId="733"/>
+    <cellStyle name="Normal 81" xfId="734"/>
+    <cellStyle name="Normal 81 2" xfId="735"/>
+    <cellStyle name="Normal 82" xfId="736"/>
+    <cellStyle name="Normal 82 2" xfId="737"/>
+    <cellStyle name="Normal 82 2 2" xfId="738"/>
+    <cellStyle name="Normal 83" xfId="739"/>
+    <cellStyle name="Normal 83 2" xfId="740"/>
+    <cellStyle name="Normal 83 2 2" xfId="741"/>
+    <cellStyle name="Normal 84" xfId="742"/>
+    <cellStyle name="Normal 84 2" xfId="743"/>
+    <cellStyle name="Normal 84 3" xfId="744"/>
+    <cellStyle name="Normal 85" xfId="745"/>
+    <cellStyle name="Normal 85 2" xfId="746"/>
+    <cellStyle name="Normal 85 3" xfId="747"/>
+    <cellStyle name="Normal 86" xfId="748"/>
+    <cellStyle name="Normal 86 2" xfId="749"/>
+    <cellStyle name="Normal 86 3" xfId="750"/>
+    <cellStyle name="Normal 87" xfId="751"/>
+    <cellStyle name="Normal 87 2" xfId="752"/>
+    <cellStyle name="Normal 87 3" xfId="753"/>
+    <cellStyle name="Normal 88" xfId="754"/>
+    <cellStyle name="Normal 88 2" xfId="755"/>
+    <cellStyle name="Normal 88 3" xfId="756"/>
+    <cellStyle name="Normal 88 4" xfId="757"/>
+    <cellStyle name="Normal 89" xfId="758"/>
+    <cellStyle name="Normal 9" xfId="759"/>
+    <cellStyle name="Normal 9 2" xfId="760"/>
+    <cellStyle name="Normal 9 3" xfId="761"/>
+    <cellStyle name="Normal 9 4" xfId="762"/>
+    <cellStyle name="Normal 90" xfId="763"/>
+    <cellStyle name="Normal 91" xfId="764"/>
+    <cellStyle name="Normal 92" xfId="765"/>
+    <cellStyle name="Normal 93" xfId="766"/>
+    <cellStyle name="Normal 94" xfId="767"/>
+    <cellStyle name="Normal 94 2" xfId="768"/>
+    <cellStyle name="Normal 95" xfId="769"/>
+    <cellStyle name="Normal 95 2" xfId="770"/>
+    <cellStyle name="Normal 95 3" xfId="771"/>
+    <cellStyle name="Normal 96" xfId="772"/>
+    <cellStyle name="Normal 97" xfId="773"/>
+    <cellStyle name="Normal 97 2" xfId="774"/>
+    <cellStyle name="Normal 98" xfId="775"/>
+    <cellStyle name="Normal 98 2" xfId="776"/>
+    <cellStyle name="Normal 99" xfId="777"/>
+    <cellStyle name="Normal 99 2" xfId="778"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3"/>
+    <cellStyle name="Notas 2" xfId="779"/>
+    <cellStyle name="Notas 2 2" xfId="780"/>
+    <cellStyle name="Notas 2 3" xfId="781"/>
+    <cellStyle name="Notas 3" xfId="782"/>
+    <cellStyle name="Notas 4" xfId="783"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785"/>
+    <cellStyle name="Salida 2" xfId="786"/>
+    <cellStyle name="Salida 3" xfId="787"/>
+    <cellStyle name="Salida 4" xfId="788"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791"/>
+    <cellStyle name="Texto explicativo 2" xfId="792"/>
+    <cellStyle name="Texto explicativo 3" xfId="793"/>
+    <cellStyle name="Texto explicativo 4" xfId="794"/>
+    <cellStyle name="Título 1 2" xfId="795"/>
+    <cellStyle name="Título 2 2" xfId="796"/>
+    <cellStyle name="Título 2 3" xfId="797"/>
+    <cellStyle name="Título 2 4" xfId="798"/>
+    <cellStyle name="Título 3 2" xfId="799"/>
+    <cellStyle name="Título 3 3" xfId="800"/>
+    <cellStyle name="Título 3 4" xfId="801"/>
+    <cellStyle name="Título 4" xfId="802"/>
+    <cellStyle name="Título 5" xfId="803"/>
+    <cellStyle name="Título 6" xfId="804"/>
+    <cellStyle name="Total 2" xfId="806"/>
+    <cellStyle name="Total 3" xfId="807"/>
+    <cellStyle name="Total 4" xfId="808"/>
+    <cellStyle name="Total 5" xfId="805"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2371,7 +2383,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2423,7 +2435,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2637,25 +2649,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12C2188-7ECA-4686-95A1-CA6D9A4276B5}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2672,7 +2684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>46101</v>
       </c>
@@ -2689,7 +2701,7 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>46104</v>
       </c>
@@ -2706,7 +2718,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>46105</v>
       </c>
@@ -2723,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>46106</v>
       </c>
@@ -2740,7 +2752,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>46107</v>
       </c>
@@ -2757,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>46108</v>
       </c>
@@ -2774,7 +2786,7 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>46111</v>
       </c>
@@ -2791,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>46112</v>
       </c>
@@ -2808,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>46113</v>
       </c>
@@ -2825,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>46118</v>
       </c>
@@ -2842,7 +2854,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>46119</v>
       </c>
@@ -2859,7 +2871,7 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>46120</v>
       </c>
@@ -2876,7 +2888,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>46121</v>
       </c>
@@ -2893,7 +2905,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>46122</v>
       </c>
@@ -2910,7 +2922,7 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>46125</v>
       </c>
@@ -2927,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>46126</v>
       </c>
@@ -2944,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>46127</v>
       </c>
@@ -2961,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>46128</v>
       </c>
@@ -2978,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>46129</v>
       </c>
@@ -2995,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>46132</v>
       </c>
@@ -3012,7 +3024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>46133</v>
       </c>
@@ -3029,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>46134</v>
       </c>
@@ -3046,7 +3058,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>46135</v>
       </c>
@@ -3063,7 +3075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>46136</v>
       </c>
@@ -3080,7 +3092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>46139</v>
       </c>
@@ -3097,8 +3109,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+    <row r="27" spans="1:8">
+      <c r="A27" s="18">
         <v>46140</v>
       </c>
       <c r="B27">
@@ -3114,8 +3126,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+    <row r="28" spans="1:8">
+      <c r="A28" s="18">
         <v>46141</v>
       </c>
       <c r="B28">
@@ -3129,25 +3141,46 @@
       </c>
       <c r="H28" s="17">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="18">
+        <v>46142</v>
+      </c>
+      <c r="B29" s="19">
+        <v>37961.673699999999</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19">
+        <v>15</v>
+      </c>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19">
+        <v>25</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20">
+        <v>18.43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{195F5366-1760-4B97-B100-3707835114CC}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3161,12 +3194,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>46141</v>
-      </c>
-      <c r="B2" s="18">
-        <v>28385.438679769999</v>
+        <v>46142</v>
+      </c>
+      <c r="B2" s="21">
+        <v>87352.396084139997</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -3175,12 +3208,12 @@
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="14">
-        <v>46140</v>
-      </c>
-      <c r="B3" s="18">
-        <v>70324.097718699995</v>
+        <v>46141</v>
+      </c>
+      <c r="B3" s="22">
+        <v>28385.438679769999</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -3189,12 +3222,12 @@
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="14">
-        <v>46139</v>
-      </c>
-      <c r="B4">
-        <v>40338.944788629997</v>
+        <v>46140</v>
+      </c>
+      <c r="B4" s="22">
+        <v>70324.097718699995</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -3203,167 +3236,182 @@
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="14">
+        <v>46139</v>
+      </c>
+      <c r="B5">
+        <v>40338.944788629997</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="16">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="14">
         <v>46136</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>60973.651931649998</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+    <row r="7" spans="1:5">
+      <c r="A7" s="14">
         <v>46135</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>4652.1817311200002</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+    <row r="8" spans="1:5">
+      <c r="A8" s="14">
         <v>46134</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>17251.00486529</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+    <row r="9" spans="1:5">
+      <c r="A9" s="14">
         <v>46133</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>47981.781644150004</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+    <row r="10" spans="1:5">
+      <c r="A10" s="14">
         <v>46132</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>51339.49161813</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+    <row r="11" spans="1:5">
+      <c r="A11" s="14">
         <v>46129</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>17216.492596060001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+    <row r="12" spans="1:5">
+      <c r="A12" s="14">
         <v>46128</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>18.890111640000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+    <row r="13" spans="1:5">
+      <c r="A13" s="14">
         <v>46127</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>15.79809785</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+    <row r="14" spans="1:5">
+      <c r="A14" s="14">
         <v>46126</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>16.215898760000002</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+    <row r="15" spans="1:5">
+      <c r="A15" s="14">
         <v>46125</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>2475.4322626600001</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
+    <row r="16" spans="1:5">
+      <c r="A16" s="14">
         <v>46122</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>7956.2858669899997</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+    <row r="17" spans="1:2">
+      <c r="A17" s="14">
         <v>46121</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>41.536584740000002</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+    <row r="18" spans="1:2">
+      <c r="A18" s="14">
         <v>46120</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>580.56056466999996</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+    <row r="19" spans="1:2">
+      <c r="A19" s="14">
         <v>46119</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+    <row r="20" spans="1:2">
+      <c r="A20" s="14">
         <v>46118</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+    <row r="21" spans="1:2">
+      <c r="A21" s="14">
         <v>46113</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+    <row r="22" spans="1:2">
+      <c r="A22" s="14">
         <v>46112</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+    <row r="23" spans="1:2">
+      <c r="A23" s="14">
         <v>46111</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>22969.58967849</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55366661-589D-49F9-9E8D-716D2F156F39}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3377,7 +3425,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3391,7 +3439,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3405,7 +3453,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3417,6 +3465,20 @@
       </c>
       <c r="D4">
         <v>43.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4">
+        <v>98931.490865999993</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4946.5745432999993</v>
+      </c>
+      <c r="D5" s="19">
+        <v>64.086567600538856</v>
       </c>
     </row>
   </sheetData>
@@ -3425,16 +3487,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99F398E-57B2-42DE-947C-E12FF1DF8023}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3445,7 +3507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="5">
         <v>46024</v>
       </c>
@@ -3454,7 +3516,7 @@
       </c>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="5">
         <v>46031</v>
       </c>
@@ -3465,7 +3527,7 @@
         <v>-7.2050081634151608E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="5">
         <v>46038</v>
       </c>
@@ -3476,7 +3538,7 @@
         <v>8.9822186264706616E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="5">
         <v>46045</v>
       </c>
@@ -3487,7 +3549,7 @@
         <v>5.9816162411350016E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="5">
         <v>46052</v>
       </c>
@@ -3498,7 +3560,7 @@
         <v>0.15197009063882794</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="5">
         <v>46059</v>
       </c>
@@ -3509,7 +3571,7 @@
         <v>-2.5449418495950171E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="5">
         <v>46066</v>
       </c>
@@ -3520,7 +3582,7 @@
         <v>-2.0123569142568742E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="5">
         <v>46073</v>
       </c>
@@ -3531,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="5">
         <v>46080</v>
       </c>
@@ -3542,7 +3604,7 @@
         <v>5.8663015109889693E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="5">
         <v>46087</v>
       </c>
@@ -3553,7 +3615,7 @@
         <v>-7.2971926029340772E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="5">
         <v>46094</v>
       </c>
@@ -3564,7 +3626,7 @@
         <v>0.10290725762048258</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="5">
         <v>46101</v>
       </c>
@@ -3575,7 +3637,7 @@
         <v>0.18425106797854962</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="5">
         <v>46108</v>
       </c>
@@ -3584,6 +3646,18 @@
       </c>
       <c r="C14" s="11">
         <v>-2.1851046806061425E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="5">
+        <v>46129</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1071533894.2527295</v>
+      </c>
+      <c r="C15" s="11">
+        <f>+(B15-B14)/B14</f>
+        <v>-3.6019979820194892E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3592,21 +3666,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE869F6-32AA-4B53-98EF-3F066F5AB259}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.75" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3632,7 +3706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="5">
         <v>46108</v>
       </c>
@@ -3658,7 +3732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="5">
         <v>46115</v>
       </c>
@@ -3684,7 +3758,7 @@
         <v>-1.4067445693212388E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="5">
         <v>46122</v>
       </c>
@@ -3710,7 +3784,7 @@
         <v>9.7569377843467198E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="5">
         <v>46129</v>
       </c>
@@ -3734,6 +3808,32 @@
       </c>
       <c r="H5" s="12">
         <v>3.4749018512476804E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4">
+        <v>55330466.694130011</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1431208791.1130197</v>
+      </c>
+      <c r="D6" s="4">
+        <v>124915732.49143001</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1611454990.2985797</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1367165.0341699999</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1612822155.3327496</v>
+      </c>
+      <c r="H6" s="12">
+        <v>3.0099999999999998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3742,18 +3842,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF85497-5346-4C69-9026-E88A04F8CF22}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3773,7 +3874,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="5">
         <v>46108</v>
       </c>
@@ -3793,7 +3894,7 @@
         <v>-2.681224004753413E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="5">
         <v>46113</v>
       </c>
@@ -3813,7 +3914,7 @@
         <v>4.8691139433717501E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="5">
         <v>46122</v>
       </c>
@@ -3833,7 +3934,7 @@
         <v>-1.1061785896222975E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="5">
         <v>46129</v>
       </c>
@@ -3853,7 +3954,7 @@
         <v>6.2550592390904214E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="5">
         <v>46136</v>
       </c>
@@ -3870,6 +3971,69 @@
         <v>-1.3894983179757237E-2</v>
       </c>
       <c r="F6" s="13">
+        <v>-1.3894983179757237E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5">
+        <v>46139</v>
+      </c>
+      <c r="B7">
+        <v>13457</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>13460</v>
+      </c>
+      <c r="E7">
+        <f>+(D7-D8)/D8</f>
+        <v>1.5619105108277371E-2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>-1.3894983179757237E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5">
+        <v>46140</v>
+      </c>
+      <c r="B8">
+        <v>13250</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>13253</v>
+      </c>
+      <c r="E8">
+        <f>+(D8-D9)/D9</f>
+        <v>5.0049290968377947E-3</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-1.3894983179757237E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5">
+        <v>46141</v>
+      </c>
+      <c r="B9">
+        <v>13184</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>13187</v>
+      </c>
+      <c r="E9">
+        <f>+(D9-D6)/D6</f>
+        <v>-2.2026105013349156E-2</v>
+      </c>
+      <c r="F9" s="13">
         <v>-1.3894983179757237E-2</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1454,7 +1454,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1507,12 +1507,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="810">
@@ -2649,7 +2643,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3198,7 +3192,7 @@
       <c r="A2" s="14">
         <v>46142</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2">
         <v>87352.396084139997</v>
       </c>
       <c r="D2" t="s">
@@ -3212,7 +3206,7 @@
       <c r="A3" s="14">
         <v>46141</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3">
         <v>28385.438679769999</v>
       </c>
       <c r="D3" t="s">
@@ -3226,7 +3220,7 @@
       <c r="A4" s="14">
         <v>46140</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4">
         <v>70324.097718699995</v>
       </c>
       <c r="D4" t="s">

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.cabezas\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9303BEE2-DAC6-45BE-9630-A342337143BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>DÍA</t>
   </si>
@@ -132,14 +138,11 @@
   <si>
     <t>ABRIL</t>
   </si>
-  <si>
-    <t>24/04/2026 (*)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
@@ -148,7 +151,7 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1454,7 +1457,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1498,828 +1501,825 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="810">
-    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
-    <cellStyle name="Buena 2" xfId="74"/>
-    <cellStyle name="Buena 3" xfId="75"/>
-    <cellStyle name="Buena 4" xfId="76"/>
-    <cellStyle name="Cálculo 2" xfId="77"/>
-    <cellStyle name="Cálculo 3" xfId="78"/>
-    <cellStyle name="Cálculo 4" xfId="79"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82"/>
-    <cellStyle name="Celda vinculada 2" xfId="83"/>
-    <cellStyle name="Celda vinculada 3" xfId="84"/>
-    <cellStyle name="Celda vinculada 4" xfId="85"/>
-    <cellStyle name="Comma 2" xfId="121"/>
-    <cellStyle name="Encabezado 4 2" xfId="86"/>
-    <cellStyle name="Encabezado 4 3" xfId="87"/>
-    <cellStyle name="Encabezado 4 4" xfId="88"/>
-    <cellStyle name="Énfasis1 2" xfId="89"/>
-    <cellStyle name="Énfasis1 3" xfId="90"/>
-    <cellStyle name="Énfasis1 4" xfId="91"/>
-    <cellStyle name="Énfasis2 2" xfId="92"/>
-    <cellStyle name="Énfasis2 3" xfId="93"/>
-    <cellStyle name="Énfasis2 4" xfId="94"/>
-    <cellStyle name="Énfasis3 2" xfId="95"/>
-    <cellStyle name="Énfasis3 3" xfId="96"/>
-    <cellStyle name="Énfasis3 4" xfId="97"/>
-    <cellStyle name="Énfasis4 2" xfId="98"/>
-    <cellStyle name="Énfasis4 3" xfId="99"/>
-    <cellStyle name="Énfasis4 4" xfId="100"/>
-    <cellStyle name="Énfasis5 2" xfId="101"/>
-    <cellStyle name="Énfasis5 3" xfId="102"/>
-    <cellStyle name="Énfasis5 4" xfId="103"/>
-    <cellStyle name="Énfasis6 2" xfId="104"/>
-    <cellStyle name="Énfasis6 3" xfId="105"/>
-    <cellStyle name="Énfasis6 4" xfId="106"/>
-    <cellStyle name="Entrada 2" xfId="107"/>
-    <cellStyle name="Entrada 3" xfId="108"/>
-    <cellStyle name="Entrada 4" xfId="109"/>
-    <cellStyle name="Euro" xfId="110"/>
-    <cellStyle name="Euro 2" xfId="111"/>
-    <cellStyle name="Euro 2 2" xfId="112"/>
-    <cellStyle name="Euro 2 3" xfId="113"/>
-    <cellStyle name="Euro 2 4" xfId="114"/>
-    <cellStyle name="Euro 3" xfId="115"/>
-    <cellStyle name="Euro 4" xfId="116"/>
-    <cellStyle name="Euro 5" xfId="117"/>
-    <cellStyle name="Incorrecto 2" xfId="118"/>
-    <cellStyle name="Incorrecto 3" xfId="119"/>
-    <cellStyle name="Incorrecto 4" xfId="120"/>
-    <cellStyle name="Millares 10" xfId="122"/>
-    <cellStyle name="Millares 2" xfId="123"/>
-    <cellStyle name="Millares 2 2" xfId="124"/>
-    <cellStyle name="Millares 2 2 2" xfId="125"/>
-    <cellStyle name="Millares 2 3" xfId="126"/>
-    <cellStyle name="Millares 2 4" xfId="127"/>
-    <cellStyle name="Millares 3" xfId="128"/>
-    <cellStyle name="Millares 3 10" xfId="129"/>
-    <cellStyle name="Millares 3 100" xfId="130"/>
-    <cellStyle name="Millares 3 101" xfId="131"/>
-    <cellStyle name="Millares 3 102" xfId="132"/>
-    <cellStyle name="Millares 3 103" xfId="133"/>
-    <cellStyle name="Millares 3 103 2" xfId="134"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
-    <cellStyle name="Millares 3 104" xfId="136"/>
-    <cellStyle name="Millares 3 11" xfId="137"/>
-    <cellStyle name="Millares 3 12" xfId="138"/>
-    <cellStyle name="Millares 3 13" xfId="139"/>
-    <cellStyle name="Millares 3 14" xfId="140"/>
-    <cellStyle name="Millares 3 15" xfId="141"/>
-    <cellStyle name="Millares 3 16" xfId="142"/>
-    <cellStyle name="Millares 3 17" xfId="143"/>
-    <cellStyle name="Millares 3 18" xfId="144"/>
-    <cellStyle name="Millares 3 19" xfId="145"/>
-    <cellStyle name="Millares 3 2" xfId="146"/>
-    <cellStyle name="Millares 3 2 2" xfId="147"/>
-    <cellStyle name="Millares 3 2 3" xfId="148"/>
-    <cellStyle name="Millares 3 20" xfId="149"/>
-    <cellStyle name="Millares 3 21" xfId="150"/>
-    <cellStyle name="Millares 3 22" xfId="151"/>
-    <cellStyle name="Millares 3 23" xfId="152"/>
-    <cellStyle name="Millares 3 24" xfId="153"/>
-    <cellStyle name="Millares 3 25" xfId="154"/>
-    <cellStyle name="Millares 3 26" xfId="155"/>
-    <cellStyle name="Millares 3 27" xfId="156"/>
-    <cellStyle name="Millares 3 28" xfId="157"/>
-    <cellStyle name="Millares 3 29" xfId="158"/>
-    <cellStyle name="Millares 3 3" xfId="159"/>
-    <cellStyle name="Millares 3 30" xfId="160"/>
-    <cellStyle name="Millares 3 31" xfId="161"/>
-    <cellStyle name="Millares 3 32" xfId="162"/>
-    <cellStyle name="Millares 3 33" xfId="163"/>
-    <cellStyle name="Millares 3 34" xfId="164"/>
-    <cellStyle name="Millares 3 35" xfId="165"/>
-    <cellStyle name="Millares 3 36" xfId="166"/>
-    <cellStyle name="Millares 3 37" xfId="167"/>
-    <cellStyle name="Millares 3 38" xfId="168"/>
-    <cellStyle name="Millares 3 39" xfId="169"/>
-    <cellStyle name="Millares 3 4" xfId="170"/>
-    <cellStyle name="Millares 3 40" xfId="171"/>
-    <cellStyle name="Millares 3 41" xfId="172"/>
-    <cellStyle name="Millares 3 42" xfId="173"/>
-    <cellStyle name="Millares 3 43" xfId="174"/>
-    <cellStyle name="Millares 3 44" xfId="175"/>
-    <cellStyle name="Millares 3 45" xfId="176"/>
-    <cellStyle name="Millares 3 46" xfId="177"/>
-    <cellStyle name="Millares 3 47" xfId="178"/>
-    <cellStyle name="Millares 3 48" xfId="179"/>
-    <cellStyle name="Millares 3 49" xfId="180"/>
-    <cellStyle name="Millares 3 5" xfId="181"/>
-    <cellStyle name="Millares 3 50" xfId="182"/>
-    <cellStyle name="Millares 3 51" xfId="183"/>
-    <cellStyle name="Millares 3 52" xfId="184"/>
-    <cellStyle name="Millares 3 53" xfId="185"/>
-    <cellStyle name="Millares 3 54" xfId="186"/>
-    <cellStyle name="Millares 3 55" xfId="187"/>
-    <cellStyle name="Millares 3 56" xfId="188"/>
-    <cellStyle name="Millares 3 57" xfId="189"/>
-    <cellStyle name="Millares 3 58" xfId="190"/>
-    <cellStyle name="Millares 3 59" xfId="191"/>
-    <cellStyle name="Millares 3 6" xfId="192"/>
-    <cellStyle name="Millares 3 60" xfId="193"/>
-    <cellStyle name="Millares 3 61" xfId="194"/>
-    <cellStyle name="Millares 3 62" xfId="195"/>
-    <cellStyle name="Millares 3 63" xfId="196"/>
-    <cellStyle name="Millares 3 64" xfId="197"/>
-    <cellStyle name="Millares 3 65" xfId="198"/>
-    <cellStyle name="Millares 3 66" xfId="199"/>
-    <cellStyle name="Millares 3 67" xfId="200"/>
-    <cellStyle name="Millares 3 68" xfId="201"/>
-    <cellStyle name="Millares 3 69" xfId="202"/>
-    <cellStyle name="Millares 3 7" xfId="203"/>
-    <cellStyle name="Millares 3 70" xfId="204"/>
-    <cellStyle name="Millares 3 71" xfId="205"/>
-    <cellStyle name="Millares 3 72" xfId="206"/>
-    <cellStyle name="Millares 3 73" xfId="207"/>
-    <cellStyle name="Millares 3 74" xfId="208"/>
-    <cellStyle name="Millares 3 75" xfId="209"/>
-    <cellStyle name="Millares 3 76" xfId="210"/>
-    <cellStyle name="Millares 3 77" xfId="211"/>
-    <cellStyle name="Millares 3 78" xfId="212"/>
-    <cellStyle name="Millares 3 79" xfId="213"/>
-    <cellStyle name="Millares 3 8" xfId="214"/>
-    <cellStyle name="Millares 3 80" xfId="215"/>
-    <cellStyle name="Millares 3 81" xfId="216"/>
-    <cellStyle name="Millares 3 82" xfId="217"/>
-    <cellStyle name="Millares 3 83" xfId="218"/>
-    <cellStyle name="Millares 3 84" xfId="219"/>
-    <cellStyle name="Millares 3 85" xfId="220"/>
-    <cellStyle name="Millares 3 86" xfId="221"/>
-    <cellStyle name="Millares 3 87" xfId="222"/>
-    <cellStyle name="Millares 3 88" xfId="223"/>
-    <cellStyle name="Millares 3 89" xfId="224"/>
-    <cellStyle name="Millares 3 9" xfId="225"/>
-    <cellStyle name="Millares 3 90" xfId="226"/>
-    <cellStyle name="Millares 3 91" xfId="227"/>
-    <cellStyle name="Millares 3 92" xfId="228"/>
-    <cellStyle name="Millares 3 93" xfId="229"/>
-    <cellStyle name="Millares 3 94" xfId="230"/>
-    <cellStyle name="Millares 3 95" xfId="231"/>
-    <cellStyle name="Millares 3 96" xfId="232"/>
-    <cellStyle name="Millares 3 97" xfId="233"/>
-    <cellStyle name="Millares 3 98" xfId="234"/>
-    <cellStyle name="Millares 3 99" xfId="235"/>
-    <cellStyle name="Millares 4" xfId="236"/>
-    <cellStyle name="Millares 4 2" xfId="237"/>
-    <cellStyle name="Millares 5" xfId="238"/>
-    <cellStyle name="Millares 5 2" xfId="239"/>
-    <cellStyle name="Millares 5 3" xfId="240"/>
-    <cellStyle name="Millares 6" xfId="241"/>
-    <cellStyle name="Millares 6 2" xfId="242"/>
-    <cellStyle name="Millares 6 3" xfId="243"/>
-    <cellStyle name="Millares 7" xfId="244"/>
-    <cellStyle name="Millares 8" xfId="245"/>
-    <cellStyle name="Millares 8 2" xfId="246"/>
-    <cellStyle name="Millares 9" xfId="247"/>
-    <cellStyle name="Neutral 2" xfId="249"/>
-    <cellStyle name="Neutral 3" xfId="250"/>
-    <cellStyle name="Neutral 4" xfId="251"/>
-    <cellStyle name="Neutral 5" xfId="248"/>
-    <cellStyle name="NivelFila_3 2" xfId="809"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252"/>
-    <cellStyle name="Normal 10 2" xfId="253"/>
-    <cellStyle name="Normal 10 3" xfId="254"/>
-    <cellStyle name="Normal 10 4" xfId="255"/>
-    <cellStyle name="Normal 100" xfId="256"/>
-    <cellStyle name="Normal 100 2" xfId="257"/>
-    <cellStyle name="Normal 101" xfId="258"/>
-    <cellStyle name="Normal 101 2" xfId="259"/>
-    <cellStyle name="Normal 102" xfId="260"/>
-    <cellStyle name="Normal 102 2" xfId="261"/>
-    <cellStyle name="Normal 103" xfId="262"/>
-    <cellStyle name="Normal 103 2" xfId="263"/>
-    <cellStyle name="Normal 104" xfId="264"/>
-    <cellStyle name="Normal 104 2" xfId="265"/>
-    <cellStyle name="Normal 104 3" xfId="266"/>
-    <cellStyle name="Normal 105" xfId="267"/>
-    <cellStyle name="Normal 106" xfId="268"/>
-    <cellStyle name="Normal 106 2" xfId="269"/>
-    <cellStyle name="Normal 106 3" xfId="270"/>
-    <cellStyle name="Normal 107" xfId="271"/>
-    <cellStyle name="Normal 107 2" xfId="272"/>
-    <cellStyle name="Normal 108" xfId="273"/>
-    <cellStyle name="Normal 109" xfId="274"/>
-    <cellStyle name="Normal 11" xfId="275"/>
-    <cellStyle name="Normal 11 2" xfId="276"/>
-    <cellStyle name="Normal 11 3" xfId="277"/>
-    <cellStyle name="Normal 11 4" xfId="278"/>
-    <cellStyle name="Normal 110" xfId="279"/>
-    <cellStyle name="Normal 111" xfId="280"/>
-    <cellStyle name="Normal 112" xfId="281"/>
-    <cellStyle name="Normal 112 2" xfId="282"/>
-    <cellStyle name="Normal 113" xfId="283"/>
-    <cellStyle name="Normal 113 2" xfId="284"/>
-    <cellStyle name="Normal 114" xfId="285"/>
-    <cellStyle name="Normal 114 2" xfId="286"/>
-    <cellStyle name="Normal 115" xfId="287"/>
-    <cellStyle name="Normal 115 2" xfId="288"/>
-    <cellStyle name="Normal 116" xfId="289"/>
-    <cellStyle name="Normal 116 2" xfId="290"/>
-    <cellStyle name="Normal 116 3" xfId="291"/>
-    <cellStyle name="Normal 117" xfId="292"/>
-    <cellStyle name="Normal 117 2" xfId="293"/>
-    <cellStyle name="Normal 118" xfId="294"/>
-    <cellStyle name="Normal 118 2" xfId="295"/>
-    <cellStyle name="Normal 118 3" xfId="296"/>
-    <cellStyle name="Normal 119" xfId="297"/>
-    <cellStyle name="Normal 119 2" xfId="298"/>
-    <cellStyle name="Normal 119 3" xfId="299"/>
-    <cellStyle name="Normal 12" xfId="300"/>
-    <cellStyle name="Normal 12 2" xfId="301"/>
-    <cellStyle name="Normal 12 3" xfId="302"/>
-    <cellStyle name="Normal 12 4" xfId="303"/>
-    <cellStyle name="Normal 120" xfId="304"/>
-    <cellStyle name="Normal 120 2" xfId="305"/>
-    <cellStyle name="Normal 121" xfId="306"/>
-    <cellStyle name="Normal 121 2" xfId="307"/>
-    <cellStyle name="Normal 122" xfId="308"/>
-    <cellStyle name="Normal 122 2" xfId="309"/>
-    <cellStyle name="Normal 123" xfId="310"/>
-    <cellStyle name="Normal 124" xfId="311"/>
-    <cellStyle name="Normal 124 2" xfId="312"/>
-    <cellStyle name="Normal 125" xfId="313"/>
-    <cellStyle name="Normal 125 2" xfId="314"/>
-    <cellStyle name="Normal 126" xfId="315"/>
-    <cellStyle name="Normal 127" xfId="316"/>
-    <cellStyle name="Normal 127 2" xfId="317"/>
-    <cellStyle name="Normal 128" xfId="318"/>
-    <cellStyle name="Normal 129" xfId="319"/>
-    <cellStyle name="Normal 13" xfId="320"/>
-    <cellStyle name="Normal 13 2" xfId="321"/>
-    <cellStyle name="Normal 13 3" xfId="322"/>
-    <cellStyle name="Normal 13 4" xfId="323"/>
-    <cellStyle name="Normal 130" xfId="324"/>
-    <cellStyle name="Normal 130 2" xfId="325"/>
-    <cellStyle name="Normal 131" xfId="326"/>
-    <cellStyle name="Normal 131 2" xfId="327"/>
-    <cellStyle name="Normal 132" xfId="328"/>
-    <cellStyle name="Normal 132 2" xfId="329"/>
-    <cellStyle name="Normal 133" xfId="330"/>
-    <cellStyle name="Normal 133 2" xfId="331"/>
-    <cellStyle name="Normal 134" xfId="332"/>
-    <cellStyle name="Normal 135" xfId="333"/>
-    <cellStyle name="Normal 135 2" xfId="334"/>
-    <cellStyle name="Normal 136" xfId="335"/>
-    <cellStyle name="Normal 136 2" xfId="336"/>
-    <cellStyle name="Normal 137" xfId="337"/>
-    <cellStyle name="Normal 137 2" xfId="338"/>
-    <cellStyle name="Normal 138" xfId="339"/>
-    <cellStyle name="Normal 138 2" xfId="340"/>
-    <cellStyle name="Normal 139" xfId="341"/>
-    <cellStyle name="Normal 139 2" xfId="342"/>
-    <cellStyle name="Normal 14" xfId="343"/>
-    <cellStyle name="Normal 14 2" xfId="344"/>
-    <cellStyle name="Normal 14 3" xfId="345"/>
-    <cellStyle name="Normal 14 4" xfId="346"/>
-    <cellStyle name="Normal 140" xfId="347"/>
-    <cellStyle name="Normal 140 2" xfId="348"/>
-    <cellStyle name="Normal 141" xfId="349"/>
-    <cellStyle name="Normal 142" xfId="350"/>
-    <cellStyle name="Normal 142 2" xfId="351"/>
-    <cellStyle name="Normal 143" xfId="352"/>
-    <cellStyle name="Normal 143 2" xfId="353"/>
-    <cellStyle name="Normal 143 3" xfId="354"/>
-    <cellStyle name="Normal 144" xfId="355"/>
-    <cellStyle name="Normal 144 2" xfId="356"/>
-    <cellStyle name="Normal 145" xfId="357"/>
-    <cellStyle name="Normal 145 2" xfId="358"/>
-    <cellStyle name="Normal 146" xfId="359"/>
-    <cellStyle name="Normal 147" xfId="360"/>
-    <cellStyle name="Normal 15" xfId="361"/>
-    <cellStyle name="Normal 15 2" xfId="362"/>
-    <cellStyle name="Normal 15 3" xfId="363"/>
-    <cellStyle name="Normal 15 4" xfId="364"/>
-    <cellStyle name="Normal 16" xfId="365"/>
-    <cellStyle name="Normal 16 2" xfId="366"/>
-    <cellStyle name="Normal 16 3" xfId="367"/>
-    <cellStyle name="Normal 16 4" xfId="368"/>
-    <cellStyle name="Normal 17" xfId="369"/>
-    <cellStyle name="Normal 17 2" xfId="370"/>
-    <cellStyle name="Normal 17 3" xfId="371"/>
-    <cellStyle name="Normal 17 4" xfId="372"/>
-    <cellStyle name="Normal 18" xfId="373"/>
-    <cellStyle name="Normal 18 2" xfId="374"/>
-    <cellStyle name="Normal 18 3" xfId="375"/>
-    <cellStyle name="Normal 18 4" xfId="376"/>
-    <cellStyle name="Normal 19" xfId="377"/>
-    <cellStyle name="Normal 19 2" xfId="378"/>
-    <cellStyle name="Normal 19 3" xfId="379"/>
-    <cellStyle name="Normal 19 4" xfId="380"/>
-    <cellStyle name="Normal 2" xfId="381"/>
-    <cellStyle name="Normal 2 10" xfId="382"/>
-    <cellStyle name="Normal 2 100" xfId="383"/>
-    <cellStyle name="Normal 2 101" xfId="384"/>
-    <cellStyle name="Normal 2 102" xfId="385"/>
-    <cellStyle name="Normal 2 103" xfId="386"/>
-    <cellStyle name="Normal 2 103 2" xfId="387"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
-    <cellStyle name="Normal 2 104" xfId="389"/>
-    <cellStyle name="Normal 2 104 2" xfId="390"/>
-    <cellStyle name="Normal 2 105" xfId="391"/>
-    <cellStyle name="Normal 2 105 2" xfId="392"/>
-    <cellStyle name="Normal 2 106" xfId="393"/>
-    <cellStyle name="Normal 2 106 2" xfId="394"/>
-    <cellStyle name="Normal 2 106 3" xfId="395"/>
-    <cellStyle name="Normal 2 107" xfId="396"/>
-    <cellStyle name="Normal 2 107 2" xfId="397"/>
-    <cellStyle name="Normal 2 108" xfId="398"/>
-    <cellStyle name="Normal 2 108 2" xfId="399"/>
-    <cellStyle name="Normal 2 109" xfId="400"/>
-    <cellStyle name="Normal 2 109 2" xfId="401"/>
-    <cellStyle name="Normal 2 11" xfId="402"/>
-    <cellStyle name="Normal 2 110" xfId="403"/>
-    <cellStyle name="Normal 2 111" xfId="404"/>
-    <cellStyle name="Normal 2 112" xfId="405"/>
-    <cellStyle name="Normal 2 113" xfId="406"/>
-    <cellStyle name="Normal 2 114" xfId="407"/>
-    <cellStyle name="Normal 2 115" xfId="408"/>
-    <cellStyle name="Normal 2 12" xfId="409"/>
-    <cellStyle name="Normal 2 13" xfId="410"/>
-    <cellStyle name="Normal 2 14" xfId="411"/>
-    <cellStyle name="Normal 2 15" xfId="412"/>
-    <cellStyle name="Normal 2 16" xfId="413"/>
-    <cellStyle name="Normal 2 17" xfId="414"/>
-    <cellStyle name="Normal 2 18" xfId="415"/>
-    <cellStyle name="Normal 2 19" xfId="416"/>
-    <cellStyle name="Normal 2 2" xfId="417"/>
-    <cellStyle name="Normal 2 2 2" xfId="418"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
-    <cellStyle name="Normal 2 2 3" xfId="420"/>
-    <cellStyle name="Normal 2 2 4" xfId="421"/>
-    <cellStyle name="Normal 2 20" xfId="422"/>
-    <cellStyle name="Normal 2 21" xfId="423"/>
-    <cellStyle name="Normal 2 22" xfId="424"/>
-    <cellStyle name="Normal 2 23" xfId="425"/>
-    <cellStyle name="Normal 2 24" xfId="426"/>
-    <cellStyle name="Normal 2 25" xfId="427"/>
-    <cellStyle name="Normal 2 26" xfId="428"/>
-    <cellStyle name="Normal 2 27" xfId="429"/>
-    <cellStyle name="Normal 2 28" xfId="430"/>
-    <cellStyle name="Normal 2 29" xfId="431"/>
-    <cellStyle name="Normal 2 3" xfId="432"/>
-    <cellStyle name="Normal 2 3 2" xfId="433"/>
-    <cellStyle name="Normal 2 3 3" xfId="434"/>
-    <cellStyle name="Normal 2 30" xfId="435"/>
-    <cellStyle name="Normal 2 31" xfId="436"/>
-    <cellStyle name="Normal 2 32" xfId="437"/>
-    <cellStyle name="Normal 2 33" xfId="438"/>
-    <cellStyle name="Normal 2 34" xfId="439"/>
-    <cellStyle name="Normal 2 35" xfId="440"/>
-    <cellStyle name="Normal 2 36" xfId="441"/>
-    <cellStyle name="Normal 2 37" xfId="442"/>
-    <cellStyle name="Normal 2 38" xfId="443"/>
-    <cellStyle name="Normal 2 39" xfId="444"/>
-    <cellStyle name="Normal 2 4" xfId="445"/>
-    <cellStyle name="Normal 2 4 2" xfId="446"/>
-    <cellStyle name="Normal 2 4 3" xfId="447"/>
-    <cellStyle name="Normal 2 4 4" xfId="448"/>
-    <cellStyle name="Normal 2 40" xfId="449"/>
-    <cellStyle name="Normal 2 41" xfId="450"/>
-    <cellStyle name="Normal 2 42" xfId="451"/>
-    <cellStyle name="Normal 2 43" xfId="452"/>
-    <cellStyle name="Normal 2 44" xfId="453"/>
-    <cellStyle name="Normal 2 45" xfId="454"/>
-    <cellStyle name="Normal 2 45 10" xfId="455"/>
-    <cellStyle name="Normal 2 45 11" xfId="456"/>
-    <cellStyle name="Normal 2 45 12" xfId="457"/>
-    <cellStyle name="Normal 2 45 13" xfId="458"/>
-    <cellStyle name="Normal 2 45 14" xfId="459"/>
-    <cellStyle name="Normal 2 45 15" xfId="460"/>
-    <cellStyle name="Normal 2 45 16" xfId="461"/>
-    <cellStyle name="Normal 2 45 17" xfId="462"/>
-    <cellStyle name="Normal 2 45 18" xfId="463"/>
-    <cellStyle name="Normal 2 45 19" xfId="464"/>
-    <cellStyle name="Normal 2 45 2" xfId="465"/>
-    <cellStyle name="Normal 2 45 20" xfId="466"/>
-    <cellStyle name="Normal 2 45 21" xfId="467"/>
-    <cellStyle name="Normal 2 45 22" xfId="468"/>
-    <cellStyle name="Normal 2 45 23" xfId="469"/>
-    <cellStyle name="Normal 2 45 24" xfId="470"/>
-    <cellStyle name="Normal 2 45 25" xfId="471"/>
-    <cellStyle name="Normal 2 45 26" xfId="472"/>
-    <cellStyle name="Normal 2 45 27" xfId="473"/>
-    <cellStyle name="Normal 2 45 28" xfId="474"/>
-    <cellStyle name="Normal 2 45 29" xfId="475"/>
-    <cellStyle name="Normal 2 45 3" xfId="476"/>
-    <cellStyle name="Normal 2 45 30" xfId="477"/>
-    <cellStyle name="Normal 2 45 31" xfId="478"/>
-    <cellStyle name="Normal 2 45 32" xfId="479"/>
-    <cellStyle name="Normal 2 45 33" xfId="480"/>
-    <cellStyle name="Normal 2 45 34" xfId="481"/>
-    <cellStyle name="Normal 2 45 35" xfId="482"/>
-    <cellStyle name="Normal 2 45 36" xfId="483"/>
-    <cellStyle name="Normal 2 45 37" xfId="484"/>
-    <cellStyle name="Normal 2 45 38" xfId="485"/>
-    <cellStyle name="Normal 2 45 39" xfId="486"/>
-    <cellStyle name="Normal 2 45 4" xfId="487"/>
-    <cellStyle name="Normal 2 45 40" xfId="488"/>
-    <cellStyle name="Normal 2 45 41" xfId="489"/>
-    <cellStyle name="Normal 2 45 42" xfId="490"/>
-    <cellStyle name="Normal 2 45 43" xfId="491"/>
-    <cellStyle name="Normal 2 45 44" xfId="492"/>
-    <cellStyle name="Normal 2 45 45" xfId="493"/>
-    <cellStyle name="Normal 2 45 46" xfId="494"/>
-    <cellStyle name="Normal 2 45 47" xfId="495"/>
-    <cellStyle name="Normal 2 45 48" xfId="496"/>
-    <cellStyle name="Normal 2 45 49" xfId="497"/>
-    <cellStyle name="Normal 2 45 5" xfId="498"/>
-    <cellStyle name="Normal 2 45 50" xfId="499"/>
-    <cellStyle name="Normal 2 45 51" xfId="500"/>
-    <cellStyle name="Normal 2 45 52" xfId="501"/>
-    <cellStyle name="Normal 2 45 53" xfId="502"/>
-    <cellStyle name="Normal 2 45 54" xfId="503"/>
-    <cellStyle name="Normal 2 45 55" xfId="504"/>
-    <cellStyle name="Normal 2 45 56" xfId="505"/>
-    <cellStyle name="Normal 2 45 57" xfId="506"/>
-    <cellStyle name="Normal 2 45 58" xfId="507"/>
-    <cellStyle name="Normal 2 45 59" xfId="508"/>
-    <cellStyle name="Normal 2 45 6" xfId="509"/>
-    <cellStyle name="Normal 2 45 7" xfId="510"/>
-    <cellStyle name="Normal 2 45 8" xfId="511"/>
-    <cellStyle name="Normal 2 45 9" xfId="512"/>
-    <cellStyle name="Normal 2 46" xfId="513"/>
-    <cellStyle name="Normal 2 47" xfId="514"/>
-    <cellStyle name="Normal 2 48" xfId="515"/>
-    <cellStyle name="Normal 2 49" xfId="516"/>
-    <cellStyle name="Normal 2 5" xfId="517"/>
-    <cellStyle name="Normal 2 5 2" xfId="518"/>
-    <cellStyle name="Normal 2 5 3" xfId="519"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
-    <cellStyle name="Normal 2 5 4" xfId="521"/>
-    <cellStyle name="Normal 2 50" xfId="522"/>
-    <cellStyle name="Normal 2 51" xfId="523"/>
-    <cellStyle name="Normal 2 52" xfId="524"/>
-    <cellStyle name="Normal 2 53" xfId="525"/>
-    <cellStyle name="Normal 2 54" xfId="526"/>
-    <cellStyle name="Normal 2 55" xfId="527"/>
-    <cellStyle name="Normal 2 56" xfId="528"/>
-    <cellStyle name="Normal 2 57" xfId="529"/>
-    <cellStyle name="Normal 2 58" xfId="530"/>
-    <cellStyle name="Normal 2 59" xfId="531"/>
-    <cellStyle name="Normal 2 6" xfId="532"/>
-    <cellStyle name="Normal 2 6 2" xfId="533"/>
-    <cellStyle name="Normal 2 60" xfId="534"/>
-    <cellStyle name="Normal 2 61" xfId="535"/>
-    <cellStyle name="Normal 2 62" xfId="536"/>
-    <cellStyle name="Normal 2 63" xfId="537"/>
-    <cellStyle name="Normal 2 64" xfId="538"/>
-    <cellStyle name="Normal 2 65" xfId="539"/>
-    <cellStyle name="Normal 2 66" xfId="540"/>
-    <cellStyle name="Normal 2 67" xfId="541"/>
-    <cellStyle name="Normal 2 68" xfId="542"/>
-    <cellStyle name="Normal 2 69" xfId="543"/>
-    <cellStyle name="Normal 2 7" xfId="544"/>
-    <cellStyle name="Normal 2 70" xfId="545"/>
-    <cellStyle name="Normal 2 71" xfId="546"/>
-    <cellStyle name="Normal 2 72" xfId="547"/>
-    <cellStyle name="Normal 2 73" xfId="548"/>
-    <cellStyle name="Normal 2 74" xfId="549"/>
-    <cellStyle name="Normal 2 75" xfId="550"/>
-    <cellStyle name="Normal 2 76" xfId="551"/>
-    <cellStyle name="Normal 2 77" xfId="552"/>
-    <cellStyle name="Normal 2 78" xfId="553"/>
-    <cellStyle name="Normal 2 79" xfId="554"/>
-    <cellStyle name="Normal 2 8" xfId="555"/>
-    <cellStyle name="Normal 2 80" xfId="556"/>
-    <cellStyle name="Normal 2 81" xfId="557"/>
-    <cellStyle name="Normal 2 82" xfId="558"/>
-    <cellStyle name="Normal 2 83" xfId="559"/>
-    <cellStyle name="Normal 2 84" xfId="560"/>
-    <cellStyle name="Normal 2 85" xfId="561"/>
-    <cellStyle name="Normal 2 86" xfId="562"/>
-    <cellStyle name="Normal 2 87" xfId="563"/>
-    <cellStyle name="Normal 2 88" xfId="564"/>
-    <cellStyle name="Normal 2 89" xfId="565"/>
-    <cellStyle name="Normal 2 9" xfId="566"/>
-    <cellStyle name="Normal 2 90" xfId="567"/>
-    <cellStyle name="Normal 2 91" xfId="568"/>
-    <cellStyle name="Normal 2 92" xfId="569"/>
-    <cellStyle name="Normal 2 93" xfId="570"/>
-    <cellStyle name="Normal 2 94" xfId="571"/>
-    <cellStyle name="Normal 2 95" xfId="572"/>
-    <cellStyle name="Normal 2 96" xfId="573"/>
-    <cellStyle name="Normal 2 97" xfId="574"/>
-    <cellStyle name="Normal 2 98" xfId="575"/>
-    <cellStyle name="Normal 2 99" xfId="576"/>
-    <cellStyle name="Normal 20" xfId="577"/>
-    <cellStyle name="Normal 20 2" xfId="578"/>
-    <cellStyle name="Normal 20 3" xfId="579"/>
-    <cellStyle name="Normal 20 4" xfId="580"/>
-    <cellStyle name="Normal 21" xfId="581"/>
-    <cellStyle name="Normal 21 2" xfId="582"/>
-    <cellStyle name="Normal 21 3" xfId="583"/>
-    <cellStyle name="Normal 21 4" xfId="584"/>
-    <cellStyle name="Normal 22" xfId="585"/>
-    <cellStyle name="Normal 22 2" xfId="586"/>
-    <cellStyle name="Normal 22 3" xfId="587"/>
-    <cellStyle name="Normal 22 4" xfId="588"/>
-    <cellStyle name="Normal 23" xfId="589"/>
-    <cellStyle name="Normal 23 2" xfId="590"/>
-    <cellStyle name="Normal 23 3" xfId="591"/>
-    <cellStyle name="Normal 24" xfId="592"/>
-    <cellStyle name="Normal 24 2" xfId="593"/>
-    <cellStyle name="Normal 24 3" xfId="594"/>
-    <cellStyle name="Normal 25" xfId="595"/>
-    <cellStyle name="Normal 26" xfId="596"/>
-    <cellStyle name="Normal 27" xfId="597"/>
-    <cellStyle name="Normal 28" xfId="598"/>
-    <cellStyle name="Normal 29" xfId="599"/>
-    <cellStyle name="Normal 3" xfId="600"/>
-    <cellStyle name="Normal 3 2" xfId="601"/>
-    <cellStyle name="Normal 3 2 2" xfId="602"/>
-    <cellStyle name="Normal 3 3" xfId="603"/>
-    <cellStyle name="Normal 3 3 2" xfId="604"/>
-    <cellStyle name="Normal 3 3 3" xfId="605"/>
-    <cellStyle name="Normal 3 4" xfId="606"/>
-    <cellStyle name="Normal 3 5" xfId="607"/>
-    <cellStyle name="Normal 30" xfId="608"/>
-    <cellStyle name="Normal 31" xfId="609"/>
-    <cellStyle name="Normal 32" xfId="610"/>
-    <cellStyle name="Normal 33" xfId="611"/>
-    <cellStyle name="Normal 34" xfId="612"/>
-    <cellStyle name="Normal 35" xfId="613"/>
-    <cellStyle name="Normal 36" xfId="614"/>
-    <cellStyle name="Normal 37" xfId="615"/>
-    <cellStyle name="Normal 38" xfId="616"/>
-    <cellStyle name="Normal 39" xfId="617"/>
-    <cellStyle name="Normal 4" xfId="618"/>
-    <cellStyle name="Normal 4 2" xfId="619"/>
-    <cellStyle name="Normal 4 2 2" xfId="620"/>
-    <cellStyle name="Normal 4 3" xfId="621"/>
-    <cellStyle name="Normal 4 4" xfId="622"/>
-    <cellStyle name="Normal 40" xfId="623"/>
-    <cellStyle name="Normal 41" xfId="624"/>
-    <cellStyle name="Normal 42" xfId="625"/>
-    <cellStyle name="Normal 43" xfId="626"/>
-    <cellStyle name="Normal 44" xfId="627"/>
-    <cellStyle name="Normal 45" xfId="628"/>
-    <cellStyle name="Normal 46" xfId="629"/>
-    <cellStyle name="Normal 47" xfId="630"/>
-    <cellStyle name="Normal 48" xfId="631"/>
-    <cellStyle name="Normal 49" xfId="632"/>
-    <cellStyle name="Normal 5" xfId="633"/>
-    <cellStyle name="Normal 5 10" xfId="634"/>
-    <cellStyle name="Normal 5 11" xfId="635"/>
-    <cellStyle name="Normal 5 12" xfId="636"/>
-    <cellStyle name="Normal 5 13" xfId="637"/>
-    <cellStyle name="Normal 5 14" xfId="638"/>
-    <cellStyle name="Normal 5 15" xfId="639"/>
-    <cellStyle name="Normal 5 16" xfId="640"/>
-    <cellStyle name="Normal 5 17" xfId="641"/>
-    <cellStyle name="Normal 5 18" xfId="642"/>
-    <cellStyle name="Normal 5 19" xfId="643"/>
-    <cellStyle name="Normal 5 2" xfId="644"/>
-    <cellStyle name="Normal 5 20" xfId="645"/>
-    <cellStyle name="Normal 5 21" xfId="646"/>
-    <cellStyle name="Normal 5 22" xfId="647"/>
-    <cellStyle name="Normal 5 23" xfId="648"/>
-    <cellStyle name="Normal 5 24" xfId="649"/>
-    <cellStyle name="Normal 5 25" xfId="650"/>
-    <cellStyle name="Normal 5 26" xfId="651"/>
-    <cellStyle name="Normal 5 27" xfId="652"/>
-    <cellStyle name="Normal 5 28" xfId="653"/>
-    <cellStyle name="Normal 5 28 10" xfId="654"/>
-    <cellStyle name="Normal 5 28 11" xfId="655"/>
-    <cellStyle name="Normal 5 28 12" xfId="656"/>
-    <cellStyle name="Normal 5 28 13" xfId="657"/>
-    <cellStyle name="Normal 5 28 14" xfId="658"/>
-    <cellStyle name="Normal 5 28 15" xfId="659"/>
-    <cellStyle name="Normal 5 28 16" xfId="660"/>
-    <cellStyle name="Normal 5 28 17" xfId="661"/>
-    <cellStyle name="Normal 5 28 18" xfId="662"/>
-    <cellStyle name="Normal 5 28 19" xfId="663"/>
-    <cellStyle name="Normal 5 28 2" xfId="664"/>
-    <cellStyle name="Normal 5 28 20" xfId="665"/>
-    <cellStyle name="Normal 5 28 21" xfId="666"/>
-    <cellStyle name="Normal 5 28 22" xfId="667"/>
-    <cellStyle name="Normal 5 28 23" xfId="668"/>
-    <cellStyle name="Normal 5 28 24" xfId="669"/>
-    <cellStyle name="Normal 5 28 25" xfId="670"/>
-    <cellStyle name="Normal 5 28 3" xfId="671"/>
-    <cellStyle name="Normal 5 28 4" xfId="672"/>
-    <cellStyle name="Normal 5 28 5" xfId="673"/>
-    <cellStyle name="Normal 5 28 6" xfId="674"/>
-    <cellStyle name="Normal 5 28 7" xfId="675"/>
-    <cellStyle name="Normal 5 28 8" xfId="676"/>
-    <cellStyle name="Normal 5 28 9" xfId="677"/>
-    <cellStyle name="Normal 5 29" xfId="678"/>
-    <cellStyle name="Normal 5 3" xfId="679"/>
-    <cellStyle name="Normal 5 4" xfId="680"/>
-    <cellStyle name="Normal 5 5" xfId="681"/>
-    <cellStyle name="Normal 5 6" xfId="682"/>
-    <cellStyle name="Normal 5 7" xfId="683"/>
-    <cellStyle name="Normal 5 8" xfId="684"/>
-    <cellStyle name="Normal 5 9" xfId="685"/>
-    <cellStyle name="Normal 50" xfId="686"/>
-    <cellStyle name="Normal 51" xfId="687"/>
-    <cellStyle name="Normal 52" xfId="688"/>
-    <cellStyle name="Normal 53" xfId="689"/>
-    <cellStyle name="Normal 54" xfId="690"/>
-    <cellStyle name="Normal 55" xfId="691"/>
-    <cellStyle name="Normal 56" xfId="2"/>
-    <cellStyle name="Normal 56 2" xfId="692"/>
-    <cellStyle name="Normal 57" xfId="693"/>
-    <cellStyle name="Normal 58" xfId="694"/>
-    <cellStyle name="Normal 59" xfId="695"/>
-    <cellStyle name="Normal 6" xfId="696"/>
-    <cellStyle name="Normal 6 2" xfId="697"/>
-    <cellStyle name="Normal 6 2 2" xfId="698"/>
-    <cellStyle name="Normal 6 2 3" xfId="699"/>
-    <cellStyle name="Normal 6 3" xfId="700"/>
-    <cellStyle name="Normal 6 4" xfId="701"/>
-    <cellStyle name="Normal 60" xfId="702"/>
-    <cellStyle name="Normal 61" xfId="703"/>
-    <cellStyle name="Normal 62" xfId="704"/>
-    <cellStyle name="Normal 63" xfId="705"/>
-    <cellStyle name="Normal 64" xfId="706"/>
-    <cellStyle name="Normal 65" xfId="707"/>
-    <cellStyle name="Normal 66" xfId="708"/>
-    <cellStyle name="Normal 67" xfId="709"/>
-    <cellStyle name="Normal 68" xfId="710"/>
-    <cellStyle name="Normal 69" xfId="711"/>
-    <cellStyle name="Normal 7" xfId="712"/>
-    <cellStyle name="Normal 7 2" xfId="713"/>
-    <cellStyle name="Normal 7 3" xfId="714"/>
-    <cellStyle name="Normal 7 4" xfId="715"/>
-    <cellStyle name="Normal 70" xfId="716"/>
-    <cellStyle name="Normal 71" xfId="717"/>
-    <cellStyle name="Normal 72" xfId="718"/>
-    <cellStyle name="Normal 73" xfId="719"/>
-    <cellStyle name="Normal 74" xfId="720"/>
-    <cellStyle name="Normal 75" xfId="721"/>
-    <cellStyle name="Normal 76" xfId="722"/>
-    <cellStyle name="Normal 77" xfId="723"/>
-    <cellStyle name="Normal 78" xfId="724"/>
-    <cellStyle name="Normal 79" xfId="725"/>
-    <cellStyle name="Normal 79 2" xfId="726"/>
-    <cellStyle name="Normal 79 3" xfId="727"/>
-    <cellStyle name="Normal 8" xfId="728"/>
-    <cellStyle name="Normal 8 2" xfId="729"/>
-    <cellStyle name="Normal 8 3" xfId="730"/>
-    <cellStyle name="Normal 8 4" xfId="731"/>
-    <cellStyle name="Normal 80" xfId="732"/>
-    <cellStyle name="Normal 80 2" xfId="733"/>
-    <cellStyle name="Normal 81" xfId="734"/>
-    <cellStyle name="Normal 81 2" xfId="735"/>
-    <cellStyle name="Normal 82" xfId="736"/>
-    <cellStyle name="Normal 82 2" xfId="737"/>
-    <cellStyle name="Normal 82 2 2" xfId="738"/>
-    <cellStyle name="Normal 83" xfId="739"/>
-    <cellStyle name="Normal 83 2" xfId="740"/>
-    <cellStyle name="Normal 83 2 2" xfId="741"/>
-    <cellStyle name="Normal 84" xfId="742"/>
-    <cellStyle name="Normal 84 2" xfId="743"/>
-    <cellStyle name="Normal 84 3" xfId="744"/>
-    <cellStyle name="Normal 85" xfId="745"/>
-    <cellStyle name="Normal 85 2" xfId="746"/>
-    <cellStyle name="Normal 85 3" xfId="747"/>
-    <cellStyle name="Normal 86" xfId="748"/>
-    <cellStyle name="Normal 86 2" xfId="749"/>
-    <cellStyle name="Normal 86 3" xfId="750"/>
-    <cellStyle name="Normal 87" xfId="751"/>
-    <cellStyle name="Normal 87 2" xfId="752"/>
-    <cellStyle name="Normal 87 3" xfId="753"/>
-    <cellStyle name="Normal 88" xfId="754"/>
-    <cellStyle name="Normal 88 2" xfId="755"/>
-    <cellStyle name="Normal 88 3" xfId="756"/>
-    <cellStyle name="Normal 88 4" xfId="757"/>
-    <cellStyle name="Normal 89" xfId="758"/>
-    <cellStyle name="Normal 9" xfId="759"/>
-    <cellStyle name="Normal 9 2" xfId="760"/>
-    <cellStyle name="Normal 9 3" xfId="761"/>
-    <cellStyle name="Normal 9 4" xfId="762"/>
-    <cellStyle name="Normal 90" xfId="763"/>
-    <cellStyle name="Normal 91" xfId="764"/>
-    <cellStyle name="Normal 92" xfId="765"/>
-    <cellStyle name="Normal 93" xfId="766"/>
-    <cellStyle name="Normal 94" xfId="767"/>
-    <cellStyle name="Normal 94 2" xfId="768"/>
-    <cellStyle name="Normal 95" xfId="769"/>
-    <cellStyle name="Normal 95 2" xfId="770"/>
-    <cellStyle name="Normal 95 3" xfId="771"/>
-    <cellStyle name="Normal 96" xfId="772"/>
-    <cellStyle name="Normal 97" xfId="773"/>
-    <cellStyle name="Normal 97 2" xfId="774"/>
-    <cellStyle name="Normal 98" xfId="775"/>
-    <cellStyle name="Normal 98 2" xfId="776"/>
-    <cellStyle name="Normal 99" xfId="777"/>
-    <cellStyle name="Normal 99 2" xfId="778"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3"/>
-    <cellStyle name="Notas 2" xfId="779"/>
-    <cellStyle name="Notas 2 2" xfId="780"/>
-    <cellStyle name="Notas 2 3" xfId="781"/>
-    <cellStyle name="Notas 3" xfId="782"/>
-    <cellStyle name="Notas 4" xfId="783"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785"/>
-    <cellStyle name="Salida 2" xfId="786"/>
-    <cellStyle name="Salida 3" xfId="787"/>
-    <cellStyle name="Salida 4" xfId="788"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791"/>
-    <cellStyle name="Texto explicativo 2" xfId="792"/>
-    <cellStyle name="Texto explicativo 3" xfId="793"/>
-    <cellStyle name="Texto explicativo 4" xfId="794"/>
-    <cellStyle name="Título 1 2" xfId="795"/>
-    <cellStyle name="Título 2 2" xfId="796"/>
-    <cellStyle name="Título 2 3" xfId="797"/>
-    <cellStyle name="Título 2 4" xfId="798"/>
-    <cellStyle name="Título 3 2" xfId="799"/>
-    <cellStyle name="Título 3 3" xfId="800"/>
-    <cellStyle name="Título 3 4" xfId="801"/>
-    <cellStyle name="Título 4" xfId="802"/>
-    <cellStyle name="Título 5" xfId="803"/>
-    <cellStyle name="Título 6" xfId="804"/>
-    <cellStyle name="Total 2" xfId="806"/>
-    <cellStyle name="Total 3" xfId="807"/>
-    <cellStyle name="Total 4" xfId="808"/>
-    <cellStyle name="Total 5" xfId="805"/>
+    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2643,25 +2643,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46101</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46104</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46105</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46106</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46107</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46108</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46111</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46112</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46113</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46118</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46119</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46120</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46121</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46122</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46125</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46126</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46127</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46128</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46129</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46132</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46133</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46134</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46135</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46136</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46139</v>
       </c>
@@ -3103,8 +3103,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="18">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
         <v>46140</v>
       </c>
       <c r="B27">
@@ -3116,12 +3116,12 @@
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="H27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="18">
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
         <v>46141</v>
       </c>
       <c r="B28">
@@ -3133,27 +3133,27 @@
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="H28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="18">
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
         <v>46142</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="18">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19">
+      <c r="C29" s="18"/>
+      <c r="D29" s="18">
         <v>15</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19">
+      <c r="E29" s="18"/>
+      <c r="F29" s="18">
         <v>25</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20">
+      <c r="G29" s="18"/>
+      <c r="H29" s="19">
         <v>18.43</v>
       </c>
     </row>
@@ -3164,17 +3164,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>46142</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>46141</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>46140</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>46139</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>46136</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>60973.651931649998</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>46135</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>4652.1817311200002</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>46134</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>17251.00486529</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>46133</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>47981.781644150004</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>46132</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>51339.49161813</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>46129</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>17216.492596060001</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>46128</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>18.890111640000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>46127</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>15.79809785</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>46126</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>16.215898760000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>46125</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>2475.4322626600001</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>46122</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>7956.2858669899997</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>46121</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>41.536584740000002</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>46120</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>580.56056466999996</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>46119</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>46118</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>46113</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>46112</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>46111</v>
       </c>
@@ -3395,17 +3395,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3471,8 +3471,8 @@
       <c r="C5" s="4">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="19">
-        <v>64.086567600538856</v>
+      <c r="D5" s="18">
+        <v>64.08</v>
       </c>
     </row>
   </sheetData>
@@ -3481,16 +3481,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46024</v>
       </c>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46031</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>-7.2050081634151608E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46038</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>8.9822186264706616E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46045</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>5.9816162411350016E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46052</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>0.15197009063882794</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46059</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>-2.5449418495950171E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1">
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46066</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>-2.0123569142568742E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46073</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>46080</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>5.8663015109889693E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>46087</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>-7.2971926029340772E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46094</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>0.10290725762048258</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46101</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>0.18425106797854962</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1">
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46108</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>-2.1851046806061425E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1">
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>46129</v>
       </c>
@@ -3660,21 +3660,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.75" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46108</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46115</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>-1.4067445693212388E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46122</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>9.7569377843467198E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46129</v>
       </c>
@@ -3804,9 +3804,9 @@
         <v>3.4749018512476804E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>31</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>46136</v>
       </c>
       <c r="B6" s="4">
         <v>55330466.694130011</v>
@@ -3836,19 +3836,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
-    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46108</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>-2.681224004753413E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46113</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>4.8691139433717501E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46122</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>-1.1061785896222975E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46129</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>6.2550592390904214E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46136</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>-1.3894983179757237E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46139</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>-1.3894983179757237E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46140</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>-1.3894983179757237E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46141</v>
       </c>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.cabezas\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9303BEE2-DAC6-45BE-9630-A342337143BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -142,16 +136,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="170" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1457,17 +1453,8 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1505,821 +1492,821 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="810">
-    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
+    <cellStyle name="Buena 2" xfId="74"/>
+    <cellStyle name="Buena 3" xfId="75"/>
+    <cellStyle name="Buena 4" xfId="76"/>
+    <cellStyle name="Cálculo 2" xfId="77"/>
+    <cellStyle name="Cálculo 3" xfId="78"/>
+    <cellStyle name="Cálculo 4" xfId="79"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82"/>
+    <cellStyle name="Celda vinculada 2" xfId="83"/>
+    <cellStyle name="Celda vinculada 3" xfId="84"/>
+    <cellStyle name="Celda vinculada 4" xfId="85"/>
+    <cellStyle name="Comma 2" xfId="121"/>
+    <cellStyle name="Encabezado 4 2" xfId="86"/>
+    <cellStyle name="Encabezado 4 3" xfId="87"/>
+    <cellStyle name="Encabezado 4 4" xfId="88"/>
+    <cellStyle name="Énfasis1 2" xfId="89"/>
+    <cellStyle name="Énfasis1 3" xfId="90"/>
+    <cellStyle name="Énfasis1 4" xfId="91"/>
+    <cellStyle name="Énfasis2 2" xfId="92"/>
+    <cellStyle name="Énfasis2 3" xfId="93"/>
+    <cellStyle name="Énfasis2 4" xfId="94"/>
+    <cellStyle name="Énfasis3 2" xfId="95"/>
+    <cellStyle name="Énfasis3 3" xfId="96"/>
+    <cellStyle name="Énfasis3 4" xfId="97"/>
+    <cellStyle name="Énfasis4 2" xfId="98"/>
+    <cellStyle name="Énfasis4 3" xfId="99"/>
+    <cellStyle name="Énfasis4 4" xfId="100"/>
+    <cellStyle name="Énfasis5 2" xfId="101"/>
+    <cellStyle name="Énfasis5 3" xfId="102"/>
+    <cellStyle name="Énfasis5 4" xfId="103"/>
+    <cellStyle name="Énfasis6 2" xfId="104"/>
+    <cellStyle name="Énfasis6 3" xfId="105"/>
+    <cellStyle name="Énfasis6 4" xfId="106"/>
+    <cellStyle name="Entrada 2" xfId="107"/>
+    <cellStyle name="Entrada 3" xfId="108"/>
+    <cellStyle name="Entrada 4" xfId="109"/>
+    <cellStyle name="Euro" xfId="110"/>
+    <cellStyle name="Euro 2" xfId="111"/>
+    <cellStyle name="Euro 2 2" xfId="112"/>
+    <cellStyle name="Euro 2 3" xfId="113"/>
+    <cellStyle name="Euro 2 4" xfId="114"/>
+    <cellStyle name="Euro 3" xfId="115"/>
+    <cellStyle name="Euro 4" xfId="116"/>
+    <cellStyle name="Euro 5" xfId="117"/>
+    <cellStyle name="Incorrecto 2" xfId="118"/>
+    <cellStyle name="Incorrecto 3" xfId="119"/>
+    <cellStyle name="Incorrecto 4" xfId="120"/>
+    <cellStyle name="Millares 10" xfId="122"/>
+    <cellStyle name="Millares 2" xfId="123"/>
+    <cellStyle name="Millares 2 2" xfId="124"/>
+    <cellStyle name="Millares 2 2 2" xfId="125"/>
+    <cellStyle name="Millares 2 3" xfId="126"/>
+    <cellStyle name="Millares 2 4" xfId="127"/>
+    <cellStyle name="Millares 3" xfId="128"/>
+    <cellStyle name="Millares 3 10" xfId="129"/>
+    <cellStyle name="Millares 3 100" xfId="130"/>
+    <cellStyle name="Millares 3 101" xfId="131"/>
+    <cellStyle name="Millares 3 102" xfId="132"/>
+    <cellStyle name="Millares 3 103" xfId="133"/>
+    <cellStyle name="Millares 3 103 2" xfId="134"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
+    <cellStyle name="Millares 3 104" xfId="136"/>
+    <cellStyle name="Millares 3 11" xfId="137"/>
+    <cellStyle name="Millares 3 12" xfId="138"/>
+    <cellStyle name="Millares 3 13" xfId="139"/>
+    <cellStyle name="Millares 3 14" xfId="140"/>
+    <cellStyle name="Millares 3 15" xfId="141"/>
+    <cellStyle name="Millares 3 16" xfId="142"/>
+    <cellStyle name="Millares 3 17" xfId="143"/>
+    <cellStyle name="Millares 3 18" xfId="144"/>
+    <cellStyle name="Millares 3 19" xfId="145"/>
+    <cellStyle name="Millares 3 2" xfId="146"/>
+    <cellStyle name="Millares 3 2 2" xfId="147"/>
+    <cellStyle name="Millares 3 2 3" xfId="148"/>
+    <cellStyle name="Millares 3 20" xfId="149"/>
+    <cellStyle name="Millares 3 21" xfId="150"/>
+    <cellStyle name="Millares 3 22" xfId="151"/>
+    <cellStyle name="Millares 3 23" xfId="152"/>
+    <cellStyle name="Millares 3 24" xfId="153"/>
+    <cellStyle name="Millares 3 25" xfId="154"/>
+    <cellStyle name="Millares 3 26" xfId="155"/>
+    <cellStyle name="Millares 3 27" xfId="156"/>
+    <cellStyle name="Millares 3 28" xfId="157"/>
+    <cellStyle name="Millares 3 29" xfId="158"/>
+    <cellStyle name="Millares 3 3" xfId="159"/>
+    <cellStyle name="Millares 3 30" xfId="160"/>
+    <cellStyle name="Millares 3 31" xfId="161"/>
+    <cellStyle name="Millares 3 32" xfId="162"/>
+    <cellStyle name="Millares 3 33" xfId="163"/>
+    <cellStyle name="Millares 3 34" xfId="164"/>
+    <cellStyle name="Millares 3 35" xfId="165"/>
+    <cellStyle name="Millares 3 36" xfId="166"/>
+    <cellStyle name="Millares 3 37" xfId="167"/>
+    <cellStyle name="Millares 3 38" xfId="168"/>
+    <cellStyle name="Millares 3 39" xfId="169"/>
+    <cellStyle name="Millares 3 4" xfId="170"/>
+    <cellStyle name="Millares 3 40" xfId="171"/>
+    <cellStyle name="Millares 3 41" xfId="172"/>
+    <cellStyle name="Millares 3 42" xfId="173"/>
+    <cellStyle name="Millares 3 43" xfId="174"/>
+    <cellStyle name="Millares 3 44" xfId="175"/>
+    <cellStyle name="Millares 3 45" xfId="176"/>
+    <cellStyle name="Millares 3 46" xfId="177"/>
+    <cellStyle name="Millares 3 47" xfId="178"/>
+    <cellStyle name="Millares 3 48" xfId="179"/>
+    <cellStyle name="Millares 3 49" xfId="180"/>
+    <cellStyle name="Millares 3 5" xfId="181"/>
+    <cellStyle name="Millares 3 50" xfId="182"/>
+    <cellStyle name="Millares 3 51" xfId="183"/>
+    <cellStyle name="Millares 3 52" xfId="184"/>
+    <cellStyle name="Millares 3 53" xfId="185"/>
+    <cellStyle name="Millares 3 54" xfId="186"/>
+    <cellStyle name="Millares 3 55" xfId="187"/>
+    <cellStyle name="Millares 3 56" xfId="188"/>
+    <cellStyle name="Millares 3 57" xfId="189"/>
+    <cellStyle name="Millares 3 58" xfId="190"/>
+    <cellStyle name="Millares 3 59" xfId="191"/>
+    <cellStyle name="Millares 3 6" xfId="192"/>
+    <cellStyle name="Millares 3 60" xfId="193"/>
+    <cellStyle name="Millares 3 61" xfId="194"/>
+    <cellStyle name="Millares 3 62" xfId="195"/>
+    <cellStyle name="Millares 3 63" xfId="196"/>
+    <cellStyle name="Millares 3 64" xfId="197"/>
+    <cellStyle name="Millares 3 65" xfId="198"/>
+    <cellStyle name="Millares 3 66" xfId="199"/>
+    <cellStyle name="Millares 3 67" xfId="200"/>
+    <cellStyle name="Millares 3 68" xfId="201"/>
+    <cellStyle name="Millares 3 69" xfId="202"/>
+    <cellStyle name="Millares 3 7" xfId="203"/>
+    <cellStyle name="Millares 3 70" xfId="204"/>
+    <cellStyle name="Millares 3 71" xfId="205"/>
+    <cellStyle name="Millares 3 72" xfId="206"/>
+    <cellStyle name="Millares 3 73" xfId="207"/>
+    <cellStyle name="Millares 3 74" xfId="208"/>
+    <cellStyle name="Millares 3 75" xfId="209"/>
+    <cellStyle name="Millares 3 76" xfId="210"/>
+    <cellStyle name="Millares 3 77" xfId="211"/>
+    <cellStyle name="Millares 3 78" xfId="212"/>
+    <cellStyle name="Millares 3 79" xfId="213"/>
+    <cellStyle name="Millares 3 8" xfId="214"/>
+    <cellStyle name="Millares 3 80" xfId="215"/>
+    <cellStyle name="Millares 3 81" xfId="216"/>
+    <cellStyle name="Millares 3 82" xfId="217"/>
+    <cellStyle name="Millares 3 83" xfId="218"/>
+    <cellStyle name="Millares 3 84" xfId="219"/>
+    <cellStyle name="Millares 3 85" xfId="220"/>
+    <cellStyle name="Millares 3 86" xfId="221"/>
+    <cellStyle name="Millares 3 87" xfId="222"/>
+    <cellStyle name="Millares 3 88" xfId="223"/>
+    <cellStyle name="Millares 3 89" xfId="224"/>
+    <cellStyle name="Millares 3 9" xfId="225"/>
+    <cellStyle name="Millares 3 90" xfId="226"/>
+    <cellStyle name="Millares 3 91" xfId="227"/>
+    <cellStyle name="Millares 3 92" xfId="228"/>
+    <cellStyle name="Millares 3 93" xfId="229"/>
+    <cellStyle name="Millares 3 94" xfId="230"/>
+    <cellStyle name="Millares 3 95" xfId="231"/>
+    <cellStyle name="Millares 3 96" xfId="232"/>
+    <cellStyle name="Millares 3 97" xfId="233"/>
+    <cellStyle name="Millares 3 98" xfId="234"/>
+    <cellStyle name="Millares 3 99" xfId="235"/>
+    <cellStyle name="Millares 4" xfId="236"/>
+    <cellStyle name="Millares 4 2" xfId="237"/>
+    <cellStyle name="Millares 5" xfId="238"/>
+    <cellStyle name="Millares 5 2" xfId="239"/>
+    <cellStyle name="Millares 5 3" xfId="240"/>
+    <cellStyle name="Millares 6" xfId="241"/>
+    <cellStyle name="Millares 6 2" xfId="242"/>
+    <cellStyle name="Millares 6 3" xfId="243"/>
+    <cellStyle name="Millares 7" xfId="244"/>
+    <cellStyle name="Millares 8" xfId="245"/>
+    <cellStyle name="Millares 8 2" xfId="246"/>
+    <cellStyle name="Millares 9" xfId="247"/>
+    <cellStyle name="Neutral 2" xfId="249"/>
+    <cellStyle name="Neutral 3" xfId="250"/>
+    <cellStyle name="Neutral 4" xfId="251"/>
+    <cellStyle name="Neutral 5" xfId="248"/>
+    <cellStyle name="NivelFila_3 2" xfId="809"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
-    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Normal 10" xfId="252"/>
+    <cellStyle name="Normal 10 2" xfId="253"/>
+    <cellStyle name="Normal 10 3" xfId="254"/>
+    <cellStyle name="Normal 10 4" xfId="255"/>
+    <cellStyle name="Normal 100" xfId="256"/>
+    <cellStyle name="Normal 100 2" xfId="257"/>
+    <cellStyle name="Normal 101" xfId="258"/>
+    <cellStyle name="Normal 101 2" xfId="259"/>
+    <cellStyle name="Normal 102" xfId="260"/>
+    <cellStyle name="Normal 102 2" xfId="261"/>
+    <cellStyle name="Normal 103" xfId="262"/>
+    <cellStyle name="Normal 103 2" xfId="263"/>
+    <cellStyle name="Normal 104" xfId="264"/>
+    <cellStyle name="Normal 104 2" xfId="265"/>
+    <cellStyle name="Normal 104 3" xfId="266"/>
+    <cellStyle name="Normal 105" xfId="267"/>
+    <cellStyle name="Normal 106" xfId="268"/>
+    <cellStyle name="Normal 106 2" xfId="269"/>
+    <cellStyle name="Normal 106 3" xfId="270"/>
+    <cellStyle name="Normal 107" xfId="271"/>
+    <cellStyle name="Normal 107 2" xfId="272"/>
+    <cellStyle name="Normal 108" xfId="273"/>
+    <cellStyle name="Normal 109" xfId="274"/>
+    <cellStyle name="Normal 11" xfId="275"/>
+    <cellStyle name="Normal 11 2" xfId="276"/>
+    <cellStyle name="Normal 11 3" xfId="277"/>
+    <cellStyle name="Normal 11 4" xfId="278"/>
+    <cellStyle name="Normal 110" xfId="279"/>
+    <cellStyle name="Normal 111" xfId="280"/>
+    <cellStyle name="Normal 112" xfId="281"/>
+    <cellStyle name="Normal 112 2" xfId="282"/>
+    <cellStyle name="Normal 113" xfId="283"/>
+    <cellStyle name="Normal 113 2" xfId="284"/>
+    <cellStyle name="Normal 114" xfId="285"/>
+    <cellStyle name="Normal 114 2" xfId="286"/>
+    <cellStyle name="Normal 115" xfId="287"/>
+    <cellStyle name="Normal 115 2" xfId="288"/>
+    <cellStyle name="Normal 116" xfId="289"/>
+    <cellStyle name="Normal 116 2" xfId="290"/>
+    <cellStyle name="Normal 116 3" xfId="291"/>
+    <cellStyle name="Normal 117" xfId="292"/>
+    <cellStyle name="Normal 117 2" xfId="293"/>
+    <cellStyle name="Normal 118" xfId="294"/>
+    <cellStyle name="Normal 118 2" xfId="295"/>
+    <cellStyle name="Normal 118 3" xfId="296"/>
+    <cellStyle name="Normal 119" xfId="297"/>
+    <cellStyle name="Normal 119 2" xfId="298"/>
+    <cellStyle name="Normal 119 3" xfId="299"/>
+    <cellStyle name="Normal 12" xfId="300"/>
+    <cellStyle name="Normal 12 2" xfId="301"/>
+    <cellStyle name="Normal 12 3" xfId="302"/>
+    <cellStyle name="Normal 12 4" xfId="303"/>
+    <cellStyle name="Normal 120" xfId="304"/>
+    <cellStyle name="Normal 120 2" xfId="305"/>
+    <cellStyle name="Normal 121" xfId="306"/>
+    <cellStyle name="Normal 121 2" xfId="307"/>
+    <cellStyle name="Normal 122" xfId="308"/>
+    <cellStyle name="Normal 122 2" xfId="309"/>
+    <cellStyle name="Normal 123" xfId="310"/>
+    <cellStyle name="Normal 124" xfId="311"/>
+    <cellStyle name="Normal 124 2" xfId="312"/>
+    <cellStyle name="Normal 125" xfId="313"/>
+    <cellStyle name="Normal 125 2" xfId="314"/>
+    <cellStyle name="Normal 126" xfId="315"/>
+    <cellStyle name="Normal 127" xfId="316"/>
+    <cellStyle name="Normal 127 2" xfId="317"/>
+    <cellStyle name="Normal 128" xfId="318"/>
+    <cellStyle name="Normal 129" xfId="319"/>
+    <cellStyle name="Normal 13" xfId="320"/>
+    <cellStyle name="Normal 13 2" xfId="321"/>
+    <cellStyle name="Normal 13 3" xfId="322"/>
+    <cellStyle name="Normal 13 4" xfId="323"/>
+    <cellStyle name="Normal 130" xfId="324"/>
+    <cellStyle name="Normal 130 2" xfId="325"/>
+    <cellStyle name="Normal 131" xfId="326"/>
+    <cellStyle name="Normal 131 2" xfId="327"/>
+    <cellStyle name="Normal 132" xfId="328"/>
+    <cellStyle name="Normal 132 2" xfId="329"/>
+    <cellStyle name="Normal 133" xfId="330"/>
+    <cellStyle name="Normal 133 2" xfId="331"/>
+    <cellStyle name="Normal 134" xfId="332"/>
+    <cellStyle name="Normal 135" xfId="333"/>
+    <cellStyle name="Normal 135 2" xfId="334"/>
+    <cellStyle name="Normal 136" xfId="335"/>
+    <cellStyle name="Normal 136 2" xfId="336"/>
+    <cellStyle name="Normal 137" xfId="337"/>
+    <cellStyle name="Normal 137 2" xfId="338"/>
+    <cellStyle name="Normal 138" xfId="339"/>
+    <cellStyle name="Normal 138 2" xfId="340"/>
+    <cellStyle name="Normal 139" xfId="341"/>
+    <cellStyle name="Normal 139 2" xfId="342"/>
+    <cellStyle name="Normal 14" xfId="343"/>
+    <cellStyle name="Normal 14 2" xfId="344"/>
+    <cellStyle name="Normal 14 3" xfId="345"/>
+    <cellStyle name="Normal 14 4" xfId="346"/>
+    <cellStyle name="Normal 140" xfId="347"/>
+    <cellStyle name="Normal 140 2" xfId="348"/>
+    <cellStyle name="Normal 141" xfId="349"/>
+    <cellStyle name="Normal 142" xfId="350"/>
+    <cellStyle name="Normal 142 2" xfId="351"/>
+    <cellStyle name="Normal 143" xfId="352"/>
+    <cellStyle name="Normal 143 2" xfId="353"/>
+    <cellStyle name="Normal 143 3" xfId="354"/>
+    <cellStyle name="Normal 144" xfId="355"/>
+    <cellStyle name="Normal 144 2" xfId="356"/>
+    <cellStyle name="Normal 145" xfId="357"/>
+    <cellStyle name="Normal 145 2" xfId="358"/>
+    <cellStyle name="Normal 146" xfId="359"/>
+    <cellStyle name="Normal 147" xfId="360"/>
+    <cellStyle name="Normal 15" xfId="361"/>
+    <cellStyle name="Normal 15 2" xfId="362"/>
+    <cellStyle name="Normal 15 3" xfId="363"/>
+    <cellStyle name="Normal 15 4" xfId="364"/>
+    <cellStyle name="Normal 16" xfId="365"/>
+    <cellStyle name="Normal 16 2" xfId="366"/>
+    <cellStyle name="Normal 16 3" xfId="367"/>
+    <cellStyle name="Normal 16 4" xfId="368"/>
+    <cellStyle name="Normal 17" xfId="369"/>
+    <cellStyle name="Normal 17 2" xfId="370"/>
+    <cellStyle name="Normal 17 3" xfId="371"/>
+    <cellStyle name="Normal 17 4" xfId="372"/>
+    <cellStyle name="Normal 18" xfId="373"/>
+    <cellStyle name="Normal 18 2" xfId="374"/>
+    <cellStyle name="Normal 18 3" xfId="375"/>
+    <cellStyle name="Normal 18 4" xfId="376"/>
+    <cellStyle name="Normal 19" xfId="377"/>
+    <cellStyle name="Normal 19 2" xfId="378"/>
+    <cellStyle name="Normal 19 3" xfId="379"/>
+    <cellStyle name="Normal 19 4" xfId="380"/>
+    <cellStyle name="Normal 2" xfId="381"/>
+    <cellStyle name="Normal 2 10" xfId="382"/>
+    <cellStyle name="Normal 2 100" xfId="383"/>
+    <cellStyle name="Normal 2 101" xfId="384"/>
+    <cellStyle name="Normal 2 102" xfId="385"/>
+    <cellStyle name="Normal 2 103" xfId="386"/>
+    <cellStyle name="Normal 2 103 2" xfId="387"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
+    <cellStyle name="Normal 2 104" xfId="389"/>
+    <cellStyle name="Normal 2 104 2" xfId="390"/>
+    <cellStyle name="Normal 2 105" xfId="391"/>
+    <cellStyle name="Normal 2 105 2" xfId="392"/>
+    <cellStyle name="Normal 2 106" xfId="393"/>
+    <cellStyle name="Normal 2 106 2" xfId="394"/>
+    <cellStyle name="Normal 2 106 3" xfId="395"/>
+    <cellStyle name="Normal 2 107" xfId="396"/>
+    <cellStyle name="Normal 2 107 2" xfId="397"/>
+    <cellStyle name="Normal 2 108" xfId="398"/>
+    <cellStyle name="Normal 2 108 2" xfId="399"/>
+    <cellStyle name="Normal 2 109" xfId="400"/>
+    <cellStyle name="Normal 2 109 2" xfId="401"/>
+    <cellStyle name="Normal 2 11" xfId="402"/>
+    <cellStyle name="Normal 2 110" xfId="403"/>
+    <cellStyle name="Normal 2 111" xfId="404"/>
+    <cellStyle name="Normal 2 112" xfId="405"/>
+    <cellStyle name="Normal 2 113" xfId="406"/>
+    <cellStyle name="Normal 2 114" xfId="407"/>
+    <cellStyle name="Normal 2 115" xfId="408"/>
+    <cellStyle name="Normal 2 12" xfId="409"/>
+    <cellStyle name="Normal 2 13" xfId="410"/>
+    <cellStyle name="Normal 2 14" xfId="411"/>
+    <cellStyle name="Normal 2 15" xfId="412"/>
+    <cellStyle name="Normal 2 16" xfId="413"/>
+    <cellStyle name="Normal 2 17" xfId="414"/>
+    <cellStyle name="Normal 2 18" xfId="415"/>
+    <cellStyle name="Normal 2 19" xfId="416"/>
+    <cellStyle name="Normal 2 2" xfId="417"/>
+    <cellStyle name="Normal 2 2 2" xfId="418"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
+    <cellStyle name="Normal 2 2 3" xfId="420"/>
+    <cellStyle name="Normal 2 2 4" xfId="421"/>
+    <cellStyle name="Normal 2 20" xfId="422"/>
+    <cellStyle name="Normal 2 21" xfId="423"/>
+    <cellStyle name="Normal 2 22" xfId="424"/>
+    <cellStyle name="Normal 2 23" xfId="425"/>
+    <cellStyle name="Normal 2 24" xfId="426"/>
+    <cellStyle name="Normal 2 25" xfId="427"/>
+    <cellStyle name="Normal 2 26" xfId="428"/>
+    <cellStyle name="Normal 2 27" xfId="429"/>
+    <cellStyle name="Normal 2 28" xfId="430"/>
+    <cellStyle name="Normal 2 29" xfId="431"/>
+    <cellStyle name="Normal 2 3" xfId="432"/>
+    <cellStyle name="Normal 2 3 2" xfId="433"/>
+    <cellStyle name="Normal 2 3 3" xfId="434"/>
+    <cellStyle name="Normal 2 30" xfId="435"/>
+    <cellStyle name="Normal 2 31" xfId="436"/>
+    <cellStyle name="Normal 2 32" xfId="437"/>
+    <cellStyle name="Normal 2 33" xfId="438"/>
+    <cellStyle name="Normal 2 34" xfId="439"/>
+    <cellStyle name="Normal 2 35" xfId="440"/>
+    <cellStyle name="Normal 2 36" xfId="441"/>
+    <cellStyle name="Normal 2 37" xfId="442"/>
+    <cellStyle name="Normal 2 38" xfId="443"/>
+    <cellStyle name="Normal 2 39" xfId="444"/>
+    <cellStyle name="Normal 2 4" xfId="445"/>
+    <cellStyle name="Normal 2 4 2" xfId="446"/>
+    <cellStyle name="Normal 2 4 3" xfId="447"/>
+    <cellStyle name="Normal 2 4 4" xfId="448"/>
+    <cellStyle name="Normal 2 40" xfId="449"/>
+    <cellStyle name="Normal 2 41" xfId="450"/>
+    <cellStyle name="Normal 2 42" xfId="451"/>
+    <cellStyle name="Normal 2 43" xfId="452"/>
+    <cellStyle name="Normal 2 44" xfId="453"/>
+    <cellStyle name="Normal 2 45" xfId="454"/>
+    <cellStyle name="Normal 2 45 10" xfId="455"/>
+    <cellStyle name="Normal 2 45 11" xfId="456"/>
+    <cellStyle name="Normal 2 45 12" xfId="457"/>
+    <cellStyle name="Normal 2 45 13" xfId="458"/>
+    <cellStyle name="Normal 2 45 14" xfId="459"/>
+    <cellStyle name="Normal 2 45 15" xfId="460"/>
+    <cellStyle name="Normal 2 45 16" xfId="461"/>
+    <cellStyle name="Normal 2 45 17" xfId="462"/>
+    <cellStyle name="Normal 2 45 18" xfId="463"/>
+    <cellStyle name="Normal 2 45 19" xfId="464"/>
+    <cellStyle name="Normal 2 45 2" xfId="465"/>
+    <cellStyle name="Normal 2 45 20" xfId="466"/>
+    <cellStyle name="Normal 2 45 21" xfId="467"/>
+    <cellStyle name="Normal 2 45 22" xfId="468"/>
+    <cellStyle name="Normal 2 45 23" xfId="469"/>
+    <cellStyle name="Normal 2 45 24" xfId="470"/>
+    <cellStyle name="Normal 2 45 25" xfId="471"/>
+    <cellStyle name="Normal 2 45 26" xfId="472"/>
+    <cellStyle name="Normal 2 45 27" xfId="473"/>
+    <cellStyle name="Normal 2 45 28" xfId="474"/>
+    <cellStyle name="Normal 2 45 29" xfId="475"/>
+    <cellStyle name="Normal 2 45 3" xfId="476"/>
+    <cellStyle name="Normal 2 45 30" xfId="477"/>
+    <cellStyle name="Normal 2 45 31" xfId="478"/>
+    <cellStyle name="Normal 2 45 32" xfId="479"/>
+    <cellStyle name="Normal 2 45 33" xfId="480"/>
+    <cellStyle name="Normal 2 45 34" xfId="481"/>
+    <cellStyle name="Normal 2 45 35" xfId="482"/>
+    <cellStyle name="Normal 2 45 36" xfId="483"/>
+    <cellStyle name="Normal 2 45 37" xfId="484"/>
+    <cellStyle name="Normal 2 45 38" xfId="485"/>
+    <cellStyle name="Normal 2 45 39" xfId="486"/>
+    <cellStyle name="Normal 2 45 4" xfId="487"/>
+    <cellStyle name="Normal 2 45 40" xfId="488"/>
+    <cellStyle name="Normal 2 45 41" xfId="489"/>
+    <cellStyle name="Normal 2 45 42" xfId="490"/>
+    <cellStyle name="Normal 2 45 43" xfId="491"/>
+    <cellStyle name="Normal 2 45 44" xfId="492"/>
+    <cellStyle name="Normal 2 45 45" xfId="493"/>
+    <cellStyle name="Normal 2 45 46" xfId="494"/>
+    <cellStyle name="Normal 2 45 47" xfId="495"/>
+    <cellStyle name="Normal 2 45 48" xfId="496"/>
+    <cellStyle name="Normal 2 45 49" xfId="497"/>
+    <cellStyle name="Normal 2 45 5" xfId="498"/>
+    <cellStyle name="Normal 2 45 50" xfId="499"/>
+    <cellStyle name="Normal 2 45 51" xfId="500"/>
+    <cellStyle name="Normal 2 45 52" xfId="501"/>
+    <cellStyle name="Normal 2 45 53" xfId="502"/>
+    <cellStyle name="Normal 2 45 54" xfId="503"/>
+    <cellStyle name="Normal 2 45 55" xfId="504"/>
+    <cellStyle name="Normal 2 45 56" xfId="505"/>
+    <cellStyle name="Normal 2 45 57" xfId="506"/>
+    <cellStyle name="Normal 2 45 58" xfId="507"/>
+    <cellStyle name="Normal 2 45 59" xfId="508"/>
+    <cellStyle name="Normal 2 45 6" xfId="509"/>
+    <cellStyle name="Normal 2 45 7" xfId="510"/>
+    <cellStyle name="Normal 2 45 8" xfId="511"/>
+    <cellStyle name="Normal 2 45 9" xfId="512"/>
+    <cellStyle name="Normal 2 46" xfId="513"/>
+    <cellStyle name="Normal 2 47" xfId="514"/>
+    <cellStyle name="Normal 2 48" xfId="515"/>
+    <cellStyle name="Normal 2 49" xfId="516"/>
+    <cellStyle name="Normal 2 5" xfId="517"/>
+    <cellStyle name="Normal 2 5 2" xfId="518"/>
+    <cellStyle name="Normal 2 5 3" xfId="519"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
+    <cellStyle name="Normal 2 5 4" xfId="521"/>
+    <cellStyle name="Normal 2 50" xfId="522"/>
+    <cellStyle name="Normal 2 51" xfId="523"/>
+    <cellStyle name="Normal 2 52" xfId="524"/>
+    <cellStyle name="Normal 2 53" xfId="525"/>
+    <cellStyle name="Normal 2 54" xfId="526"/>
+    <cellStyle name="Normal 2 55" xfId="527"/>
+    <cellStyle name="Normal 2 56" xfId="528"/>
+    <cellStyle name="Normal 2 57" xfId="529"/>
+    <cellStyle name="Normal 2 58" xfId="530"/>
+    <cellStyle name="Normal 2 59" xfId="531"/>
+    <cellStyle name="Normal 2 6" xfId="532"/>
+    <cellStyle name="Normal 2 6 2" xfId="533"/>
+    <cellStyle name="Normal 2 60" xfId="534"/>
+    <cellStyle name="Normal 2 61" xfId="535"/>
+    <cellStyle name="Normal 2 62" xfId="536"/>
+    <cellStyle name="Normal 2 63" xfId="537"/>
+    <cellStyle name="Normal 2 64" xfId="538"/>
+    <cellStyle name="Normal 2 65" xfId="539"/>
+    <cellStyle name="Normal 2 66" xfId="540"/>
+    <cellStyle name="Normal 2 67" xfId="541"/>
+    <cellStyle name="Normal 2 68" xfId="542"/>
+    <cellStyle name="Normal 2 69" xfId="543"/>
+    <cellStyle name="Normal 2 7" xfId="544"/>
+    <cellStyle name="Normal 2 70" xfId="545"/>
+    <cellStyle name="Normal 2 71" xfId="546"/>
+    <cellStyle name="Normal 2 72" xfId="547"/>
+    <cellStyle name="Normal 2 73" xfId="548"/>
+    <cellStyle name="Normal 2 74" xfId="549"/>
+    <cellStyle name="Normal 2 75" xfId="550"/>
+    <cellStyle name="Normal 2 76" xfId="551"/>
+    <cellStyle name="Normal 2 77" xfId="552"/>
+    <cellStyle name="Normal 2 78" xfId="553"/>
+    <cellStyle name="Normal 2 79" xfId="554"/>
+    <cellStyle name="Normal 2 8" xfId="555"/>
+    <cellStyle name="Normal 2 80" xfId="556"/>
+    <cellStyle name="Normal 2 81" xfId="557"/>
+    <cellStyle name="Normal 2 82" xfId="558"/>
+    <cellStyle name="Normal 2 83" xfId="559"/>
+    <cellStyle name="Normal 2 84" xfId="560"/>
+    <cellStyle name="Normal 2 85" xfId="561"/>
+    <cellStyle name="Normal 2 86" xfId="562"/>
+    <cellStyle name="Normal 2 87" xfId="563"/>
+    <cellStyle name="Normal 2 88" xfId="564"/>
+    <cellStyle name="Normal 2 89" xfId="565"/>
+    <cellStyle name="Normal 2 9" xfId="566"/>
+    <cellStyle name="Normal 2 90" xfId="567"/>
+    <cellStyle name="Normal 2 91" xfId="568"/>
+    <cellStyle name="Normal 2 92" xfId="569"/>
+    <cellStyle name="Normal 2 93" xfId="570"/>
+    <cellStyle name="Normal 2 94" xfId="571"/>
+    <cellStyle name="Normal 2 95" xfId="572"/>
+    <cellStyle name="Normal 2 96" xfId="573"/>
+    <cellStyle name="Normal 2 97" xfId="574"/>
+    <cellStyle name="Normal 2 98" xfId="575"/>
+    <cellStyle name="Normal 2 99" xfId="576"/>
+    <cellStyle name="Normal 20" xfId="577"/>
+    <cellStyle name="Normal 20 2" xfId="578"/>
+    <cellStyle name="Normal 20 3" xfId="579"/>
+    <cellStyle name="Normal 20 4" xfId="580"/>
+    <cellStyle name="Normal 21" xfId="581"/>
+    <cellStyle name="Normal 21 2" xfId="582"/>
+    <cellStyle name="Normal 21 3" xfId="583"/>
+    <cellStyle name="Normal 21 4" xfId="584"/>
+    <cellStyle name="Normal 22" xfId="585"/>
+    <cellStyle name="Normal 22 2" xfId="586"/>
+    <cellStyle name="Normal 22 3" xfId="587"/>
+    <cellStyle name="Normal 22 4" xfId="588"/>
+    <cellStyle name="Normal 23" xfId="589"/>
+    <cellStyle name="Normal 23 2" xfId="590"/>
+    <cellStyle name="Normal 23 3" xfId="591"/>
+    <cellStyle name="Normal 24" xfId="592"/>
+    <cellStyle name="Normal 24 2" xfId="593"/>
+    <cellStyle name="Normal 24 3" xfId="594"/>
+    <cellStyle name="Normal 25" xfId="595"/>
+    <cellStyle name="Normal 26" xfId="596"/>
+    <cellStyle name="Normal 27" xfId="597"/>
+    <cellStyle name="Normal 28" xfId="598"/>
+    <cellStyle name="Normal 29" xfId="599"/>
+    <cellStyle name="Normal 3" xfId="600"/>
+    <cellStyle name="Normal 3 2" xfId="601"/>
+    <cellStyle name="Normal 3 2 2" xfId="602"/>
+    <cellStyle name="Normal 3 3" xfId="603"/>
+    <cellStyle name="Normal 3 3 2" xfId="604"/>
+    <cellStyle name="Normal 3 3 3" xfId="605"/>
+    <cellStyle name="Normal 3 4" xfId="606"/>
+    <cellStyle name="Normal 3 5" xfId="607"/>
+    <cellStyle name="Normal 30" xfId="608"/>
+    <cellStyle name="Normal 31" xfId="609"/>
+    <cellStyle name="Normal 32" xfId="610"/>
+    <cellStyle name="Normal 33" xfId="611"/>
+    <cellStyle name="Normal 34" xfId="612"/>
+    <cellStyle name="Normal 35" xfId="613"/>
+    <cellStyle name="Normal 36" xfId="614"/>
+    <cellStyle name="Normal 37" xfId="615"/>
+    <cellStyle name="Normal 38" xfId="616"/>
+    <cellStyle name="Normal 39" xfId="617"/>
+    <cellStyle name="Normal 4" xfId="618"/>
+    <cellStyle name="Normal 4 2" xfId="619"/>
+    <cellStyle name="Normal 4 2 2" xfId="620"/>
+    <cellStyle name="Normal 4 3" xfId="621"/>
+    <cellStyle name="Normal 4 4" xfId="622"/>
+    <cellStyle name="Normal 40" xfId="623"/>
+    <cellStyle name="Normal 41" xfId="624"/>
+    <cellStyle name="Normal 42" xfId="625"/>
+    <cellStyle name="Normal 43" xfId="626"/>
+    <cellStyle name="Normal 44" xfId="627"/>
+    <cellStyle name="Normal 45" xfId="628"/>
+    <cellStyle name="Normal 46" xfId="629"/>
+    <cellStyle name="Normal 47" xfId="630"/>
+    <cellStyle name="Normal 48" xfId="631"/>
+    <cellStyle name="Normal 49" xfId="632"/>
+    <cellStyle name="Normal 5" xfId="633"/>
+    <cellStyle name="Normal 5 10" xfId="634"/>
+    <cellStyle name="Normal 5 11" xfId="635"/>
+    <cellStyle name="Normal 5 12" xfId="636"/>
+    <cellStyle name="Normal 5 13" xfId="637"/>
+    <cellStyle name="Normal 5 14" xfId="638"/>
+    <cellStyle name="Normal 5 15" xfId="639"/>
+    <cellStyle name="Normal 5 16" xfId="640"/>
+    <cellStyle name="Normal 5 17" xfId="641"/>
+    <cellStyle name="Normal 5 18" xfId="642"/>
+    <cellStyle name="Normal 5 19" xfId="643"/>
+    <cellStyle name="Normal 5 2" xfId="644"/>
+    <cellStyle name="Normal 5 20" xfId="645"/>
+    <cellStyle name="Normal 5 21" xfId="646"/>
+    <cellStyle name="Normal 5 22" xfId="647"/>
+    <cellStyle name="Normal 5 23" xfId="648"/>
+    <cellStyle name="Normal 5 24" xfId="649"/>
+    <cellStyle name="Normal 5 25" xfId="650"/>
+    <cellStyle name="Normal 5 26" xfId="651"/>
+    <cellStyle name="Normal 5 27" xfId="652"/>
+    <cellStyle name="Normal 5 28" xfId="653"/>
+    <cellStyle name="Normal 5 28 10" xfId="654"/>
+    <cellStyle name="Normal 5 28 11" xfId="655"/>
+    <cellStyle name="Normal 5 28 12" xfId="656"/>
+    <cellStyle name="Normal 5 28 13" xfId="657"/>
+    <cellStyle name="Normal 5 28 14" xfId="658"/>
+    <cellStyle name="Normal 5 28 15" xfId="659"/>
+    <cellStyle name="Normal 5 28 16" xfId="660"/>
+    <cellStyle name="Normal 5 28 17" xfId="661"/>
+    <cellStyle name="Normal 5 28 18" xfId="662"/>
+    <cellStyle name="Normal 5 28 19" xfId="663"/>
+    <cellStyle name="Normal 5 28 2" xfId="664"/>
+    <cellStyle name="Normal 5 28 20" xfId="665"/>
+    <cellStyle name="Normal 5 28 21" xfId="666"/>
+    <cellStyle name="Normal 5 28 22" xfId="667"/>
+    <cellStyle name="Normal 5 28 23" xfId="668"/>
+    <cellStyle name="Normal 5 28 24" xfId="669"/>
+    <cellStyle name="Normal 5 28 25" xfId="670"/>
+    <cellStyle name="Normal 5 28 3" xfId="671"/>
+    <cellStyle name="Normal 5 28 4" xfId="672"/>
+    <cellStyle name="Normal 5 28 5" xfId="673"/>
+    <cellStyle name="Normal 5 28 6" xfId="674"/>
+    <cellStyle name="Normal 5 28 7" xfId="675"/>
+    <cellStyle name="Normal 5 28 8" xfId="676"/>
+    <cellStyle name="Normal 5 28 9" xfId="677"/>
+    <cellStyle name="Normal 5 29" xfId="678"/>
+    <cellStyle name="Normal 5 3" xfId="679"/>
+    <cellStyle name="Normal 5 4" xfId="680"/>
+    <cellStyle name="Normal 5 5" xfId="681"/>
+    <cellStyle name="Normal 5 6" xfId="682"/>
+    <cellStyle name="Normal 5 7" xfId="683"/>
+    <cellStyle name="Normal 5 8" xfId="684"/>
+    <cellStyle name="Normal 5 9" xfId="685"/>
+    <cellStyle name="Normal 50" xfId="686"/>
+    <cellStyle name="Normal 51" xfId="687"/>
+    <cellStyle name="Normal 52" xfId="688"/>
+    <cellStyle name="Normal 53" xfId="689"/>
+    <cellStyle name="Normal 54" xfId="690"/>
+    <cellStyle name="Normal 55" xfId="691"/>
+    <cellStyle name="Normal 56" xfId="2"/>
+    <cellStyle name="Normal 56 2" xfId="692"/>
+    <cellStyle name="Normal 57" xfId="693"/>
+    <cellStyle name="Normal 58" xfId="694"/>
+    <cellStyle name="Normal 59" xfId="695"/>
+    <cellStyle name="Normal 6" xfId="696"/>
+    <cellStyle name="Normal 6 2" xfId="697"/>
+    <cellStyle name="Normal 6 2 2" xfId="698"/>
+    <cellStyle name="Normal 6 2 3" xfId="699"/>
+    <cellStyle name="Normal 6 3" xfId="700"/>
+    <cellStyle name="Normal 6 4" xfId="701"/>
+    <cellStyle name="Normal 60" xfId="702"/>
+    <cellStyle name="Normal 61" xfId="703"/>
+    <cellStyle name="Normal 62" xfId="704"/>
+    <cellStyle name="Normal 63" xfId="705"/>
+    <cellStyle name="Normal 64" xfId="706"/>
+    <cellStyle name="Normal 65" xfId="707"/>
+    <cellStyle name="Normal 66" xfId="708"/>
+    <cellStyle name="Normal 67" xfId="709"/>
+    <cellStyle name="Normal 68" xfId="710"/>
+    <cellStyle name="Normal 69" xfId="711"/>
+    <cellStyle name="Normal 7" xfId="712"/>
+    <cellStyle name="Normal 7 2" xfId="713"/>
+    <cellStyle name="Normal 7 3" xfId="714"/>
+    <cellStyle name="Normal 7 4" xfId="715"/>
+    <cellStyle name="Normal 70" xfId="716"/>
+    <cellStyle name="Normal 71" xfId="717"/>
+    <cellStyle name="Normal 72" xfId="718"/>
+    <cellStyle name="Normal 73" xfId="719"/>
+    <cellStyle name="Normal 74" xfId="720"/>
+    <cellStyle name="Normal 75" xfId="721"/>
+    <cellStyle name="Normal 76" xfId="722"/>
+    <cellStyle name="Normal 77" xfId="723"/>
+    <cellStyle name="Normal 78" xfId="724"/>
+    <cellStyle name="Normal 79" xfId="725"/>
+    <cellStyle name="Normal 79 2" xfId="726"/>
+    <cellStyle name="Normal 79 3" xfId="727"/>
+    <cellStyle name="Normal 8" xfId="728"/>
+    <cellStyle name="Normal 8 2" xfId="729"/>
+    <cellStyle name="Normal 8 3" xfId="730"/>
+    <cellStyle name="Normal 8 4" xfId="731"/>
+    <cellStyle name="Normal 80" xfId="732"/>
+    <cellStyle name="Normal 80 2" xfId="733"/>
+    <cellStyle name="Normal 81" xfId="734"/>
+    <cellStyle name="Normal 81 2" xfId="735"/>
+    <cellStyle name="Normal 82" xfId="736"/>
+    <cellStyle name="Normal 82 2" xfId="737"/>
+    <cellStyle name="Normal 82 2 2" xfId="738"/>
+    <cellStyle name="Normal 83" xfId="739"/>
+    <cellStyle name="Normal 83 2" xfId="740"/>
+    <cellStyle name="Normal 83 2 2" xfId="741"/>
+    <cellStyle name="Normal 84" xfId="742"/>
+    <cellStyle name="Normal 84 2" xfId="743"/>
+    <cellStyle name="Normal 84 3" xfId="744"/>
+    <cellStyle name="Normal 85" xfId="745"/>
+    <cellStyle name="Normal 85 2" xfId="746"/>
+    <cellStyle name="Normal 85 3" xfId="747"/>
+    <cellStyle name="Normal 86" xfId="748"/>
+    <cellStyle name="Normal 86 2" xfId="749"/>
+    <cellStyle name="Normal 86 3" xfId="750"/>
+    <cellStyle name="Normal 87" xfId="751"/>
+    <cellStyle name="Normal 87 2" xfId="752"/>
+    <cellStyle name="Normal 87 3" xfId="753"/>
+    <cellStyle name="Normal 88" xfId="754"/>
+    <cellStyle name="Normal 88 2" xfId="755"/>
+    <cellStyle name="Normal 88 3" xfId="756"/>
+    <cellStyle name="Normal 88 4" xfId="757"/>
+    <cellStyle name="Normal 89" xfId="758"/>
+    <cellStyle name="Normal 9" xfId="759"/>
+    <cellStyle name="Normal 9 2" xfId="760"/>
+    <cellStyle name="Normal 9 3" xfId="761"/>
+    <cellStyle name="Normal 9 4" xfId="762"/>
+    <cellStyle name="Normal 90" xfId="763"/>
+    <cellStyle name="Normal 91" xfId="764"/>
+    <cellStyle name="Normal 92" xfId="765"/>
+    <cellStyle name="Normal 93" xfId="766"/>
+    <cellStyle name="Normal 94" xfId="767"/>
+    <cellStyle name="Normal 94 2" xfId="768"/>
+    <cellStyle name="Normal 95" xfId="769"/>
+    <cellStyle name="Normal 95 2" xfId="770"/>
+    <cellStyle name="Normal 95 3" xfId="771"/>
+    <cellStyle name="Normal 96" xfId="772"/>
+    <cellStyle name="Normal 97" xfId="773"/>
+    <cellStyle name="Normal 97 2" xfId="774"/>
+    <cellStyle name="Normal 98" xfId="775"/>
+    <cellStyle name="Normal 98 2" xfId="776"/>
+    <cellStyle name="Normal 99" xfId="777"/>
+    <cellStyle name="Normal 99 2" xfId="778"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3"/>
+    <cellStyle name="Notas 2" xfId="779"/>
+    <cellStyle name="Notas 2 2" xfId="780"/>
+    <cellStyle name="Notas 2 3" xfId="781"/>
+    <cellStyle name="Notas 3" xfId="782"/>
+    <cellStyle name="Notas 4" xfId="783"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785"/>
+    <cellStyle name="Salida 2" xfId="786"/>
+    <cellStyle name="Salida 3" xfId="787"/>
+    <cellStyle name="Salida 4" xfId="788"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791"/>
+    <cellStyle name="Texto explicativo 2" xfId="792"/>
+    <cellStyle name="Texto explicativo 3" xfId="793"/>
+    <cellStyle name="Texto explicativo 4" xfId="794"/>
+    <cellStyle name="Título 1 2" xfId="795"/>
+    <cellStyle name="Título 2 2" xfId="796"/>
+    <cellStyle name="Título 2 3" xfId="797"/>
+    <cellStyle name="Título 2 4" xfId="798"/>
+    <cellStyle name="Título 3 2" xfId="799"/>
+    <cellStyle name="Título 3 3" xfId="800"/>
+    <cellStyle name="Título 3 4" xfId="801"/>
+    <cellStyle name="Título 4" xfId="802"/>
+    <cellStyle name="Título 5" xfId="803"/>
+    <cellStyle name="Título 6" xfId="804"/>
+    <cellStyle name="Total 2" xfId="806"/>
+    <cellStyle name="Total 3" xfId="807"/>
+    <cellStyle name="Total 4" xfId="808"/>
+    <cellStyle name="Total 5" xfId="805"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2643,25 +2630,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2678,484 +2665,544 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="2" spans="1:8">
+      <c r="A2" s="14">
         <v>46101</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>12581.194</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:8">
+      <c r="A3" s="14">
         <v>46104</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>7000</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:8">
+      <c r="A4" s="14">
         <v>46105</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="14">
         <v>46106</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>31373.66</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.1</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>15</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:8">
+      <c r="A6" s="14">
         <v>46107</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="14">
         <v>46108</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>17816.601900000001</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>15</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:8">
+      <c r="A8" s="14">
         <v>46111</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="14">
         <v>46112</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="14">
         <v>46113</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="14">
         <v>46118</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>2034.26</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>90</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>100</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="1">
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:8">
+      <c r="A12" s="14">
         <v>46119</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>2105.5</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>100</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>101</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="1">
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13" spans="1:8">
+      <c r="A13" s="14">
         <v>46120</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>3874.3249999999998</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>100</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>110</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="1">
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:8">
+      <c r="A14" s="14">
         <v>46121</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>5291.1750000000002</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>120</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>120</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:8">
+      <c r="A15" s="14">
         <v>46122</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>8851</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>35</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="1">
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16" spans="1:8">
+      <c r="A16" s="14">
         <v>46125</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="14">
         <v>46126</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="14">
         <v>46127</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="14">
         <v>46128</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="14">
         <v>46129</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="14">
         <v>46132</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="14">
         <v>46133</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="14">
         <v>46134</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>300</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>100</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>140</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24" spans="1:8">
+      <c r="A24" s="14">
         <v>46135</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>38366.589999999997</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>100</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>100.01</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25" spans="1:8">
+      <c r="A25" s="14">
         <v>46136</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>146.97</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>35</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>35</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26" spans="1:8">
+      <c r="A26" s="14">
         <v>46139</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="14">
         <v>46140</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="14">
         <v>46141</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="14">
         <v>46142</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18">
+      <c r="C29" s="15"/>
+      <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18">
+      <c r="E29" s="15"/>
+      <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19">
+      <c r="G29" s="15"/>
+      <c r="H29" s="1">
         <v>18.43</v>
       </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="14">
+        <v>46146</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="17"/>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3164,17 +3211,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3188,8 +3235,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+    <row r="2" spans="1:5">
+      <c r="A2" s="11">
         <v>46142</v>
       </c>
       <c r="B2">
@@ -3198,12 +3245,12 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="12">
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+    <row r="3" spans="1:5">
+      <c r="A3" s="11">
         <v>46141</v>
       </c>
       <c r="B3">
@@ -3212,12 +3259,12 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="12">
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:5">
+      <c r="A4" s="11">
         <v>46140</v>
       </c>
       <c r="B4">
@@ -3226,12 +3273,12 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="13">
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+    <row r="5" spans="1:5">
+      <c r="A5" s="11">
         <v>46139</v>
       </c>
       <c r="B5">
@@ -3240,152 +3287,160 @@
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="13">
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+    <row r="6" spans="1:5">
+      <c r="A6" s="11">
         <v>46136</v>
       </c>
       <c r="B6">
         <v>60973.651931649998</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+    <row r="7" spans="1:5">
+      <c r="A7" s="11">
         <v>46135</v>
       </c>
       <c r="B7">
         <v>4652.1817311200002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+    <row r="8" spans="1:5">
+      <c r="A8" s="11">
         <v>46134</v>
       </c>
       <c r="B8">
         <v>17251.00486529</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+    <row r="9" spans="1:5">
+      <c r="A9" s="11">
         <v>46133</v>
       </c>
       <c r="B9">
         <v>47981.781644150004</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+    <row r="10" spans="1:5">
+      <c r="A10" s="11">
         <v>46132</v>
       </c>
       <c r="B10">
         <v>51339.49161813</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+    <row r="11" spans="1:5">
+      <c r="A11" s="11">
         <v>46129</v>
       </c>
       <c r="B11">
         <v>17216.492596060001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+    <row r="12" spans="1:5">
+      <c r="A12" s="11">
         <v>46128</v>
       </c>
       <c r="B12">
         <v>18.890111640000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+    <row r="13" spans="1:5">
+      <c r="A13" s="11">
         <v>46127</v>
       </c>
       <c r="B13">
         <v>15.79809785</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+    <row r="14" spans="1:5">
+      <c r="A14" s="11">
         <v>46126</v>
       </c>
       <c r="B14">
         <v>16.215898760000002</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
+    <row r="15" spans="1:5">
+      <c r="A15" s="11">
         <v>46125</v>
       </c>
       <c r="B15">
         <v>2475.4322626600001</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+    <row r="16" spans="1:5">
+      <c r="A16" s="11">
         <v>46122</v>
       </c>
       <c r="B16">
         <v>7956.2858669899997</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+    <row r="17" spans="1:2">
+      <c r="A17" s="11">
         <v>46121</v>
       </c>
       <c r="B17">
         <v>41.536584740000002</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+    <row r="18" spans="1:2">
+      <c r="A18" s="11">
         <v>46120</v>
       </c>
       <c r="B18">
         <v>580.56056466999996</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+    <row r="19" spans="1:2">
+      <c r="A19" s="11">
         <v>46119</v>
       </c>
       <c r="B19">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+    <row r="20" spans="1:2">
+      <c r="A20" s="11">
         <v>46118</v>
       </c>
       <c r="B20">
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+    <row r="21" spans="1:2">
+      <c r="A21" s="11">
         <v>46113</v>
       </c>
       <c r="B21">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+    <row r="22" spans="1:2">
+      <c r="A22" s="11">
         <v>46112</v>
       </c>
       <c r="B22">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+    <row r="23" spans="1:2">
+      <c r="A23" s="11">
         <v>46111</v>
       </c>
       <c r="B23">
         <v>22969.58967849</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B24">
+        <v>49567.396050169998</v>
       </c>
     </row>
   </sheetData>
@@ -3395,17 +3450,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3419,78 +3474,79 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="1">
         <v>233000.41606600001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>12263.179792947369</v>
       </c>
       <c r="D2">
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="1">
         <v>222685.80931400001</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>12371.433850777779</v>
       </c>
       <c r="D3">
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="1">
         <v>217064.39708600001</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>10336.399861238096</v>
       </c>
       <c r="D4">
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>98931.490865999993</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="18">
-        <v>64.08</v>
+      <c r="D5" s="16">
+        <v>64.09</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3501,155 +3557,155 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2" spans="1:3">
+      <c r="A2" s="2">
         <v>46024</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="1">
         <v>680053310.5984205</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
         <v>46031</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="1">
         <v>631055414.05422926</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="4">
         <v>-7.2050081634151608E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
         <v>46038</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="1">
         <v>687738190.99875975</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>8.9822186264706616E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
         <v>46045</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>728876050.32802963</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>5.9816162411350016E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
         <v>46052</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="1">
         <v>839643409.76085114</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>0.15197009063882794</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+    <row r="7" spans="1:3">
+      <c r="A7" s="2">
         <v>46059</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="1">
         <v>818274973.23848069</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>-2.5449418495950171E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+    <row r="8" spans="1:3" ht="15" thickBot="1">
+      <c r="A8" s="2">
         <v>46066</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="1">
         <v>801808360.23688257</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
         <v>-2.0123569142568742E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+    <row r="9" spans="1:3">
+      <c r="A9" s="2">
         <v>46073</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="1">
         <v>886542333.87268889</v>
       </c>
-      <c r="C9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2">
         <v>46080</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="1">
         <v>938549580.20021927</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="7">
         <v>5.8663015109889693E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
         <v>46087</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="1">
         <v>870061809.65898001</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <v>-7.2971926029340772E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
         <v>46094</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="1">
         <v>959597484.45129991</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="7">
         <v>0.10290725762048258</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+    <row r="13" spans="1:3">
+      <c r="A13" s="2">
         <v>46101</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="1">
         <v>1136404345.7909815</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="7">
         <v>0.18425106797854962</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="A14" s="2">
         <v>46108</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="1">
         <v>1111572721.2404912</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>-2.1851046806061425E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="2">
         <v>46129</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="1">
         <v>1071533894.2527295</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <f>+(B15-B14)/B14</f>
         <v>-3.6019979820194892E-2</v>
       </c>
@@ -3660,21 +3716,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.75" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3700,133 +3756,133 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
         <v>46108</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="1">
         <v>51894238.144249998</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>1352008822.1469994</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>114591064.00208002</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="1">
         <v>1518494124.2933292</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="1">
         <v>1312229.331</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="H2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
         <v>46115</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="1">
         <v>53037714.146710016</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>1339307607.9621801</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>104752190.86271001</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="1">
         <v>1497097512.9716001</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>1329047.3089199997</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="9">
         <v>-1.4067445693212388E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
         <v>46122</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="1">
         <v>51300407.269250013</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>1366557520.0739398</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="1">
         <v>93957855.953770012</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="1">
         <v>1511815783.2969596</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="1">
         <v>1230831.7066299999</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="9">
         <v>9.7569377843467198E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
         <v>46129</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>52072039.455540009</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>1390532008.0185997</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>121700977.86743999</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="1">
         <v>1564305025.3415797</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>1318474.4970099996</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="9">
         <v>3.4749018512476804E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
         <v>46136</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="1">
         <v>55330466.694130011</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>1431208791.1130197</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>124915732.49143001</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="1">
         <v>1611454990.2985797</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="1">
         <v>1367165.0341699999</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="9">
         <v>3.0099999999999998E-2</v>
       </c>
     </row>
@@ -3836,19 +3892,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3868,8 +3924,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
         <v>46108</v>
       </c>
       <c r="B2">
@@ -3881,15 +3937,15 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="18">
         <v>-2.681224004753413E-2</v>
       </c>
-      <c r="F2" s="13">
-        <v>-2.681224004753413E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="F2" s="10">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
         <v>46113</v>
       </c>
       <c r="B3">
@@ -3904,12 +3960,12 @@
       <c r="E3">
         <v>4.8691139433717501E-2</v>
       </c>
-      <c r="F3" s="13">
-        <v>4.8691139433717501E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="F3" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
         <v>46122</v>
       </c>
       <c r="B4">
@@ -3924,12 +3980,12 @@
       <c r="E4">
         <v>-1.1061785896222975E-2</v>
       </c>
-      <c r="F4" s="13">
-        <v>-1.1061785896222975E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="F4" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
         <v>46129</v>
       </c>
       <c r="B5">
@@ -3944,12 +4000,12 @@
       <c r="E5">
         <v>6.2550592390904214E-3</v>
       </c>
-      <c r="F5" s="13">
-        <v>6.2550592390904214E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="F5" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
         <v>46136</v>
       </c>
       <c r="B6">
@@ -3964,12 +4020,12 @@
       <c r="E6">
         <v>-1.3894983179757237E-2</v>
       </c>
-      <c r="F6" s="13">
-        <v>-1.3894983179757237E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="F6" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
         <v>46139</v>
       </c>
       <c r="B7">
@@ -3985,12 +4041,12 @@
         <f>+(D7-D8)/D8</f>
         <v>1.5619105108277371E-2</v>
       </c>
-      <c r="F7" s="13">
-        <v>-1.3894983179757237E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="F7" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
         <v>46140</v>
       </c>
       <c r="B8">
@@ -4006,12 +4062,12 @@
         <f>+(D8-D9)/D9</f>
         <v>5.0049290968377947E-3</v>
       </c>
-      <c r="F8" s="13">
-        <v>-1.3894983179757237E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="F8" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
         <v>46141</v>
       </c>
       <c r="B9">
@@ -4027,8 +4083,29 @@
         <f>+(D9-D6)/D6</f>
         <v>-2.2026105013349156E-2</v>
       </c>
-      <c r="F9" s="13">
-        <v>-1.3894983179757237E-2</v>
+      <c r="F9" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B10">
+        <v>13277</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>13280</v>
+      </c>
+      <c r="E10">
+        <f>+(D10-D7)/D7</f>
+        <v>-1.3372956909361069E-2</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819"/>
+    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2630,7 +2630,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3212,7 +3212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3236,11 +3236,11 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="11">
-        <v>46142</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="11">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B3">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="11">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B4">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B5">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -3293,155 +3293,158 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B6">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B7">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B8">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B9">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B10">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B11">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="11">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B12">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B13">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B14">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B15">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B16">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="11">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B18">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B19">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="11">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B20">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B21">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B22">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B23">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="11">
         <v>46111</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>22969.58967849</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2">
-        <v>46146</v>
-      </c>
-      <c r="B24">
-        <v>49567.396050169998</v>
-      </c>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1320" windowWidth="16200" windowHeight="9300" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -3164,6 +3164,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="14">
+        <v>46147</v>
+      </c>
+      <c r="B31" s="1">
+        <v>39236.082000000002</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="1">
+        <v>100</v>
+      </c>
+      <c r="G31" s="17"/>
+      <c r="H31" s="1">
+        <v>100</v>
+      </c>
+    </row>
     <row r="33" spans="1:8">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
@@ -3212,7 +3232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3237,10 +3257,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B2">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -3250,11 +3270,11 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11">
-        <v>46142</v>
+      <c r="A3" s="2">
+        <v>46146</v>
       </c>
       <c r="B3">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -3265,10 +3285,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="11">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B4">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -3279,10 +3299,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B5">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -3293,158 +3313,166 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B6">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B7">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B8">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B9">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B10">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B11">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="11">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B12">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B13">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B14">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B15">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B16">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="11">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B18">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B19">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="11">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B20">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B21">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B22">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B23">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B24">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="11">
         <v>46111</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>22969.58967849</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2"/>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3896,7 +3924,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4111,6 +4139,27 @@
         <v>-0.01</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B11">
+        <v>14058</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>14061</v>
+      </c>
+      <c r="E11">
+        <f>+(D11-D8)/D8</f>
+        <v>6.0967328152116501E-2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1453,7 +1453,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1488,13 +1488,20 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="810">
     <cellStyle name="20% - Énfasis1 2" xfId="4"/>
@@ -2630,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2641,7 +2648,7 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="19" customWidth="1"/>
     <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
@@ -2649,7 +2656,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2666,7 +2673,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
+      <c r="A2" s="18">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -2683,7 +2690,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="14">
+      <c r="A3" s="18">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -2700,7 +2707,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="14">
+      <c r="A4" s="18">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -2717,7 +2724,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="14">
+      <c r="A5" s="18">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -2734,7 +2741,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="14">
+      <c r="A6" s="18">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -2751,7 +2758,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="14">
+      <c r="A7" s="18">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -2768,7 +2775,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="14">
+      <c r="A8" s="18">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -2785,7 +2792,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="14">
+      <c r="A9" s="18">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -2802,7 +2809,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="14">
+      <c r="A10" s="18">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -2819,7 +2826,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="14">
+      <c r="A11" s="18">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -2836,7 +2843,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="14">
+      <c r="A12" s="18">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -2853,7 +2860,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="14">
+      <c r="A13" s="18">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -2870,7 +2877,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="14">
+      <c r="A14" s="18">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -2887,7 +2894,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="14">
+      <c r="A15" s="18">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -2904,7 +2911,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="14">
+      <c r="A16" s="18">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -2921,7 +2928,7 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="14">
+      <c r="A17" s="18">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -2938,7 +2945,7 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="14">
+      <c r="A18" s="18">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -2955,7 +2962,7 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="14">
+      <c r="A19" s="18">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -2972,7 +2979,7 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="14">
+      <c r="A20" s="18">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -2989,7 +2996,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="14">
+      <c r="A21" s="18">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -3006,7 +3013,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="14">
+      <c r="A22" s="18">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -3023,7 +3030,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="14">
+      <c r="A23" s="18">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3040,7 +3047,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="14">
+      <c r="A24" s="18">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3057,7 +3064,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="14">
+      <c r="A25" s="18">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3074,7 +3081,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="14">
+      <c r="A26" s="18">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3091,7 +3098,7 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="14">
+      <c r="A27" s="18">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3108,7 +3115,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="14">
+      <c r="A28" s="18">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3125,103 +3132,123 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="14">
+      <c r="A29" s="18">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="15"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="15"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="15"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="1">
         <v>18.43</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="14">
+      <c r="A30" s="18">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="17"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="17"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="14">
+      <c r="A31" s="18">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="17"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="18">
+        <v>46148</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="1">
+        <v>100</v>
+      </c>
+      <c r="G32" s="16"/>
+      <c r="H32" s="1">
+        <v>100</v>
+      </c>
+    </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="2"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="17"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="17"/>
+      <c r="E36" s="16"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="17"/>
+      <c r="G36" s="16"/>
       <c r="H36" s="1"/>
     </row>
   </sheetData>
@@ -3257,10 +3284,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B2">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -3271,10 +3298,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B3">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -3284,11 +3311,11 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11">
-        <v>46142</v>
+      <c r="A4" s="2">
+        <v>46146</v>
       </c>
       <c r="B4">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -3299,10 +3326,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B5">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -3313,166 +3340,171 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B6">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B7">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B8">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B9">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B10">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B11">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="11">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B12">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B13">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B14">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B15">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B16">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="11">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B18">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="11">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B19">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="11">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B20">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="11">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B21">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="11">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B22">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="11">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B23">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="11">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B24">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B25">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="11">
         <v>46111</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>22969.58967849</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3557,7 +3589,7 @@
       <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>64.09</v>
       </c>
     </row>
@@ -3924,7 +3956,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -3968,7 +4000,7 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <v>-2.681224004753413E-2</v>
       </c>
       <c r="F2" s="10">
@@ -4157,6 +4189,27 @@
         <v>6.0967328152116501E-2</v>
       </c>
       <c r="F11" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B12" s="21">
+        <v>13869</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="21">
+        <v>13872</v>
+      </c>
+      <c r="E12">
+        <f>+(D12-D9)/D9</f>
+        <v>5.1945097444452873E-2</v>
+      </c>
+      <c r="F12" s="10">
         <v>-0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2637,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2637,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C5BFA2-57D2-488A-85AA-445E28DB294A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>DÍA</t>
   </si>
@@ -136,8 +142,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
@@ -145,9 +151,8 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="170" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,7 +442,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -450,49 +455,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -719,15 +681,15 @@
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -749,9 +711,9 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1421,61 +1383,46 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1491,7 +1438,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1502,818 +1448,830 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="810">
-    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
-    <cellStyle name="Buena 2" xfId="74"/>
-    <cellStyle name="Buena 3" xfId="75"/>
-    <cellStyle name="Buena 4" xfId="76"/>
-    <cellStyle name="Cálculo 2" xfId="77"/>
-    <cellStyle name="Cálculo 3" xfId="78"/>
-    <cellStyle name="Cálculo 4" xfId="79"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82"/>
-    <cellStyle name="Celda vinculada 2" xfId="83"/>
-    <cellStyle name="Celda vinculada 3" xfId="84"/>
-    <cellStyle name="Celda vinculada 4" xfId="85"/>
-    <cellStyle name="Comma 2" xfId="121"/>
-    <cellStyle name="Encabezado 4 2" xfId="86"/>
-    <cellStyle name="Encabezado 4 3" xfId="87"/>
-    <cellStyle name="Encabezado 4 4" xfId="88"/>
-    <cellStyle name="Énfasis1 2" xfId="89"/>
-    <cellStyle name="Énfasis1 3" xfId="90"/>
-    <cellStyle name="Énfasis1 4" xfId="91"/>
-    <cellStyle name="Énfasis2 2" xfId="92"/>
-    <cellStyle name="Énfasis2 3" xfId="93"/>
-    <cellStyle name="Énfasis2 4" xfId="94"/>
-    <cellStyle name="Énfasis3 2" xfId="95"/>
-    <cellStyle name="Énfasis3 3" xfId="96"/>
-    <cellStyle name="Énfasis3 4" xfId="97"/>
-    <cellStyle name="Énfasis4 2" xfId="98"/>
-    <cellStyle name="Énfasis4 3" xfId="99"/>
-    <cellStyle name="Énfasis4 4" xfId="100"/>
-    <cellStyle name="Énfasis5 2" xfId="101"/>
-    <cellStyle name="Énfasis5 3" xfId="102"/>
-    <cellStyle name="Énfasis5 4" xfId="103"/>
-    <cellStyle name="Énfasis6 2" xfId="104"/>
-    <cellStyle name="Énfasis6 3" xfId="105"/>
-    <cellStyle name="Énfasis6 4" xfId="106"/>
-    <cellStyle name="Entrada 2" xfId="107"/>
-    <cellStyle name="Entrada 3" xfId="108"/>
-    <cellStyle name="Entrada 4" xfId="109"/>
-    <cellStyle name="Euro" xfId="110"/>
-    <cellStyle name="Euro 2" xfId="111"/>
-    <cellStyle name="Euro 2 2" xfId="112"/>
-    <cellStyle name="Euro 2 3" xfId="113"/>
-    <cellStyle name="Euro 2 4" xfId="114"/>
-    <cellStyle name="Euro 3" xfId="115"/>
-    <cellStyle name="Euro 4" xfId="116"/>
-    <cellStyle name="Euro 5" xfId="117"/>
-    <cellStyle name="Incorrecto 2" xfId="118"/>
-    <cellStyle name="Incorrecto 3" xfId="119"/>
-    <cellStyle name="Incorrecto 4" xfId="120"/>
-    <cellStyle name="Millares 10" xfId="122"/>
-    <cellStyle name="Millares 2" xfId="123"/>
-    <cellStyle name="Millares 2 2" xfId="124"/>
-    <cellStyle name="Millares 2 2 2" xfId="125"/>
-    <cellStyle name="Millares 2 3" xfId="126"/>
-    <cellStyle name="Millares 2 4" xfId="127"/>
-    <cellStyle name="Millares 3" xfId="128"/>
-    <cellStyle name="Millares 3 10" xfId="129"/>
-    <cellStyle name="Millares 3 100" xfId="130"/>
-    <cellStyle name="Millares 3 101" xfId="131"/>
-    <cellStyle name="Millares 3 102" xfId="132"/>
-    <cellStyle name="Millares 3 103" xfId="133"/>
-    <cellStyle name="Millares 3 103 2" xfId="134"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
-    <cellStyle name="Millares 3 104" xfId="136"/>
-    <cellStyle name="Millares 3 11" xfId="137"/>
-    <cellStyle name="Millares 3 12" xfId="138"/>
-    <cellStyle name="Millares 3 13" xfId="139"/>
-    <cellStyle name="Millares 3 14" xfId="140"/>
-    <cellStyle name="Millares 3 15" xfId="141"/>
-    <cellStyle name="Millares 3 16" xfId="142"/>
-    <cellStyle name="Millares 3 17" xfId="143"/>
-    <cellStyle name="Millares 3 18" xfId="144"/>
-    <cellStyle name="Millares 3 19" xfId="145"/>
-    <cellStyle name="Millares 3 2" xfId="146"/>
-    <cellStyle name="Millares 3 2 2" xfId="147"/>
-    <cellStyle name="Millares 3 2 3" xfId="148"/>
-    <cellStyle name="Millares 3 20" xfId="149"/>
-    <cellStyle name="Millares 3 21" xfId="150"/>
-    <cellStyle name="Millares 3 22" xfId="151"/>
-    <cellStyle name="Millares 3 23" xfId="152"/>
-    <cellStyle name="Millares 3 24" xfId="153"/>
-    <cellStyle name="Millares 3 25" xfId="154"/>
-    <cellStyle name="Millares 3 26" xfId="155"/>
-    <cellStyle name="Millares 3 27" xfId="156"/>
-    <cellStyle name="Millares 3 28" xfId="157"/>
-    <cellStyle name="Millares 3 29" xfId="158"/>
-    <cellStyle name="Millares 3 3" xfId="159"/>
-    <cellStyle name="Millares 3 30" xfId="160"/>
-    <cellStyle name="Millares 3 31" xfId="161"/>
-    <cellStyle name="Millares 3 32" xfId="162"/>
-    <cellStyle name="Millares 3 33" xfId="163"/>
-    <cellStyle name="Millares 3 34" xfId="164"/>
-    <cellStyle name="Millares 3 35" xfId="165"/>
-    <cellStyle name="Millares 3 36" xfId="166"/>
-    <cellStyle name="Millares 3 37" xfId="167"/>
-    <cellStyle name="Millares 3 38" xfId="168"/>
-    <cellStyle name="Millares 3 39" xfId="169"/>
-    <cellStyle name="Millares 3 4" xfId="170"/>
-    <cellStyle name="Millares 3 40" xfId="171"/>
-    <cellStyle name="Millares 3 41" xfId="172"/>
-    <cellStyle name="Millares 3 42" xfId="173"/>
-    <cellStyle name="Millares 3 43" xfId="174"/>
-    <cellStyle name="Millares 3 44" xfId="175"/>
-    <cellStyle name="Millares 3 45" xfId="176"/>
-    <cellStyle name="Millares 3 46" xfId="177"/>
-    <cellStyle name="Millares 3 47" xfId="178"/>
-    <cellStyle name="Millares 3 48" xfId="179"/>
-    <cellStyle name="Millares 3 49" xfId="180"/>
-    <cellStyle name="Millares 3 5" xfId="181"/>
-    <cellStyle name="Millares 3 50" xfId="182"/>
-    <cellStyle name="Millares 3 51" xfId="183"/>
-    <cellStyle name="Millares 3 52" xfId="184"/>
-    <cellStyle name="Millares 3 53" xfId="185"/>
-    <cellStyle name="Millares 3 54" xfId="186"/>
-    <cellStyle name="Millares 3 55" xfId="187"/>
-    <cellStyle name="Millares 3 56" xfId="188"/>
-    <cellStyle name="Millares 3 57" xfId="189"/>
-    <cellStyle name="Millares 3 58" xfId="190"/>
-    <cellStyle name="Millares 3 59" xfId="191"/>
-    <cellStyle name="Millares 3 6" xfId="192"/>
-    <cellStyle name="Millares 3 60" xfId="193"/>
-    <cellStyle name="Millares 3 61" xfId="194"/>
-    <cellStyle name="Millares 3 62" xfId="195"/>
-    <cellStyle name="Millares 3 63" xfId="196"/>
-    <cellStyle name="Millares 3 64" xfId="197"/>
-    <cellStyle name="Millares 3 65" xfId="198"/>
-    <cellStyle name="Millares 3 66" xfId="199"/>
-    <cellStyle name="Millares 3 67" xfId="200"/>
-    <cellStyle name="Millares 3 68" xfId="201"/>
-    <cellStyle name="Millares 3 69" xfId="202"/>
-    <cellStyle name="Millares 3 7" xfId="203"/>
-    <cellStyle name="Millares 3 70" xfId="204"/>
-    <cellStyle name="Millares 3 71" xfId="205"/>
-    <cellStyle name="Millares 3 72" xfId="206"/>
-    <cellStyle name="Millares 3 73" xfId="207"/>
-    <cellStyle name="Millares 3 74" xfId="208"/>
-    <cellStyle name="Millares 3 75" xfId="209"/>
-    <cellStyle name="Millares 3 76" xfId="210"/>
-    <cellStyle name="Millares 3 77" xfId="211"/>
-    <cellStyle name="Millares 3 78" xfId="212"/>
-    <cellStyle name="Millares 3 79" xfId="213"/>
-    <cellStyle name="Millares 3 8" xfId="214"/>
-    <cellStyle name="Millares 3 80" xfId="215"/>
-    <cellStyle name="Millares 3 81" xfId="216"/>
-    <cellStyle name="Millares 3 82" xfId="217"/>
-    <cellStyle name="Millares 3 83" xfId="218"/>
-    <cellStyle name="Millares 3 84" xfId="219"/>
-    <cellStyle name="Millares 3 85" xfId="220"/>
-    <cellStyle name="Millares 3 86" xfId="221"/>
-    <cellStyle name="Millares 3 87" xfId="222"/>
-    <cellStyle name="Millares 3 88" xfId="223"/>
-    <cellStyle name="Millares 3 89" xfId="224"/>
-    <cellStyle name="Millares 3 9" xfId="225"/>
-    <cellStyle name="Millares 3 90" xfId="226"/>
-    <cellStyle name="Millares 3 91" xfId="227"/>
-    <cellStyle name="Millares 3 92" xfId="228"/>
-    <cellStyle name="Millares 3 93" xfId="229"/>
-    <cellStyle name="Millares 3 94" xfId="230"/>
-    <cellStyle name="Millares 3 95" xfId="231"/>
-    <cellStyle name="Millares 3 96" xfId="232"/>
-    <cellStyle name="Millares 3 97" xfId="233"/>
-    <cellStyle name="Millares 3 98" xfId="234"/>
-    <cellStyle name="Millares 3 99" xfId="235"/>
-    <cellStyle name="Millares 4" xfId="236"/>
-    <cellStyle name="Millares 4 2" xfId="237"/>
-    <cellStyle name="Millares 5" xfId="238"/>
-    <cellStyle name="Millares 5 2" xfId="239"/>
-    <cellStyle name="Millares 5 3" xfId="240"/>
-    <cellStyle name="Millares 6" xfId="241"/>
-    <cellStyle name="Millares 6 2" xfId="242"/>
-    <cellStyle name="Millares 6 3" xfId="243"/>
-    <cellStyle name="Millares 7" xfId="244"/>
-    <cellStyle name="Millares 8" xfId="245"/>
-    <cellStyle name="Millares 8 2" xfId="246"/>
-    <cellStyle name="Millares 9" xfId="247"/>
-    <cellStyle name="Neutral 2" xfId="249"/>
-    <cellStyle name="Neutral 3" xfId="250"/>
-    <cellStyle name="Neutral 4" xfId="251"/>
-    <cellStyle name="Neutral 5" xfId="248"/>
-    <cellStyle name="NivelFila_3 2" xfId="809"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252"/>
-    <cellStyle name="Normal 10 2" xfId="253"/>
-    <cellStyle name="Normal 10 3" xfId="254"/>
-    <cellStyle name="Normal 10 4" xfId="255"/>
-    <cellStyle name="Normal 100" xfId="256"/>
-    <cellStyle name="Normal 100 2" xfId="257"/>
-    <cellStyle name="Normal 101" xfId="258"/>
-    <cellStyle name="Normal 101 2" xfId="259"/>
-    <cellStyle name="Normal 102" xfId="260"/>
-    <cellStyle name="Normal 102 2" xfId="261"/>
-    <cellStyle name="Normal 103" xfId="262"/>
-    <cellStyle name="Normal 103 2" xfId="263"/>
-    <cellStyle name="Normal 104" xfId="264"/>
-    <cellStyle name="Normal 104 2" xfId="265"/>
-    <cellStyle name="Normal 104 3" xfId="266"/>
-    <cellStyle name="Normal 105" xfId="267"/>
-    <cellStyle name="Normal 106" xfId="268"/>
-    <cellStyle name="Normal 106 2" xfId="269"/>
-    <cellStyle name="Normal 106 3" xfId="270"/>
-    <cellStyle name="Normal 107" xfId="271"/>
-    <cellStyle name="Normal 107 2" xfId="272"/>
-    <cellStyle name="Normal 108" xfId="273"/>
-    <cellStyle name="Normal 109" xfId="274"/>
-    <cellStyle name="Normal 11" xfId="275"/>
-    <cellStyle name="Normal 11 2" xfId="276"/>
-    <cellStyle name="Normal 11 3" xfId="277"/>
-    <cellStyle name="Normal 11 4" xfId="278"/>
-    <cellStyle name="Normal 110" xfId="279"/>
-    <cellStyle name="Normal 111" xfId="280"/>
-    <cellStyle name="Normal 112" xfId="281"/>
-    <cellStyle name="Normal 112 2" xfId="282"/>
-    <cellStyle name="Normal 113" xfId="283"/>
-    <cellStyle name="Normal 113 2" xfId="284"/>
-    <cellStyle name="Normal 114" xfId="285"/>
-    <cellStyle name="Normal 114 2" xfId="286"/>
-    <cellStyle name="Normal 115" xfId="287"/>
-    <cellStyle name="Normal 115 2" xfId="288"/>
-    <cellStyle name="Normal 116" xfId="289"/>
-    <cellStyle name="Normal 116 2" xfId="290"/>
-    <cellStyle name="Normal 116 3" xfId="291"/>
-    <cellStyle name="Normal 117" xfId="292"/>
-    <cellStyle name="Normal 117 2" xfId="293"/>
-    <cellStyle name="Normal 118" xfId="294"/>
-    <cellStyle name="Normal 118 2" xfId="295"/>
-    <cellStyle name="Normal 118 3" xfId="296"/>
-    <cellStyle name="Normal 119" xfId="297"/>
-    <cellStyle name="Normal 119 2" xfId="298"/>
-    <cellStyle name="Normal 119 3" xfId="299"/>
-    <cellStyle name="Normal 12" xfId="300"/>
-    <cellStyle name="Normal 12 2" xfId="301"/>
-    <cellStyle name="Normal 12 3" xfId="302"/>
-    <cellStyle name="Normal 12 4" xfId="303"/>
-    <cellStyle name="Normal 120" xfId="304"/>
-    <cellStyle name="Normal 120 2" xfId="305"/>
-    <cellStyle name="Normal 121" xfId="306"/>
-    <cellStyle name="Normal 121 2" xfId="307"/>
-    <cellStyle name="Normal 122" xfId="308"/>
-    <cellStyle name="Normal 122 2" xfId="309"/>
-    <cellStyle name="Normal 123" xfId="310"/>
-    <cellStyle name="Normal 124" xfId="311"/>
-    <cellStyle name="Normal 124 2" xfId="312"/>
-    <cellStyle name="Normal 125" xfId="313"/>
-    <cellStyle name="Normal 125 2" xfId="314"/>
-    <cellStyle name="Normal 126" xfId="315"/>
-    <cellStyle name="Normal 127" xfId="316"/>
-    <cellStyle name="Normal 127 2" xfId="317"/>
-    <cellStyle name="Normal 128" xfId="318"/>
-    <cellStyle name="Normal 129" xfId="319"/>
-    <cellStyle name="Normal 13" xfId="320"/>
-    <cellStyle name="Normal 13 2" xfId="321"/>
-    <cellStyle name="Normal 13 3" xfId="322"/>
-    <cellStyle name="Normal 13 4" xfId="323"/>
-    <cellStyle name="Normal 130" xfId="324"/>
-    <cellStyle name="Normal 130 2" xfId="325"/>
-    <cellStyle name="Normal 131" xfId="326"/>
-    <cellStyle name="Normal 131 2" xfId="327"/>
-    <cellStyle name="Normal 132" xfId="328"/>
-    <cellStyle name="Normal 132 2" xfId="329"/>
-    <cellStyle name="Normal 133" xfId="330"/>
-    <cellStyle name="Normal 133 2" xfId="331"/>
-    <cellStyle name="Normal 134" xfId="332"/>
-    <cellStyle name="Normal 135" xfId="333"/>
-    <cellStyle name="Normal 135 2" xfId="334"/>
-    <cellStyle name="Normal 136" xfId="335"/>
-    <cellStyle name="Normal 136 2" xfId="336"/>
-    <cellStyle name="Normal 137" xfId="337"/>
-    <cellStyle name="Normal 137 2" xfId="338"/>
-    <cellStyle name="Normal 138" xfId="339"/>
-    <cellStyle name="Normal 138 2" xfId="340"/>
-    <cellStyle name="Normal 139" xfId="341"/>
-    <cellStyle name="Normal 139 2" xfId="342"/>
-    <cellStyle name="Normal 14" xfId="343"/>
-    <cellStyle name="Normal 14 2" xfId="344"/>
-    <cellStyle name="Normal 14 3" xfId="345"/>
-    <cellStyle name="Normal 14 4" xfId="346"/>
-    <cellStyle name="Normal 140" xfId="347"/>
-    <cellStyle name="Normal 140 2" xfId="348"/>
-    <cellStyle name="Normal 141" xfId="349"/>
-    <cellStyle name="Normal 142" xfId="350"/>
-    <cellStyle name="Normal 142 2" xfId="351"/>
-    <cellStyle name="Normal 143" xfId="352"/>
-    <cellStyle name="Normal 143 2" xfId="353"/>
-    <cellStyle name="Normal 143 3" xfId="354"/>
-    <cellStyle name="Normal 144" xfId="355"/>
-    <cellStyle name="Normal 144 2" xfId="356"/>
-    <cellStyle name="Normal 145" xfId="357"/>
-    <cellStyle name="Normal 145 2" xfId="358"/>
-    <cellStyle name="Normal 146" xfId="359"/>
-    <cellStyle name="Normal 147" xfId="360"/>
-    <cellStyle name="Normal 15" xfId="361"/>
-    <cellStyle name="Normal 15 2" xfId="362"/>
-    <cellStyle name="Normal 15 3" xfId="363"/>
-    <cellStyle name="Normal 15 4" xfId="364"/>
-    <cellStyle name="Normal 16" xfId="365"/>
-    <cellStyle name="Normal 16 2" xfId="366"/>
-    <cellStyle name="Normal 16 3" xfId="367"/>
-    <cellStyle name="Normal 16 4" xfId="368"/>
-    <cellStyle name="Normal 17" xfId="369"/>
-    <cellStyle name="Normal 17 2" xfId="370"/>
-    <cellStyle name="Normal 17 3" xfId="371"/>
-    <cellStyle name="Normal 17 4" xfId="372"/>
-    <cellStyle name="Normal 18" xfId="373"/>
-    <cellStyle name="Normal 18 2" xfId="374"/>
-    <cellStyle name="Normal 18 3" xfId="375"/>
-    <cellStyle name="Normal 18 4" xfId="376"/>
-    <cellStyle name="Normal 19" xfId="377"/>
-    <cellStyle name="Normal 19 2" xfId="378"/>
-    <cellStyle name="Normal 19 3" xfId="379"/>
-    <cellStyle name="Normal 19 4" xfId="380"/>
-    <cellStyle name="Normal 2" xfId="381"/>
-    <cellStyle name="Normal 2 10" xfId="382"/>
-    <cellStyle name="Normal 2 100" xfId="383"/>
-    <cellStyle name="Normal 2 101" xfId="384"/>
-    <cellStyle name="Normal 2 102" xfId="385"/>
-    <cellStyle name="Normal 2 103" xfId="386"/>
-    <cellStyle name="Normal 2 103 2" xfId="387"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
-    <cellStyle name="Normal 2 104" xfId="389"/>
-    <cellStyle name="Normal 2 104 2" xfId="390"/>
-    <cellStyle name="Normal 2 105" xfId="391"/>
-    <cellStyle name="Normal 2 105 2" xfId="392"/>
-    <cellStyle name="Normal 2 106" xfId="393"/>
-    <cellStyle name="Normal 2 106 2" xfId="394"/>
-    <cellStyle name="Normal 2 106 3" xfId="395"/>
-    <cellStyle name="Normal 2 107" xfId="396"/>
-    <cellStyle name="Normal 2 107 2" xfId="397"/>
-    <cellStyle name="Normal 2 108" xfId="398"/>
-    <cellStyle name="Normal 2 108 2" xfId="399"/>
-    <cellStyle name="Normal 2 109" xfId="400"/>
-    <cellStyle name="Normal 2 109 2" xfId="401"/>
-    <cellStyle name="Normal 2 11" xfId="402"/>
-    <cellStyle name="Normal 2 110" xfId="403"/>
-    <cellStyle name="Normal 2 111" xfId="404"/>
-    <cellStyle name="Normal 2 112" xfId="405"/>
-    <cellStyle name="Normal 2 113" xfId="406"/>
-    <cellStyle name="Normal 2 114" xfId="407"/>
-    <cellStyle name="Normal 2 115" xfId="408"/>
-    <cellStyle name="Normal 2 12" xfId="409"/>
-    <cellStyle name="Normal 2 13" xfId="410"/>
-    <cellStyle name="Normal 2 14" xfId="411"/>
-    <cellStyle name="Normal 2 15" xfId="412"/>
-    <cellStyle name="Normal 2 16" xfId="413"/>
-    <cellStyle name="Normal 2 17" xfId="414"/>
-    <cellStyle name="Normal 2 18" xfId="415"/>
-    <cellStyle name="Normal 2 19" xfId="416"/>
-    <cellStyle name="Normal 2 2" xfId="417"/>
-    <cellStyle name="Normal 2 2 2" xfId="418"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
-    <cellStyle name="Normal 2 2 3" xfId="420"/>
-    <cellStyle name="Normal 2 2 4" xfId="421"/>
-    <cellStyle name="Normal 2 20" xfId="422"/>
-    <cellStyle name="Normal 2 21" xfId="423"/>
-    <cellStyle name="Normal 2 22" xfId="424"/>
-    <cellStyle name="Normal 2 23" xfId="425"/>
-    <cellStyle name="Normal 2 24" xfId="426"/>
-    <cellStyle name="Normal 2 25" xfId="427"/>
-    <cellStyle name="Normal 2 26" xfId="428"/>
-    <cellStyle name="Normal 2 27" xfId="429"/>
-    <cellStyle name="Normal 2 28" xfId="430"/>
-    <cellStyle name="Normal 2 29" xfId="431"/>
-    <cellStyle name="Normal 2 3" xfId="432"/>
-    <cellStyle name="Normal 2 3 2" xfId="433"/>
-    <cellStyle name="Normal 2 3 3" xfId="434"/>
-    <cellStyle name="Normal 2 30" xfId="435"/>
-    <cellStyle name="Normal 2 31" xfId="436"/>
-    <cellStyle name="Normal 2 32" xfId="437"/>
-    <cellStyle name="Normal 2 33" xfId="438"/>
-    <cellStyle name="Normal 2 34" xfId="439"/>
-    <cellStyle name="Normal 2 35" xfId="440"/>
-    <cellStyle name="Normal 2 36" xfId="441"/>
-    <cellStyle name="Normal 2 37" xfId="442"/>
-    <cellStyle name="Normal 2 38" xfId="443"/>
-    <cellStyle name="Normal 2 39" xfId="444"/>
-    <cellStyle name="Normal 2 4" xfId="445"/>
-    <cellStyle name="Normal 2 4 2" xfId="446"/>
-    <cellStyle name="Normal 2 4 3" xfId="447"/>
-    <cellStyle name="Normal 2 4 4" xfId="448"/>
-    <cellStyle name="Normal 2 40" xfId="449"/>
-    <cellStyle name="Normal 2 41" xfId="450"/>
-    <cellStyle name="Normal 2 42" xfId="451"/>
-    <cellStyle name="Normal 2 43" xfId="452"/>
-    <cellStyle name="Normal 2 44" xfId="453"/>
-    <cellStyle name="Normal 2 45" xfId="454"/>
-    <cellStyle name="Normal 2 45 10" xfId="455"/>
-    <cellStyle name="Normal 2 45 11" xfId="456"/>
-    <cellStyle name="Normal 2 45 12" xfId="457"/>
-    <cellStyle name="Normal 2 45 13" xfId="458"/>
-    <cellStyle name="Normal 2 45 14" xfId="459"/>
-    <cellStyle name="Normal 2 45 15" xfId="460"/>
-    <cellStyle name="Normal 2 45 16" xfId="461"/>
-    <cellStyle name="Normal 2 45 17" xfId="462"/>
-    <cellStyle name="Normal 2 45 18" xfId="463"/>
-    <cellStyle name="Normal 2 45 19" xfId="464"/>
-    <cellStyle name="Normal 2 45 2" xfId="465"/>
-    <cellStyle name="Normal 2 45 20" xfId="466"/>
-    <cellStyle name="Normal 2 45 21" xfId="467"/>
-    <cellStyle name="Normal 2 45 22" xfId="468"/>
-    <cellStyle name="Normal 2 45 23" xfId="469"/>
-    <cellStyle name="Normal 2 45 24" xfId="470"/>
-    <cellStyle name="Normal 2 45 25" xfId="471"/>
-    <cellStyle name="Normal 2 45 26" xfId="472"/>
-    <cellStyle name="Normal 2 45 27" xfId="473"/>
-    <cellStyle name="Normal 2 45 28" xfId="474"/>
-    <cellStyle name="Normal 2 45 29" xfId="475"/>
-    <cellStyle name="Normal 2 45 3" xfId="476"/>
-    <cellStyle name="Normal 2 45 30" xfId="477"/>
-    <cellStyle name="Normal 2 45 31" xfId="478"/>
-    <cellStyle name="Normal 2 45 32" xfId="479"/>
-    <cellStyle name="Normal 2 45 33" xfId="480"/>
-    <cellStyle name="Normal 2 45 34" xfId="481"/>
-    <cellStyle name="Normal 2 45 35" xfId="482"/>
-    <cellStyle name="Normal 2 45 36" xfId="483"/>
-    <cellStyle name="Normal 2 45 37" xfId="484"/>
-    <cellStyle name="Normal 2 45 38" xfId="485"/>
-    <cellStyle name="Normal 2 45 39" xfId="486"/>
-    <cellStyle name="Normal 2 45 4" xfId="487"/>
-    <cellStyle name="Normal 2 45 40" xfId="488"/>
-    <cellStyle name="Normal 2 45 41" xfId="489"/>
-    <cellStyle name="Normal 2 45 42" xfId="490"/>
-    <cellStyle name="Normal 2 45 43" xfId="491"/>
-    <cellStyle name="Normal 2 45 44" xfId="492"/>
-    <cellStyle name="Normal 2 45 45" xfId="493"/>
-    <cellStyle name="Normal 2 45 46" xfId="494"/>
-    <cellStyle name="Normal 2 45 47" xfId="495"/>
-    <cellStyle name="Normal 2 45 48" xfId="496"/>
-    <cellStyle name="Normal 2 45 49" xfId="497"/>
-    <cellStyle name="Normal 2 45 5" xfId="498"/>
-    <cellStyle name="Normal 2 45 50" xfId="499"/>
-    <cellStyle name="Normal 2 45 51" xfId="500"/>
-    <cellStyle name="Normal 2 45 52" xfId="501"/>
-    <cellStyle name="Normal 2 45 53" xfId="502"/>
-    <cellStyle name="Normal 2 45 54" xfId="503"/>
-    <cellStyle name="Normal 2 45 55" xfId="504"/>
-    <cellStyle name="Normal 2 45 56" xfId="505"/>
-    <cellStyle name="Normal 2 45 57" xfId="506"/>
-    <cellStyle name="Normal 2 45 58" xfId="507"/>
-    <cellStyle name="Normal 2 45 59" xfId="508"/>
-    <cellStyle name="Normal 2 45 6" xfId="509"/>
-    <cellStyle name="Normal 2 45 7" xfId="510"/>
-    <cellStyle name="Normal 2 45 8" xfId="511"/>
-    <cellStyle name="Normal 2 45 9" xfId="512"/>
-    <cellStyle name="Normal 2 46" xfId="513"/>
-    <cellStyle name="Normal 2 47" xfId="514"/>
-    <cellStyle name="Normal 2 48" xfId="515"/>
-    <cellStyle name="Normal 2 49" xfId="516"/>
-    <cellStyle name="Normal 2 5" xfId="517"/>
-    <cellStyle name="Normal 2 5 2" xfId="518"/>
-    <cellStyle name="Normal 2 5 3" xfId="519"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
-    <cellStyle name="Normal 2 5 4" xfId="521"/>
-    <cellStyle name="Normal 2 50" xfId="522"/>
-    <cellStyle name="Normal 2 51" xfId="523"/>
-    <cellStyle name="Normal 2 52" xfId="524"/>
-    <cellStyle name="Normal 2 53" xfId="525"/>
-    <cellStyle name="Normal 2 54" xfId="526"/>
-    <cellStyle name="Normal 2 55" xfId="527"/>
-    <cellStyle name="Normal 2 56" xfId="528"/>
-    <cellStyle name="Normal 2 57" xfId="529"/>
-    <cellStyle name="Normal 2 58" xfId="530"/>
-    <cellStyle name="Normal 2 59" xfId="531"/>
-    <cellStyle name="Normal 2 6" xfId="532"/>
-    <cellStyle name="Normal 2 6 2" xfId="533"/>
-    <cellStyle name="Normal 2 60" xfId="534"/>
-    <cellStyle name="Normal 2 61" xfId="535"/>
-    <cellStyle name="Normal 2 62" xfId="536"/>
-    <cellStyle name="Normal 2 63" xfId="537"/>
-    <cellStyle name="Normal 2 64" xfId="538"/>
-    <cellStyle name="Normal 2 65" xfId="539"/>
-    <cellStyle name="Normal 2 66" xfId="540"/>
-    <cellStyle name="Normal 2 67" xfId="541"/>
-    <cellStyle name="Normal 2 68" xfId="542"/>
-    <cellStyle name="Normal 2 69" xfId="543"/>
-    <cellStyle name="Normal 2 7" xfId="544"/>
-    <cellStyle name="Normal 2 70" xfId="545"/>
-    <cellStyle name="Normal 2 71" xfId="546"/>
-    <cellStyle name="Normal 2 72" xfId="547"/>
-    <cellStyle name="Normal 2 73" xfId="548"/>
-    <cellStyle name="Normal 2 74" xfId="549"/>
-    <cellStyle name="Normal 2 75" xfId="550"/>
-    <cellStyle name="Normal 2 76" xfId="551"/>
-    <cellStyle name="Normal 2 77" xfId="552"/>
-    <cellStyle name="Normal 2 78" xfId="553"/>
-    <cellStyle name="Normal 2 79" xfId="554"/>
-    <cellStyle name="Normal 2 8" xfId="555"/>
-    <cellStyle name="Normal 2 80" xfId="556"/>
-    <cellStyle name="Normal 2 81" xfId="557"/>
-    <cellStyle name="Normal 2 82" xfId="558"/>
-    <cellStyle name="Normal 2 83" xfId="559"/>
-    <cellStyle name="Normal 2 84" xfId="560"/>
-    <cellStyle name="Normal 2 85" xfId="561"/>
-    <cellStyle name="Normal 2 86" xfId="562"/>
-    <cellStyle name="Normal 2 87" xfId="563"/>
-    <cellStyle name="Normal 2 88" xfId="564"/>
-    <cellStyle name="Normal 2 89" xfId="565"/>
-    <cellStyle name="Normal 2 9" xfId="566"/>
-    <cellStyle name="Normal 2 90" xfId="567"/>
-    <cellStyle name="Normal 2 91" xfId="568"/>
-    <cellStyle name="Normal 2 92" xfId="569"/>
-    <cellStyle name="Normal 2 93" xfId="570"/>
-    <cellStyle name="Normal 2 94" xfId="571"/>
-    <cellStyle name="Normal 2 95" xfId="572"/>
-    <cellStyle name="Normal 2 96" xfId="573"/>
-    <cellStyle name="Normal 2 97" xfId="574"/>
-    <cellStyle name="Normal 2 98" xfId="575"/>
-    <cellStyle name="Normal 2 99" xfId="576"/>
-    <cellStyle name="Normal 20" xfId="577"/>
-    <cellStyle name="Normal 20 2" xfId="578"/>
-    <cellStyle name="Normal 20 3" xfId="579"/>
-    <cellStyle name="Normal 20 4" xfId="580"/>
-    <cellStyle name="Normal 21" xfId="581"/>
-    <cellStyle name="Normal 21 2" xfId="582"/>
-    <cellStyle name="Normal 21 3" xfId="583"/>
-    <cellStyle name="Normal 21 4" xfId="584"/>
-    <cellStyle name="Normal 22" xfId="585"/>
-    <cellStyle name="Normal 22 2" xfId="586"/>
-    <cellStyle name="Normal 22 3" xfId="587"/>
-    <cellStyle name="Normal 22 4" xfId="588"/>
-    <cellStyle name="Normal 23" xfId="589"/>
-    <cellStyle name="Normal 23 2" xfId="590"/>
-    <cellStyle name="Normal 23 3" xfId="591"/>
-    <cellStyle name="Normal 24" xfId="592"/>
-    <cellStyle name="Normal 24 2" xfId="593"/>
-    <cellStyle name="Normal 24 3" xfId="594"/>
-    <cellStyle name="Normal 25" xfId="595"/>
-    <cellStyle name="Normal 26" xfId="596"/>
-    <cellStyle name="Normal 27" xfId="597"/>
-    <cellStyle name="Normal 28" xfId="598"/>
-    <cellStyle name="Normal 29" xfId="599"/>
-    <cellStyle name="Normal 3" xfId="600"/>
-    <cellStyle name="Normal 3 2" xfId="601"/>
-    <cellStyle name="Normal 3 2 2" xfId="602"/>
-    <cellStyle name="Normal 3 3" xfId="603"/>
-    <cellStyle name="Normal 3 3 2" xfId="604"/>
-    <cellStyle name="Normal 3 3 3" xfId="605"/>
-    <cellStyle name="Normal 3 4" xfId="606"/>
-    <cellStyle name="Normal 3 5" xfId="607"/>
-    <cellStyle name="Normal 30" xfId="608"/>
-    <cellStyle name="Normal 31" xfId="609"/>
-    <cellStyle name="Normal 32" xfId="610"/>
-    <cellStyle name="Normal 33" xfId="611"/>
-    <cellStyle name="Normal 34" xfId="612"/>
-    <cellStyle name="Normal 35" xfId="613"/>
-    <cellStyle name="Normal 36" xfId="614"/>
-    <cellStyle name="Normal 37" xfId="615"/>
-    <cellStyle name="Normal 38" xfId="616"/>
-    <cellStyle name="Normal 39" xfId="617"/>
-    <cellStyle name="Normal 4" xfId="618"/>
-    <cellStyle name="Normal 4 2" xfId="619"/>
-    <cellStyle name="Normal 4 2 2" xfId="620"/>
-    <cellStyle name="Normal 4 3" xfId="621"/>
-    <cellStyle name="Normal 4 4" xfId="622"/>
-    <cellStyle name="Normal 40" xfId="623"/>
-    <cellStyle name="Normal 41" xfId="624"/>
-    <cellStyle name="Normal 42" xfId="625"/>
-    <cellStyle name="Normal 43" xfId="626"/>
-    <cellStyle name="Normal 44" xfId="627"/>
-    <cellStyle name="Normal 45" xfId="628"/>
-    <cellStyle name="Normal 46" xfId="629"/>
-    <cellStyle name="Normal 47" xfId="630"/>
-    <cellStyle name="Normal 48" xfId="631"/>
-    <cellStyle name="Normal 49" xfId="632"/>
-    <cellStyle name="Normal 5" xfId="633"/>
-    <cellStyle name="Normal 5 10" xfId="634"/>
-    <cellStyle name="Normal 5 11" xfId="635"/>
-    <cellStyle name="Normal 5 12" xfId="636"/>
-    <cellStyle name="Normal 5 13" xfId="637"/>
-    <cellStyle name="Normal 5 14" xfId="638"/>
-    <cellStyle name="Normal 5 15" xfId="639"/>
-    <cellStyle name="Normal 5 16" xfId="640"/>
-    <cellStyle name="Normal 5 17" xfId="641"/>
-    <cellStyle name="Normal 5 18" xfId="642"/>
-    <cellStyle name="Normal 5 19" xfId="643"/>
-    <cellStyle name="Normal 5 2" xfId="644"/>
-    <cellStyle name="Normal 5 20" xfId="645"/>
-    <cellStyle name="Normal 5 21" xfId="646"/>
-    <cellStyle name="Normal 5 22" xfId="647"/>
-    <cellStyle name="Normal 5 23" xfId="648"/>
-    <cellStyle name="Normal 5 24" xfId="649"/>
-    <cellStyle name="Normal 5 25" xfId="650"/>
-    <cellStyle name="Normal 5 26" xfId="651"/>
-    <cellStyle name="Normal 5 27" xfId="652"/>
-    <cellStyle name="Normal 5 28" xfId="653"/>
-    <cellStyle name="Normal 5 28 10" xfId="654"/>
-    <cellStyle name="Normal 5 28 11" xfId="655"/>
-    <cellStyle name="Normal 5 28 12" xfId="656"/>
-    <cellStyle name="Normal 5 28 13" xfId="657"/>
-    <cellStyle name="Normal 5 28 14" xfId="658"/>
-    <cellStyle name="Normal 5 28 15" xfId="659"/>
-    <cellStyle name="Normal 5 28 16" xfId="660"/>
-    <cellStyle name="Normal 5 28 17" xfId="661"/>
-    <cellStyle name="Normal 5 28 18" xfId="662"/>
-    <cellStyle name="Normal 5 28 19" xfId="663"/>
-    <cellStyle name="Normal 5 28 2" xfId="664"/>
-    <cellStyle name="Normal 5 28 20" xfId="665"/>
-    <cellStyle name="Normal 5 28 21" xfId="666"/>
-    <cellStyle name="Normal 5 28 22" xfId="667"/>
-    <cellStyle name="Normal 5 28 23" xfId="668"/>
-    <cellStyle name="Normal 5 28 24" xfId="669"/>
-    <cellStyle name="Normal 5 28 25" xfId="670"/>
-    <cellStyle name="Normal 5 28 3" xfId="671"/>
-    <cellStyle name="Normal 5 28 4" xfId="672"/>
-    <cellStyle name="Normal 5 28 5" xfId="673"/>
-    <cellStyle name="Normal 5 28 6" xfId="674"/>
-    <cellStyle name="Normal 5 28 7" xfId="675"/>
-    <cellStyle name="Normal 5 28 8" xfId="676"/>
-    <cellStyle name="Normal 5 28 9" xfId="677"/>
-    <cellStyle name="Normal 5 29" xfId="678"/>
-    <cellStyle name="Normal 5 3" xfId="679"/>
-    <cellStyle name="Normal 5 4" xfId="680"/>
-    <cellStyle name="Normal 5 5" xfId="681"/>
-    <cellStyle name="Normal 5 6" xfId="682"/>
-    <cellStyle name="Normal 5 7" xfId="683"/>
-    <cellStyle name="Normal 5 8" xfId="684"/>
-    <cellStyle name="Normal 5 9" xfId="685"/>
-    <cellStyle name="Normal 50" xfId="686"/>
-    <cellStyle name="Normal 51" xfId="687"/>
-    <cellStyle name="Normal 52" xfId="688"/>
-    <cellStyle name="Normal 53" xfId="689"/>
-    <cellStyle name="Normal 54" xfId="690"/>
-    <cellStyle name="Normal 55" xfId="691"/>
-    <cellStyle name="Normal 56" xfId="2"/>
-    <cellStyle name="Normal 56 2" xfId="692"/>
-    <cellStyle name="Normal 57" xfId="693"/>
-    <cellStyle name="Normal 58" xfId="694"/>
-    <cellStyle name="Normal 59" xfId="695"/>
-    <cellStyle name="Normal 6" xfId="696"/>
-    <cellStyle name="Normal 6 2" xfId="697"/>
-    <cellStyle name="Normal 6 2 2" xfId="698"/>
-    <cellStyle name="Normal 6 2 3" xfId="699"/>
-    <cellStyle name="Normal 6 3" xfId="700"/>
-    <cellStyle name="Normal 6 4" xfId="701"/>
-    <cellStyle name="Normal 60" xfId="702"/>
-    <cellStyle name="Normal 61" xfId="703"/>
-    <cellStyle name="Normal 62" xfId="704"/>
-    <cellStyle name="Normal 63" xfId="705"/>
-    <cellStyle name="Normal 64" xfId="706"/>
-    <cellStyle name="Normal 65" xfId="707"/>
-    <cellStyle name="Normal 66" xfId="708"/>
-    <cellStyle name="Normal 67" xfId="709"/>
-    <cellStyle name="Normal 68" xfId="710"/>
-    <cellStyle name="Normal 69" xfId="711"/>
-    <cellStyle name="Normal 7" xfId="712"/>
-    <cellStyle name="Normal 7 2" xfId="713"/>
-    <cellStyle name="Normal 7 3" xfId="714"/>
-    <cellStyle name="Normal 7 4" xfId="715"/>
-    <cellStyle name="Normal 70" xfId="716"/>
-    <cellStyle name="Normal 71" xfId="717"/>
-    <cellStyle name="Normal 72" xfId="718"/>
-    <cellStyle name="Normal 73" xfId="719"/>
-    <cellStyle name="Normal 74" xfId="720"/>
-    <cellStyle name="Normal 75" xfId="721"/>
-    <cellStyle name="Normal 76" xfId="722"/>
-    <cellStyle name="Normal 77" xfId="723"/>
-    <cellStyle name="Normal 78" xfId="724"/>
-    <cellStyle name="Normal 79" xfId="725"/>
-    <cellStyle name="Normal 79 2" xfId="726"/>
-    <cellStyle name="Normal 79 3" xfId="727"/>
-    <cellStyle name="Normal 8" xfId="728"/>
-    <cellStyle name="Normal 8 2" xfId="729"/>
-    <cellStyle name="Normal 8 3" xfId="730"/>
-    <cellStyle name="Normal 8 4" xfId="731"/>
-    <cellStyle name="Normal 80" xfId="732"/>
-    <cellStyle name="Normal 80 2" xfId="733"/>
-    <cellStyle name="Normal 81" xfId="734"/>
-    <cellStyle name="Normal 81 2" xfId="735"/>
-    <cellStyle name="Normal 82" xfId="736"/>
-    <cellStyle name="Normal 82 2" xfId="737"/>
-    <cellStyle name="Normal 82 2 2" xfId="738"/>
-    <cellStyle name="Normal 83" xfId="739"/>
-    <cellStyle name="Normal 83 2" xfId="740"/>
-    <cellStyle name="Normal 83 2 2" xfId="741"/>
-    <cellStyle name="Normal 84" xfId="742"/>
-    <cellStyle name="Normal 84 2" xfId="743"/>
-    <cellStyle name="Normal 84 3" xfId="744"/>
-    <cellStyle name="Normal 85" xfId="745"/>
-    <cellStyle name="Normal 85 2" xfId="746"/>
-    <cellStyle name="Normal 85 3" xfId="747"/>
-    <cellStyle name="Normal 86" xfId="748"/>
-    <cellStyle name="Normal 86 2" xfId="749"/>
-    <cellStyle name="Normal 86 3" xfId="750"/>
-    <cellStyle name="Normal 87" xfId="751"/>
-    <cellStyle name="Normal 87 2" xfId="752"/>
-    <cellStyle name="Normal 87 3" xfId="753"/>
-    <cellStyle name="Normal 88" xfId="754"/>
-    <cellStyle name="Normal 88 2" xfId="755"/>
-    <cellStyle name="Normal 88 3" xfId="756"/>
-    <cellStyle name="Normal 88 4" xfId="757"/>
-    <cellStyle name="Normal 89" xfId="758"/>
-    <cellStyle name="Normal 9" xfId="759"/>
-    <cellStyle name="Normal 9 2" xfId="760"/>
-    <cellStyle name="Normal 9 3" xfId="761"/>
-    <cellStyle name="Normal 9 4" xfId="762"/>
-    <cellStyle name="Normal 90" xfId="763"/>
-    <cellStyle name="Normal 91" xfId="764"/>
-    <cellStyle name="Normal 92" xfId="765"/>
-    <cellStyle name="Normal 93" xfId="766"/>
-    <cellStyle name="Normal 94" xfId="767"/>
-    <cellStyle name="Normal 94 2" xfId="768"/>
-    <cellStyle name="Normal 95" xfId="769"/>
-    <cellStyle name="Normal 95 2" xfId="770"/>
-    <cellStyle name="Normal 95 3" xfId="771"/>
-    <cellStyle name="Normal 96" xfId="772"/>
-    <cellStyle name="Normal 97" xfId="773"/>
-    <cellStyle name="Normal 97 2" xfId="774"/>
-    <cellStyle name="Normal 98" xfId="775"/>
-    <cellStyle name="Normal 98 2" xfId="776"/>
-    <cellStyle name="Normal 99" xfId="777"/>
-    <cellStyle name="Normal 99 2" xfId="778"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3"/>
-    <cellStyle name="Notas 2" xfId="779"/>
-    <cellStyle name="Notas 2 2" xfId="780"/>
-    <cellStyle name="Notas 2 3" xfId="781"/>
-    <cellStyle name="Notas 3" xfId="782"/>
-    <cellStyle name="Notas 4" xfId="783"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785"/>
-    <cellStyle name="Salida 2" xfId="786"/>
-    <cellStyle name="Salida 3" xfId="787"/>
-    <cellStyle name="Salida 4" xfId="788"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791"/>
-    <cellStyle name="Texto explicativo 2" xfId="792"/>
-    <cellStyle name="Texto explicativo 3" xfId="793"/>
-    <cellStyle name="Texto explicativo 4" xfId="794"/>
-    <cellStyle name="Título 1 2" xfId="795"/>
-    <cellStyle name="Título 2 2" xfId="796"/>
-    <cellStyle name="Título 2 3" xfId="797"/>
-    <cellStyle name="Título 2 4" xfId="798"/>
-    <cellStyle name="Título 3 2" xfId="799"/>
-    <cellStyle name="Título 3 3" xfId="800"/>
-    <cellStyle name="Título 3 4" xfId="801"/>
-    <cellStyle name="Título 4" xfId="802"/>
-    <cellStyle name="Título 5" xfId="803"/>
-    <cellStyle name="Título 6" xfId="804"/>
-    <cellStyle name="Total 2" xfId="806"/>
-    <cellStyle name="Total 3" xfId="807"/>
-    <cellStyle name="Total 4" xfId="808"/>
-    <cellStyle name="Total 5" xfId="805"/>
+    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2637,26 +2595,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2672,8 +2630,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="18">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -2689,8 +2647,8 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="18">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -2706,8 +2664,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="18">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -2723,8 +2681,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="18">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -2740,8 +2698,8 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="18">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -2757,8 +2715,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="18">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -2774,8 +2732,8 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="18">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -2791,8 +2749,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="18">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -2808,8 +2766,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="18">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -2825,8 +2783,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="18">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -2842,8 +2800,8 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="18">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -2859,8 +2817,8 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="18">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -2876,8 +2834,8 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="18">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -2893,8 +2851,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="18">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -2910,8 +2868,8 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="18">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -2927,8 +2885,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="18">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -2944,8 +2902,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -2961,8 +2919,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="18">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -2978,8 +2936,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="18">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -2995,8 +2953,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="18">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -3012,8 +2970,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="18">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -3029,8 +2987,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="18">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3046,8 +3004,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="18">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3063,8 +3021,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="18">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3080,8 +3038,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="18">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3097,8 +3055,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="18">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3114,8 +3072,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="18">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3131,124 +3089,124 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="18">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="14"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="9"/>
       <c r="H29" s="1">
         <v>18.43</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="18">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="16"/>
+      <c r="E30" s="11"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="16"/>
+      <c r="G30" s="11"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="18">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="16"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="18">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
         <v>46148</v>
       </c>
       <c r="B32" s="1">
         <v>1200</v>
       </c>
-      <c r="C32" s="16"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="1">
         <v>100</v>
       </c>
-      <c r="E32" s="16"/>
+      <c r="E32" s="11"/>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="16"/>
+      <c r="G32" s="11"/>
       <c r="H32" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="20"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="20"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="20"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="18"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="14"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="14"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="16"/>
+      <c r="E36" s="11"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="16"/>
+      <c r="G36" s="11"/>
       <c r="H36" s="1"/>
     </row>
   </sheetData>
@@ -3258,23 +3216,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" style="16" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
+      <c r="C1" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
@@ -3282,228 +3244,327 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46148</v>
       </c>
       <c r="B2">
         <v>745.52443231999996</v>
       </c>
+      <c r="C2" s="19">
+        <f>+((B2-B3)/B3)*100</f>
+        <v>-99.115816107458954</v>
+      </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="7">
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46147</v>
       </c>
       <c r="B3">
         <v>84317.802960360001</v>
       </c>
+      <c r="C3" s="19">
+        <f t="shared" ref="C3:C26" si="0">+((B3-B4)/B4)*100</f>
+        <v>70.107388483787062</v>
+      </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="7">
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46146</v>
       </c>
       <c r="B4">
         <v>49567.396050169998</v>
       </c>
+      <c r="C4" s="19">
+        <f t="shared" si="0"/>
+        <v>-43.255825515735765</v>
+      </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="8">
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>46142</v>
       </c>
       <c r="B5">
         <v>87352.396084139997</v>
       </c>
+      <c r="C5" s="19">
+        <f t="shared" si="0"/>
+        <v>207.73664296544806</v>
+      </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="8">
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="11">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>46141</v>
       </c>
       <c r="B6">
         <v>28385.438679769999</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="11">
+      <c r="C6" s="19">
+        <f t="shared" si="0"/>
+        <v>-59.636256133262869</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>46140</v>
       </c>
       <c r="B7">
         <v>70324.097718699995</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="11">
+      <c r="C7" s="19">
+        <f t="shared" si="0"/>
+        <v>74.333012643706198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>46139</v>
       </c>
       <c r="B8">
         <v>40338.944788629997</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="11">
+      <c r="C8" s="19">
+        <f t="shared" si="0"/>
+        <v>-33.842006324553125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>46136</v>
       </c>
       <c r="B9">
         <v>60973.651931649998</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="11">
+      <c r="C9" s="19">
+        <f t="shared" si="0"/>
+        <v>1210.6463903543759</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>46135</v>
       </c>
       <c r="B10">
         <v>4652.1817311200002</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="11">
+      <c r="C10" s="19">
+        <f t="shared" si="0"/>
+        <v>-73.032401489373797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>46134</v>
       </c>
       <c r="B11">
         <v>17251.00486529</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="11">
+      <c r="C11" s="19">
+        <f t="shared" si="0"/>
+        <v>-64.046760511667529</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>46133</v>
       </c>
       <c r="B12">
         <v>47981.781644150004</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="11">
+      <c r="C12" s="19">
+        <f t="shared" si="0"/>
+        <v>-6.5402088492716128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>46132</v>
       </c>
       <c r="B13">
         <v>51339.49161813</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="11">
+      <c r="C13" s="19">
+        <f t="shared" si="0"/>
+        <v>198.19948129202027</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>46129</v>
       </c>
       <c r="B14">
         <v>17216.492596060001</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="11">
+      <c r="C14" s="19">
+        <f t="shared" si="0"/>
+        <v>91040.237411852577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>46128</v>
       </c>
       <c r="B15">
         <v>18.890111640000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="11">
+      <c r="C15" s="19">
+        <f t="shared" si="0"/>
+        <v>19.572063797541304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>46127</v>
       </c>
       <c r="B16">
         <v>15.79809785</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="11">
+      <c r="C16" s="19">
+        <f t="shared" si="0"/>
+        <v>-2.5764893835585476</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>46126</v>
       </c>
       <c r="B17">
         <v>16.215898760000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="11">
+      <c r="C17" s="19">
+        <f t="shared" si="0"/>
+        <v>-99.344926580920657</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>46125</v>
       </c>
       <c r="B18">
         <v>2475.4322626600001</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="11">
+      <c r="C18" s="19">
+        <f t="shared" si="0"/>
+        <v>-68.887087467151304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>46122</v>
       </c>
       <c r="B19">
         <v>7956.2858669899997</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="11">
+      <c r="C19" s="19">
+        <f t="shared" si="0"/>
+        <v>19054.886991293832</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>46121</v>
       </c>
       <c r="B20">
         <v>41.536584740000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="11">
+      <c r="C20" s="19">
+        <f t="shared" si="0"/>
+        <v>-92.845434694034026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>46120</v>
       </c>
       <c r="B21">
         <v>580.56056466999996</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="11">
+      <c r="C21" s="19">
+        <f t="shared" si="0"/>
+        <v>396.32497533121034</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>46119</v>
       </c>
       <c r="B22">
         <v>116.97186189</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="11">
+      <c r="C22" s="19">
+        <f t="shared" si="0"/>
+        <v>-98.322351149824243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
         <v>46118</v>
       </c>
       <c r="B23">
         <v>6972.36861443</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="11">
+      <c r="C23" s="19">
+        <f t="shared" si="0"/>
+        <v>1191.1589836815915</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
         <v>46113</v>
       </c>
       <c r="B24">
         <v>540.00852741999995</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="11">
+      <c r="C24" s="19">
+        <f t="shared" si="0"/>
+        <v>-89.738241267184833</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>46112</v>
       </c>
       <c r="B25">
         <v>5262.3389565099997</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="11">
+      <c r="C25" s="19">
+        <f t="shared" si="0"/>
+        <v>-77.08997404756451</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
         <v>46111</v>
       </c>
       <c r="B26">
         <v>22969.58967849</v>
+      </c>
+      <c r="C26" s="19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3513,17 +3574,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3537,7 +3598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3551,7 +3612,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3565,7 +3626,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3579,7 +3640,7 @@
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3589,7 +3650,7 @@
       <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="10">
         <v>64.09</v>
       </c>
     </row>
@@ -3600,16 +3661,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3620,7 +3681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46024</v>
       </c>
@@ -3629,7 +3690,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46031</v>
       </c>
@@ -3637,10 +3698,10 @@
         <v>631055414.05422926</v>
       </c>
       <c r="C3" s="4">
-        <v>-7.2050081634151608E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-7.2050081634151582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46038</v>
       </c>
@@ -3648,10 +3709,10 @@
         <v>687738190.99875975</v>
       </c>
       <c r="C4" s="4">
-        <v>8.9822186264706616E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>8.9822186264706527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46045</v>
       </c>
@@ -3659,10 +3720,10 @@
         <v>728876050.32802963</v>
       </c>
       <c r="C5" s="4">
-        <v>5.9816162411350016E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>5.9816162411350033</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46052</v>
       </c>
@@ -3670,10 +3731,10 @@
         <v>839643409.76085114</v>
       </c>
       <c r="C6" s="4">
-        <v>0.15197009063882794</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>15.197009063882785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46059</v>
       </c>
@@ -3681,96 +3742,97 @@
         <v>818274973.23848069</v>
       </c>
       <c r="C7" s="4">
-        <v>-2.5449418495950171E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1">
+        <v>-2.5449418495950149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46066</v>
       </c>
       <c r="B8" s="1">
         <v>801808360.23688257</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.0123569142568742E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="C8" s="4">
+        <v>-2.0123569142568702</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46073</v>
       </c>
       <c r="B9" s="1">
         <v>886542333.87268889</v>
       </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="C9" s="4">
+        <v>10.56785858540723</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46080</v>
       </c>
       <c r="B10" s="1">
         <v>938549580.20021927</v>
       </c>
-      <c r="C10" s="7">
-        <v>5.8663015109889693E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="C10" s="4">
+        <v>5.8663015109889649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46087</v>
       </c>
       <c r="B11" s="1">
         <v>870061809.65898001</v>
       </c>
-      <c r="C11" s="7">
-        <v>-7.2971926029340772E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="C11" s="4">
+        <v>-7.2971926029340803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46094</v>
       </c>
       <c r="B12" s="1">
         <v>959597484.45129991</v>
       </c>
-      <c r="C12" s="7">
-        <v>0.10290725762048258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="C12" s="4">
+        <v>10.290725762048252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46101</v>
       </c>
       <c r="B13" s="1">
         <v>1136404345.7909815</v>
       </c>
-      <c r="C13" s="7">
-        <v>0.18425106797854962</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="C13" s="4">
+        <v>18.425106797854955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>46108</v>
       </c>
       <c r="B14" s="1">
         <v>1111572721.2404912</v>
       </c>
-      <c r="C14" s="8">
-        <v>-2.1851046806061425E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="C14" s="4">
+        <f>+((B14-B13)/B13)*100</f>
+        <v>-2.1851046806061447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>46129</v>
       </c>
       <c r="B15" s="1">
         <v>1071533894.2527295</v>
       </c>
-      <c r="C15" s="8">
-        <f>+(B15-B14)/B14</f>
-        <v>-3.6019979820194892E-2</v>
+      <c r="C15" s="4">
+        <f>+((B15-B14)/B14)*100</f>
+        <v>-3.6019979820194892</v>
       </c>
     </row>
   </sheetData>
@@ -3779,21 +3841,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.75" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3819,7 +3881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -3841,11 +3903,11 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46115</v>
       </c>
@@ -3867,11 +3929,12 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="9">
-        <v>-1.4067445693212388E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3" s="18">
+        <f>+((G3-G2)/G2)*100</f>
+        <v>-1.4067445693212368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -3893,11 +3956,12 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="9">
-        <v>9.7569377843467198E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="18">
+        <f>+((G4-G3)/G3)*100</f>
+        <v>0.9756937784346702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -3919,11 +3983,12 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="9">
-        <v>3.4749018512476804E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="18">
+        <f>+((G5-G4)/G4)*100</f>
+        <v>3.4749018512476764</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -3945,8 +4010,9 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="9">
-        <v>3.0099999999999998E-2</v>
+      <c r="H6" s="18">
+        <f>+((G6-G5)/G5)*100</f>
+        <v>3.0146874710954426</v>
       </c>
     </row>
   </sheetData>
@@ -3955,19 +4021,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
-    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3980,14 +4046,14 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -4000,14 +4066,14 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="17">
-        <v>-2.681224004753413E-2</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46113</v>
       </c>
@@ -4020,14 +4086,15 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3">
-        <v>4.8691139433717501E-2</v>
-      </c>
-      <c r="F3" s="10">
+      <c r="E3" s="5">
+        <f>+((D3-D2)/D2)*100</f>
+        <v>4.8691139433717465</v>
+      </c>
+      <c r="F3" s="5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -4040,14 +4107,15 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4">
-        <v>-1.1061785896222975E-2</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="E4" s="5">
+        <f>+((D4-D3)/D3)*100</f>
+        <v>-1.1061785896222982</v>
+      </c>
+      <c r="F4" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -4060,14 +4128,15 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5">
-        <v>6.2550592390904214E-3</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="5">
+        <f>+((D5-D4)/D4)*100</f>
+        <v>0.62550592390904403</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4080,14 +4149,15 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6">
-        <v>-1.3894983179757237E-2</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="5">
+        <f>+((D6-D5)/D5)*100</f>
+        <v>-1.3894983179757203</v>
+      </c>
+      <c r="F6" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46139</v>
       </c>
@@ -4100,15 +4170,15 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7">
-        <f>+(D7-D8)/D8</f>
-        <v>1.5619105108277371E-2</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="5">
+        <f>+((D7-D6)/D6)*100</f>
+        <v>-0.17798872738059923</v>
+      </c>
+      <c r="F7" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46140</v>
       </c>
@@ -4121,15 +4191,15 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8">
-        <f>+(D8-D9)/D9</f>
-        <v>5.0049290968377947E-3</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="E8" s="5">
+        <f>+((D8-D7)/D7)*100</f>
+        <v>-1.5378900445765229</v>
+      </c>
+      <c r="F8" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46141</v>
       </c>
@@ -4142,15 +4212,15 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9">
-        <f>+(D9-D6)/D6</f>
-        <v>-2.2026105013349156E-2</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="E9" s="5">
+        <f>+((D9-D8)/D8)*100</f>
+        <v>-0.49800045272768434</v>
+      </c>
+      <c r="F9" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46142</v>
       </c>
@@ -4163,15 +4233,16 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10">
-        <f>+(D10-D7)/D7</f>
-        <v>-1.3372956909361069E-2</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="5">
+        <f>+((D10-D9)/D9)*100</f>
+        <v>0.70524000909987106</v>
+      </c>
+      <c r="F10" s="5">
         <v>-0.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46146</v>
       </c>
@@ -4184,32 +4255,32 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11">
-        <f>+(D11-D8)/D8</f>
-        <v>6.0967328152116501E-2</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="E11" s="5">
+        <f>+((D11-D10)/D10)*100</f>
+        <v>5.8810240963855422</v>
+      </c>
+      <c r="F11" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="15">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="15">
         <v>13872</v>
       </c>
-      <c r="E12">
-        <f>+(D12-D9)/D9</f>
-        <v>5.1945097444452873E-2</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="E12" s="5">
+        <f>+((D12-D11)/D11)*100</f>
+        <v>-1.3441433752933647</v>
+      </c>
+      <c r="F12" s="5">
         <v>-0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C5BFA2-57D2-488A-85AA-445E28DB294A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>DÍA</t>
   </si>
@@ -142,8 +136,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
@@ -151,8 +145,9 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="170" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,7 +437,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -455,6 +450,49 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -681,15 +719,15 @@
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -711,9 +749,9 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1383,46 +1421,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1438,6 +1491,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1448,830 +1502,818 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="810">
-    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
+    <cellStyle name="Buena 2" xfId="74"/>
+    <cellStyle name="Buena 3" xfId="75"/>
+    <cellStyle name="Buena 4" xfId="76"/>
+    <cellStyle name="Cálculo 2" xfId="77"/>
+    <cellStyle name="Cálculo 3" xfId="78"/>
+    <cellStyle name="Cálculo 4" xfId="79"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82"/>
+    <cellStyle name="Celda vinculada 2" xfId="83"/>
+    <cellStyle name="Celda vinculada 3" xfId="84"/>
+    <cellStyle name="Celda vinculada 4" xfId="85"/>
+    <cellStyle name="Comma 2" xfId="121"/>
+    <cellStyle name="Encabezado 4 2" xfId="86"/>
+    <cellStyle name="Encabezado 4 3" xfId="87"/>
+    <cellStyle name="Encabezado 4 4" xfId="88"/>
+    <cellStyle name="Énfasis1 2" xfId="89"/>
+    <cellStyle name="Énfasis1 3" xfId="90"/>
+    <cellStyle name="Énfasis1 4" xfId="91"/>
+    <cellStyle name="Énfasis2 2" xfId="92"/>
+    <cellStyle name="Énfasis2 3" xfId="93"/>
+    <cellStyle name="Énfasis2 4" xfId="94"/>
+    <cellStyle name="Énfasis3 2" xfId="95"/>
+    <cellStyle name="Énfasis3 3" xfId="96"/>
+    <cellStyle name="Énfasis3 4" xfId="97"/>
+    <cellStyle name="Énfasis4 2" xfId="98"/>
+    <cellStyle name="Énfasis4 3" xfId="99"/>
+    <cellStyle name="Énfasis4 4" xfId="100"/>
+    <cellStyle name="Énfasis5 2" xfId="101"/>
+    <cellStyle name="Énfasis5 3" xfId="102"/>
+    <cellStyle name="Énfasis5 4" xfId="103"/>
+    <cellStyle name="Énfasis6 2" xfId="104"/>
+    <cellStyle name="Énfasis6 3" xfId="105"/>
+    <cellStyle name="Énfasis6 4" xfId="106"/>
+    <cellStyle name="Entrada 2" xfId="107"/>
+    <cellStyle name="Entrada 3" xfId="108"/>
+    <cellStyle name="Entrada 4" xfId="109"/>
+    <cellStyle name="Euro" xfId="110"/>
+    <cellStyle name="Euro 2" xfId="111"/>
+    <cellStyle name="Euro 2 2" xfId="112"/>
+    <cellStyle name="Euro 2 3" xfId="113"/>
+    <cellStyle name="Euro 2 4" xfId="114"/>
+    <cellStyle name="Euro 3" xfId="115"/>
+    <cellStyle name="Euro 4" xfId="116"/>
+    <cellStyle name="Euro 5" xfId="117"/>
+    <cellStyle name="Incorrecto 2" xfId="118"/>
+    <cellStyle name="Incorrecto 3" xfId="119"/>
+    <cellStyle name="Incorrecto 4" xfId="120"/>
+    <cellStyle name="Millares 10" xfId="122"/>
+    <cellStyle name="Millares 2" xfId="123"/>
+    <cellStyle name="Millares 2 2" xfId="124"/>
+    <cellStyle name="Millares 2 2 2" xfId="125"/>
+    <cellStyle name="Millares 2 3" xfId="126"/>
+    <cellStyle name="Millares 2 4" xfId="127"/>
+    <cellStyle name="Millares 3" xfId="128"/>
+    <cellStyle name="Millares 3 10" xfId="129"/>
+    <cellStyle name="Millares 3 100" xfId="130"/>
+    <cellStyle name="Millares 3 101" xfId="131"/>
+    <cellStyle name="Millares 3 102" xfId="132"/>
+    <cellStyle name="Millares 3 103" xfId="133"/>
+    <cellStyle name="Millares 3 103 2" xfId="134"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
+    <cellStyle name="Millares 3 104" xfId="136"/>
+    <cellStyle name="Millares 3 11" xfId="137"/>
+    <cellStyle name="Millares 3 12" xfId="138"/>
+    <cellStyle name="Millares 3 13" xfId="139"/>
+    <cellStyle name="Millares 3 14" xfId="140"/>
+    <cellStyle name="Millares 3 15" xfId="141"/>
+    <cellStyle name="Millares 3 16" xfId="142"/>
+    <cellStyle name="Millares 3 17" xfId="143"/>
+    <cellStyle name="Millares 3 18" xfId="144"/>
+    <cellStyle name="Millares 3 19" xfId="145"/>
+    <cellStyle name="Millares 3 2" xfId="146"/>
+    <cellStyle name="Millares 3 2 2" xfId="147"/>
+    <cellStyle name="Millares 3 2 3" xfId="148"/>
+    <cellStyle name="Millares 3 20" xfId="149"/>
+    <cellStyle name="Millares 3 21" xfId="150"/>
+    <cellStyle name="Millares 3 22" xfId="151"/>
+    <cellStyle name="Millares 3 23" xfId="152"/>
+    <cellStyle name="Millares 3 24" xfId="153"/>
+    <cellStyle name="Millares 3 25" xfId="154"/>
+    <cellStyle name="Millares 3 26" xfId="155"/>
+    <cellStyle name="Millares 3 27" xfId="156"/>
+    <cellStyle name="Millares 3 28" xfId="157"/>
+    <cellStyle name="Millares 3 29" xfId="158"/>
+    <cellStyle name="Millares 3 3" xfId="159"/>
+    <cellStyle name="Millares 3 30" xfId="160"/>
+    <cellStyle name="Millares 3 31" xfId="161"/>
+    <cellStyle name="Millares 3 32" xfId="162"/>
+    <cellStyle name="Millares 3 33" xfId="163"/>
+    <cellStyle name="Millares 3 34" xfId="164"/>
+    <cellStyle name="Millares 3 35" xfId="165"/>
+    <cellStyle name="Millares 3 36" xfId="166"/>
+    <cellStyle name="Millares 3 37" xfId="167"/>
+    <cellStyle name="Millares 3 38" xfId="168"/>
+    <cellStyle name="Millares 3 39" xfId="169"/>
+    <cellStyle name="Millares 3 4" xfId="170"/>
+    <cellStyle name="Millares 3 40" xfId="171"/>
+    <cellStyle name="Millares 3 41" xfId="172"/>
+    <cellStyle name="Millares 3 42" xfId="173"/>
+    <cellStyle name="Millares 3 43" xfId="174"/>
+    <cellStyle name="Millares 3 44" xfId="175"/>
+    <cellStyle name="Millares 3 45" xfId="176"/>
+    <cellStyle name="Millares 3 46" xfId="177"/>
+    <cellStyle name="Millares 3 47" xfId="178"/>
+    <cellStyle name="Millares 3 48" xfId="179"/>
+    <cellStyle name="Millares 3 49" xfId="180"/>
+    <cellStyle name="Millares 3 5" xfId="181"/>
+    <cellStyle name="Millares 3 50" xfId="182"/>
+    <cellStyle name="Millares 3 51" xfId="183"/>
+    <cellStyle name="Millares 3 52" xfId="184"/>
+    <cellStyle name="Millares 3 53" xfId="185"/>
+    <cellStyle name="Millares 3 54" xfId="186"/>
+    <cellStyle name="Millares 3 55" xfId="187"/>
+    <cellStyle name="Millares 3 56" xfId="188"/>
+    <cellStyle name="Millares 3 57" xfId="189"/>
+    <cellStyle name="Millares 3 58" xfId="190"/>
+    <cellStyle name="Millares 3 59" xfId="191"/>
+    <cellStyle name="Millares 3 6" xfId="192"/>
+    <cellStyle name="Millares 3 60" xfId="193"/>
+    <cellStyle name="Millares 3 61" xfId="194"/>
+    <cellStyle name="Millares 3 62" xfId="195"/>
+    <cellStyle name="Millares 3 63" xfId="196"/>
+    <cellStyle name="Millares 3 64" xfId="197"/>
+    <cellStyle name="Millares 3 65" xfId="198"/>
+    <cellStyle name="Millares 3 66" xfId="199"/>
+    <cellStyle name="Millares 3 67" xfId="200"/>
+    <cellStyle name="Millares 3 68" xfId="201"/>
+    <cellStyle name="Millares 3 69" xfId="202"/>
+    <cellStyle name="Millares 3 7" xfId="203"/>
+    <cellStyle name="Millares 3 70" xfId="204"/>
+    <cellStyle name="Millares 3 71" xfId="205"/>
+    <cellStyle name="Millares 3 72" xfId="206"/>
+    <cellStyle name="Millares 3 73" xfId="207"/>
+    <cellStyle name="Millares 3 74" xfId="208"/>
+    <cellStyle name="Millares 3 75" xfId="209"/>
+    <cellStyle name="Millares 3 76" xfId="210"/>
+    <cellStyle name="Millares 3 77" xfId="211"/>
+    <cellStyle name="Millares 3 78" xfId="212"/>
+    <cellStyle name="Millares 3 79" xfId="213"/>
+    <cellStyle name="Millares 3 8" xfId="214"/>
+    <cellStyle name="Millares 3 80" xfId="215"/>
+    <cellStyle name="Millares 3 81" xfId="216"/>
+    <cellStyle name="Millares 3 82" xfId="217"/>
+    <cellStyle name="Millares 3 83" xfId="218"/>
+    <cellStyle name="Millares 3 84" xfId="219"/>
+    <cellStyle name="Millares 3 85" xfId="220"/>
+    <cellStyle name="Millares 3 86" xfId="221"/>
+    <cellStyle name="Millares 3 87" xfId="222"/>
+    <cellStyle name="Millares 3 88" xfId="223"/>
+    <cellStyle name="Millares 3 89" xfId="224"/>
+    <cellStyle name="Millares 3 9" xfId="225"/>
+    <cellStyle name="Millares 3 90" xfId="226"/>
+    <cellStyle name="Millares 3 91" xfId="227"/>
+    <cellStyle name="Millares 3 92" xfId="228"/>
+    <cellStyle name="Millares 3 93" xfId="229"/>
+    <cellStyle name="Millares 3 94" xfId="230"/>
+    <cellStyle name="Millares 3 95" xfId="231"/>
+    <cellStyle name="Millares 3 96" xfId="232"/>
+    <cellStyle name="Millares 3 97" xfId="233"/>
+    <cellStyle name="Millares 3 98" xfId="234"/>
+    <cellStyle name="Millares 3 99" xfId="235"/>
+    <cellStyle name="Millares 4" xfId="236"/>
+    <cellStyle name="Millares 4 2" xfId="237"/>
+    <cellStyle name="Millares 5" xfId="238"/>
+    <cellStyle name="Millares 5 2" xfId="239"/>
+    <cellStyle name="Millares 5 3" xfId="240"/>
+    <cellStyle name="Millares 6" xfId="241"/>
+    <cellStyle name="Millares 6 2" xfId="242"/>
+    <cellStyle name="Millares 6 3" xfId="243"/>
+    <cellStyle name="Millares 7" xfId="244"/>
+    <cellStyle name="Millares 8" xfId="245"/>
+    <cellStyle name="Millares 8 2" xfId="246"/>
+    <cellStyle name="Millares 9" xfId="247"/>
+    <cellStyle name="Neutral 2" xfId="249"/>
+    <cellStyle name="Neutral 3" xfId="250"/>
+    <cellStyle name="Neutral 4" xfId="251"/>
+    <cellStyle name="Neutral 5" xfId="248"/>
+    <cellStyle name="NivelFila_3 2" xfId="809"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
-    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Normal 10" xfId="252"/>
+    <cellStyle name="Normal 10 2" xfId="253"/>
+    <cellStyle name="Normal 10 3" xfId="254"/>
+    <cellStyle name="Normal 10 4" xfId="255"/>
+    <cellStyle name="Normal 100" xfId="256"/>
+    <cellStyle name="Normal 100 2" xfId="257"/>
+    <cellStyle name="Normal 101" xfId="258"/>
+    <cellStyle name="Normal 101 2" xfId="259"/>
+    <cellStyle name="Normal 102" xfId="260"/>
+    <cellStyle name="Normal 102 2" xfId="261"/>
+    <cellStyle name="Normal 103" xfId="262"/>
+    <cellStyle name="Normal 103 2" xfId="263"/>
+    <cellStyle name="Normal 104" xfId="264"/>
+    <cellStyle name="Normal 104 2" xfId="265"/>
+    <cellStyle name="Normal 104 3" xfId="266"/>
+    <cellStyle name="Normal 105" xfId="267"/>
+    <cellStyle name="Normal 106" xfId="268"/>
+    <cellStyle name="Normal 106 2" xfId="269"/>
+    <cellStyle name="Normal 106 3" xfId="270"/>
+    <cellStyle name="Normal 107" xfId="271"/>
+    <cellStyle name="Normal 107 2" xfId="272"/>
+    <cellStyle name="Normal 108" xfId="273"/>
+    <cellStyle name="Normal 109" xfId="274"/>
+    <cellStyle name="Normal 11" xfId="275"/>
+    <cellStyle name="Normal 11 2" xfId="276"/>
+    <cellStyle name="Normal 11 3" xfId="277"/>
+    <cellStyle name="Normal 11 4" xfId="278"/>
+    <cellStyle name="Normal 110" xfId="279"/>
+    <cellStyle name="Normal 111" xfId="280"/>
+    <cellStyle name="Normal 112" xfId="281"/>
+    <cellStyle name="Normal 112 2" xfId="282"/>
+    <cellStyle name="Normal 113" xfId="283"/>
+    <cellStyle name="Normal 113 2" xfId="284"/>
+    <cellStyle name="Normal 114" xfId="285"/>
+    <cellStyle name="Normal 114 2" xfId="286"/>
+    <cellStyle name="Normal 115" xfId="287"/>
+    <cellStyle name="Normal 115 2" xfId="288"/>
+    <cellStyle name="Normal 116" xfId="289"/>
+    <cellStyle name="Normal 116 2" xfId="290"/>
+    <cellStyle name="Normal 116 3" xfId="291"/>
+    <cellStyle name="Normal 117" xfId="292"/>
+    <cellStyle name="Normal 117 2" xfId="293"/>
+    <cellStyle name="Normal 118" xfId="294"/>
+    <cellStyle name="Normal 118 2" xfId="295"/>
+    <cellStyle name="Normal 118 3" xfId="296"/>
+    <cellStyle name="Normal 119" xfId="297"/>
+    <cellStyle name="Normal 119 2" xfId="298"/>
+    <cellStyle name="Normal 119 3" xfId="299"/>
+    <cellStyle name="Normal 12" xfId="300"/>
+    <cellStyle name="Normal 12 2" xfId="301"/>
+    <cellStyle name="Normal 12 3" xfId="302"/>
+    <cellStyle name="Normal 12 4" xfId="303"/>
+    <cellStyle name="Normal 120" xfId="304"/>
+    <cellStyle name="Normal 120 2" xfId="305"/>
+    <cellStyle name="Normal 121" xfId="306"/>
+    <cellStyle name="Normal 121 2" xfId="307"/>
+    <cellStyle name="Normal 122" xfId="308"/>
+    <cellStyle name="Normal 122 2" xfId="309"/>
+    <cellStyle name="Normal 123" xfId="310"/>
+    <cellStyle name="Normal 124" xfId="311"/>
+    <cellStyle name="Normal 124 2" xfId="312"/>
+    <cellStyle name="Normal 125" xfId="313"/>
+    <cellStyle name="Normal 125 2" xfId="314"/>
+    <cellStyle name="Normal 126" xfId="315"/>
+    <cellStyle name="Normal 127" xfId="316"/>
+    <cellStyle name="Normal 127 2" xfId="317"/>
+    <cellStyle name="Normal 128" xfId="318"/>
+    <cellStyle name="Normal 129" xfId="319"/>
+    <cellStyle name="Normal 13" xfId="320"/>
+    <cellStyle name="Normal 13 2" xfId="321"/>
+    <cellStyle name="Normal 13 3" xfId="322"/>
+    <cellStyle name="Normal 13 4" xfId="323"/>
+    <cellStyle name="Normal 130" xfId="324"/>
+    <cellStyle name="Normal 130 2" xfId="325"/>
+    <cellStyle name="Normal 131" xfId="326"/>
+    <cellStyle name="Normal 131 2" xfId="327"/>
+    <cellStyle name="Normal 132" xfId="328"/>
+    <cellStyle name="Normal 132 2" xfId="329"/>
+    <cellStyle name="Normal 133" xfId="330"/>
+    <cellStyle name="Normal 133 2" xfId="331"/>
+    <cellStyle name="Normal 134" xfId="332"/>
+    <cellStyle name="Normal 135" xfId="333"/>
+    <cellStyle name="Normal 135 2" xfId="334"/>
+    <cellStyle name="Normal 136" xfId="335"/>
+    <cellStyle name="Normal 136 2" xfId="336"/>
+    <cellStyle name="Normal 137" xfId="337"/>
+    <cellStyle name="Normal 137 2" xfId="338"/>
+    <cellStyle name="Normal 138" xfId="339"/>
+    <cellStyle name="Normal 138 2" xfId="340"/>
+    <cellStyle name="Normal 139" xfId="341"/>
+    <cellStyle name="Normal 139 2" xfId="342"/>
+    <cellStyle name="Normal 14" xfId="343"/>
+    <cellStyle name="Normal 14 2" xfId="344"/>
+    <cellStyle name="Normal 14 3" xfId="345"/>
+    <cellStyle name="Normal 14 4" xfId="346"/>
+    <cellStyle name="Normal 140" xfId="347"/>
+    <cellStyle name="Normal 140 2" xfId="348"/>
+    <cellStyle name="Normal 141" xfId="349"/>
+    <cellStyle name="Normal 142" xfId="350"/>
+    <cellStyle name="Normal 142 2" xfId="351"/>
+    <cellStyle name="Normal 143" xfId="352"/>
+    <cellStyle name="Normal 143 2" xfId="353"/>
+    <cellStyle name="Normal 143 3" xfId="354"/>
+    <cellStyle name="Normal 144" xfId="355"/>
+    <cellStyle name="Normal 144 2" xfId="356"/>
+    <cellStyle name="Normal 145" xfId="357"/>
+    <cellStyle name="Normal 145 2" xfId="358"/>
+    <cellStyle name="Normal 146" xfId="359"/>
+    <cellStyle name="Normal 147" xfId="360"/>
+    <cellStyle name="Normal 15" xfId="361"/>
+    <cellStyle name="Normal 15 2" xfId="362"/>
+    <cellStyle name="Normal 15 3" xfId="363"/>
+    <cellStyle name="Normal 15 4" xfId="364"/>
+    <cellStyle name="Normal 16" xfId="365"/>
+    <cellStyle name="Normal 16 2" xfId="366"/>
+    <cellStyle name="Normal 16 3" xfId="367"/>
+    <cellStyle name="Normal 16 4" xfId="368"/>
+    <cellStyle name="Normal 17" xfId="369"/>
+    <cellStyle name="Normal 17 2" xfId="370"/>
+    <cellStyle name="Normal 17 3" xfId="371"/>
+    <cellStyle name="Normal 17 4" xfId="372"/>
+    <cellStyle name="Normal 18" xfId="373"/>
+    <cellStyle name="Normal 18 2" xfId="374"/>
+    <cellStyle name="Normal 18 3" xfId="375"/>
+    <cellStyle name="Normal 18 4" xfId="376"/>
+    <cellStyle name="Normal 19" xfId="377"/>
+    <cellStyle name="Normal 19 2" xfId="378"/>
+    <cellStyle name="Normal 19 3" xfId="379"/>
+    <cellStyle name="Normal 19 4" xfId="380"/>
+    <cellStyle name="Normal 2" xfId="381"/>
+    <cellStyle name="Normal 2 10" xfId="382"/>
+    <cellStyle name="Normal 2 100" xfId="383"/>
+    <cellStyle name="Normal 2 101" xfId="384"/>
+    <cellStyle name="Normal 2 102" xfId="385"/>
+    <cellStyle name="Normal 2 103" xfId="386"/>
+    <cellStyle name="Normal 2 103 2" xfId="387"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
+    <cellStyle name="Normal 2 104" xfId="389"/>
+    <cellStyle name="Normal 2 104 2" xfId="390"/>
+    <cellStyle name="Normal 2 105" xfId="391"/>
+    <cellStyle name="Normal 2 105 2" xfId="392"/>
+    <cellStyle name="Normal 2 106" xfId="393"/>
+    <cellStyle name="Normal 2 106 2" xfId="394"/>
+    <cellStyle name="Normal 2 106 3" xfId="395"/>
+    <cellStyle name="Normal 2 107" xfId="396"/>
+    <cellStyle name="Normal 2 107 2" xfId="397"/>
+    <cellStyle name="Normal 2 108" xfId="398"/>
+    <cellStyle name="Normal 2 108 2" xfId="399"/>
+    <cellStyle name="Normal 2 109" xfId="400"/>
+    <cellStyle name="Normal 2 109 2" xfId="401"/>
+    <cellStyle name="Normal 2 11" xfId="402"/>
+    <cellStyle name="Normal 2 110" xfId="403"/>
+    <cellStyle name="Normal 2 111" xfId="404"/>
+    <cellStyle name="Normal 2 112" xfId="405"/>
+    <cellStyle name="Normal 2 113" xfId="406"/>
+    <cellStyle name="Normal 2 114" xfId="407"/>
+    <cellStyle name="Normal 2 115" xfId="408"/>
+    <cellStyle name="Normal 2 12" xfId="409"/>
+    <cellStyle name="Normal 2 13" xfId="410"/>
+    <cellStyle name="Normal 2 14" xfId="411"/>
+    <cellStyle name="Normal 2 15" xfId="412"/>
+    <cellStyle name="Normal 2 16" xfId="413"/>
+    <cellStyle name="Normal 2 17" xfId="414"/>
+    <cellStyle name="Normal 2 18" xfId="415"/>
+    <cellStyle name="Normal 2 19" xfId="416"/>
+    <cellStyle name="Normal 2 2" xfId="417"/>
+    <cellStyle name="Normal 2 2 2" xfId="418"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
+    <cellStyle name="Normal 2 2 3" xfId="420"/>
+    <cellStyle name="Normal 2 2 4" xfId="421"/>
+    <cellStyle name="Normal 2 20" xfId="422"/>
+    <cellStyle name="Normal 2 21" xfId="423"/>
+    <cellStyle name="Normal 2 22" xfId="424"/>
+    <cellStyle name="Normal 2 23" xfId="425"/>
+    <cellStyle name="Normal 2 24" xfId="426"/>
+    <cellStyle name="Normal 2 25" xfId="427"/>
+    <cellStyle name="Normal 2 26" xfId="428"/>
+    <cellStyle name="Normal 2 27" xfId="429"/>
+    <cellStyle name="Normal 2 28" xfId="430"/>
+    <cellStyle name="Normal 2 29" xfId="431"/>
+    <cellStyle name="Normal 2 3" xfId="432"/>
+    <cellStyle name="Normal 2 3 2" xfId="433"/>
+    <cellStyle name="Normal 2 3 3" xfId="434"/>
+    <cellStyle name="Normal 2 30" xfId="435"/>
+    <cellStyle name="Normal 2 31" xfId="436"/>
+    <cellStyle name="Normal 2 32" xfId="437"/>
+    <cellStyle name="Normal 2 33" xfId="438"/>
+    <cellStyle name="Normal 2 34" xfId="439"/>
+    <cellStyle name="Normal 2 35" xfId="440"/>
+    <cellStyle name="Normal 2 36" xfId="441"/>
+    <cellStyle name="Normal 2 37" xfId="442"/>
+    <cellStyle name="Normal 2 38" xfId="443"/>
+    <cellStyle name="Normal 2 39" xfId="444"/>
+    <cellStyle name="Normal 2 4" xfId="445"/>
+    <cellStyle name="Normal 2 4 2" xfId="446"/>
+    <cellStyle name="Normal 2 4 3" xfId="447"/>
+    <cellStyle name="Normal 2 4 4" xfId="448"/>
+    <cellStyle name="Normal 2 40" xfId="449"/>
+    <cellStyle name="Normal 2 41" xfId="450"/>
+    <cellStyle name="Normal 2 42" xfId="451"/>
+    <cellStyle name="Normal 2 43" xfId="452"/>
+    <cellStyle name="Normal 2 44" xfId="453"/>
+    <cellStyle name="Normal 2 45" xfId="454"/>
+    <cellStyle name="Normal 2 45 10" xfId="455"/>
+    <cellStyle name="Normal 2 45 11" xfId="456"/>
+    <cellStyle name="Normal 2 45 12" xfId="457"/>
+    <cellStyle name="Normal 2 45 13" xfId="458"/>
+    <cellStyle name="Normal 2 45 14" xfId="459"/>
+    <cellStyle name="Normal 2 45 15" xfId="460"/>
+    <cellStyle name="Normal 2 45 16" xfId="461"/>
+    <cellStyle name="Normal 2 45 17" xfId="462"/>
+    <cellStyle name="Normal 2 45 18" xfId="463"/>
+    <cellStyle name="Normal 2 45 19" xfId="464"/>
+    <cellStyle name="Normal 2 45 2" xfId="465"/>
+    <cellStyle name="Normal 2 45 20" xfId="466"/>
+    <cellStyle name="Normal 2 45 21" xfId="467"/>
+    <cellStyle name="Normal 2 45 22" xfId="468"/>
+    <cellStyle name="Normal 2 45 23" xfId="469"/>
+    <cellStyle name="Normal 2 45 24" xfId="470"/>
+    <cellStyle name="Normal 2 45 25" xfId="471"/>
+    <cellStyle name="Normal 2 45 26" xfId="472"/>
+    <cellStyle name="Normal 2 45 27" xfId="473"/>
+    <cellStyle name="Normal 2 45 28" xfId="474"/>
+    <cellStyle name="Normal 2 45 29" xfId="475"/>
+    <cellStyle name="Normal 2 45 3" xfId="476"/>
+    <cellStyle name="Normal 2 45 30" xfId="477"/>
+    <cellStyle name="Normal 2 45 31" xfId="478"/>
+    <cellStyle name="Normal 2 45 32" xfId="479"/>
+    <cellStyle name="Normal 2 45 33" xfId="480"/>
+    <cellStyle name="Normal 2 45 34" xfId="481"/>
+    <cellStyle name="Normal 2 45 35" xfId="482"/>
+    <cellStyle name="Normal 2 45 36" xfId="483"/>
+    <cellStyle name="Normal 2 45 37" xfId="484"/>
+    <cellStyle name="Normal 2 45 38" xfId="485"/>
+    <cellStyle name="Normal 2 45 39" xfId="486"/>
+    <cellStyle name="Normal 2 45 4" xfId="487"/>
+    <cellStyle name="Normal 2 45 40" xfId="488"/>
+    <cellStyle name="Normal 2 45 41" xfId="489"/>
+    <cellStyle name="Normal 2 45 42" xfId="490"/>
+    <cellStyle name="Normal 2 45 43" xfId="491"/>
+    <cellStyle name="Normal 2 45 44" xfId="492"/>
+    <cellStyle name="Normal 2 45 45" xfId="493"/>
+    <cellStyle name="Normal 2 45 46" xfId="494"/>
+    <cellStyle name="Normal 2 45 47" xfId="495"/>
+    <cellStyle name="Normal 2 45 48" xfId="496"/>
+    <cellStyle name="Normal 2 45 49" xfId="497"/>
+    <cellStyle name="Normal 2 45 5" xfId="498"/>
+    <cellStyle name="Normal 2 45 50" xfId="499"/>
+    <cellStyle name="Normal 2 45 51" xfId="500"/>
+    <cellStyle name="Normal 2 45 52" xfId="501"/>
+    <cellStyle name="Normal 2 45 53" xfId="502"/>
+    <cellStyle name="Normal 2 45 54" xfId="503"/>
+    <cellStyle name="Normal 2 45 55" xfId="504"/>
+    <cellStyle name="Normal 2 45 56" xfId="505"/>
+    <cellStyle name="Normal 2 45 57" xfId="506"/>
+    <cellStyle name="Normal 2 45 58" xfId="507"/>
+    <cellStyle name="Normal 2 45 59" xfId="508"/>
+    <cellStyle name="Normal 2 45 6" xfId="509"/>
+    <cellStyle name="Normal 2 45 7" xfId="510"/>
+    <cellStyle name="Normal 2 45 8" xfId="511"/>
+    <cellStyle name="Normal 2 45 9" xfId="512"/>
+    <cellStyle name="Normal 2 46" xfId="513"/>
+    <cellStyle name="Normal 2 47" xfId="514"/>
+    <cellStyle name="Normal 2 48" xfId="515"/>
+    <cellStyle name="Normal 2 49" xfId="516"/>
+    <cellStyle name="Normal 2 5" xfId="517"/>
+    <cellStyle name="Normal 2 5 2" xfId="518"/>
+    <cellStyle name="Normal 2 5 3" xfId="519"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
+    <cellStyle name="Normal 2 5 4" xfId="521"/>
+    <cellStyle name="Normal 2 50" xfId="522"/>
+    <cellStyle name="Normal 2 51" xfId="523"/>
+    <cellStyle name="Normal 2 52" xfId="524"/>
+    <cellStyle name="Normal 2 53" xfId="525"/>
+    <cellStyle name="Normal 2 54" xfId="526"/>
+    <cellStyle name="Normal 2 55" xfId="527"/>
+    <cellStyle name="Normal 2 56" xfId="528"/>
+    <cellStyle name="Normal 2 57" xfId="529"/>
+    <cellStyle name="Normal 2 58" xfId="530"/>
+    <cellStyle name="Normal 2 59" xfId="531"/>
+    <cellStyle name="Normal 2 6" xfId="532"/>
+    <cellStyle name="Normal 2 6 2" xfId="533"/>
+    <cellStyle name="Normal 2 60" xfId="534"/>
+    <cellStyle name="Normal 2 61" xfId="535"/>
+    <cellStyle name="Normal 2 62" xfId="536"/>
+    <cellStyle name="Normal 2 63" xfId="537"/>
+    <cellStyle name="Normal 2 64" xfId="538"/>
+    <cellStyle name="Normal 2 65" xfId="539"/>
+    <cellStyle name="Normal 2 66" xfId="540"/>
+    <cellStyle name="Normal 2 67" xfId="541"/>
+    <cellStyle name="Normal 2 68" xfId="542"/>
+    <cellStyle name="Normal 2 69" xfId="543"/>
+    <cellStyle name="Normal 2 7" xfId="544"/>
+    <cellStyle name="Normal 2 70" xfId="545"/>
+    <cellStyle name="Normal 2 71" xfId="546"/>
+    <cellStyle name="Normal 2 72" xfId="547"/>
+    <cellStyle name="Normal 2 73" xfId="548"/>
+    <cellStyle name="Normal 2 74" xfId="549"/>
+    <cellStyle name="Normal 2 75" xfId="550"/>
+    <cellStyle name="Normal 2 76" xfId="551"/>
+    <cellStyle name="Normal 2 77" xfId="552"/>
+    <cellStyle name="Normal 2 78" xfId="553"/>
+    <cellStyle name="Normal 2 79" xfId="554"/>
+    <cellStyle name="Normal 2 8" xfId="555"/>
+    <cellStyle name="Normal 2 80" xfId="556"/>
+    <cellStyle name="Normal 2 81" xfId="557"/>
+    <cellStyle name="Normal 2 82" xfId="558"/>
+    <cellStyle name="Normal 2 83" xfId="559"/>
+    <cellStyle name="Normal 2 84" xfId="560"/>
+    <cellStyle name="Normal 2 85" xfId="561"/>
+    <cellStyle name="Normal 2 86" xfId="562"/>
+    <cellStyle name="Normal 2 87" xfId="563"/>
+    <cellStyle name="Normal 2 88" xfId="564"/>
+    <cellStyle name="Normal 2 89" xfId="565"/>
+    <cellStyle name="Normal 2 9" xfId="566"/>
+    <cellStyle name="Normal 2 90" xfId="567"/>
+    <cellStyle name="Normal 2 91" xfId="568"/>
+    <cellStyle name="Normal 2 92" xfId="569"/>
+    <cellStyle name="Normal 2 93" xfId="570"/>
+    <cellStyle name="Normal 2 94" xfId="571"/>
+    <cellStyle name="Normal 2 95" xfId="572"/>
+    <cellStyle name="Normal 2 96" xfId="573"/>
+    <cellStyle name="Normal 2 97" xfId="574"/>
+    <cellStyle name="Normal 2 98" xfId="575"/>
+    <cellStyle name="Normal 2 99" xfId="576"/>
+    <cellStyle name="Normal 20" xfId="577"/>
+    <cellStyle name="Normal 20 2" xfId="578"/>
+    <cellStyle name="Normal 20 3" xfId="579"/>
+    <cellStyle name="Normal 20 4" xfId="580"/>
+    <cellStyle name="Normal 21" xfId="581"/>
+    <cellStyle name="Normal 21 2" xfId="582"/>
+    <cellStyle name="Normal 21 3" xfId="583"/>
+    <cellStyle name="Normal 21 4" xfId="584"/>
+    <cellStyle name="Normal 22" xfId="585"/>
+    <cellStyle name="Normal 22 2" xfId="586"/>
+    <cellStyle name="Normal 22 3" xfId="587"/>
+    <cellStyle name="Normal 22 4" xfId="588"/>
+    <cellStyle name="Normal 23" xfId="589"/>
+    <cellStyle name="Normal 23 2" xfId="590"/>
+    <cellStyle name="Normal 23 3" xfId="591"/>
+    <cellStyle name="Normal 24" xfId="592"/>
+    <cellStyle name="Normal 24 2" xfId="593"/>
+    <cellStyle name="Normal 24 3" xfId="594"/>
+    <cellStyle name="Normal 25" xfId="595"/>
+    <cellStyle name="Normal 26" xfId="596"/>
+    <cellStyle name="Normal 27" xfId="597"/>
+    <cellStyle name="Normal 28" xfId="598"/>
+    <cellStyle name="Normal 29" xfId="599"/>
+    <cellStyle name="Normal 3" xfId="600"/>
+    <cellStyle name="Normal 3 2" xfId="601"/>
+    <cellStyle name="Normal 3 2 2" xfId="602"/>
+    <cellStyle name="Normal 3 3" xfId="603"/>
+    <cellStyle name="Normal 3 3 2" xfId="604"/>
+    <cellStyle name="Normal 3 3 3" xfId="605"/>
+    <cellStyle name="Normal 3 4" xfId="606"/>
+    <cellStyle name="Normal 3 5" xfId="607"/>
+    <cellStyle name="Normal 30" xfId="608"/>
+    <cellStyle name="Normal 31" xfId="609"/>
+    <cellStyle name="Normal 32" xfId="610"/>
+    <cellStyle name="Normal 33" xfId="611"/>
+    <cellStyle name="Normal 34" xfId="612"/>
+    <cellStyle name="Normal 35" xfId="613"/>
+    <cellStyle name="Normal 36" xfId="614"/>
+    <cellStyle name="Normal 37" xfId="615"/>
+    <cellStyle name="Normal 38" xfId="616"/>
+    <cellStyle name="Normal 39" xfId="617"/>
+    <cellStyle name="Normal 4" xfId="618"/>
+    <cellStyle name="Normal 4 2" xfId="619"/>
+    <cellStyle name="Normal 4 2 2" xfId="620"/>
+    <cellStyle name="Normal 4 3" xfId="621"/>
+    <cellStyle name="Normal 4 4" xfId="622"/>
+    <cellStyle name="Normal 40" xfId="623"/>
+    <cellStyle name="Normal 41" xfId="624"/>
+    <cellStyle name="Normal 42" xfId="625"/>
+    <cellStyle name="Normal 43" xfId="626"/>
+    <cellStyle name="Normal 44" xfId="627"/>
+    <cellStyle name="Normal 45" xfId="628"/>
+    <cellStyle name="Normal 46" xfId="629"/>
+    <cellStyle name="Normal 47" xfId="630"/>
+    <cellStyle name="Normal 48" xfId="631"/>
+    <cellStyle name="Normal 49" xfId="632"/>
+    <cellStyle name="Normal 5" xfId="633"/>
+    <cellStyle name="Normal 5 10" xfId="634"/>
+    <cellStyle name="Normal 5 11" xfId="635"/>
+    <cellStyle name="Normal 5 12" xfId="636"/>
+    <cellStyle name="Normal 5 13" xfId="637"/>
+    <cellStyle name="Normal 5 14" xfId="638"/>
+    <cellStyle name="Normal 5 15" xfId="639"/>
+    <cellStyle name="Normal 5 16" xfId="640"/>
+    <cellStyle name="Normal 5 17" xfId="641"/>
+    <cellStyle name="Normal 5 18" xfId="642"/>
+    <cellStyle name="Normal 5 19" xfId="643"/>
+    <cellStyle name="Normal 5 2" xfId="644"/>
+    <cellStyle name="Normal 5 20" xfId="645"/>
+    <cellStyle name="Normal 5 21" xfId="646"/>
+    <cellStyle name="Normal 5 22" xfId="647"/>
+    <cellStyle name="Normal 5 23" xfId="648"/>
+    <cellStyle name="Normal 5 24" xfId="649"/>
+    <cellStyle name="Normal 5 25" xfId="650"/>
+    <cellStyle name="Normal 5 26" xfId="651"/>
+    <cellStyle name="Normal 5 27" xfId="652"/>
+    <cellStyle name="Normal 5 28" xfId="653"/>
+    <cellStyle name="Normal 5 28 10" xfId="654"/>
+    <cellStyle name="Normal 5 28 11" xfId="655"/>
+    <cellStyle name="Normal 5 28 12" xfId="656"/>
+    <cellStyle name="Normal 5 28 13" xfId="657"/>
+    <cellStyle name="Normal 5 28 14" xfId="658"/>
+    <cellStyle name="Normal 5 28 15" xfId="659"/>
+    <cellStyle name="Normal 5 28 16" xfId="660"/>
+    <cellStyle name="Normal 5 28 17" xfId="661"/>
+    <cellStyle name="Normal 5 28 18" xfId="662"/>
+    <cellStyle name="Normal 5 28 19" xfId="663"/>
+    <cellStyle name="Normal 5 28 2" xfId="664"/>
+    <cellStyle name="Normal 5 28 20" xfId="665"/>
+    <cellStyle name="Normal 5 28 21" xfId="666"/>
+    <cellStyle name="Normal 5 28 22" xfId="667"/>
+    <cellStyle name="Normal 5 28 23" xfId="668"/>
+    <cellStyle name="Normal 5 28 24" xfId="669"/>
+    <cellStyle name="Normal 5 28 25" xfId="670"/>
+    <cellStyle name="Normal 5 28 3" xfId="671"/>
+    <cellStyle name="Normal 5 28 4" xfId="672"/>
+    <cellStyle name="Normal 5 28 5" xfId="673"/>
+    <cellStyle name="Normal 5 28 6" xfId="674"/>
+    <cellStyle name="Normal 5 28 7" xfId="675"/>
+    <cellStyle name="Normal 5 28 8" xfId="676"/>
+    <cellStyle name="Normal 5 28 9" xfId="677"/>
+    <cellStyle name="Normal 5 29" xfId="678"/>
+    <cellStyle name="Normal 5 3" xfId="679"/>
+    <cellStyle name="Normal 5 4" xfId="680"/>
+    <cellStyle name="Normal 5 5" xfId="681"/>
+    <cellStyle name="Normal 5 6" xfId="682"/>
+    <cellStyle name="Normal 5 7" xfId="683"/>
+    <cellStyle name="Normal 5 8" xfId="684"/>
+    <cellStyle name="Normal 5 9" xfId="685"/>
+    <cellStyle name="Normal 50" xfId="686"/>
+    <cellStyle name="Normal 51" xfId="687"/>
+    <cellStyle name="Normal 52" xfId="688"/>
+    <cellStyle name="Normal 53" xfId="689"/>
+    <cellStyle name="Normal 54" xfId="690"/>
+    <cellStyle name="Normal 55" xfId="691"/>
+    <cellStyle name="Normal 56" xfId="2"/>
+    <cellStyle name="Normal 56 2" xfId="692"/>
+    <cellStyle name="Normal 57" xfId="693"/>
+    <cellStyle name="Normal 58" xfId="694"/>
+    <cellStyle name="Normal 59" xfId="695"/>
+    <cellStyle name="Normal 6" xfId="696"/>
+    <cellStyle name="Normal 6 2" xfId="697"/>
+    <cellStyle name="Normal 6 2 2" xfId="698"/>
+    <cellStyle name="Normal 6 2 3" xfId="699"/>
+    <cellStyle name="Normal 6 3" xfId="700"/>
+    <cellStyle name="Normal 6 4" xfId="701"/>
+    <cellStyle name="Normal 60" xfId="702"/>
+    <cellStyle name="Normal 61" xfId="703"/>
+    <cellStyle name="Normal 62" xfId="704"/>
+    <cellStyle name="Normal 63" xfId="705"/>
+    <cellStyle name="Normal 64" xfId="706"/>
+    <cellStyle name="Normal 65" xfId="707"/>
+    <cellStyle name="Normal 66" xfId="708"/>
+    <cellStyle name="Normal 67" xfId="709"/>
+    <cellStyle name="Normal 68" xfId="710"/>
+    <cellStyle name="Normal 69" xfId="711"/>
+    <cellStyle name="Normal 7" xfId="712"/>
+    <cellStyle name="Normal 7 2" xfId="713"/>
+    <cellStyle name="Normal 7 3" xfId="714"/>
+    <cellStyle name="Normal 7 4" xfId="715"/>
+    <cellStyle name="Normal 70" xfId="716"/>
+    <cellStyle name="Normal 71" xfId="717"/>
+    <cellStyle name="Normal 72" xfId="718"/>
+    <cellStyle name="Normal 73" xfId="719"/>
+    <cellStyle name="Normal 74" xfId="720"/>
+    <cellStyle name="Normal 75" xfId="721"/>
+    <cellStyle name="Normal 76" xfId="722"/>
+    <cellStyle name="Normal 77" xfId="723"/>
+    <cellStyle name="Normal 78" xfId="724"/>
+    <cellStyle name="Normal 79" xfId="725"/>
+    <cellStyle name="Normal 79 2" xfId="726"/>
+    <cellStyle name="Normal 79 3" xfId="727"/>
+    <cellStyle name="Normal 8" xfId="728"/>
+    <cellStyle name="Normal 8 2" xfId="729"/>
+    <cellStyle name="Normal 8 3" xfId="730"/>
+    <cellStyle name="Normal 8 4" xfId="731"/>
+    <cellStyle name="Normal 80" xfId="732"/>
+    <cellStyle name="Normal 80 2" xfId="733"/>
+    <cellStyle name="Normal 81" xfId="734"/>
+    <cellStyle name="Normal 81 2" xfId="735"/>
+    <cellStyle name="Normal 82" xfId="736"/>
+    <cellStyle name="Normal 82 2" xfId="737"/>
+    <cellStyle name="Normal 82 2 2" xfId="738"/>
+    <cellStyle name="Normal 83" xfId="739"/>
+    <cellStyle name="Normal 83 2" xfId="740"/>
+    <cellStyle name="Normal 83 2 2" xfId="741"/>
+    <cellStyle name="Normal 84" xfId="742"/>
+    <cellStyle name="Normal 84 2" xfId="743"/>
+    <cellStyle name="Normal 84 3" xfId="744"/>
+    <cellStyle name="Normal 85" xfId="745"/>
+    <cellStyle name="Normal 85 2" xfId="746"/>
+    <cellStyle name="Normal 85 3" xfId="747"/>
+    <cellStyle name="Normal 86" xfId="748"/>
+    <cellStyle name="Normal 86 2" xfId="749"/>
+    <cellStyle name="Normal 86 3" xfId="750"/>
+    <cellStyle name="Normal 87" xfId="751"/>
+    <cellStyle name="Normal 87 2" xfId="752"/>
+    <cellStyle name="Normal 87 3" xfId="753"/>
+    <cellStyle name="Normal 88" xfId="754"/>
+    <cellStyle name="Normal 88 2" xfId="755"/>
+    <cellStyle name="Normal 88 3" xfId="756"/>
+    <cellStyle name="Normal 88 4" xfId="757"/>
+    <cellStyle name="Normal 89" xfId="758"/>
+    <cellStyle name="Normal 9" xfId="759"/>
+    <cellStyle name="Normal 9 2" xfId="760"/>
+    <cellStyle name="Normal 9 3" xfId="761"/>
+    <cellStyle name="Normal 9 4" xfId="762"/>
+    <cellStyle name="Normal 90" xfId="763"/>
+    <cellStyle name="Normal 91" xfId="764"/>
+    <cellStyle name="Normal 92" xfId="765"/>
+    <cellStyle name="Normal 93" xfId="766"/>
+    <cellStyle name="Normal 94" xfId="767"/>
+    <cellStyle name="Normal 94 2" xfId="768"/>
+    <cellStyle name="Normal 95" xfId="769"/>
+    <cellStyle name="Normal 95 2" xfId="770"/>
+    <cellStyle name="Normal 95 3" xfId="771"/>
+    <cellStyle name="Normal 96" xfId="772"/>
+    <cellStyle name="Normal 97" xfId="773"/>
+    <cellStyle name="Normal 97 2" xfId="774"/>
+    <cellStyle name="Normal 98" xfId="775"/>
+    <cellStyle name="Normal 98 2" xfId="776"/>
+    <cellStyle name="Normal 99" xfId="777"/>
+    <cellStyle name="Normal 99 2" xfId="778"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3"/>
+    <cellStyle name="Notas 2" xfId="779"/>
+    <cellStyle name="Notas 2 2" xfId="780"/>
+    <cellStyle name="Notas 2 3" xfId="781"/>
+    <cellStyle name="Notas 3" xfId="782"/>
+    <cellStyle name="Notas 4" xfId="783"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785"/>
+    <cellStyle name="Salida 2" xfId="786"/>
+    <cellStyle name="Salida 3" xfId="787"/>
+    <cellStyle name="Salida 4" xfId="788"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791"/>
+    <cellStyle name="Texto explicativo 2" xfId="792"/>
+    <cellStyle name="Texto explicativo 3" xfId="793"/>
+    <cellStyle name="Texto explicativo 4" xfId="794"/>
+    <cellStyle name="Título 1 2" xfId="795"/>
+    <cellStyle name="Título 2 2" xfId="796"/>
+    <cellStyle name="Título 2 3" xfId="797"/>
+    <cellStyle name="Título 2 4" xfId="798"/>
+    <cellStyle name="Título 3 2" xfId="799"/>
+    <cellStyle name="Título 3 3" xfId="800"/>
+    <cellStyle name="Título 3 4" xfId="801"/>
+    <cellStyle name="Título 4" xfId="802"/>
+    <cellStyle name="Título 5" xfId="803"/>
+    <cellStyle name="Título 6" xfId="804"/>
+    <cellStyle name="Total 2" xfId="806"/>
+    <cellStyle name="Total 3" xfId="807"/>
+    <cellStyle name="Total 4" xfId="808"/>
+    <cellStyle name="Total 5" xfId="805"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2595,26 +2637,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2630,8 +2672,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+    <row r="2" spans="1:8">
+      <c r="A2" s="18">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -2647,8 +2689,8 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+    <row r="3" spans="1:8">
+      <c r="A3" s="18">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -2664,8 +2706,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+    <row r="4" spans="1:8">
+      <c r="A4" s="18">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -2681,8 +2723,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+    <row r="5" spans="1:8">
+      <c r="A5" s="18">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -2698,8 +2740,8 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:8">
+      <c r="A6" s="18">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -2715,8 +2757,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+    <row r="7" spans="1:8">
+      <c r="A7" s="18">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -2732,8 +2774,8 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+    <row r="8" spans="1:8">
+      <c r="A8" s="18">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -2749,8 +2791,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+    <row r="9" spans="1:8">
+      <c r="A9" s="18">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -2766,8 +2808,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+    <row r="10" spans="1:8">
+      <c r="A10" s="18">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -2783,8 +2825,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+    <row r="11" spans="1:8">
+      <c r="A11" s="18">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -2800,8 +2842,8 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+    <row r="12" spans="1:8">
+      <c r="A12" s="18">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -2817,8 +2859,8 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+    <row r="13" spans="1:8">
+      <c r="A13" s="18">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -2834,8 +2876,8 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+    <row r="14" spans="1:8">
+      <c r="A14" s="18">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -2851,8 +2893,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
+    <row r="15" spans="1:8">
+      <c r="A15" s="18">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -2868,8 +2910,8 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+    <row r="16" spans="1:8">
+      <c r="A16" s="18">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -2885,8 +2927,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
+    <row r="17" spans="1:8">
+      <c r="A17" s="18">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -2902,8 +2944,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
+    <row r="18" spans="1:8">
+      <c r="A18" s="18">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -2919,8 +2961,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
+    <row r="19" spans="1:8">
+      <c r="A19" s="18">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -2936,8 +2978,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
+    <row r="20" spans="1:8">
+      <c r="A20" s="18">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -2953,8 +2995,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+    <row r="21" spans="1:8">
+      <c r="A21" s="18">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -2970,8 +3012,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+    <row r="22" spans="1:8">
+      <c r="A22" s="18">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -2987,8 +3029,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+    <row r="23" spans="1:8">
+      <c r="A23" s="18">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3004,8 +3046,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
+    <row r="24" spans="1:8">
+      <c r="A24" s="18">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3021,8 +3063,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
+    <row r="25" spans="1:8">
+      <c r="A25" s="18">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3038,8 +3080,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+    <row r="26" spans="1:8">
+      <c r="A26" s="18">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3055,8 +3097,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
+    <row r="27" spans="1:8">
+      <c r="A27" s="18">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3072,8 +3114,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
+    <row r="28" spans="1:8">
+      <c r="A28" s="18">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3089,124 +3131,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
+    <row r="29" spans="1:8">
+      <c r="A29" s="18">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="9"/>
+      <c r="E29" s="14"/>
       <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="9"/>
+      <c r="G29" s="14"/>
       <c r="H29" s="1">
         <v>18.43</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
+    <row r="30" spans="1:8">
+      <c r="A30" s="18">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
+    <row r="31" spans="1:8">
+      <c r="A31" s="18">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="11"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+    <row r="32" spans="1:8">
+      <c r="A32" s="18">
         <v>46148</v>
       </c>
       <c r="B32" s="1">
         <v>1200</v>
       </c>
-      <c r="C32" s="11"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="1">
         <v>100</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="11"/>
+      <c r="G32" s="16"/>
       <c r="H32" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
+    <row r="33" spans="1:8">
+      <c r="A33" s="18">
+        <v>46149</v>
+      </c>
+      <c r="B33" s="1">
+        <v>32505.648000000001</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="1">
+        <v>150</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="1">
+        <v>300</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="1">
+        <v>243.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="18"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="20"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="18"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="11"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="11"/>
+      <c r="E36" s="16"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="11"/>
+      <c r="G36" s="16"/>
       <c r="H36" s="1"/>
     </row>
   </sheetData>
@@ -3216,27 +3268,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14" style="16" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
@@ -3244,327 +3292,236 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C2" s="19">
-        <f>+((B2-B3)/B3)*100</f>
-        <v>-99.115816107458954</v>
+        <v>131.99794839</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="12">
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B3">
-        <v>84317.802960360001</v>
-      </c>
-      <c r="C3" s="19">
-        <f t="shared" ref="C3:C26" si="0">+((B3-B4)/B4)*100</f>
-        <v>70.107388483787062</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="12">
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B4">
-        <v>49567.396050169998</v>
-      </c>
-      <c r="C4" s="19">
-        <f t="shared" si="0"/>
-        <v>-43.255825515735765</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="13">
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>46142</v>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>46146</v>
       </c>
       <c r="B5">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C5" s="19">
-        <f t="shared" si="0"/>
-        <v>207.73664296544806</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="13">
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:5">
+      <c r="A6" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B6">
+        <v>87352.396084139997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="11">
         <v>46141</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>28385.438679769999</v>
       </c>
-      <c r="C6" s="19">
-        <f t="shared" si="0"/>
-        <v>-59.636256133262869</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="11">
         <v>46140</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>70324.097718699995</v>
       </c>
-      <c r="C7" s="19">
-        <f t="shared" si="0"/>
-        <v>74.333012643706198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="11">
         <v>46139</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>40338.944788629997</v>
       </c>
-      <c r="C8" s="19">
-        <f t="shared" si="0"/>
-        <v>-33.842006324553125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="11">
         <v>46136</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>60973.651931649998</v>
       </c>
-      <c r="C9" s="19">
-        <f t="shared" si="0"/>
-        <v>1210.6463903543759</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="11">
         <v>46135</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C10" s="19">
-        <f t="shared" si="0"/>
-        <v>-73.032401489373797</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="11">
         <v>46134</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>17251.00486529</v>
       </c>
-      <c r="C11" s="19">
-        <f t="shared" si="0"/>
-        <v>-64.046760511667529</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11">
         <v>46133</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>47981.781644150004</v>
       </c>
-      <c r="C12" s="19">
-        <f t="shared" si="0"/>
-        <v>-6.5402088492716128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="11">
         <v>46132</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>51339.49161813</v>
       </c>
-      <c r="C13" s="19">
-        <f t="shared" si="0"/>
-        <v>198.19948129202027</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="11">
         <v>46129</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C14" s="19">
-        <f t="shared" si="0"/>
-        <v>91040.237411852577</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="11">
         <v>46128</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C15" s="19">
-        <f t="shared" si="0"/>
-        <v>19.572063797541304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="11">
         <v>46127</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>15.79809785</v>
       </c>
-      <c r="C16" s="19">
-        <f t="shared" si="0"/>
-        <v>-2.5764893835585476</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="11">
         <v>46126</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>16.215898760000002</v>
       </c>
-      <c r="C17" s="19">
-        <f t="shared" si="0"/>
-        <v>-99.344926580920657</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="11">
         <v>46125</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C18" s="19">
-        <f t="shared" si="0"/>
-        <v>-68.887087467151304</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="11">
         <v>46122</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C19" s="19">
-        <f t="shared" si="0"/>
-        <v>19054.886991293832</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11">
         <v>46121</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>41.536584740000002</v>
       </c>
-      <c r="C20" s="19">
-        <f t="shared" si="0"/>
-        <v>-92.845434694034026</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="11">
         <v>46120</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>580.56056466999996</v>
       </c>
-      <c r="C21" s="19">
-        <f t="shared" si="0"/>
-        <v>396.32497533121034</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="11">
         <v>46119</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>116.97186189</v>
       </c>
-      <c r="C22" s="19">
-        <f t="shared" si="0"/>
-        <v>-98.322351149824243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="11">
         <v>46118</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>6972.36861443</v>
       </c>
-      <c r="C23" s="19">
-        <f t="shared" si="0"/>
-        <v>1191.1589836815915</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="11">
         <v>46113</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>540.00852741999995</v>
       </c>
-      <c r="C24" s="19">
-        <f t="shared" si="0"/>
-        <v>-89.738241267184833</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="11">
         <v>46112</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>5262.3389565099997</v>
       </c>
-      <c r="C25" s="19">
-        <f t="shared" si="0"/>
-        <v>-77.08997404756451</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="11">
         <v>46111</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>22969.58967849</v>
-      </c>
-      <c r="C26" s="19">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3574,17 +3531,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3598,7 +3555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3612,7 +3569,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3626,7 +3583,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3640,7 +3597,7 @@
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3650,7 +3607,7 @@
       <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="15">
         <v>64.09</v>
       </c>
     </row>
@@ -3661,16 +3618,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3681,7 +3638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>46024</v>
       </c>
@@ -3690,7 +3647,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2">
         <v>46031</v>
       </c>
@@ -3698,10 +3655,10 @@
         <v>631055414.05422926</v>
       </c>
       <c r="C3" s="4">
-        <v>-7.2050081634151582</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-7.2050081634151608E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>46038</v>
       </c>
@@ -3709,10 +3666,10 @@
         <v>687738190.99875975</v>
       </c>
       <c r="C4" s="4">
-        <v>8.9822186264706527</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8.9822186264706616E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2">
         <v>46045</v>
       </c>
@@ -3720,10 +3677,10 @@
         <v>728876050.32802963</v>
       </c>
       <c r="C5" s="4">
-        <v>5.9816162411350033</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.9816162411350016E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="2">
         <v>46052</v>
       </c>
@@ -3731,10 +3688,10 @@
         <v>839643409.76085114</v>
       </c>
       <c r="C6" s="4">
-        <v>15.197009063882785</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.15197009063882794</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2">
         <v>46059</v>
       </c>
@@ -3742,97 +3699,96 @@
         <v>818274973.23848069</v>
       </c>
       <c r="C7" s="4">
-        <v>-2.5449418495950149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-2.5449418495950171E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="2">
         <v>46066</v>
       </c>
       <c r="B8" s="1">
         <v>801808360.23688257</v>
       </c>
-      <c r="C8" s="4">
-        <v>-2.0123569142568702</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="5">
+        <v>-2.0123569142568742E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>46073</v>
       </c>
       <c r="B9" s="1">
         <v>886542333.87268889</v>
       </c>
-      <c r="C9" s="4">
-        <v>10.56785858540723</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>46080</v>
       </c>
       <c r="B10" s="1">
         <v>938549580.20021927</v>
       </c>
-      <c r="C10" s="4">
-        <v>5.8663015109889649</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="7">
+        <v>5.8663015109889693E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>46087</v>
       </c>
       <c r="B11" s="1">
         <v>870061809.65898001</v>
       </c>
-      <c r="C11" s="4">
-        <v>-7.2971926029340803</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="7">
+        <v>-7.2971926029340772E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>46094</v>
       </c>
       <c r="B12" s="1">
         <v>959597484.45129991</v>
       </c>
-      <c r="C12" s="4">
-        <v>10.290725762048252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="7">
+        <v>0.10290725762048258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>46101</v>
       </c>
       <c r="B13" s="1">
         <v>1136404345.7909815</v>
       </c>
-      <c r="C13" s="4">
-        <v>18.425106797854955</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="7">
+        <v>0.18425106797854962</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="2">
         <v>46108</v>
       </c>
       <c r="B14" s="1">
         <v>1111572721.2404912</v>
       </c>
-      <c r="C14" s="4">
-        <f>+((B14-B13)/B13)*100</f>
-        <v>-2.1851046806061447</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="8">
+        <v>-2.1851046806061425E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="2">
         <v>46129</v>
       </c>
       <c r="B15" s="1">
         <v>1071533894.2527295</v>
       </c>
-      <c r="C15" s="4">
-        <f>+((B15-B14)/B14)*100</f>
-        <v>-3.6019979820194892</v>
+      <c r="C15" s="8">
+        <f>+(B15-B14)/B14</f>
+        <v>-3.6019979820194892E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3841,21 +3797,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.75" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3881,7 +3837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -3903,11 +3859,11 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>46115</v>
       </c>
@@ -3929,12 +3885,11 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="18">
-        <f>+((G3-G2)/G2)*100</f>
-        <v>-1.4067445693212368</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="9">
+        <v>-1.4067445693212388E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -3956,12 +3911,11 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="18">
-        <f>+((G4-G3)/G3)*100</f>
-        <v>0.9756937784346702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H4" s="9">
+        <v>9.7569377843467198E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -3983,12 +3937,11 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="18">
-        <f>+((G5-G4)/G4)*100</f>
-        <v>3.4749018512476764</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="9">
+        <v>3.4749018512476804E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4010,9 +3963,8 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="18">
-        <f>+((G6-G5)/G5)*100</f>
-        <v>3.0146874710954426</v>
+      <c r="H6" s="9">
+        <v>3.0099999999999998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4021,19 +3973,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -4046,14 +3998,14 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -4066,14 +4018,14 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="17">
+        <v>-2.681224004753413E-2</v>
+      </c>
+      <c r="F2" s="10">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>46113</v>
       </c>
@@ -4086,15 +4038,14 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3" s="5">
-        <f>+((D3-D2)/D2)*100</f>
-        <v>4.8691139433717465</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3">
+        <v>4.8691139433717501E-2</v>
+      </c>
+      <c r="F3" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -4107,15 +4058,14 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4" s="5">
-        <f>+((D4-D3)/D3)*100</f>
-        <v>-1.1061785896222982</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4">
+        <v>-1.1061785896222975E-2</v>
+      </c>
+      <c r="F4" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -4128,15 +4078,14 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5" s="5">
-        <f>+((D5-D4)/D4)*100</f>
-        <v>0.62550592390904403</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5">
+        <v>6.2550592390904214E-3</v>
+      </c>
+      <c r="F5" s="10">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4149,15 +4098,14 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6" s="5">
-        <f>+((D6-D5)/D5)*100</f>
-        <v>-1.3894983179757203</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6">
+        <v>-1.3894983179757237E-2</v>
+      </c>
+      <c r="F6" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>46139</v>
       </c>
@@ -4170,15 +4118,15 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7" s="5">
-        <f>+((D7-D6)/D6)*100</f>
-        <v>-0.17798872738059923</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7">
+        <f>+(D7-D8)/D8</f>
+        <v>1.5619105108277371E-2</v>
+      </c>
+      <c r="F7" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>46140</v>
       </c>
@@ -4191,15 +4139,15 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8" s="5">
-        <f>+((D8-D7)/D7)*100</f>
-        <v>-1.5378900445765229</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8">
+        <f>+(D8-D9)/D9</f>
+        <v>5.0049290968377947E-3</v>
+      </c>
+      <c r="F8" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>46141</v>
       </c>
@@ -4212,15 +4160,15 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9" s="5">
-        <f>+((D9-D8)/D8)*100</f>
-        <v>-0.49800045272768434</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9">
+        <f>+(D9-D6)/D6</f>
+        <v>-2.2026105013349156E-2</v>
+      </c>
+      <c r="F9" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>46142</v>
       </c>
@@ -4233,16 +4181,15 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10" s="5">
-        <f>+((D10-D9)/D9)*100</f>
-        <v>0.70524000909987106</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10">
+        <f>+(D10-D7)/D7</f>
+        <v>-1.3372956909361069E-2</v>
+      </c>
+      <c r="F10" s="10">
         <v>-0.01</v>
       </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>46146</v>
       </c>
@@ -4255,33 +4202,54 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11" s="5">
-        <f>+((D11-D10)/D10)*100</f>
-        <v>5.8810240963855422</v>
-      </c>
-      <c r="F11" s="5">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <f>+(D11-D8)/D8</f>
+        <v>6.0967328152116501E-2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="21">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="21">
         <v>13872</v>
       </c>
-      <c r="E12" s="5">
-        <f>+((D12-D11)/D11)*100</f>
-        <v>-1.3441433752933647</v>
-      </c>
-      <c r="F12" s="5">
-        <v>-0.01</v>
+      <c r="E12">
+        <f>+(D12-D9)/D9</f>
+        <v>5.1945097444452873E-2</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B13" s="21">
+        <v>13411</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="21">
+        <v>13414</v>
+      </c>
+      <c r="E13">
+        <f>+(D13-D10)/D10</f>
+        <v>1.0090361445783132E-2</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2637,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2637,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3293,7 +3293,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
+      <c r="A2" s="11">
         <v>46149</v>
       </c>
       <c r="B2">
@@ -3307,7 +3307,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2">
+      <c r="A3" s="11">
         <v>46148</v>
       </c>
       <c r="B3">
@@ -3321,7 +3321,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2">
+      <c r="A4" s="11">
         <v>46147</v>
       </c>
       <c r="B4">
@@ -3335,7 +3335,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2">
+      <c r="A5" s="11">
         <v>46146</v>
       </c>
       <c r="B5">
@@ -3373,156 +3373,61 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11">
-        <v>46139</v>
-      </c>
-      <c r="B9">
-        <v>40338.944788629997</v>
-      </c>
+      <c r="A9" s="11"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="11">
-        <v>46136</v>
-      </c>
-      <c r="B10">
-        <v>60973.651931649998</v>
-      </c>
+      <c r="A10" s="11"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11">
-        <v>46135</v>
-      </c>
-      <c r="B11">
-        <v>4652.1817311200002</v>
-      </c>
+      <c r="A11" s="11"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="11">
-        <v>46134</v>
-      </c>
-      <c r="B12">
-        <v>17251.00486529</v>
-      </c>
+      <c r="A12" s="11"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="11">
-        <v>46133</v>
-      </c>
-      <c r="B13">
-        <v>47981.781644150004</v>
-      </c>
+      <c r="A13" s="11"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="11">
-        <v>46132</v>
-      </c>
-      <c r="B14">
-        <v>51339.49161813</v>
-      </c>
+      <c r="A14" s="11"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="11">
-        <v>46129</v>
-      </c>
-      <c r="B15">
-        <v>17216.492596060001</v>
-      </c>
+      <c r="A15" s="11"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="11">
-        <v>46128</v>
-      </c>
-      <c r="B16">
-        <v>18.890111640000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="11">
-        <v>46127</v>
-      </c>
-      <c r="B17">
-        <v>15.79809785</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="11">
-        <v>46126</v>
-      </c>
-      <c r="B18">
-        <v>16.215898760000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="11">
-        <v>46125</v>
-      </c>
-      <c r="B19">
-        <v>2475.4322626600001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="11">
-        <v>46122</v>
-      </c>
-      <c r="B20">
-        <v>7956.2858669899997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="11">
-        <v>46121</v>
-      </c>
-      <c r="B21">
-        <v>41.536584740000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="11">
-        <v>46120</v>
-      </c>
-      <c r="B22">
-        <v>580.56056466999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="11">
-        <v>46119</v>
-      </c>
-      <c r="B23">
-        <v>116.97186189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="11">
-        <v>46118</v>
-      </c>
-      <c r="B24">
-        <v>6972.36861443</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="11">
-        <v>46113</v>
-      </c>
-      <c r="B25">
-        <v>540.00852741999995</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="11">
-        <v>46112</v>
-      </c>
-      <c r="B26">
-        <v>5262.3389565099997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="11">
-        <v>46111</v>
-      </c>
-      <c r="B27">
-        <v>22969.58967849</v>
-      </c>
+      <c r="A16" s="11"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="11"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="11"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="11"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="11"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="11"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="11"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="11"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="11"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="11"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="11"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2637,7 +2637,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3274,6 +3274,7 @@
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -3299,6 +3300,9 @@
       <c r="B2">
         <v>131.99794839</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
@@ -3313,6 +3317,10 @@
       <c r="B3">
         <v>745.52443231999996</v>
       </c>
+      <c r="C3">
+        <f t="shared" ref="C2:C7" si="0">+(B3-B2)/B2</f>
+        <v>4.6480001501029387</v>
+      </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
@@ -3327,6 +3335,10 @@
       <c r="B4">
         <v>84317.802960360001</v>
       </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>112.098644799569</v>
+      </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
@@ -3341,6 +3353,10 @@
       <c r="B5">
         <v>49567.396050169998</v>
       </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>-0.41213605774959622</v>
+      </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
@@ -3355,6 +3371,10 @@
       <c r="B6">
         <v>87352.396084139997</v>
       </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>0.76229544105414848</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11">
@@ -3363,6 +3383,10 @@
       <c r="B7">
         <v>28385.438679769999</v>
       </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>-0.67504682238563396</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11">
@@ -3370,6 +3394,10 @@
       </c>
       <c r="B8">
         <v>70324.097718699995</v>
+      </c>
+      <c r="C8">
+        <f>+(B8-B7)/B7</f>
+        <v>1.4774708790679791</v>
       </c>
     </row>
     <row r="9" spans="1:5">

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32558D-1272-4B69-8CBD-6536FE8D2D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="1380" windowWidth="16200" windowHeight="9240" tabRatio="819" activeTab="1"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>DÍA</t>
   </si>
@@ -136,7 +142,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
@@ -145,9 +151,9 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="170" formatCode="0.000000000"/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -450,49 +456,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -641,7 +604,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="810">
+  <cellStyleXfs count="934">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
@@ -719,15 +682,15 @@
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -749,9 +712,9 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1421,67 +1384,173 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1491,7 +1560,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1502,818 +1570,972 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="810">
-    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
-    <cellStyle name="Buena 2" xfId="74"/>
-    <cellStyle name="Buena 3" xfId="75"/>
-    <cellStyle name="Buena 4" xfId="76"/>
-    <cellStyle name="Cálculo 2" xfId="77"/>
-    <cellStyle name="Cálculo 3" xfId="78"/>
-    <cellStyle name="Cálculo 4" xfId="79"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82"/>
-    <cellStyle name="Celda vinculada 2" xfId="83"/>
-    <cellStyle name="Celda vinculada 3" xfId="84"/>
-    <cellStyle name="Celda vinculada 4" xfId="85"/>
-    <cellStyle name="Comma 2" xfId="121"/>
-    <cellStyle name="Encabezado 4 2" xfId="86"/>
-    <cellStyle name="Encabezado 4 3" xfId="87"/>
-    <cellStyle name="Encabezado 4 4" xfId="88"/>
-    <cellStyle name="Énfasis1 2" xfId="89"/>
-    <cellStyle name="Énfasis1 3" xfId="90"/>
-    <cellStyle name="Énfasis1 4" xfId="91"/>
-    <cellStyle name="Énfasis2 2" xfId="92"/>
-    <cellStyle name="Énfasis2 3" xfId="93"/>
-    <cellStyle name="Énfasis2 4" xfId="94"/>
-    <cellStyle name="Énfasis3 2" xfId="95"/>
-    <cellStyle name="Énfasis3 3" xfId="96"/>
-    <cellStyle name="Énfasis3 4" xfId="97"/>
-    <cellStyle name="Énfasis4 2" xfId="98"/>
-    <cellStyle name="Énfasis4 3" xfId="99"/>
-    <cellStyle name="Énfasis4 4" xfId="100"/>
-    <cellStyle name="Énfasis5 2" xfId="101"/>
-    <cellStyle name="Énfasis5 3" xfId="102"/>
-    <cellStyle name="Énfasis5 4" xfId="103"/>
-    <cellStyle name="Énfasis6 2" xfId="104"/>
-    <cellStyle name="Énfasis6 3" xfId="105"/>
-    <cellStyle name="Énfasis6 4" xfId="106"/>
-    <cellStyle name="Entrada 2" xfId="107"/>
-    <cellStyle name="Entrada 3" xfId="108"/>
-    <cellStyle name="Entrada 4" xfId="109"/>
-    <cellStyle name="Euro" xfId="110"/>
-    <cellStyle name="Euro 2" xfId="111"/>
-    <cellStyle name="Euro 2 2" xfId="112"/>
-    <cellStyle name="Euro 2 3" xfId="113"/>
-    <cellStyle name="Euro 2 4" xfId="114"/>
-    <cellStyle name="Euro 3" xfId="115"/>
-    <cellStyle name="Euro 4" xfId="116"/>
-    <cellStyle name="Euro 5" xfId="117"/>
-    <cellStyle name="Incorrecto 2" xfId="118"/>
-    <cellStyle name="Incorrecto 3" xfId="119"/>
-    <cellStyle name="Incorrecto 4" xfId="120"/>
-    <cellStyle name="Millares 10" xfId="122"/>
-    <cellStyle name="Millares 2" xfId="123"/>
-    <cellStyle name="Millares 2 2" xfId="124"/>
-    <cellStyle name="Millares 2 2 2" xfId="125"/>
-    <cellStyle name="Millares 2 3" xfId="126"/>
-    <cellStyle name="Millares 2 4" xfId="127"/>
-    <cellStyle name="Millares 3" xfId="128"/>
-    <cellStyle name="Millares 3 10" xfId="129"/>
-    <cellStyle name="Millares 3 100" xfId="130"/>
-    <cellStyle name="Millares 3 101" xfId="131"/>
-    <cellStyle name="Millares 3 102" xfId="132"/>
-    <cellStyle name="Millares 3 103" xfId="133"/>
-    <cellStyle name="Millares 3 103 2" xfId="134"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
-    <cellStyle name="Millares 3 104" xfId="136"/>
-    <cellStyle name="Millares 3 11" xfId="137"/>
-    <cellStyle name="Millares 3 12" xfId="138"/>
-    <cellStyle name="Millares 3 13" xfId="139"/>
-    <cellStyle name="Millares 3 14" xfId="140"/>
-    <cellStyle name="Millares 3 15" xfId="141"/>
-    <cellStyle name="Millares 3 16" xfId="142"/>
-    <cellStyle name="Millares 3 17" xfId="143"/>
-    <cellStyle name="Millares 3 18" xfId="144"/>
-    <cellStyle name="Millares 3 19" xfId="145"/>
-    <cellStyle name="Millares 3 2" xfId="146"/>
-    <cellStyle name="Millares 3 2 2" xfId="147"/>
-    <cellStyle name="Millares 3 2 3" xfId="148"/>
-    <cellStyle name="Millares 3 20" xfId="149"/>
-    <cellStyle name="Millares 3 21" xfId="150"/>
-    <cellStyle name="Millares 3 22" xfId="151"/>
-    <cellStyle name="Millares 3 23" xfId="152"/>
-    <cellStyle name="Millares 3 24" xfId="153"/>
-    <cellStyle name="Millares 3 25" xfId="154"/>
-    <cellStyle name="Millares 3 26" xfId="155"/>
-    <cellStyle name="Millares 3 27" xfId="156"/>
-    <cellStyle name="Millares 3 28" xfId="157"/>
-    <cellStyle name="Millares 3 29" xfId="158"/>
-    <cellStyle name="Millares 3 3" xfId="159"/>
-    <cellStyle name="Millares 3 30" xfId="160"/>
-    <cellStyle name="Millares 3 31" xfId="161"/>
-    <cellStyle name="Millares 3 32" xfId="162"/>
-    <cellStyle name="Millares 3 33" xfId="163"/>
-    <cellStyle name="Millares 3 34" xfId="164"/>
-    <cellStyle name="Millares 3 35" xfId="165"/>
-    <cellStyle name="Millares 3 36" xfId="166"/>
-    <cellStyle name="Millares 3 37" xfId="167"/>
-    <cellStyle name="Millares 3 38" xfId="168"/>
-    <cellStyle name="Millares 3 39" xfId="169"/>
-    <cellStyle name="Millares 3 4" xfId="170"/>
-    <cellStyle name="Millares 3 40" xfId="171"/>
-    <cellStyle name="Millares 3 41" xfId="172"/>
-    <cellStyle name="Millares 3 42" xfId="173"/>
-    <cellStyle name="Millares 3 43" xfId="174"/>
-    <cellStyle name="Millares 3 44" xfId="175"/>
-    <cellStyle name="Millares 3 45" xfId="176"/>
-    <cellStyle name="Millares 3 46" xfId="177"/>
-    <cellStyle name="Millares 3 47" xfId="178"/>
-    <cellStyle name="Millares 3 48" xfId="179"/>
-    <cellStyle name="Millares 3 49" xfId="180"/>
-    <cellStyle name="Millares 3 5" xfId="181"/>
-    <cellStyle name="Millares 3 50" xfId="182"/>
-    <cellStyle name="Millares 3 51" xfId="183"/>
-    <cellStyle name="Millares 3 52" xfId="184"/>
-    <cellStyle name="Millares 3 53" xfId="185"/>
-    <cellStyle name="Millares 3 54" xfId="186"/>
-    <cellStyle name="Millares 3 55" xfId="187"/>
-    <cellStyle name="Millares 3 56" xfId="188"/>
-    <cellStyle name="Millares 3 57" xfId="189"/>
-    <cellStyle name="Millares 3 58" xfId="190"/>
-    <cellStyle name="Millares 3 59" xfId="191"/>
-    <cellStyle name="Millares 3 6" xfId="192"/>
-    <cellStyle name="Millares 3 60" xfId="193"/>
-    <cellStyle name="Millares 3 61" xfId="194"/>
-    <cellStyle name="Millares 3 62" xfId="195"/>
-    <cellStyle name="Millares 3 63" xfId="196"/>
-    <cellStyle name="Millares 3 64" xfId="197"/>
-    <cellStyle name="Millares 3 65" xfId="198"/>
-    <cellStyle name="Millares 3 66" xfId="199"/>
-    <cellStyle name="Millares 3 67" xfId="200"/>
-    <cellStyle name="Millares 3 68" xfId="201"/>
-    <cellStyle name="Millares 3 69" xfId="202"/>
-    <cellStyle name="Millares 3 7" xfId="203"/>
-    <cellStyle name="Millares 3 70" xfId="204"/>
-    <cellStyle name="Millares 3 71" xfId="205"/>
-    <cellStyle name="Millares 3 72" xfId="206"/>
-    <cellStyle name="Millares 3 73" xfId="207"/>
-    <cellStyle name="Millares 3 74" xfId="208"/>
-    <cellStyle name="Millares 3 75" xfId="209"/>
-    <cellStyle name="Millares 3 76" xfId="210"/>
-    <cellStyle name="Millares 3 77" xfId="211"/>
-    <cellStyle name="Millares 3 78" xfId="212"/>
-    <cellStyle name="Millares 3 79" xfId="213"/>
-    <cellStyle name="Millares 3 8" xfId="214"/>
-    <cellStyle name="Millares 3 80" xfId="215"/>
-    <cellStyle name="Millares 3 81" xfId="216"/>
-    <cellStyle name="Millares 3 82" xfId="217"/>
-    <cellStyle name="Millares 3 83" xfId="218"/>
-    <cellStyle name="Millares 3 84" xfId="219"/>
-    <cellStyle name="Millares 3 85" xfId="220"/>
-    <cellStyle name="Millares 3 86" xfId="221"/>
-    <cellStyle name="Millares 3 87" xfId="222"/>
-    <cellStyle name="Millares 3 88" xfId="223"/>
-    <cellStyle name="Millares 3 89" xfId="224"/>
-    <cellStyle name="Millares 3 9" xfId="225"/>
-    <cellStyle name="Millares 3 90" xfId="226"/>
-    <cellStyle name="Millares 3 91" xfId="227"/>
-    <cellStyle name="Millares 3 92" xfId="228"/>
-    <cellStyle name="Millares 3 93" xfId="229"/>
-    <cellStyle name="Millares 3 94" xfId="230"/>
-    <cellStyle name="Millares 3 95" xfId="231"/>
-    <cellStyle name="Millares 3 96" xfId="232"/>
-    <cellStyle name="Millares 3 97" xfId="233"/>
-    <cellStyle name="Millares 3 98" xfId="234"/>
-    <cellStyle name="Millares 3 99" xfId="235"/>
-    <cellStyle name="Millares 4" xfId="236"/>
-    <cellStyle name="Millares 4 2" xfId="237"/>
-    <cellStyle name="Millares 5" xfId="238"/>
-    <cellStyle name="Millares 5 2" xfId="239"/>
-    <cellStyle name="Millares 5 3" xfId="240"/>
-    <cellStyle name="Millares 6" xfId="241"/>
-    <cellStyle name="Millares 6 2" xfId="242"/>
-    <cellStyle name="Millares 6 3" xfId="243"/>
-    <cellStyle name="Millares 7" xfId="244"/>
-    <cellStyle name="Millares 8" xfId="245"/>
-    <cellStyle name="Millares 8 2" xfId="246"/>
-    <cellStyle name="Millares 9" xfId="247"/>
-    <cellStyle name="Neutral 2" xfId="249"/>
-    <cellStyle name="Neutral 3" xfId="250"/>
-    <cellStyle name="Neutral 4" xfId="251"/>
-    <cellStyle name="Neutral 5" xfId="248"/>
-    <cellStyle name="NivelFila_3 2" xfId="809"/>
+  <cellStyles count="934">
+    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="Millares 10 2" xfId="810" xr:uid="{E3BE1A0E-643F-4DA2-9FEF-D3292D216AEF}"/>
+    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="Millares 2 2 2 2" xfId="813" xr:uid="{FCB04ABF-8C61-49F3-9359-C0F722E02539}"/>
+    <cellStyle name="Millares 2 2 3" xfId="812" xr:uid="{4A34FD68-4836-4139-8705-03C6BA64778B}"/>
+    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="Millares 2 3 2" xfId="814" xr:uid="{785AA2A6-22D3-45AA-8515-E3CD7201DB57}"/>
+    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="Millares 2 4 2" xfId="815" xr:uid="{00A4F4D6-4B8F-4137-AC89-73348D3CCEF9}"/>
+    <cellStyle name="Millares 2 5" xfId="811" xr:uid="{15A0947F-1B27-4B4B-A9B3-B771F1BAF6E1}"/>
+    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="Millares 3 10 2" xfId="817" xr:uid="{BB6EF659-F6EE-40A7-B1BB-E5969AE2A0E1}"/>
+    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="Millares 3 100 2" xfId="818" xr:uid="{B716BD20-7629-4A01-AC51-8C990718388B}"/>
+    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="Millares 3 101 2" xfId="819" xr:uid="{AFC048E7-05BC-4BAB-9219-37AB95F2D614}"/>
+    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="Millares 3 102 2" xfId="820" xr:uid="{9AF2D0D5-A9E3-412E-B3F0-1BD9E8C08569}"/>
+    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Millares 3 103 2 2 2" xfId="823" xr:uid="{B7B9A306-F0AA-4232-8473-4C9BB726944C}"/>
+    <cellStyle name="Millares 3 103 2 3" xfId="822" xr:uid="{CC0DAF05-E42F-4BAC-9FA4-08070944FAEF}"/>
+    <cellStyle name="Millares 3 103 3" xfId="821" xr:uid="{587EA548-D0E8-4924-8665-9F69FA096132}"/>
+    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Millares 3 104 2" xfId="824" xr:uid="{E5FB7CC0-ADAE-4444-8EA2-9FFAA23EDE66}"/>
+    <cellStyle name="Millares 3 105" xfId="816" xr:uid="{59B02820-C013-4198-95B4-7890E41C4A0D}"/>
+    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="Millares 3 11 2" xfId="825" xr:uid="{3E35174C-AC2D-4593-92DB-1CDABCDEAB69}"/>
+    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="Millares 3 12 2" xfId="826" xr:uid="{1FE2E48F-5310-4DAE-BF2A-D2AB45F065FF}"/>
+    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="Millares 3 13 2" xfId="827" xr:uid="{8663BA92-359B-41B1-B31D-2108670B0686}"/>
+    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="Millares 3 14 2" xfId="828" xr:uid="{5AEAEDF6-A00D-4735-B0A9-908E0781C76A}"/>
+    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="Millares 3 15 2" xfId="829" xr:uid="{DA647F8E-C76E-4095-A07B-3C95270A86D4}"/>
+    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="Millares 3 16 2" xfId="830" xr:uid="{47E95EF9-7ADD-4F17-933E-7A564DE5B3BC}"/>
+    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="Millares 3 17 2" xfId="831" xr:uid="{E46068E3-44F1-430E-9E61-2F1D6C51F65C}"/>
+    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="Millares 3 18 2" xfId="832" xr:uid="{D50CECFD-7332-406D-B851-C7FF8551A21F}"/>
+    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="Millares 3 19 2" xfId="833" xr:uid="{5B6712A6-9C90-45DC-A06A-220E69A87192}"/>
+    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="Millares 3 2 2 2" xfId="835" xr:uid="{2C5AF6EB-B3DE-4084-A7F9-462802461298}"/>
+    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="Millares 3 2 3 2" xfId="836" xr:uid="{1EA22512-8B15-4669-8C5D-AD949DA506A4}"/>
+    <cellStyle name="Millares 3 2 4" xfId="834" xr:uid="{6898A4B4-8613-40A3-9A21-EBD8EAAA6017}"/>
+    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="Millares 3 20 2" xfId="837" xr:uid="{D4859FF7-3C76-4A21-917B-DE13B6B81DA3}"/>
+    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="Millares 3 21 2" xfId="838" xr:uid="{DACD326E-DE22-4541-8F55-62CB631AEEF7}"/>
+    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="Millares 3 22 2" xfId="839" xr:uid="{01476297-2662-49A7-86F3-16F7790C0C05}"/>
+    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="Millares 3 23 2" xfId="840" xr:uid="{9C2D6B42-7086-4B38-AE6E-4B120A29FFF7}"/>
+    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="Millares 3 24 2" xfId="841" xr:uid="{2F8DC138-0C42-46B3-BB78-D95373ED5CE0}"/>
+    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="Millares 3 25 2" xfId="842" xr:uid="{841A6F5E-F660-4E14-9B4C-136C1B2E04E1}"/>
+    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="Millares 3 26 2" xfId="843" xr:uid="{77A268C7-AFAB-4632-B4E1-A33E1EA91703}"/>
+    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="Millares 3 27 2" xfId="844" xr:uid="{83FD97AD-5BF6-43FC-B6E5-546A2607305A}"/>
+    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="Millares 3 28 2" xfId="845" xr:uid="{99AB8C30-EC0E-411D-B715-ADCAF06556F8}"/>
+    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Millares 3 29 2" xfId="846" xr:uid="{221C0615-50FC-4711-9C88-2AC1EDBF8A45}"/>
+    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="Millares 3 3 2" xfId="847" xr:uid="{4D14D279-F1E9-4B0B-B414-518ED5DA8115}"/>
+    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="Millares 3 30 2" xfId="848" xr:uid="{6E1BFB95-1E49-4A6E-AFD4-9E1C98BC5664}"/>
+    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="Millares 3 31 2" xfId="849" xr:uid="{6FE3F810-28BD-4607-B093-D2AB9B7BB902}"/>
+    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="Millares 3 32 2" xfId="850" xr:uid="{27DB0AA5-884F-4BB6-97D7-C96C75185B7D}"/>
+    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Millares 3 33 2" xfId="851" xr:uid="{287C84A7-8332-43FD-93B0-554D8E541216}"/>
+    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Millares 3 34 2" xfId="852" xr:uid="{BC50C21E-AC67-4DDB-B63F-7CD133B973A4}"/>
+    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Millares 3 35 2" xfId="853" xr:uid="{770B22E1-F213-4DFD-84FF-F70F2B842BC6}"/>
+    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Millares 3 36 2" xfId="854" xr:uid="{6E3A52D3-858A-47F8-8EE8-4CFBC71C29C9}"/>
+    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="Millares 3 37 2" xfId="855" xr:uid="{121923B9-E38B-4354-BFE4-5AF3D0457D9D}"/>
+    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="Millares 3 38 2" xfId="856" xr:uid="{984E725D-5E1B-49D7-A7A5-9F0424CA5F50}"/>
+    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Millares 3 39 2" xfId="857" xr:uid="{578C0061-E270-4825-9527-E2C8794FEB08}"/>
+    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Millares 3 4 2" xfId="858" xr:uid="{310DFB30-7C13-4786-9FD4-58C54A40FD36}"/>
+    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Millares 3 40 2" xfId="859" xr:uid="{6453D6DA-58AA-43D3-8C5A-386D2049C70F}"/>
+    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="Millares 3 41 2" xfId="860" xr:uid="{555594B0-91D2-40FA-A2E5-4CEDA68A6840}"/>
+    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="Millares 3 42 2" xfId="861" xr:uid="{7984DEF4-D48D-4637-A472-E0AE56493E51}"/>
+    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Millares 3 43 2" xfId="862" xr:uid="{5C2D335A-28FE-40CE-8374-1245A5C55AD2}"/>
+    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Millares 3 44 2" xfId="863" xr:uid="{A21713B7-112F-4CC2-8986-5026AC65B088}"/>
+    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Millares 3 45 2" xfId="864" xr:uid="{7B73BAD1-1DD4-42AA-B9C4-16D5B5A36EAB}"/>
+    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="Millares 3 46 2" xfId="865" xr:uid="{3C98026D-45FD-406E-A9FD-00673001C59F}"/>
+    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="Millares 3 47 2" xfId="866" xr:uid="{CA217B6B-33D6-4082-B54A-405BFDDB3187}"/>
+    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Millares 3 48 2" xfId="867" xr:uid="{10FA8A53-6B5F-454A-9736-6EBAAE0F8710}"/>
+    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Millares 3 49 2" xfId="868" xr:uid="{09D8A2A1-C9E4-4333-9455-524161B08F08}"/>
+    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Millares 3 5 2" xfId="869" xr:uid="{9877A682-AEE4-48A3-A205-68BCEF45A467}"/>
+    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="Millares 3 50 2" xfId="870" xr:uid="{14F087DA-8A96-4BB0-AF04-F0890C064590}"/>
+    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="Millares 3 51 2" xfId="871" xr:uid="{1BA05B00-6C64-4C42-BE69-CEA4A4A2584F}"/>
+    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Millares 3 52 2" xfId="872" xr:uid="{D3FE3383-5CE0-4498-815D-EFC5FBB0ADD5}"/>
+    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Millares 3 53 2" xfId="873" xr:uid="{1767C15A-880C-4784-9445-37361A8B8B51}"/>
+    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="Millares 3 54 2" xfId="874" xr:uid="{D524B04B-B629-408C-B5F8-15D394AB91DB}"/>
+    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="Millares 3 55 2" xfId="875" xr:uid="{9FE87D24-FB41-4A3B-B037-79BFDA0AAD73}"/>
+    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="Millares 3 56 2" xfId="876" xr:uid="{6F31C240-461F-447A-BDB0-F899D2EF3464}"/>
+    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="Millares 3 57 2" xfId="877" xr:uid="{F31C38FE-EB21-43C8-A4BF-599471099C17}"/>
+    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="Millares 3 58 2" xfId="878" xr:uid="{02D3D2A0-9AC3-4A10-BDF2-7211AE4DE15E}"/>
+    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="Millares 3 59 2" xfId="879" xr:uid="{A3C5BF1B-DA26-40CF-AA51-D78A1FB99DAC}"/>
+    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="Millares 3 6 2" xfId="880" xr:uid="{671D07CF-106E-4CA0-9CE9-D401C7B81311}"/>
+    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="Millares 3 60 2" xfId="881" xr:uid="{C74B50D4-CEED-4853-A4A4-15628A65EA4E}"/>
+    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="Millares 3 61 2" xfId="882" xr:uid="{5EC62C5B-0382-4451-90C4-68BA5F987B21}"/>
+    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="Millares 3 62 2" xfId="883" xr:uid="{E91A577A-E2B7-47E5-8EBA-F0017C783C4B}"/>
+    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="Millares 3 63 2" xfId="884" xr:uid="{3EADE132-CD1A-4875-BB69-0EC8EE78EB89}"/>
+    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="Millares 3 64 2" xfId="885" xr:uid="{F739C55A-DA9D-4FB6-8373-1423E3C46080}"/>
+    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="Millares 3 65 2" xfId="886" xr:uid="{29738D1D-828B-457B-9C72-FEB418EB27AE}"/>
+    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="Millares 3 66 2" xfId="887" xr:uid="{0E950C99-E32C-4E3F-9110-E43579F949BE}"/>
+    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="Millares 3 67 2" xfId="888" xr:uid="{E9EDC08F-07FD-427B-8CAD-AC18C00C27AE}"/>
+    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="Millares 3 68 2" xfId="889" xr:uid="{CF67FC17-C8C6-471D-AFF6-464DFE3D81D3}"/>
+    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="Millares 3 69 2" xfId="890" xr:uid="{735F2FA4-1ED3-44AF-8CAF-A6319C20A03D}"/>
+    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="Millares 3 7 2" xfId="891" xr:uid="{54D20EDD-52D7-41AA-84EF-CEAFA48147EB}"/>
+    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="Millares 3 70 2" xfId="892" xr:uid="{8528E107-B3F7-435B-8A97-7C87B29646B1}"/>
+    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="Millares 3 71 2" xfId="893" xr:uid="{2067E852-C04B-4671-90BC-6D368D36BE5A}"/>
+    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="Millares 3 72 2" xfId="894" xr:uid="{9705390D-3D73-4612-90BB-2DA1FFEFBDC5}"/>
+    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="Millares 3 73 2" xfId="895" xr:uid="{6425655C-8FEB-4E18-89AF-A08FAF71F9E9}"/>
+    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="Millares 3 74 2" xfId="896" xr:uid="{D640C94F-8F67-4869-945A-98FC67BA1223}"/>
+    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="Millares 3 75 2" xfId="897" xr:uid="{F54D0ADC-603F-4325-A055-3874F1C6BEC4}"/>
+    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="Millares 3 76 2" xfId="898" xr:uid="{39E19090-1834-4574-BDE1-0BE90CF08AEA}"/>
+    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="Millares 3 77 2" xfId="899" xr:uid="{0CAF3401-9876-44B7-BEC6-E0F2C11D6904}"/>
+    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="Millares 3 78 2" xfId="900" xr:uid="{96A07176-B9DB-4D5A-859D-3D74B158A8E8}"/>
+    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="Millares 3 79 2" xfId="901" xr:uid="{C5F6E8AF-BC34-4A34-930E-F957EE52AD33}"/>
+    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="Millares 3 8 2" xfId="902" xr:uid="{227B9690-C2D3-427D-AA4E-63AE8209710A}"/>
+    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="Millares 3 80 2" xfId="903" xr:uid="{1C0E4AAE-5511-4711-8CF5-E7746B907238}"/>
+    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="Millares 3 81 2" xfId="904" xr:uid="{CE6EDD92-E3E4-4104-8BC0-2FF2D3E5C267}"/>
+    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="Millares 3 82 2" xfId="905" xr:uid="{6163A47D-0035-4A09-B4A4-F255E3176861}"/>
+    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="Millares 3 83 2" xfId="906" xr:uid="{C061AEEC-3E96-4F5B-9D13-3C9B6D9E0C8E}"/>
+    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="Millares 3 84 2" xfId="907" xr:uid="{7F438CC1-8647-4369-9026-E5D3DE8A6918}"/>
+    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="Millares 3 85 2" xfId="908" xr:uid="{979B3EAC-B69C-457E-9F60-852B4211C648}"/>
+    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="Millares 3 86 2" xfId="909" xr:uid="{4FCBD3F1-4DC9-4C8B-92B4-A6CC16CE97D4}"/>
+    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="Millares 3 87 2" xfId="910" xr:uid="{E7E4DCAD-1D04-4CDB-84CB-DC5A839FB55A}"/>
+    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="Millares 3 88 2" xfId="911" xr:uid="{C44B3B1D-28D6-4462-83D2-9C6A9EF0769F}"/>
+    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="Millares 3 89 2" xfId="912" xr:uid="{99763C95-3916-480E-9A13-1A44F768B79D}"/>
+    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="Millares 3 9 2" xfId="913" xr:uid="{C0114674-3500-42D6-B84B-25D29301730E}"/>
+    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="Millares 3 90 2" xfId="914" xr:uid="{5C1F68DF-8E3F-4EFB-A968-4CEFC4CCD5AF}"/>
+    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="Millares 3 91 2" xfId="915" xr:uid="{3360A8A7-EC35-413D-9165-71FE257E86C7}"/>
+    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="Millares 3 92 2" xfId="916" xr:uid="{1212C964-8CF2-4A2A-8BB0-F161FB21FCCF}"/>
+    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="Millares 3 93 2" xfId="917" xr:uid="{EB2BD4B3-FC0B-4FA1-A90F-33E4AE0651B8}"/>
+    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="Millares 3 94 2" xfId="918" xr:uid="{8213782F-2358-4A2F-98F2-D930CE749901}"/>
+    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="Millares 3 95 2" xfId="919" xr:uid="{932518D2-1990-4196-830E-124BE718AB41}"/>
+    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="Millares 3 96 2" xfId="920" xr:uid="{EDE4E994-92AB-4486-B71F-FF0B2023E308}"/>
+    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="Millares 3 97 2" xfId="921" xr:uid="{49F94B35-0409-4C6D-94B4-01CFE0270C2F}"/>
+    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="Millares 3 98 2" xfId="922" xr:uid="{7CA7B20B-F612-403E-B7E5-6BDFB8E62D72}"/>
+    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="Millares 3 99 2" xfId="923" xr:uid="{588AAA04-14A3-4112-8401-85F287F3B1D1}"/>
+    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="Millares 4 2 2" xfId="925" xr:uid="{632E5153-739F-49B0-87B4-DA422CAB2917}"/>
+    <cellStyle name="Millares 4 3" xfId="924" xr:uid="{9636C4B6-5205-4D11-8AD2-95728FB18F49}"/>
+    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="Millares 5 2 2" xfId="927" xr:uid="{6B039BC7-2E98-40F5-83E3-9E4F59F8828D}"/>
+    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="Millares 5 3 2" xfId="928" xr:uid="{9AEEF321-1C47-4FB4-82C2-BEA39434E7F8}"/>
+    <cellStyle name="Millares 5 4" xfId="926" xr:uid="{C483AC5F-BB36-404C-85F5-CB5F7D9A6B55}"/>
+    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="Millares 6 2 2" xfId="929" xr:uid="{A7799074-2321-463A-A10C-292DA2BE0629}"/>
+    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="Millares 7 2" xfId="930" xr:uid="{42B5A3B7-F168-45C6-A163-A0BBB4F476C0}"/>
+    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="Millares 8 2 2" xfId="932" xr:uid="{22CA6473-034B-4955-A46D-6C28A880DF39}"/>
+    <cellStyle name="Millares 8 3" xfId="931" xr:uid="{7533A74B-739D-4BE6-BF6F-B7C0CC329668}"/>
+    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="Millares 9 2" xfId="933" xr:uid="{DAC0DBE0-3508-4BA0-ACA9-FB9190183533}"/>
+    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252"/>
-    <cellStyle name="Normal 10 2" xfId="253"/>
-    <cellStyle name="Normal 10 3" xfId="254"/>
-    <cellStyle name="Normal 10 4" xfId="255"/>
-    <cellStyle name="Normal 100" xfId="256"/>
-    <cellStyle name="Normal 100 2" xfId="257"/>
-    <cellStyle name="Normal 101" xfId="258"/>
-    <cellStyle name="Normal 101 2" xfId="259"/>
-    <cellStyle name="Normal 102" xfId="260"/>
-    <cellStyle name="Normal 102 2" xfId="261"/>
-    <cellStyle name="Normal 103" xfId="262"/>
-    <cellStyle name="Normal 103 2" xfId="263"/>
-    <cellStyle name="Normal 104" xfId="264"/>
-    <cellStyle name="Normal 104 2" xfId="265"/>
-    <cellStyle name="Normal 104 3" xfId="266"/>
-    <cellStyle name="Normal 105" xfId="267"/>
-    <cellStyle name="Normal 106" xfId="268"/>
-    <cellStyle name="Normal 106 2" xfId="269"/>
-    <cellStyle name="Normal 106 3" xfId="270"/>
-    <cellStyle name="Normal 107" xfId="271"/>
-    <cellStyle name="Normal 107 2" xfId="272"/>
-    <cellStyle name="Normal 108" xfId="273"/>
-    <cellStyle name="Normal 109" xfId="274"/>
-    <cellStyle name="Normal 11" xfId="275"/>
-    <cellStyle name="Normal 11 2" xfId="276"/>
-    <cellStyle name="Normal 11 3" xfId="277"/>
-    <cellStyle name="Normal 11 4" xfId="278"/>
-    <cellStyle name="Normal 110" xfId="279"/>
-    <cellStyle name="Normal 111" xfId="280"/>
-    <cellStyle name="Normal 112" xfId="281"/>
-    <cellStyle name="Normal 112 2" xfId="282"/>
-    <cellStyle name="Normal 113" xfId="283"/>
-    <cellStyle name="Normal 113 2" xfId="284"/>
-    <cellStyle name="Normal 114" xfId="285"/>
-    <cellStyle name="Normal 114 2" xfId="286"/>
-    <cellStyle name="Normal 115" xfId="287"/>
-    <cellStyle name="Normal 115 2" xfId="288"/>
-    <cellStyle name="Normal 116" xfId="289"/>
-    <cellStyle name="Normal 116 2" xfId="290"/>
-    <cellStyle name="Normal 116 3" xfId="291"/>
-    <cellStyle name="Normal 117" xfId="292"/>
-    <cellStyle name="Normal 117 2" xfId="293"/>
-    <cellStyle name="Normal 118" xfId="294"/>
-    <cellStyle name="Normal 118 2" xfId="295"/>
-    <cellStyle name="Normal 118 3" xfId="296"/>
-    <cellStyle name="Normal 119" xfId="297"/>
-    <cellStyle name="Normal 119 2" xfId="298"/>
-    <cellStyle name="Normal 119 3" xfId="299"/>
-    <cellStyle name="Normal 12" xfId="300"/>
-    <cellStyle name="Normal 12 2" xfId="301"/>
-    <cellStyle name="Normal 12 3" xfId="302"/>
-    <cellStyle name="Normal 12 4" xfId="303"/>
-    <cellStyle name="Normal 120" xfId="304"/>
-    <cellStyle name="Normal 120 2" xfId="305"/>
-    <cellStyle name="Normal 121" xfId="306"/>
-    <cellStyle name="Normal 121 2" xfId="307"/>
-    <cellStyle name="Normal 122" xfId="308"/>
-    <cellStyle name="Normal 122 2" xfId="309"/>
-    <cellStyle name="Normal 123" xfId="310"/>
-    <cellStyle name="Normal 124" xfId="311"/>
-    <cellStyle name="Normal 124 2" xfId="312"/>
-    <cellStyle name="Normal 125" xfId="313"/>
-    <cellStyle name="Normal 125 2" xfId="314"/>
-    <cellStyle name="Normal 126" xfId="315"/>
-    <cellStyle name="Normal 127" xfId="316"/>
-    <cellStyle name="Normal 127 2" xfId="317"/>
-    <cellStyle name="Normal 128" xfId="318"/>
-    <cellStyle name="Normal 129" xfId="319"/>
-    <cellStyle name="Normal 13" xfId="320"/>
-    <cellStyle name="Normal 13 2" xfId="321"/>
-    <cellStyle name="Normal 13 3" xfId="322"/>
-    <cellStyle name="Normal 13 4" xfId="323"/>
-    <cellStyle name="Normal 130" xfId="324"/>
-    <cellStyle name="Normal 130 2" xfId="325"/>
-    <cellStyle name="Normal 131" xfId="326"/>
-    <cellStyle name="Normal 131 2" xfId="327"/>
-    <cellStyle name="Normal 132" xfId="328"/>
-    <cellStyle name="Normal 132 2" xfId="329"/>
-    <cellStyle name="Normal 133" xfId="330"/>
-    <cellStyle name="Normal 133 2" xfId="331"/>
-    <cellStyle name="Normal 134" xfId="332"/>
-    <cellStyle name="Normal 135" xfId="333"/>
-    <cellStyle name="Normal 135 2" xfId="334"/>
-    <cellStyle name="Normal 136" xfId="335"/>
-    <cellStyle name="Normal 136 2" xfId="336"/>
-    <cellStyle name="Normal 137" xfId="337"/>
-    <cellStyle name="Normal 137 2" xfId="338"/>
-    <cellStyle name="Normal 138" xfId="339"/>
-    <cellStyle name="Normal 138 2" xfId="340"/>
-    <cellStyle name="Normal 139" xfId="341"/>
-    <cellStyle name="Normal 139 2" xfId="342"/>
-    <cellStyle name="Normal 14" xfId="343"/>
-    <cellStyle name="Normal 14 2" xfId="344"/>
-    <cellStyle name="Normal 14 3" xfId="345"/>
-    <cellStyle name="Normal 14 4" xfId="346"/>
-    <cellStyle name="Normal 140" xfId="347"/>
-    <cellStyle name="Normal 140 2" xfId="348"/>
-    <cellStyle name="Normal 141" xfId="349"/>
-    <cellStyle name="Normal 142" xfId="350"/>
-    <cellStyle name="Normal 142 2" xfId="351"/>
-    <cellStyle name="Normal 143" xfId="352"/>
-    <cellStyle name="Normal 143 2" xfId="353"/>
-    <cellStyle name="Normal 143 3" xfId="354"/>
-    <cellStyle name="Normal 144" xfId="355"/>
-    <cellStyle name="Normal 144 2" xfId="356"/>
-    <cellStyle name="Normal 145" xfId="357"/>
-    <cellStyle name="Normal 145 2" xfId="358"/>
-    <cellStyle name="Normal 146" xfId="359"/>
-    <cellStyle name="Normal 147" xfId="360"/>
-    <cellStyle name="Normal 15" xfId="361"/>
-    <cellStyle name="Normal 15 2" xfId="362"/>
-    <cellStyle name="Normal 15 3" xfId="363"/>
-    <cellStyle name="Normal 15 4" xfId="364"/>
-    <cellStyle name="Normal 16" xfId="365"/>
-    <cellStyle name="Normal 16 2" xfId="366"/>
-    <cellStyle name="Normal 16 3" xfId="367"/>
-    <cellStyle name="Normal 16 4" xfId="368"/>
-    <cellStyle name="Normal 17" xfId="369"/>
-    <cellStyle name="Normal 17 2" xfId="370"/>
-    <cellStyle name="Normal 17 3" xfId="371"/>
-    <cellStyle name="Normal 17 4" xfId="372"/>
-    <cellStyle name="Normal 18" xfId="373"/>
-    <cellStyle name="Normal 18 2" xfId="374"/>
-    <cellStyle name="Normal 18 3" xfId="375"/>
-    <cellStyle name="Normal 18 4" xfId="376"/>
-    <cellStyle name="Normal 19" xfId="377"/>
-    <cellStyle name="Normal 19 2" xfId="378"/>
-    <cellStyle name="Normal 19 3" xfId="379"/>
-    <cellStyle name="Normal 19 4" xfId="380"/>
-    <cellStyle name="Normal 2" xfId="381"/>
-    <cellStyle name="Normal 2 10" xfId="382"/>
-    <cellStyle name="Normal 2 100" xfId="383"/>
-    <cellStyle name="Normal 2 101" xfId="384"/>
-    <cellStyle name="Normal 2 102" xfId="385"/>
-    <cellStyle name="Normal 2 103" xfId="386"/>
-    <cellStyle name="Normal 2 103 2" xfId="387"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
-    <cellStyle name="Normal 2 104" xfId="389"/>
-    <cellStyle name="Normal 2 104 2" xfId="390"/>
-    <cellStyle name="Normal 2 105" xfId="391"/>
-    <cellStyle name="Normal 2 105 2" xfId="392"/>
-    <cellStyle name="Normal 2 106" xfId="393"/>
-    <cellStyle name="Normal 2 106 2" xfId="394"/>
-    <cellStyle name="Normal 2 106 3" xfId="395"/>
-    <cellStyle name="Normal 2 107" xfId="396"/>
-    <cellStyle name="Normal 2 107 2" xfId="397"/>
-    <cellStyle name="Normal 2 108" xfId="398"/>
-    <cellStyle name="Normal 2 108 2" xfId="399"/>
-    <cellStyle name="Normal 2 109" xfId="400"/>
-    <cellStyle name="Normal 2 109 2" xfId="401"/>
-    <cellStyle name="Normal 2 11" xfId="402"/>
-    <cellStyle name="Normal 2 110" xfId="403"/>
-    <cellStyle name="Normal 2 111" xfId="404"/>
-    <cellStyle name="Normal 2 112" xfId="405"/>
-    <cellStyle name="Normal 2 113" xfId="406"/>
-    <cellStyle name="Normal 2 114" xfId="407"/>
-    <cellStyle name="Normal 2 115" xfId="408"/>
-    <cellStyle name="Normal 2 12" xfId="409"/>
-    <cellStyle name="Normal 2 13" xfId="410"/>
-    <cellStyle name="Normal 2 14" xfId="411"/>
-    <cellStyle name="Normal 2 15" xfId="412"/>
-    <cellStyle name="Normal 2 16" xfId="413"/>
-    <cellStyle name="Normal 2 17" xfId="414"/>
-    <cellStyle name="Normal 2 18" xfId="415"/>
-    <cellStyle name="Normal 2 19" xfId="416"/>
-    <cellStyle name="Normal 2 2" xfId="417"/>
-    <cellStyle name="Normal 2 2 2" xfId="418"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
-    <cellStyle name="Normal 2 2 3" xfId="420"/>
-    <cellStyle name="Normal 2 2 4" xfId="421"/>
-    <cellStyle name="Normal 2 20" xfId="422"/>
-    <cellStyle name="Normal 2 21" xfId="423"/>
-    <cellStyle name="Normal 2 22" xfId="424"/>
-    <cellStyle name="Normal 2 23" xfId="425"/>
-    <cellStyle name="Normal 2 24" xfId="426"/>
-    <cellStyle name="Normal 2 25" xfId="427"/>
-    <cellStyle name="Normal 2 26" xfId="428"/>
-    <cellStyle name="Normal 2 27" xfId="429"/>
-    <cellStyle name="Normal 2 28" xfId="430"/>
-    <cellStyle name="Normal 2 29" xfId="431"/>
-    <cellStyle name="Normal 2 3" xfId="432"/>
-    <cellStyle name="Normal 2 3 2" xfId="433"/>
-    <cellStyle name="Normal 2 3 3" xfId="434"/>
-    <cellStyle name="Normal 2 30" xfId="435"/>
-    <cellStyle name="Normal 2 31" xfId="436"/>
-    <cellStyle name="Normal 2 32" xfId="437"/>
-    <cellStyle name="Normal 2 33" xfId="438"/>
-    <cellStyle name="Normal 2 34" xfId="439"/>
-    <cellStyle name="Normal 2 35" xfId="440"/>
-    <cellStyle name="Normal 2 36" xfId="441"/>
-    <cellStyle name="Normal 2 37" xfId="442"/>
-    <cellStyle name="Normal 2 38" xfId="443"/>
-    <cellStyle name="Normal 2 39" xfId="444"/>
-    <cellStyle name="Normal 2 4" xfId="445"/>
-    <cellStyle name="Normal 2 4 2" xfId="446"/>
-    <cellStyle name="Normal 2 4 3" xfId="447"/>
-    <cellStyle name="Normal 2 4 4" xfId="448"/>
-    <cellStyle name="Normal 2 40" xfId="449"/>
-    <cellStyle name="Normal 2 41" xfId="450"/>
-    <cellStyle name="Normal 2 42" xfId="451"/>
-    <cellStyle name="Normal 2 43" xfId="452"/>
-    <cellStyle name="Normal 2 44" xfId="453"/>
-    <cellStyle name="Normal 2 45" xfId="454"/>
-    <cellStyle name="Normal 2 45 10" xfId="455"/>
-    <cellStyle name="Normal 2 45 11" xfId="456"/>
-    <cellStyle name="Normal 2 45 12" xfId="457"/>
-    <cellStyle name="Normal 2 45 13" xfId="458"/>
-    <cellStyle name="Normal 2 45 14" xfId="459"/>
-    <cellStyle name="Normal 2 45 15" xfId="460"/>
-    <cellStyle name="Normal 2 45 16" xfId="461"/>
-    <cellStyle name="Normal 2 45 17" xfId="462"/>
-    <cellStyle name="Normal 2 45 18" xfId="463"/>
-    <cellStyle name="Normal 2 45 19" xfId="464"/>
-    <cellStyle name="Normal 2 45 2" xfId="465"/>
-    <cellStyle name="Normal 2 45 20" xfId="466"/>
-    <cellStyle name="Normal 2 45 21" xfId="467"/>
-    <cellStyle name="Normal 2 45 22" xfId="468"/>
-    <cellStyle name="Normal 2 45 23" xfId="469"/>
-    <cellStyle name="Normal 2 45 24" xfId="470"/>
-    <cellStyle name="Normal 2 45 25" xfId="471"/>
-    <cellStyle name="Normal 2 45 26" xfId="472"/>
-    <cellStyle name="Normal 2 45 27" xfId="473"/>
-    <cellStyle name="Normal 2 45 28" xfId="474"/>
-    <cellStyle name="Normal 2 45 29" xfId="475"/>
-    <cellStyle name="Normal 2 45 3" xfId="476"/>
-    <cellStyle name="Normal 2 45 30" xfId="477"/>
-    <cellStyle name="Normal 2 45 31" xfId="478"/>
-    <cellStyle name="Normal 2 45 32" xfId="479"/>
-    <cellStyle name="Normal 2 45 33" xfId="480"/>
-    <cellStyle name="Normal 2 45 34" xfId="481"/>
-    <cellStyle name="Normal 2 45 35" xfId="482"/>
-    <cellStyle name="Normal 2 45 36" xfId="483"/>
-    <cellStyle name="Normal 2 45 37" xfId="484"/>
-    <cellStyle name="Normal 2 45 38" xfId="485"/>
-    <cellStyle name="Normal 2 45 39" xfId="486"/>
-    <cellStyle name="Normal 2 45 4" xfId="487"/>
-    <cellStyle name="Normal 2 45 40" xfId="488"/>
-    <cellStyle name="Normal 2 45 41" xfId="489"/>
-    <cellStyle name="Normal 2 45 42" xfId="490"/>
-    <cellStyle name="Normal 2 45 43" xfId="491"/>
-    <cellStyle name="Normal 2 45 44" xfId="492"/>
-    <cellStyle name="Normal 2 45 45" xfId="493"/>
-    <cellStyle name="Normal 2 45 46" xfId="494"/>
-    <cellStyle name="Normal 2 45 47" xfId="495"/>
-    <cellStyle name="Normal 2 45 48" xfId="496"/>
-    <cellStyle name="Normal 2 45 49" xfId="497"/>
-    <cellStyle name="Normal 2 45 5" xfId="498"/>
-    <cellStyle name="Normal 2 45 50" xfId="499"/>
-    <cellStyle name="Normal 2 45 51" xfId="500"/>
-    <cellStyle name="Normal 2 45 52" xfId="501"/>
-    <cellStyle name="Normal 2 45 53" xfId="502"/>
-    <cellStyle name="Normal 2 45 54" xfId="503"/>
-    <cellStyle name="Normal 2 45 55" xfId="504"/>
-    <cellStyle name="Normal 2 45 56" xfId="505"/>
-    <cellStyle name="Normal 2 45 57" xfId="506"/>
-    <cellStyle name="Normal 2 45 58" xfId="507"/>
-    <cellStyle name="Normal 2 45 59" xfId="508"/>
-    <cellStyle name="Normal 2 45 6" xfId="509"/>
-    <cellStyle name="Normal 2 45 7" xfId="510"/>
-    <cellStyle name="Normal 2 45 8" xfId="511"/>
-    <cellStyle name="Normal 2 45 9" xfId="512"/>
-    <cellStyle name="Normal 2 46" xfId="513"/>
-    <cellStyle name="Normal 2 47" xfId="514"/>
-    <cellStyle name="Normal 2 48" xfId="515"/>
-    <cellStyle name="Normal 2 49" xfId="516"/>
-    <cellStyle name="Normal 2 5" xfId="517"/>
-    <cellStyle name="Normal 2 5 2" xfId="518"/>
-    <cellStyle name="Normal 2 5 3" xfId="519"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
-    <cellStyle name="Normal 2 5 4" xfId="521"/>
-    <cellStyle name="Normal 2 50" xfId="522"/>
-    <cellStyle name="Normal 2 51" xfId="523"/>
-    <cellStyle name="Normal 2 52" xfId="524"/>
-    <cellStyle name="Normal 2 53" xfId="525"/>
-    <cellStyle name="Normal 2 54" xfId="526"/>
-    <cellStyle name="Normal 2 55" xfId="527"/>
-    <cellStyle name="Normal 2 56" xfId="528"/>
-    <cellStyle name="Normal 2 57" xfId="529"/>
-    <cellStyle name="Normal 2 58" xfId="530"/>
-    <cellStyle name="Normal 2 59" xfId="531"/>
-    <cellStyle name="Normal 2 6" xfId="532"/>
-    <cellStyle name="Normal 2 6 2" xfId="533"/>
-    <cellStyle name="Normal 2 60" xfId="534"/>
-    <cellStyle name="Normal 2 61" xfId="535"/>
-    <cellStyle name="Normal 2 62" xfId="536"/>
-    <cellStyle name="Normal 2 63" xfId="537"/>
-    <cellStyle name="Normal 2 64" xfId="538"/>
-    <cellStyle name="Normal 2 65" xfId="539"/>
-    <cellStyle name="Normal 2 66" xfId="540"/>
-    <cellStyle name="Normal 2 67" xfId="541"/>
-    <cellStyle name="Normal 2 68" xfId="542"/>
-    <cellStyle name="Normal 2 69" xfId="543"/>
-    <cellStyle name="Normal 2 7" xfId="544"/>
-    <cellStyle name="Normal 2 70" xfId="545"/>
-    <cellStyle name="Normal 2 71" xfId="546"/>
-    <cellStyle name="Normal 2 72" xfId="547"/>
-    <cellStyle name="Normal 2 73" xfId="548"/>
-    <cellStyle name="Normal 2 74" xfId="549"/>
-    <cellStyle name="Normal 2 75" xfId="550"/>
-    <cellStyle name="Normal 2 76" xfId="551"/>
-    <cellStyle name="Normal 2 77" xfId="552"/>
-    <cellStyle name="Normal 2 78" xfId="553"/>
-    <cellStyle name="Normal 2 79" xfId="554"/>
-    <cellStyle name="Normal 2 8" xfId="555"/>
-    <cellStyle name="Normal 2 80" xfId="556"/>
-    <cellStyle name="Normal 2 81" xfId="557"/>
-    <cellStyle name="Normal 2 82" xfId="558"/>
-    <cellStyle name="Normal 2 83" xfId="559"/>
-    <cellStyle name="Normal 2 84" xfId="560"/>
-    <cellStyle name="Normal 2 85" xfId="561"/>
-    <cellStyle name="Normal 2 86" xfId="562"/>
-    <cellStyle name="Normal 2 87" xfId="563"/>
-    <cellStyle name="Normal 2 88" xfId="564"/>
-    <cellStyle name="Normal 2 89" xfId="565"/>
-    <cellStyle name="Normal 2 9" xfId="566"/>
-    <cellStyle name="Normal 2 90" xfId="567"/>
-    <cellStyle name="Normal 2 91" xfId="568"/>
-    <cellStyle name="Normal 2 92" xfId="569"/>
-    <cellStyle name="Normal 2 93" xfId="570"/>
-    <cellStyle name="Normal 2 94" xfId="571"/>
-    <cellStyle name="Normal 2 95" xfId="572"/>
-    <cellStyle name="Normal 2 96" xfId="573"/>
-    <cellStyle name="Normal 2 97" xfId="574"/>
-    <cellStyle name="Normal 2 98" xfId="575"/>
-    <cellStyle name="Normal 2 99" xfId="576"/>
-    <cellStyle name="Normal 20" xfId="577"/>
-    <cellStyle name="Normal 20 2" xfId="578"/>
-    <cellStyle name="Normal 20 3" xfId="579"/>
-    <cellStyle name="Normal 20 4" xfId="580"/>
-    <cellStyle name="Normal 21" xfId="581"/>
-    <cellStyle name="Normal 21 2" xfId="582"/>
-    <cellStyle name="Normal 21 3" xfId="583"/>
-    <cellStyle name="Normal 21 4" xfId="584"/>
-    <cellStyle name="Normal 22" xfId="585"/>
-    <cellStyle name="Normal 22 2" xfId="586"/>
-    <cellStyle name="Normal 22 3" xfId="587"/>
-    <cellStyle name="Normal 22 4" xfId="588"/>
-    <cellStyle name="Normal 23" xfId="589"/>
-    <cellStyle name="Normal 23 2" xfId="590"/>
-    <cellStyle name="Normal 23 3" xfId="591"/>
-    <cellStyle name="Normal 24" xfId="592"/>
-    <cellStyle name="Normal 24 2" xfId="593"/>
-    <cellStyle name="Normal 24 3" xfId="594"/>
-    <cellStyle name="Normal 25" xfId="595"/>
-    <cellStyle name="Normal 26" xfId="596"/>
-    <cellStyle name="Normal 27" xfId="597"/>
-    <cellStyle name="Normal 28" xfId="598"/>
-    <cellStyle name="Normal 29" xfId="599"/>
-    <cellStyle name="Normal 3" xfId="600"/>
-    <cellStyle name="Normal 3 2" xfId="601"/>
-    <cellStyle name="Normal 3 2 2" xfId="602"/>
-    <cellStyle name="Normal 3 3" xfId="603"/>
-    <cellStyle name="Normal 3 3 2" xfId="604"/>
-    <cellStyle name="Normal 3 3 3" xfId="605"/>
-    <cellStyle name="Normal 3 4" xfId="606"/>
-    <cellStyle name="Normal 3 5" xfId="607"/>
-    <cellStyle name="Normal 30" xfId="608"/>
-    <cellStyle name="Normal 31" xfId="609"/>
-    <cellStyle name="Normal 32" xfId="610"/>
-    <cellStyle name="Normal 33" xfId="611"/>
-    <cellStyle name="Normal 34" xfId="612"/>
-    <cellStyle name="Normal 35" xfId="613"/>
-    <cellStyle name="Normal 36" xfId="614"/>
-    <cellStyle name="Normal 37" xfId="615"/>
-    <cellStyle name="Normal 38" xfId="616"/>
-    <cellStyle name="Normal 39" xfId="617"/>
-    <cellStyle name="Normal 4" xfId="618"/>
-    <cellStyle name="Normal 4 2" xfId="619"/>
-    <cellStyle name="Normal 4 2 2" xfId="620"/>
-    <cellStyle name="Normal 4 3" xfId="621"/>
-    <cellStyle name="Normal 4 4" xfId="622"/>
-    <cellStyle name="Normal 40" xfId="623"/>
-    <cellStyle name="Normal 41" xfId="624"/>
-    <cellStyle name="Normal 42" xfId="625"/>
-    <cellStyle name="Normal 43" xfId="626"/>
-    <cellStyle name="Normal 44" xfId="627"/>
-    <cellStyle name="Normal 45" xfId="628"/>
-    <cellStyle name="Normal 46" xfId="629"/>
-    <cellStyle name="Normal 47" xfId="630"/>
-    <cellStyle name="Normal 48" xfId="631"/>
-    <cellStyle name="Normal 49" xfId="632"/>
-    <cellStyle name="Normal 5" xfId="633"/>
-    <cellStyle name="Normal 5 10" xfId="634"/>
-    <cellStyle name="Normal 5 11" xfId="635"/>
-    <cellStyle name="Normal 5 12" xfId="636"/>
-    <cellStyle name="Normal 5 13" xfId="637"/>
-    <cellStyle name="Normal 5 14" xfId="638"/>
-    <cellStyle name="Normal 5 15" xfId="639"/>
-    <cellStyle name="Normal 5 16" xfId="640"/>
-    <cellStyle name="Normal 5 17" xfId="641"/>
-    <cellStyle name="Normal 5 18" xfId="642"/>
-    <cellStyle name="Normal 5 19" xfId="643"/>
-    <cellStyle name="Normal 5 2" xfId="644"/>
-    <cellStyle name="Normal 5 20" xfId="645"/>
-    <cellStyle name="Normal 5 21" xfId="646"/>
-    <cellStyle name="Normal 5 22" xfId="647"/>
-    <cellStyle name="Normal 5 23" xfId="648"/>
-    <cellStyle name="Normal 5 24" xfId="649"/>
-    <cellStyle name="Normal 5 25" xfId="650"/>
-    <cellStyle name="Normal 5 26" xfId="651"/>
-    <cellStyle name="Normal 5 27" xfId="652"/>
-    <cellStyle name="Normal 5 28" xfId="653"/>
-    <cellStyle name="Normal 5 28 10" xfId="654"/>
-    <cellStyle name="Normal 5 28 11" xfId="655"/>
-    <cellStyle name="Normal 5 28 12" xfId="656"/>
-    <cellStyle name="Normal 5 28 13" xfId="657"/>
-    <cellStyle name="Normal 5 28 14" xfId="658"/>
-    <cellStyle name="Normal 5 28 15" xfId="659"/>
-    <cellStyle name="Normal 5 28 16" xfId="660"/>
-    <cellStyle name="Normal 5 28 17" xfId="661"/>
-    <cellStyle name="Normal 5 28 18" xfId="662"/>
-    <cellStyle name="Normal 5 28 19" xfId="663"/>
-    <cellStyle name="Normal 5 28 2" xfId="664"/>
-    <cellStyle name="Normal 5 28 20" xfId="665"/>
-    <cellStyle name="Normal 5 28 21" xfId="666"/>
-    <cellStyle name="Normal 5 28 22" xfId="667"/>
-    <cellStyle name="Normal 5 28 23" xfId="668"/>
-    <cellStyle name="Normal 5 28 24" xfId="669"/>
-    <cellStyle name="Normal 5 28 25" xfId="670"/>
-    <cellStyle name="Normal 5 28 3" xfId="671"/>
-    <cellStyle name="Normal 5 28 4" xfId="672"/>
-    <cellStyle name="Normal 5 28 5" xfId="673"/>
-    <cellStyle name="Normal 5 28 6" xfId="674"/>
-    <cellStyle name="Normal 5 28 7" xfId="675"/>
-    <cellStyle name="Normal 5 28 8" xfId="676"/>
-    <cellStyle name="Normal 5 28 9" xfId="677"/>
-    <cellStyle name="Normal 5 29" xfId="678"/>
-    <cellStyle name="Normal 5 3" xfId="679"/>
-    <cellStyle name="Normal 5 4" xfId="680"/>
-    <cellStyle name="Normal 5 5" xfId="681"/>
-    <cellStyle name="Normal 5 6" xfId="682"/>
-    <cellStyle name="Normal 5 7" xfId="683"/>
-    <cellStyle name="Normal 5 8" xfId="684"/>
-    <cellStyle name="Normal 5 9" xfId="685"/>
-    <cellStyle name="Normal 50" xfId="686"/>
-    <cellStyle name="Normal 51" xfId="687"/>
-    <cellStyle name="Normal 52" xfId="688"/>
-    <cellStyle name="Normal 53" xfId="689"/>
-    <cellStyle name="Normal 54" xfId="690"/>
-    <cellStyle name="Normal 55" xfId="691"/>
-    <cellStyle name="Normal 56" xfId="2"/>
-    <cellStyle name="Normal 56 2" xfId="692"/>
-    <cellStyle name="Normal 57" xfId="693"/>
-    <cellStyle name="Normal 58" xfId="694"/>
-    <cellStyle name="Normal 59" xfId="695"/>
-    <cellStyle name="Normal 6" xfId="696"/>
-    <cellStyle name="Normal 6 2" xfId="697"/>
-    <cellStyle name="Normal 6 2 2" xfId="698"/>
-    <cellStyle name="Normal 6 2 3" xfId="699"/>
-    <cellStyle name="Normal 6 3" xfId="700"/>
-    <cellStyle name="Normal 6 4" xfId="701"/>
-    <cellStyle name="Normal 60" xfId="702"/>
-    <cellStyle name="Normal 61" xfId="703"/>
-    <cellStyle name="Normal 62" xfId="704"/>
-    <cellStyle name="Normal 63" xfId="705"/>
-    <cellStyle name="Normal 64" xfId="706"/>
-    <cellStyle name="Normal 65" xfId="707"/>
-    <cellStyle name="Normal 66" xfId="708"/>
-    <cellStyle name="Normal 67" xfId="709"/>
-    <cellStyle name="Normal 68" xfId="710"/>
-    <cellStyle name="Normal 69" xfId="711"/>
-    <cellStyle name="Normal 7" xfId="712"/>
-    <cellStyle name="Normal 7 2" xfId="713"/>
-    <cellStyle name="Normal 7 3" xfId="714"/>
-    <cellStyle name="Normal 7 4" xfId="715"/>
-    <cellStyle name="Normal 70" xfId="716"/>
-    <cellStyle name="Normal 71" xfId="717"/>
-    <cellStyle name="Normal 72" xfId="718"/>
-    <cellStyle name="Normal 73" xfId="719"/>
-    <cellStyle name="Normal 74" xfId="720"/>
-    <cellStyle name="Normal 75" xfId="721"/>
-    <cellStyle name="Normal 76" xfId="722"/>
-    <cellStyle name="Normal 77" xfId="723"/>
-    <cellStyle name="Normal 78" xfId="724"/>
-    <cellStyle name="Normal 79" xfId="725"/>
-    <cellStyle name="Normal 79 2" xfId="726"/>
-    <cellStyle name="Normal 79 3" xfId="727"/>
-    <cellStyle name="Normal 8" xfId="728"/>
-    <cellStyle name="Normal 8 2" xfId="729"/>
-    <cellStyle name="Normal 8 3" xfId="730"/>
-    <cellStyle name="Normal 8 4" xfId="731"/>
-    <cellStyle name="Normal 80" xfId="732"/>
-    <cellStyle name="Normal 80 2" xfId="733"/>
-    <cellStyle name="Normal 81" xfId="734"/>
-    <cellStyle name="Normal 81 2" xfId="735"/>
-    <cellStyle name="Normal 82" xfId="736"/>
-    <cellStyle name="Normal 82 2" xfId="737"/>
-    <cellStyle name="Normal 82 2 2" xfId="738"/>
-    <cellStyle name="Normal 83" xfId="739"/>
-    <cellStyle name="Normal 83 2" xfId="740"/>
-    <cellStyle name="Normal 83 2 2" xfId="741"/>
-    <cellStyle name="Normal 84" xfId="742"/>
-    <cellStyle name="Normal 84 2" xfId="743"/>
-    <cellStyle name="Normal 84 3" xfId="744"/>
-    <cellStyle name="Normal 85" xfId="745"/>
-    <cellStyle name="Normal 85 2" xfId="746"/>
-    <cellStyle name="Normal 85 3" xfId="747"/>
-    <cellStyle name="Normal 86" xfId="748"/>
-    <cellStyle name="Normal 86 2" xfId="749"/>
-    <cellStyle name="Normal 86 3" xfId="750"/>
-    <cellStyle name="Normal 87" xfId="751"/>
-    <cellStyle name="Normal 87 2" xfId="752"/>
-    <cellStyle name="Normal 87 3" xfId="753"/>
-    <cellStyle name="Normal 88" xfId="754"/>
-    <cellStyle name="Normal 88 2" xfId="755"/>
-    <cellStyle name="Normal 88 3" xfId="756"/>
-    <cellStyle name="Normal 88 4" xfId="757"/>
-    <cellStyle name="Normal 89" xfId="758"/>
-    <cellStyle name="Normal 9" xfId="759"/>
-    <cellStyle name="Normal 9 2" xfId="760"/>
-    <cellStyle name="Normal 9 3" xfId="761"/>
-    <cellStyle name="Normal 9 4" xfId="762"/>
-    <cellStyle name="Normal 90" xfId="763"/>
-    <cellStyle name="Normal 91" xfId="764"/>
-    <cellStyle name="Normal 92" xfId="765"/>
-    <cellStyle name="Normal 93" xfId="766"/>
-    <cellStyle name="Normal 94" xfId="767"/>
-    <cellStyle name="Normal 94 2" xfId="768"/>
-    <cellStyle name="Normal 95" xfId="769"/>
-    <cellStyle name="Normal 95 2" xfId="770"/>
-    <cellStyle name="Normal 95 3" xfId="771"/>
-    <cellStyle name="Normal 96" xfId="772"/>
-    <cellStyle name="Normal 97" xfId="773"/>
-    <cellStyle name="Normal 97 2" xfId="774"/>
-    <cellStyle name="Normal 98" xfId="775"/>
-    <cellStyle name="Normal 98 2" xfId="776"/>
-    <cellStyle name="Normal 99" xfId="777"/>
-    <cellStyle name="Normal 99 2" xfId="778"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3"/>
-    <cellStyle name="Notas 2" xfId="779"/>
-    <cellStyle name="Notas 2 2" xfId="780"/>
-    <cellStyle name="Notas 2 3" xfId="781"/>
-    <cellStyle name="Notas 3" xfId="782"/>
-    <cellStyle name="Notas 4" xfId="783"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785"/>
-    <cellStyle name="Salida 2" xfId="786"/>
-    <cellStyle name="Salida 3" xfId="787"/>
-    <cellStyle name="Salida 4" xfId="788"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791"/>
-    <cellStyle name="Texto explicativo 2" xfId="792"/>
-    <cellStyle name="Texto explicativo 3" xfId="793"/>
-    <cellStyle name="Texto explicativo 4" xfId="794"/>
-    <cellStyle name="Título 1 2" xfId="795"/>
-    <cellStyle name="Título 2 2" xfId="796"/>
-    <cellStyle name="Título 2 3" xfId="797"/>
-    <cellStyle name="Título 2 4" xfId="798"/>
-    <cellStyle name="Título 3 2" xfId="799"/>
-    <cellStyle name="Título 3 3" xfId="800"/>
-    <cellStyle name="Título 3 4" xfId="801"/>
-    <cellStyle name="Título 4" xfId="802"/>
-    <cellStyle name="Título 5" xfId="803"/>
-    <cellStyle name="Título 6" xfId="804"/>
-    <cellStyle name="Total 2" xfId="806"/>
-    <cellStyle name="Total 3" xfId="807"/>
-    <cellStyle name="Total 4" xfId="808"/>
-    <cellStyle name="Total 5" xfId="805"/>
+    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2637,26 +2859,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2672,8 +2894,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="18">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -2689,8 +2911,8 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="18">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -2706,8 +2928,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="18">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -2723,8 +2945,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="18">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -2740,8 +2962,8 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="18">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -2757,8 +2979,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="18">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -2774,8 +2996,8 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="18">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -2791,8 +3013,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="18">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -2808,8 +3030,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="18">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -2825,8 +3047,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="18">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -2842,8 +3064,8 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="18">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -2859,8 +3081,8 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="18">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -2876,8 +3098,8 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="18">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -2893,8 +3115,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="18">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -2910,8 +3132,8 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="18">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -2927,8 +3149,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="18">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -2944,8 +3166,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -2961,8 +3183,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="18">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -2978,8 +3200,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="18">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -2995,8 +3217,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="18">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -3012,8 +3234,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="18">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -3029,8 +3251,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="18">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3046,8 +3268,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="18">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3063,8 +3285,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="18">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3080,8 +3302,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="18">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3097,8 +3319,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="18">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3114,8 +3336,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="18">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3131,134 +3353,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="18">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="14"/>
+      <c r="C29" s="8"/>
       <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="8"/>
       <c r="H29" s="1">
         <v>18.43</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="18">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="10"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="16"/>
+      <c r="E30" s="10"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="16"/>
+      <c r="G30" s="10"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="18">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="10"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="10"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="16"/>
+      <c r="G31" s="10"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="18">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
         <v>46148</v>
       </c>
       <c r="B32" s="1">
         <v>1200</v>
       </c>
-      <c r="C32" s="16"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="1">
         <v>100</v>
       </c>
-      <c r="E32" s="16"/>
+      <c r="E32" s="10"/>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="16"/>
+      <c r="G32" s="10"/>
       <c r="H32" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="18">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="24">
         <v>46149</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="20">
         <v>32505.648000000001</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="1">
+      <c r="C33" s="23"/>
+      <c r="D33" s="20">
         <v>150</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="1">
+      <c r="E33" s="23"/>
+      <c r="F33" s="20">
         <v>300</v>
       </c>
-      <c r="G33" s="16"/>
-      <c r="H33" s="1">
+      <c r="G33" s="23"/>
+      <c r="H33" s="20">
         <v>243.9</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="18"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="20"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="18"/>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="16"/>
+      <c r="C36" s="10"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="16"/>
+      <c r="E36" s="10"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="16"/>
+      <c r="G36" s="10"/>
       <c r="H36" s="1"/>
     </row>
   </sheetData>
@@ -3268,24 +3490,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" style="15" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
+      <c r="C1" s="15" t="s">
+        <v>17</v>
+      </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
@@ -3293,169 +3518,340 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="11">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
         <v>46149</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="25">
         <v>131.99794839</v>
       </c>
-      <c r="C2">
-        <v>0</v>
+      <c r="C2" s="18">
+        <f>+((B2-B3)/B3)*100</f>
+        <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="6">
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="21">
         <v>46148</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="19">
         <v>745.52443231999996</v>
       </c>
-      <c r="C3">
-        <f t="shared" ref="C2:C7" si="0">+(B3-B2)/B2</f>
-        <v>4.6480001501029387</v>
+      <c r="C3" s="18">
+        <f>+((B3-B4)/B4)*100</f>
+        <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="6">
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="11">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
         <v>46147</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="19">
         <v>84317.802960360001</v>
       </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>112.098644799569</v>
+      <c r="C4" s="18">
+        <f t="shared" ref="C4:C27" si="0">+((B4-B5)/B5)*100</f>
+        <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="7">
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
         <v>46146</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="19">
         <v>49567.396050169998</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="18">
         <f t="shared" si="0"/>
-        <v>-0.41213605774959622</v>
+        <v>-43.255825515735765</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="7">
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="11">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
         <v>46142</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="19">
         <v>87352.396084139997</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="18">
         <f t="shared" si="0"/>
-        <v>0.76229544105414848</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="11">
+        <v>207.73664296544806</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <v>46141</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="19">
         <v>28385.438679769999</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="18">
         <f t="shared" si="0"/>
-        <v>-0.67504682238563396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="11">
+        <v>-59.636256133262869</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
         <v>46140</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="19">
         <v>70324.097718699995</v>
       </c>
-      <c r="C8">
-        <f>+(B8-B7)/B7</f>
-        <v>1.4774708790679791</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="11"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="11"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="11"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="11"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="11"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="11"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="11"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="11"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="11"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="11"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="11"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="11"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="11"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="11"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="11"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="11"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="11"/>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="11"/>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="11"/>
+      <c r="C8" s="18">
+        <f t="shared" si="0"/>
+        <v>74.333012643706198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
+        <v>46139</v>
+      </c>
+      <c r="B9" s="19">
+        <v>40338.944788629997</v>
+      </c>
+      <c r="C9" s="18">
+        <f t="shared" si="0"/>
+        <v>-33.842006324553125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="22">
+        <v>46136</v>
+      </c>
+      <c r="B10" s="19">
+        <v>60973.651931649998</v>
+      </c>
+      <c r="C10" s="18">
+        <f t="shared" si="0"/>
+        <v>1210.6463903543759</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
+        <v>46135</v>
+      </c>
+      <c r="B11" s="19">
+        <v>4652.1817311200002</v>
+      </c>
+      <c r="C11" s="18">
+        <f t="shared" si="0"/>
+        <v>-73.032401489373797</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
+        <v>46134</v>
+      </c>
+      <c r="B12" s="19">
+        <v>17251.00486529</v>
+      </c>
+      <c r="C12" s="18">
+        <f t="shared" si="0"/>
+        <v>-64.046760511667529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
+        <v>46133</v>
+      </c>
+      <c r="B13" s="19">
+        <v>47981.781644150004</v>
+      </c>
+      <c r="C13" s="18">
+        <f t="shared" si="0"/>
+        <v>-6.5402088492716128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
+        <v>46132</v>
+      </c>
+      <c r="B14" s="19">
+        <v>51339.49161813</v>
+      </c>
+      <c r="C14" s="18">
+        <f t="shared" si="0"/>
+        <v>198.19948129202027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="22">
+        <v>46129</v>
+      </c>
+      <c r="B15" s="19">
+        <v>17216.492596060001</v>
+      </c>
+      <c r="C15" s="18">
+        <f t="shared" si="0"/>
+        <v>91040.237411852577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="22">
+        <v>46128</v>
+      </c>
+      <c r="B16" s="19">
+        <v>18.890111640000001</v>
+      </c>
+      <c r="C16" s="18">
+        <f t="shared" si="0"/>
+        <v>19.572063797541304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="22">
+        <v>46127</v>
+      </c>
+      <c r="B17" s="19">
+        <v>15.79809785</v>
+      </c>
+      <c r="C17" s="18">
+        <f t="shared" si="0"/>
+        <v>-2.5764893835585476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="22">
+        <v>46126</v>
+      </c>
+      <c r="B18" s="19">
+        <v>16.215898760000002</v>
+      </c>
+      <c r="C18" s="18">
+        <f t="shared" si="0"/>
+        <v>-99.344926580920657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="22">
+        <v>46125</v>
+      </c>
+      <c r="B19" s="19">
+        <v>2475.4322626600001</v>
+      </c>
+      <c r="C19" s="18">
+        <f t="shared" si="0"/>
+        <v>-68.887087467151304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="22">
+        <v>46122</v>
+      </c>
+      <c r="B20" s="19">
+        <v>7956.2858669899997</v>
+      </c>
+      <c r="C20" s="18">
+        <f t="shared" si="0"/>
+        <v>19054.886991293832</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="22">
+        <v>46121</v>
+      </c>
+      <c r="B21" s="19">
+        <v>41.536584740000002</v>
+      </c>
+      <c r="C21" s="18">
+        <f t="shared" si="0"/>
+        <v>-92.845434694034026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="22">
+        <v>46120</v>
+      </c>
+      <c r="B22" s="19">
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C22" s="18">
+        <f t="shared" si="0"/>
+        <v>396.32497533121034</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="22">
+        <v>46119</v>
+      </c>
+      <c r="B23" s="19">
+        <v>116.97186189</v>
+      </c>
+      <c r="C23" s="18">
+        <f t="shared" si="0"/>
+        <v>-98.322351149824243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="22">
+        <v>46118</v>
+      </c>
+      <c r="B24" s="19">
+        <v>6972.36861443</v>
+      </c>
+      <c r="C24" s="18">
+        <f t="shared" si="0"/>
+        <v>1191.1589836815915</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="22">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="19">
+        <v>540.00852741999995</v>
+      </c>
+      <c r="C25" s="18">
+        <f t="shared" si="0"/>
+        <v>-89.738241267184833</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="22">
+        <v>46112</v>
+      </c>
+      <c r="B26" s="19">
+        <v>5262.3389565099997</v>
+      </c>
+      <c r="C26" s="18">
+        <f t="shared" si="0"/>
+        <v>-77.08997404756451</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="22">
+        <v>46111</v>
+      </c>
+      <c r="B27" s="19">
+        <v>22969.58967849</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3464,17 +3860,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3488,7 +3884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3502,7 +3898,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3516,7 +3912,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3530,7 +3926,7 @@
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3540,7 +3936,7 @@
       <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="9">
         <v>64.09</v>
       </c>
     </row>
@@ -3551,16 +3947,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3571,7 +3967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46024</v>
       </c>
@@ -3580,7 +3976,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46031</v>
       </c>
@@ -3588,10 +3984,10 @@
         <v>631055414.05422926</v>
       </c>
       <c r="C3" s="4">
-        <v>-7.2050081634151608E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>-7.2050081634151582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46038</v>
       </c>
@@ -3599,10 +3995,10 @@
         <v>687738190.99875975</v>
       </c>
       <c r="C4" s="4">
-        <v>8.9822186264706616E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>8.9822186264706527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46045</v>
       </c>
@@ -3610,10 +4006,10 @@
         <v>728876050.32802963</v>
       </c>
       <c r="C5" s="4">
-        <v>5.9816162411350016E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>5.9816162411350033</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46052</v>
       </c>
@@ -3621,10 +4017,10 @@
         <v>839643409.76085114</v>
       </c>
       <c r="C6" s="4">
-        <v>0.15197009063882794</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>15.197009063882785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46059</v>
       </c>
@@ -3632,96 +4028,97 @@
         <v>818274973.23848069</v>
       </c>
       <c r="C7" s="4">
-        <v>-2.5449418495950171E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1">
+        <v>-2.5449418495950149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46066</v>
       </c>
       <c r="B8" s="1">
         <v>801808360.23688257</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.0123569142568742E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="C8" s="4">
+        <v>-2.0123569142568702</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46073</v>
       </c>
       <c r="B9" s="1">
         <v>886542333.87268889</v>
       </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="C9" s="4">
+        <v>10.56785858540723</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46080</v>
       </c>
       <c r="B10" s="1">
         <v>938549580.20021927</v>
       </c>
-      <c r="C10" s="7">
-        <v>5.8663015109889693E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="C10" s="4">
+        <v>5.8663015109889649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46087</v>
       </c>
       <c r="B11" s="1">
         <v>870061809.65898001</v>
       </c>
-      <c r="C11" s="7">
-        <v>-7.2971926029340772E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="C11" s="4">
+        <v>-7.2971926029340803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46094</v>
       </c>
       <c r="B12" s="1">
         <v>959597484.45129991</v>
       </c>
-      <c r="C12" s="7">
-        <v>0.10290725762048258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="C12" s="4">
+        <v>10.290725762048252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46101</v>
       </c>
       <c r="B13" s="1">
         <v>1136404345.7909815</v>
       </c>
-      <c r="C13" s="7">
-        <v>0.18425106797854962</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="C13" s="4">
+        <v>18.425106797854955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>46108</v>
       </c>
       <c r="B14" s="1">
         <v>1111572721.2404912</v>
       </c>
-      <c r="C14" s="8">
-        <v>-2.1851046806061425E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="C14" s="4">
+        <f>+((B14-B13)/B13)*100</f>
+        <v>-2.1851046806061447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>46129</v>
       </c>
       <c r="B15" s="1">
         <v>1071533894.2527295</v>
       </c>
-      <c r="C15" s="8">
-        <f>+(B15-B14)/B14</f>
-        <v>-3.6019979820194892E-2</v>
+      <c r="C15" s="4">
+        <f>+((B15-B14)/B14)*100</f>
+        <v>-3.6019979820194892</v>
       </c>
     </row>
   </sheetData>
@@ -3730,21 +4127,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.75" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
-    <col min="5" max="5" width="21.5" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3770,7 +4167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -3792,11 +4189,11 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46115</v>
       </c>
@@ -3818,11 +4215,12 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="9">
-        <v>-1.4067445693212388E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3" s="17">
+        <f>+((G3-G2)/G2)*100</f>
+        <v>-1.4067445693212368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -3844,11 +4242,12 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="9">
-        <v>9.7569377843467198E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="17">
+        <f>+((G4-G3)/G3)*100</f>
+        <v>0.9756937784346702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -3870,11 +4269,12 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="9">
-        <v>3.4749018512476804E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="17">
+        <f>+((G5-G4)/G4)*100</f>
+        <v>3.4749018512476764</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -3896,8 +4296,9 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="9">
-        <v>3.0099999999999998E-2</v>
+      <c r="H6" s="17">
+        <f>+((G6-G5)/G5)*100</f>
+        <v>3.0146874710954426</v>
       </c>
     </row>
   </sheetData>
@@ -3906,19 +4307,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
-    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -3931,14 +4332,14 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -3951,14 +4352,14 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="17">
-        <v>-2.681224004753413E-2</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46113</v>
       </c>
@@ -3971,14 +4372,15 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3">
-        <v>4.8691139433717501E-2</v>
-      </c>
-      <c r="F3" s="10">
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E13" si="0">+((D3-D2)/D2)*100</f>
+        <v>4.8691139433717465</v>
+      </c>
+      <c r="F3" s="5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -3991,14 +4393,15 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4">
-        <v>-1.1061785896222975E-2</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.1061785896222982</v>
+      </c>
+      <c r="F4" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -4011,14 +4414,15 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5">
-        <v>6.2550592390904214E-3</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.62550592390904403</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4031,14 +4435,15 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6">
-        <v>-1.3894983179757237E-2</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.3894983179757203</v>
+      </c>
+      <c r="F6" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46139</v>
       </c>
@@ -4051,15 +4456,15 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7">
-        <f>+(D7-D8)/D8</f>
-        <v>1.5619105108277371E-2</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.17798872738059923</v>
+      </c>
+      <c r="F7" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46140</v>
       </c>
@@ -4072,15 +4477,15 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8">
-        <f>+(D8-D9)/D9</f>
-        <v>5.0049290968377947E-3</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.5378900445765229</v>
+      </c>
+      <c r="F8" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46141</v>
       </c>
@@ -4093,15 +4498,15 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9">
-        <f>+(D9-D6)/D6</f>
-        <v>-2.2026105013349156E-2</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.49800045272768434</v>
+      </c>
+      <c r="F9" s="5">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46142</v>
       </c>
@@ -4114,15 +4519,16 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10">
-        <f>+(D10-D7)/D7</f>
-        <v>-1.3372956909361069E-2</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.70524000909987106</v>
+      </c>
+      <c r="F10" s="5">
         <v>-0.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46146</v>
       </c>
@@ -4135,53 +4541,53 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11">
-        <f>+(D11-D8)/D8</f>
-        <v>6.0967328152116501E-2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8810240963855422</v>
+      </c>
+      <c r="F11" s="5">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="14">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="14">
         <v>13872</v>
       </c>
-      <c r="E12">
-        <f>+(D12-D9)/D9</f>
-        <v>5.1945097444452873E-2</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2">
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.3441433752933647</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
         <v>46148</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="30">
         <v>13411</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="27">
         <v>3</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="30">
         <v>13414</v>
       </c>
-      <c r="E13">
-        <f>+(D13-D10)/D10</f>
-        <v>1.0090361445783132E-2</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="E13" s="29">
+        <f t="shared" si="0"/>
+        <v>-3.3016147635524797</v>
+      </c>
+      <c r="F13" s="29">
         <v>0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Monitor_test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32558D-1272-4B69-8CBD-6536FE8D2D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="819" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Liquidez Monetaria" sheetId="5" r:id="rId5"/>
     <sheet name="Resev. Internacionales $" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -142,8 +136,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
@@ -151,9 +145,8 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1415,132 +1408,132 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1600,942 +1593,945 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="934">
-    <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="60% - Énfasis1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="60% - Énfasis1 3" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="60% - Énfasis1 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="60% - Énfasis2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="60% - Énfasis2 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="60% - Énfasis2 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="60% - Énfasis3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="60% - Énfasis3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="60% - Énfasis3 2 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="60% - Énfasis3 3" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="60% - Énfasis3 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="60% - Énfasis4 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="60% - Énfasis4 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="60% - Énfasis4 2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="60% - Énfasis4 3" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="60% - Énfasis4 4" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="60% - Énfasis5 2" xfId="66" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="60% - Énfasis5 3" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="60% - Énfasis5 4" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="60% - Énfasis6 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="60% - Énfasis6 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="60% - Énfasis6 2 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="60% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="60% - Énfasis6 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Buena 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Buena 3" xfId="75" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Buena 4" xfId="76" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Cálculo 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Cálculo 3" xfId="78" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Cálculo 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Celda de comprobación 2" xfId="80" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Celda de comprobación 3" xfId="81" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Celda de comprobación 4" xfId="82" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Celda vinculada 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Celda vinculada 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Celda vinculada 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Comma 2" xfId="121" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Encabezado 4 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Encabezado 4 3" xfId="87" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Encabezado 4 4" xfId="88" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Énfasis1 2" xfId="89" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Énfasis1 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Énfasis1 4" xfId="91" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Énfasis2 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Énfasis2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Énfasis2 4" xfId="94" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Énfasis3 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Énfasis3 3" xfId="96" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Énfasis3 4" xfId="97" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Énfasis4 2" xfId="98" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Énfasis4 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Énfasis4 4" xfId="100" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="Énfasis5 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="Énfasis5 3" xfId="102" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Énfasis5 4" xfId="103" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Énfasis6 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="Énfasis6 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="Énfasis6 4" xfId="106" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Entrada 2" xfId="107" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Entrada 3" xfId="108" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Entrada 4" xfId="109" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Euro" xfId="110" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Euro 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Euro 2 2" xfId="112" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Euro 2 3" xfId="113" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Euro 2 4" xfId="114" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Euro 3" xfId="115" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Euro 4" xfId="116" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Euro 5" xfId="117" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Incorrecto 2" xfId="118" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Incorrecto 3" xfId="119" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Incorrecto 4" xfId="120" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Millares 10" xfId="122" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Millares 10 2" xfId="810" xr:uid="{E3BE1A0E-643F-4DA2-9FEF-D3292D216AEF}"/>
-    <cellStyle name="Millares 2" xfId="123" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Millares 2 2" xfId="124" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Millares 2 2 2" xfId="125" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Millares 2 2 2 2" xfId="813" xr:uid="{FCB04ABF-8C61-49F3-9359-C0F722E02539}"/>
-    <cellStyle name="Millares 2 2 3" xfId="812" xr:uid="{4A34FD68-4836-4139-8705-03C6BA64778B}"/>
-    <cellStyle name="Millares 2 3" xfId="126" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Millares 2 3 2" xfId="814" xr:uid="{785AA2A6-22D3-45AA-8515-E3CD7201DB57}"/>
-    <cellStyle name="Millares 2 4" xfId="127" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Millares 2 4 2" xfId="815" xr:uid="{00A4F4D6-4B8F-4137-AC89-73348D3CCEF9}"/>
-    <cellStyle name="Millares 2 5" xfId="811" xr:uid="{15A0947F-1B27-4B4B-A9B3-B771F1BAF6E1}"/>
-    <cellStyle name="Millares 3" xfId="128" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Millares 3 10" xfId="129" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Millares 3 10 2" xfId="817" xr:uid="{BB6EF659-F6EE-40A7-B1BB-E5969AE2A0E1}"/>
-    <cellStyle name="Millares 3 100" xfId="130" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Millares 3 100 2" xfId="818" xr:uid="{B716BD20-7629-4A01-AC51-8C990718388B}"/>
-    <cellStyle name="Millares 3 101" xfId="131" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Millares 3 101 2" xfId="819" xr:uid="{AFC048E7-05BC-4BAB-9219-37AB95F2D614}"/>
-    <cellStyle name="Millares 3 102" xfId="132" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Millares 3 102 2" xfId="820" xr:uid="{9AF2D0D5-A9E3-412E-B3F0-1BD9E8C08569}"/>
-    <cellStyle name="Millares 3 103" xfId="133" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Millares 3 103 2" xfId="134" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Millares 3 103 2 2" xfId="135" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Millares 3 103 2 2 2" xfId="823" xr:uid="{B7B9A306-F0AA-4232-8473-4C9BB726944C}"/>
-    <cellStyle name="Millares 3 103 2 3" xfId="822" xr:uid="{CC0DAF05-E42F-4BAC-9FA4-08070944FAEF}"/>
-    <cellStyle name="Millares 3 103 3" xfId="821" xr:uid="{587EA548-D0E8-4924-8665-9F69FA096132}"/>
-    <cellStyle name="Millares 3 104" xfId="136" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Millares 3 104 2" xfId="824" xr:uid="{E5FB7CC0-ADAE-4444-8EA2-9FFAA23EDE66}"/>
-    <cellStyle name="Millares 3 105" xfId="816" xr:uid="{59B02820-C013-4198-95B4-7890E41C4A0D}"/>
-    <cellStyle name="Millares 3 11" xfId="137" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Millares 3 11 2" xfId="825" xr:uid="{3E35174C-AC2D-4593-92DB-1CDABCDEAB69}"/>
-    <cellStyle name="Millares 3 12" xfId="138" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Millares 3 12 2" xfId="826" xr:uid="{1FE2E48F-5310-4DAE-BF2A-D2AB45F065FF}"/>
-    <cellStyle name="Millares 3 13" xfId="139" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Millares 3 13 2" xfId="827" xr:uid="{8663BA92-359B-41B1-B31D-2108670B0686}"/>
-    <cellStyle name="Millares 3 14" xfId="140" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Millares 3 14 2" xfId="828" xr:uid="{5AEAEDF6-A00D-4735-B0A9-908E0781C76A}"/>
-    <cellStyle name="Millares 3 15" xfId="141" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Millares 3 15 2" xfId="829" xr:uid="{DA647F8E-C76E-4095-A07B-3C95270A86D4}"/>
-    <cellStyle name="Millares 3 16" xfId="142" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Millares 3 16 2" xfId="830" xr:uid="{47E95EF9-7ADD-4F17-933E-7A564DE5B3BC}"/>
-    <cellStyle name="Millares 3 17" xfId="143" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Millares 3 17 2" xfId="831" xr:uid="{E46068E3-44F1-430E-9E61-2F1D6C51F65C}"/>
-    <cellStyle name="Millares 3 18" xfId="144" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Millares 3 18 2" xfId="832" xr:uid="{D50CECFD-7332-406D-B851-C7FF8551A21F}"/>
-    <cellStyle name="Millares 3 19" xfId="145" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Millares 3 19 2" xfId="833" xr:uid="{5B6712A6-9C90-45DC-A06A-220E69A87192}"/>
-    <cellStyle name="Millares 3 2" xfId="146" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Millares 3 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Millares 3 2 2 2" xfId="835" xr:uid="{2C5AF6EB-B3DE-4084-A7F9-462802461298}"/>
-    <cellStyle name="Millares 3 2 3" xfId="148" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Millares 3 2 3 2" xfId="836" xr:uid="{1EA22512-8B15-4669-8C5D-AD949DA506A4}"/>
-    <cellStyle name="Millares 3 2 4" xfId="834" xr:uid="{6898A4B4-8613-40A3-9A21-EBD8EAAA6017}"/>
-    <cellStyle name="Millares 3 20" xfId="149" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Millares 3 20 2" xfId="837" xr:uid="{D4859FF7-3C76-4A21-917B-DE13B6B81DA3}"/>
-    <cellStyle name="Millares 3 21" xfId="150" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Millares 3 21 2" xfId="838" xr:uid="{DACD326E-DE22-4541-8F55-62CB631AEEF7}"/>
-    <cellStyle name="Millares 3 22" xfId="151" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Millares 3 22 2" xfId="839" xr:uid="{01476297-2662-49A7-86F3-16F7790C0C05}"/>
-    <cellStyle name="Millares 3 23" xfId="152" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Millares 3 23 2" xfId="840" xr:uid="{9C2D6B42-7086-4B38-AE6E-4B120A29FFF7}"/>
-    <cellStyle name="Millares 3 24" xfId="153" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Millares 3 24 2" xfId="841" xr:uid="{2F8DC138-0C42-46B3-BB78-D95373ED5CE0}"/>
-    <cellStyle name="Millares 3 25" xfId="154" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Millares 3 25 2" xfId="842" xr:uid="{841A6F5E-F660-4E14-9B4C-136C1B2E04E1}"/>
-    <cellStyle name="Millares 3 26" xfId="155" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Millares 3 26 2" xfId="843" xr:uid="{77A268C7-AFAB-4632-B4E1-A33E1EA91703}"/>
-    <cellStyle name="Millares 3 27" xfId="156" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Millares 3 27 2" xfId="844" xr:uid="{83FD97AD-5BF6-43FC-B6E5-546A2607305A}"/>
-    <cellStyle name="Millares 3 28" xfId="157" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Millares 3 28 2" xfId="845" xr:uid="{99AB8C30-EC0E-411D-B715-ADCAF06556F8}"/>
-    <cellStyle name="Millares 3 29" xfId="158" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Millares 3 29 2" xfId="846" xr:uid="{221C0615-50FC-4711-9C88-2AC1EDBF8A45}"/>
-    <cellStyle name="Millares 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Millares 3 3 2" xfId="847" xr:uid="{4D14D279-F1E9-4B0B-B414-518ED5DA8115}"/>
-    <cellStyle name="Millares 3 30" xfId="160" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Millares 3 30 2" xfId="848" xr:uid="{6E1BFB95-1E49-4A6E-AFD4-9E1C98BC5664}"/>
-    <cellStyle name="Millares 3 31" xfId="161" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Millares 3 31 2" xfId="849" xr:uid="{6FE3F810-28BD-4607-B093-D2AB9B7BB902}"/>
-    <cellStyle name="Millares 3 32" xfId="162" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Millares 3 32 2" xfId="850" xr:uid="{27DB0AA5-884F-4BB6-97D7-C96C75185B7D}"/>
-    <cellStyle name="Millares 3 33" xfId="163" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Millares 3 33 2" xfId="851" xr:uid="{287C84A7-8332-43FD-93B0-554D8E541216}"/>
-    <cellStyle name="Millares 3 34" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Millares 3 34 2" xfId="852" xr:uid="{BC50C21E-AC67-4DDB-B63F-7CD133B973A4}"/>
-    <cellStyle name="Millares 3 35" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Millares 3 35 2" xfId="853" xr:uid="{770B22E1-F213-4DFD-84FF-F70F2B842BC6}"/>
-    <cellStyle name="Millares 3 36" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Millares 3 36 2" xfId="854" xr:uid="{6E3A52D3-858A-47F8-8EE8-4CFBC71C29C9}"/>
-    <cellStyle name="Millares 3 37" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Millares 3 37 2" xfId="855" xr:uid="{121923B9-E38B-4354-BFE4-5AF3D0457D9D}"/>
-    <cellStyle name="Millares 3 38" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Millares 3 38 2" xfId="856" xr:uid="{984E725D-5E1B-49D7-A7A5-9F0424CA5F50}"/>
-    <cellStyle name="Millares 3 39" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Millares 3 39 2" xfId="857" xr:uid="{578C0061-E270-4825-9527-E2C8794FEB08}"/>
-    <cellStyle name="Millares 3 4" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Millares 3 4 2" xfId="858" xr:uid="{310DFB30-7C13-4786-9FD4-58C54A40FD36}"/>
-    <cellStyle name="Millares 3 40" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Millares 3 40 2" xfId="859" xr:uid="{6453D6DA-58AA-43D3-8C5A-386D2049C70F}"/>
-    <cellStyle name="Millares 3 41" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Millares 3 41 2" xfId="860" xr:uid="{555594B0-91D2-40FA-A2E5-4CEDA68A6840}"/>
-    <cellStyle name="Millares 3 42" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Millares 3 42 2" xfId="861" xr:uid="{7984DEF4-D48D-4637-A472-E0AE56493E51}"/>
-    <cellStyle name="Millares 3 43" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Millares 3 43 2" xfId="862" xr:uid="{5C2D335A-28FE-40CE-8374-1245A5C55AD2}"/>
-    <cellStyle name="Millares 3 44" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Millares 3 44 2" xfId="863" xr:uid="{A21713B7-112F-4CC2-8986-5026AC65B088}"/>
-    <cellStyle name="Millares 3 45" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Millares 3 45 2" xfId="864" xr:uid="{7B73BAD1-1DD4-42AA-B9C4-16D5B5A36EAB}"/>
-    <cellStyle name="Millares 3 46" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Millares 3 46 2" xfId="865" xr:uid="{3C98026D-45FD-406E-A9FD-00673001C59F}"/>
-    <cellStyle name="Millares 3 47" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Millares 3 47 2" xfId="866" xr:uid="{CA217B6B-33D6-4082-B54A-405BFDDB3187}"/>
-    <cellStyle name="Millares 3 48" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Millares 3 48 2" xfId="867" xr:uid="{10FA8A53-6B5F-454A-9736-6EBAAE0F8710}"/>
-    <cellStyle name="Millares 3 49" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Millares 3 49 2" xfId="868" xr:uid="{09D8A2A1-C9E4-4333-9455-524161B08F08}"/>
-    <cellStyle name="Millares 3 5" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Millares 3 5 2" xfId="869" xr:uid="{9877A682-AEE4-48A3-A205-68BCEF45A467}"/>
-    <cellStyle name="Millares 3 50" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Millares 3 50 2" xfId="870" xr:uid="{14F087DA-8A96-4BB0-AF04-F0890C064590}"/>
-    <cellStyle name="Millares 3 51" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Millares 3 51 2" xfId="871" xr:uid="{1BA05B00-6C64-4C42-BE69-CEA4A4A2584F}"/>
-    <cellStyle name="Millares 3 52" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Millares 3 52 2" xfId="872" xr:uid="{D3FE3383-5CE0-4498-815D-EFC5FBB0ADD5}"/>
-    <cellStyle name="Millares 3 53" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Millares 3 53 2" xfId="873" xr:uid="{1767C15A-880C-4784-9445-37361A8B8B51}"/>
-    <cellStyle name="Millares 3 54" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Millares 3 54 2" xfId="874" xr:uid="{D524B04B-B629-408C-B5F8-15D394AB91DB}"/>
-    <cellStyle name="Millares 3 55" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Millares 3 55 2" xfId="875" xr:uid="{9FE87D24-FB41-4A3B-B037-79BFDA0AAD73}"/>
-    <cellStyle name="Millares 3 56" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Millares 3 56 2" xfId="876" xr:uid="{6F31C240-461F-447A-BDB0-F899D2EF3464}"/>
-    <cellStyle name="Millares 3 57" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Millares 3 57 2" xfId="877" xr:uid="{F31C38FE-EB21-43C8-A4BF-599471099C17}"/>
-    <cellStyle name="Millares 3 58" xfId="190" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Millares 3 58 2" xfId="878" xr:uid="{02D3D2A0-9AC3-4A10-BDF2-7211AE4DE15E}"/>
-    <cellStyle name="Millares 3 59" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="Millares 3 59 2" xfId="879" xr:uid="{A3C5BF1B-DA26-40CF-AA51-D78A1FB99DAC}"/>
-    <cellStyle name="Millares 3 6" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="Millares 3 6 2" xfId="880" xr:uid="{671D07CF-106E-4CA0-9CE9-D401C7B81311}"/>
-    <cellStyle name="Millares 3 60" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="Millares 3 60 2" xfId="881" xr:uid="{C74B50D4-CEED-4853-A4A4-15628A65EA4E}"/>
-    <cellStyle name="Millares 3 61" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="Millares 3 61 2" xfId="882" xr:uid="{5EC62C5B-0382-4451-90C4-68BA5F987B21}"/>
-    <cellStyle name="Millares 3 62" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="Millares 3 62 2" xfId="883" xr:uid="{E91A577A-E2B7-47E5-8EBA-F0017C783C4B}"/>
-    <cellStyle name="Millares 3 63" xfId="196" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="Millares 3 63 2" xfId="884" xr:uid="{3EADE132-CD1A-4875-BB69-0EC8EE78EB89}"/>
-    <cellStyle name="Millares 3 64" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="Millares 3 64 2" xfId="885" xr:uid="{F739C55A-DA9D-4FB6-8373-1423E3C46080}"/>
-    <cellStyle name="Millares 3 65" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="Millares 3 65 2" xfId="886" xr:uid="{29738D1D-828B-457B-9C72-FEB418EB27AE}"/>
-    <cellStyle name="Millares 3 66" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="Millares 3 66 2" xfId="887" xr:uid="{0E950C99-E32C-4E3F-9110-E43579F949BE}"/>
-    <cellStyle name="Millares 3 67" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="Millares 3 67 2" xfId="888" xr:uid="{E9EDC08F-07FD-427B-8CAD-AC18C00C27AE}"/>
-    <cellStyle name="Millares 3 68" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="Millares 3 68 2" xfId="889" xr:uid="{CF67FC17-C8C6-471D-AFF6-464DFE3D81D3}"/>
-    <cellStyle name="Millares 3 69" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="Millares 3 69 2" xfId="890" xr:uid="{735F2FA4-1ED3-44AF-8CAF-A6319C20A03D}"/>
-    <cellStyle name="Millares 3 7" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="Millares 3 7 2" xfId="891" xr:uid="{54D20EDD-52D7-41AA-84EF-CEAFA48147EB}"/>
-    <cellStyle name="Millares 3 70" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="Millares 3 70 2" xfId="892" xr:uid="{8528E107-B3F7-435B-8A97-7C87B29646B1}"/>
-    <cellStyle name="Millares 3 71" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="Millares 3 71 2" xfId="893" xr:uid="{2067E852-C04B-4671-90BC-6D368D36BE5A}"/>
-    <cellStyle name="Millares 3 72" xfId="206" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="Millares 3 72 2" xfId="894" xr:uid="{9705390D-3D73-4612-90BB-2DA1FFEFBDC5}"/>
-    <cellStyle name="Millares 3 73" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="Millares 3 73 2" xfId="895" xr:uid="{6425655C-8FEB-4E18-89AF-A08FAF71F9E9}"/>
-    <cellStyle name="Millares 3 74" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="Millares 3 74 2" xfId="896" xr:uid="{D640C94F-8F67-4869-945A-98FC67BA1223}"/>
-    <cellStyle name="Millares 3 75" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
-    <cellStyle name="Millares 3 75 2" xfId="897" xr:uid="{F54D0ADC-603F-4325-A055-3874F1C6BEC4}"/>
-    <cellStyle name="Millares 3 76" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
-    <cellStyle name="Millares 3 76 2" xfId="898" xr:uid="{39E19090-1834-4574-BDE1-0BE90CF08AEA}"/>
-    <cellStyle name="Millares 3 77" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="Millares 3 77 2" xfId="899" xr:uid="{0CAF3401-9876-44B7-BEC6-E0F2C11D6904}"/>
-    <cellStyle name="Millares 3 78" xfId="212" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="Millares 3 78 2" xfId="900" xr:uid="{96A07176-B9DB-4D5A-859D-3D74B158A8E8}"/>
-    <cellStyle name="Millares 3 79" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="Millares 3 79 2" xfId="901" xr:uid="{C5F6E8AF-BC34-4A34-930E-F957EE52AD33}"/>
-    <cellStyle name="Millares 3 8" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="Millares 3 8 2" xfId="902" xr:uid="{227B9690-C2D3-427D-AA4E-63AE8209710A}"/>
-    <cellStyle name="Millares 3 80" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="Millares 3 80 2" xfId="903" xr:uid="{1C0E4AAE-5511-4711-8CF5-E7746B907238}"/>
-    <cellStyle name="Millares 3 81" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="Millares 3 81 2" xfId="904" xr:uid="{CE6EDD92-E3E4-4104-8BC0-2FF2D3E5C267}"/>
-    <cellStyle name="Millares 3 82" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="Millares 3 82 2" xfId="905" xr:uid="{6163A47D-0035-4A09-B4A4-F255E3176861}"/>
-    <cellStyle name="Millares 3 83" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="Millares 3 83 2" xfId="906" xr:uid="{C061AEEC-3E96-4F5B-9D13-3C9B6D9E0C8E}"/>
-    <cellStyle name="Millares 3 84" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="Millares 3 84 2" xfId="907" xr:uid="{7F438CC1-8647-4369-9026-E5D3DE8A6918}"/>
-    <cellStyle name="Millares 3 85" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="Millares 3 85 2" xfId="908" xr:uid="{979B3EAC-B69C-457E-9F60-852B4211C648}"/>
-    <cellStyle name="Millares 3 86" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="Millares 3 86 2" xfId="909" xr:uid="{4FCBD3F1-4DC9-4C8B-92B4-A6CC16CE97D4}"/>
-    <cellStyle name="Millares 3 87" xfId="222" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="Millares 3 87 2" xfId="910" xr:uid="{E7E4DCAD-1D04-4CDB-84CB-DC5A839FB55A}"/>
-    <cellStyle name="Millares 3 88" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="Millares 3 88 2" xfId="911" xr:uid="{C44B3B1D-28D6-4462-83D2-9C6A9EF0769F}"/>
-    <cellStyle name="Millares 3 89" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="Millares 3 89 2" xfId="912" xr:uid="{99763C95-3916-480E-9A13-1A44F768B79D}"/>
-    <cellStyle name="Millares 3 9" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="Millares 3 9 2" xfId="913" xr:uid="{C0114674-3500-42D6-B84B-25D29301730E}"/>
-    <cellStyle name="Millares 3 90" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="Millares 3 90 2" xfId="914" xr:uid="{5C1F68DF-8E3F-4EFB-A968-4CEFC4CCD5AF}"/>
-    <cellStyle name="Millares 3 91" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="Millares 3 91 2" xfId="915" xr:uid="{3360A8A7-EC35-413D-9165-71FE257E86C7}"/>
-    <cellStyle name="Millares 3 92" xfId="228" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="Millares 3 92 2" xfId="916" xr:uid="{1212C964-8CF2-4A2A-8BB0-F161FB21FCCF}"/>
-    <cellStyle name="Millares 3 93" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="Millares 3 93 2" xfId="917" xr:uid="{EB2BD4B3-FC0B-4FA1-A90F-33E4AE0651B8}"/>
-    <cellStyle name="Millares 3 94" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="Millares 3 94 2" xfId="918" xr:uid="{8213782F-2358-4A2F-98F2-D930CE749901}"/>
-    <cellStyle name="Millares 3 95" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="Millares 3 95 2" xfId="919" xr:uid="{932518D2-1990-4196-830E-124BE718AB41}"/>
-    <cellStyle name="Millares 3 96" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="Millares 3 96 2" xfId="920" xr:uid="{EDE4E994-92AB-4486-B71F-FF0B2023E308}"/>
-    <cellStyle name="Millares 3 97" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="Millares 3 97 2" xfId="921" xr:uid="{49F94B35-0409-4C6D-94B4-01CFE0270C2F}"/>
-    <cellStyle name="Millares 3 98" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="Millares 3 98 2" xfId="922" xr:uid="{7CA7B20B-F612-403E-B7E5-6BDFB8E62D72}"/>
-    <cellStyle name="Millares 3 99" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="Millares 3 99 2" xfId="923" xr:uid="{588AAA04-14A3-4112-8401-85F287F3B1D1}"/>
-    <cellStyle name="Millares 4" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="Millares 4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="Millares 4 2 2" xfId="925" xr:uid="{632E5153-739F-49B0-87B4-DA422CAB2917}"/>
-    <cellStyle name="Millares 4 3" xfId="924" xr:uid="{9636C4B6-5205-4D11-8AD2-95728FB18F49}"/>
-    <cellStyle name="Millares 5" xfId="238" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="Millares 5 2" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="Millares 5 2 2" xfId="927" xr:uid="{6B039BC7-2E98-40F5-83E3-9E4F59F8828D}"/>
-    <cellStyle name="Millares 5 3" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="Millares 5 3 2" xfId="928" xr:uid="{9AEEF321-1C47-4FB4-82C2-BEA39434E7F8}"/>
-    <cellStyle name="Millares 5 4" xfId="926" xr:uid="{C483AC5F-BB36-404C-85F5-CB5F7D9A6B55}"/>
-    <cellStyle name="Millares 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="Millares 6 2" xfId="242" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="Millares 6 2 2" xfId="929" xr:uid="{A7799074-2321-463A-A10C-292DA2BE0629}"/>
-    <cellStyle name="Millares 6 3" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="Millares 7" xfId="244" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="Millares 7 2" xfId="930" xr:uid="{42B5A3B7-F168-45C6-A163-A0BBB4F476C0}"/>
-    <cellStyle name="Millares 8" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="Millares 8 2" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="Millares 8 2 2" xfId="932" xr:uid="{22CA6473-034B-4955-A46D-6C28A880DF39}"/>
-    <cellStyle name="Millares 8 3" xfId="931" xr:uid="{7533A74B-739D-4BE6-BF6F-B7C0CC329668}"/>
-    <cellStyle name="Millares 9" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="Millares 9 2" xfId="933" xr:uid="{DAC0DBE0-3508-4BA0-ACA9-FB9190183533}"/>
-    <cellStyle name="Neutral 2" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="Neutral 3" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="Neutral 4" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="Neutral 5" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="NivelFila_3 2" xfId="809" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="4"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="7"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="8"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="9"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="10"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="11"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="12"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="13"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="14"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="15"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="16"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="17"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="18"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="19"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="20"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="21"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="22"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="23"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="24"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="25"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="26"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="27"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="28"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="29"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="30"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="31"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="32"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="33"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="34"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="35"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="36"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="37"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="38"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="39"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="40"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="41"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="42"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="43"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="44"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="45"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="46"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="47"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="48"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="49"/>
+    <cellStyle name="60% - Énfasis1 2" xfId="50"/>
+    <cellStyle name="60% - Énfasis1 3" xfId="51"/>
+    <cellStyle name="60% - Énfasis1 4" xfId="52"/>
+    <cellStyle name="60% - Énfasis2 2" xfId="53"/>
+    <cellStyle name="60% - Énfasis2 3" xfId="54"/>
+    <cellStyle name="60% - Énfasis2 4" xfId="55"/>
+    <cellStyle name="60% - Énfasis3 2" xfId="56"/>
+    <cellStyle name="60% - Énfasis3 2 2" xfId="57"/>
+    <cellStyle name="60% - Énfasis3 2 3" xfId="58"/>
+    <cellStyle name="60% - Énfasis3 3" xfId="59"/>
+    <cellStyle name="60% - Énfasis3 4" xfId="60"/>
+    <cellStyle name="60% - Énfasis4 2" xfId="61"/>
+    <cellStyle name="60% - Énfasis4 2 2" xfId="62"/>
+    <cellStyle name="60% - Énfasis4 2 3" xfId="63"/>
+    <cellStyle name="60% - Énfasis4 3" xfId="64"/>
+    <cellStyle name="60% - Énfasis4 4" xfId="65"/>
+    <cellStyle name="60% - Énfasis5 2" xfId="66"/>
+    <cellStyle name="60% - Énfasis5 3" xfId="67"/>
+    <cellStyle name="60% - Énfasis5 4" xfId="68"/>
+    <cellStyle name="60% - Énfasis6 2" xfId="69"/>
+    <cellStyle name="60% - Énfasis6 2 2" xfId="70"/>
+    <cellStyle name="60% - Énfasis6 2 3" xfId="71"/>
+    <cellStyle name="60% - Énfasis6 3" xfId="72"/>
+    <cellStyle name="60% - Énfasis6 4" xfId="73"/>
+    <cellStyle name="Buena 2" xfId="74"/>
+    <cellStyle name="Buena 3" xfId="75"/>
+    <cellStyle name="Buena 4" xfId="76"/>
+    <cellStyle name="Cálculo 2" xfId="77"/>
+    <cellStyle name="Cálculo 3" xfId="78"/>
+    <cellStyle name="Cálculo 4" xfId="79"/>
+    <cellStyle name="Celda de comprobación 2" xfId="80"/>
+    <cellStyle name="Celda de comprobación 3" xfId="81"/>
+    <cellStyle name="Celda de comprobación 4" xfId="82"/>
+    <cellStyle name="Celda vinculada 2" xfId="83"/>
+    <cellStyle name="Celda vinculada 3" xfId="84"/>
+    <cellStyle name="Celda vinculada 4" xfId="85"/>
+    <cellStyle name="Comma 2" xfId="121"/>
+    <cellStyle name="Encabezado 4 2" xfId="86"/>
+    <cellStyle name="Encabezado 4 3" xfId="87"/>
+    <cellStyle name="Encabezado 4 4" xfId="88"/>
+    <cellStyle name="Énfasis1 2" xfId="89"/>
+    <cellStyle name="Énfasis1 3" xfId="90"/>
+    <cellStyle name="Énfasis1 4" xfId="91"/>
+    <cellStyle name="Énfasis2 2" xfId="92"/>
+    <cellStyle name="Énfasis2 3" xfId="93"/>
+    <cellStyle name="Énfasis2 4" xfId="94"/>
+    <cellStyle name="Énfasis3 2" xfId="95"/>
+    <cellStyle name="Énfasis3 3" xfId="96"/>
+    <cellStyle name="Énfasis3 4" xfId="97"/>
+    <cellStyle name="Énfasis4 2" xfId="98"/>
+    <cellStyle name="Énfasis4 3" xfId="99"/>
+    <cellStyle name="Énfasis4 4" xfId="100"/>
+    <cellStyle name="Énfasis5 2" xfId="101"/>
+    <cellStyle name="Énfasis5 3" xfId="102"/>
+    <cellStyle name="Énfasis5 4" xfId="103"/>
+    <cellStyle name="Énfasis6 2" xfId="104"/>
+    <cellStyle name="Énfasis6 3" xfId="105"/>
+    <cellStyle name="Énfasis6 4" xfId="106"/>
+    <cellStyle name="Entrada 2" xfId="107"/>
+    <cellStyle name="Entrada 3" xfId="108"/>
+    <cellStyle name="Entrada 4" xfId="109"/>
+    <cellStyle name="Euro" xfId="110"/>
+    <cellStyle name="Euro 2" xfId="111"/>
+    <cellStyle name="Euro 2 2" xfId="112"/>
+    <cellStyle name="Euro 2 3" xfId="113"/>
+    <cellStyle name="Euro 2 4" xfId="114"/>
+    <cellStyle name="Euro 3" xfId="115"/>
+    <cellStyle name="Euro 4" xfId="116"/>
+    <cellStyle name="Euro 5" xfId="117"/>
+    <cellStyle name="Incorrecto 2" xfId="118"/>
+    <cellStyle name="Incorrecto 3" xfId="119"/>
+    <cellStyle name="Incorrecto 4" xfId="120"/>
+    <cellStyle name="Millares 10" xfId="122"/>
+    <cellStyle name="Millares 10 2" xfId="810"/>
+    <cellStyle name="Millares 2" xfId="123"/>
+    <cellStyle name="Millares 2 2" xfId="124"/>
+    <cellStyle name="Millares 2 2 2" xfId="125"/>
+    <cellStyle name="Millares 2 2 2 2" xfId="813"/>
+    <cellStyle name="Millares 2 2 3" xfId="812"/>
+    <cellStyle name="Millares 2 3" xfId="126"/>
+    <cellStyle name="Millares 2 3 2" xfId="814"/>
+    <cellStyle name="Millares 2 4" xfId="127"/>
+    <cellStyle name="Millares 2 4 2" xfId="815"/>
+    <cellStyle name="Millares 2 5" xfId="811"/>
+    <cellStyle name="Millares 3" xfId="128"/>
+    <cellStyle name="Millares 3 10" xfId="129"/>
+    <cellStyle name="Millares 3 10 2" xfId="817"/>
+    <cellStyle name="Millares 3 100" xfId="130"/>
+    <cellStyle name="Millares 3 100 2" xfId="818"/>
+    <cellStyle name="Millares 3 101" xfId="131"/>
+    <cellStyle name="Millares 3 101 2" xfId="819"/>
+    <cellStyle name="Millares 3 102" xfId="132"/>
+    <cellStyle name="Millares 3 102 2" xfId="820"/>
+    <cellStyle name="Millares 3 103" xfId="133"/>
+    <cellStyle name="Millares 3 103 2" xfId="134"/>
+    <cellStyle name="Millares 3 103 2 2" xfId="135"/>
+    <cellStyle name="Millares 3 103 2 2 2" xfId="823"/>
+    <cellStyle name="Millares 3 103 2 3" xfId="822"/>
+    <cellStyle name="Millares 3 103 3" xfId="821"/>
+    <cellStyle name="Millares 3 104" xfId="136"/>
+    <cellStyle name="Millares 3 104 2" xfId="824"/>
+    <cellStyle name="Millares 3 105" xfId="816"/>
+    <cellStyle name="Millares 3 11" xfId="137"/>
+    <cellStyle name="Millares 3 11 2" xfId="825"/>
+    <cellStyle name="Millares 3 12" xfId="138"/>
+    <cellStyle name="Millares 3 12 2" xfId="826"/>
+    <cellStyle name="Millares 3 13" xfId="139"/>
+    <cellStyle name="Millares 3 13 2" xfId="827"/>
+    <cellStyle name="Millares 3 14" xfId="140"/>
+    <cellStyle name="Millares 3 14 2" xfId="828"/>
+    <cellStyle name="Millares 3 15" xfId="141"/>
+    <cellStyle name="Millares 3 15 2" xfId="829"/>
+    <cellStyle name="Millares 3 16" xfId="142"/>
+    <cellStyle name="Millares 3 16 2" xfId="830"/>
+    <cellStyle name="Millares 3 17" xfId="143"/>
+    <cellStyle name="Millares 3 17 2" xfId="831"/>
+    <cellStyle name="Millares 3 18" xfId="144"/>
+    <cellStyle name="Millares 3 18 2" xfId="832"/>
+    <cellStyle name="Millares 3 19" xfId="145"/>
+    <cellStyle name="Millares 3 19 2" xfId="833"/>
+    <cellStyle name="Millares 3 2" xfId="146"/>
+    <cellStyle name="Millares 3 2 2" xfId="147"/>
+    <cellStyle name="Millares 3 2 2 2" xfId="835"/>
+    <cellStyle name="Millares 3 2 3" xfId="148"/>
+    <cellStyle name="Millares 3 2 3 2" xfId="836"/>
+    <cellStyle name="Millares 3 2 4" xfId="834"/>
+    <cellStyle name="Millares 3 20" xfId="149"/>
+    <cellStyle name="Millares 3 20 2" xfId="837"/>
+    <cellStyle name="Millares 3 21" xfId="150"/>
+    <cellStyle name="Millares 3 21 2" xfId="838"/>
+    <cellStyle name="Millares 3 22" xfId="151"/>
+    <cellStyle name="Millares 3 22 2" xfId="839"/>
+    <cellStyle name="Millares 3 23" xfId="152"/>
+    <cellStyle name="Millares 3 23 2" xfId="840"/>
+    <cellStyle name="Millares 3 24" xfId="153"/>
+    <cellStyle name="Millares 3 24 2" xfId="841"/>
+    <cellStyle name="Millares 3 25" xfId="154"/>
+    <cellStyle name="Millares 3 25 2" xfId="842"/>
+    <cellStyle name="Millares 3 26" xfId="155"/>
+    <cellStyle name="Millares 3 26 2" xfId="843"/>
+    <cellStyle name="Millares 3 27" xfId="156"/>
+    <cellStyle name="Millares 3 27 2" xfId="844"/>
+    <cellStyle name="Millares 3 28" xfId="157"/>
+    <cellStyle name="Millares 3 28 2" xfId="845"/>
+    <cellStyle name="Millares 3 29" xfId="158"/>
+    <cellStyle name="Millares 3 29 2" xfId="846"/>
+    <cellStyle name="Millares 3 3" xfId="159"/>
+    <cellStyle name="Millares 3 3 2" xfId="847"/>
+    <cellStyle name="Millares 3 30" xfId="160"/>
+    <cellStyle name="Millares 3 30 2" xfId="848"/>
+    <cellStyle name="Millares 3 31" xfId="161"/>
+    <cellStyle name="Millares 3 31 2" xfId="849"/>
+    <cellStyle name="Millares 3 32" xfId="162"/>
+    <cellStyle name="Millares 3 32 2" xfId="850"/>
+    <cellStyle name="Millares 3 33" xfId="163"/>
+    <cellStyle name="Millares 3 33 2" xfId="851"/>
+    <cellStyle name="Millares 3 34" xfId="164"/>
+    <cellStyle name="Millares 3 34 2" xfId="852"/>
+    <cellStyle name="Millares 3 35" xfId="165"/>
+    <cellStyle name="Millares 3 35 2" xfId="853"/>
+    <cellStyle name="Millares 3 36" xfId="166"/>
+    <cellStyle name="Millares 3 36 2" xfId="854"/>
+    <cellStyle name="Millares 3 37" xfId="167"/>
+    <cellStyle name="Millares 3 37 2" xfId="855"/>
+    <cellStyle name="Millares 3 38" xfId="168"/>
+    <cellStyle name="Millares 3 38 2" xfId="856"/>
+    <cellStyle name="Millares 3 39" xfId="169"/>
+    <cellStyle name="Millares 3 39 2" xfId="857"/>
+    <cellStyle name="Millares 3 4" xfId="170"/>
+    <cellStyle name="Millares 3 4 2" xfId="858"/>
+    <cellStyle name="Millares 3 40" xfId="171"/>
+    <cellStyle name="Millares 3 40 2" xfId="859"/>
+    <cellStyle name="Millares 3 41" xfId="172"/>
+    <cellStyle name="Millares 3 41 2" xfId="860"/>
+    <cellStyle name="Millares 3 42" xfId="173"/>
+    <cellStyle name="Millares 3 42 2" xfId="861"/>
+    <cellStyle name="Millares 3 43" xfId="174"/>
+    <cellStyle name="Millares 3 43 2" xfId="862"/>
+    <cellStyle name="Millares 3 44" xfId="175"/>
+    <cellStyle name="Millares 3 44 2" xfId="863"/>
+    <cellStyle name="Millares 3 45" xfId="176"/>
+    <cellStyle name="Millares 3 45 2" xfId="864"/>
+    <cellStyle name="Millares 3 46" xfId="177"/>
+    <cellStyle name="Millares 3 46 2" xfId="865"/>
+    <cellStyle name="Millares 3 47" xfId="178"/>
+    <cellStyle name="Millares 3 47 2" xfId="866"/>
+    <cellStyle name="Millares 3 48" xfId="179"/>
+    <cellStyle name="Millares 3 48 2" xfId="867"/>
+    <cellStyle name="Millares 3 49" xfId="180"/>
+    <cellStyle name="Millares 3 49 2" xfId="868"/>
+    <cellStyle name="Millares 3 5" xfId="181"/>
+    <cellStyle name="Millares 3 5 2" xfId="869"/>
+    <cellStyle name="Millares 3 50" xfId="182"/>
+    <cellStyle name="Millares 3 50 2" xfId="870"/>
+    <cellStyle name="Millares 3 51" xfId="183"/>
+    <cellStyle name="Millares 3 51 2" xfId="871"/>
+    <cellStyle name="Millares 3 52" xfId="184"/>
+    <cellStyle name="Millares 3 52 2" xfId="872"/>
+    <cellStyle name="Millares 3 53" xfId="185"/>
+    <cellStyle name="Millares 3 53 2" xfId="873"/>
+    <cellStyle name="Millares 3 54" xfId="186"/>
+    <cellStyle name="Millares 3 54 2" xfId="874"/>
+    <cellStyle name="Millares 3 55" xfId="187"/>
+    <cellStyle name="Millares 3 55 2" xfId="875"/>
+    <cellStyle name="Millares 3 56" xfId="188"/>
+    <cellStyle name="Millares 3 56 2" xfId="876"/>
+    <cellStyle name="Millares 3 57" xfId="189"/>
+    <cellStyle name="Millares 3 57 2" xfId="877"/>
+    <cellStyle name="Millares 3 58" xfId="190"/>
+    <cellStyle name="Millares 3 58 2" xfId="878"/>
+    <cellStyle name="Millares 3 59" xfId="191"/>
+    <cellStyle name="Millares 3 59 2" xfId="879"/>
+    <cellStyle name="Millares 3 6" xfId="192"/>
+    <cellStyle name="Millares 3 6 2" xfId="880"/>
+    <cellStyle name="Millares 3 60" xfId="193"/>
+    <cellStyle name="Millares 3 60 2" xfId="881"/>
+    <cellStyle name="Millares 3 61" xfId="194"/>
+    <cellStyle name="Millares 3 61 2" xfId="882"/>
+    <cellStyle name="Millares 3 62" xfId="195"/>
+    <cellStyle name="Millares 3 62 2" xfId="883"/>
+    <cellStyle name="Millares 3 63" xfId="196"/>
+    <cellStyle name="Millares 3 63 2" xfId="884"/>
+    <cellStyle name="Millares 3 64" xfId="197"/>
+    <cellStyle name="Millares 3 64 2" xfId="885"/>
+    <cellStyle name="Millares 3 65" xfId="198"/>
+    <cellStyle name="Millares 3 65 2" xfId="886"/>
+    <cellStyle name="Millares 3 66" xfId="199"/>
+    <cellStyle name="Millares 3 66 2" xfId="887"/>
+    <cellStyle name="Millares 3 67" xfId="200"/>
+    <cellStyle name="Millares 3 67 2" xfId="888"/>
+    <cellStyle name="Millares 3 68" xfId="201"/>
+    <cellStyle name="Millares 3 68 2" xfId="889"/>
+    <cellStyle name="Millares 3 69" xfId="202"/>
+    <cellStyle name="Millares 3 69 2" xfId="890"/>
+    <cellStyle name="Millares 3 7" xfId="203"/>
+    <cellStyle name="Millares 3 7 2" xfId="891"/>
+    <cellStyle name="Millares 3 70" xfId="204"/>
+    <cellStyle name="Millares 3 70 2" xfId="892"/>
+    <cellStyle name="Millares 3 71" xfId="205"/>
+    <cellStyle name="Millares 3 71 2" xfId="893"/>
+    <cellStyle name="Millares 3 72" xfId="206"/>
+    <cellStyle name="Millares 3 72 2" xfId="894"/>
+    <cellStyle name="Millares 3 73" xfId="207"/>
+    <cellStyle name="Millares 3 73 2" xfId="895"/>
+    <cellStyle name="Millares 3 74" xfId="208"/>
+    <cellStyle name="Millares 3 74 2" xfId="896"/>
+    <cellStyle name="Millares 3 75" xfId="209"/>
+    <cellStyle name="Millares 3 75 2" xfId="897"/>
+    <cellStyle name="Millares 3 76" xfId="210"/>
+    <cellStyle name="Millares 3 76 2" xfId="898"/>
+    <cellStyle name="Millares 3 77" xfId="211"/>
+    <cellStyle name="Millares 3 77 2" xfId="899"/>
+    <cellStyle name="Millares 3 78" xfId="212"/>
+    <cellStyle name="Millares 3 78 2" xfId="900"/>
+    <cellStyle name="Millares 3 79" xfId="213"/>
+    <cellStyle name="Millares 3 79 2" xfId="901"/>
+    <cellStyle name="Millares 3 8" xfId="214"/>
+    <cellStyle name="Millares 3 8 2" xfId="902"/>
+    <cellStyle name="Millares 3 80" xfId="215"/>
+    <cellStyle name="Millares 3 80 2" xfId="903"/>
+    <cellStyle name="Millares 3 81" xfId="216"/>
+    <cellStyle name="Millares 3 81 2" xfId="904"/>
+    <cellStyle name="Millares 3 82" xfId="217"/>
+    <cellStyle name="Millares 3 82 2" xfId="905"/>
+    <cellStyle name="Millares 3 83" xfId="218"/>
+    <cellStyle name="Millares 3 83 2" xfId="906"/>
+    <cellStyle name="Millares 3 84" xfId="219"/>
+    <cellStyle name="Millares 3 84 2" xfId="907"/>
+    <cellStyle name="Millares 3 85" xfId="220"/>
+    <cellStyle name="Millares 3 85 2" xfId="908"/>
+    <cellStyle name="Millares 3 86" xfId="221"/>
+    <cellStyle name="Millares 3 86 2" xfId="909"/>
+    <cellStyle name="Millares 3 87" xfId="222"/>
+    <cellStyle name="Millares 3 87 2" xfId="910"/>
+    <cellStyle name="Millares 3 88" xfId="223"/>
+    <cellStyle name="Millares 3 88 2" xfId="911"/>
+    <cellStyle name="Millares 3 89" xfId="224"/>
+    <cellStyle name="Millares 3 89 2" xfId="912"/>
+    <cellStyle name="Millares 3 9" xfId="225"/>
+    <cellStyle name="Millares 3 9 2" xfId="913"/>
+    <cellStyle name="Millares 3 90" xfId="226"/>
+    <cellStyle name="Millares 3 90 2" xfId="914"/>
+    <cellStyle name="Millares 3 91" xfId="227"/>
+    <cellStyle name="Millares 3 91 2" xfId="915"/>
+    <cellStyle name="Millares 3 92" xfId="228"/>
+    <cellStyle name="Millares 3 92 2" xfId="916"/>
+    <cellStyle name="Millares 3 93" xfId="229"/>
+    <cellStyle name="Millares 3 93 2" xfId="917"/>
+    <cellStyle name="Millares 3 94" xfId="230"/>
+    <cellStyle name="Millares 3 94 2" xfId="918"/>
+    <cellStyle name="Millares 3 95" xfId="231"/>
+    <cellStyle name="Millares 3 95 2" xfId="919"/>
+    <cellStyle name="Millares 3 96" xfId="232"/>
+    <cellStyle name="Millares 3 96 2" xfId="920"/>
+    <cellStyle name="Millares 3 97" xfId="233"/>
+    <cellStyle name="Millares 3 97 2" xfId="921"/>
+    <cellStyle name="Millares 3 98" xfId="234"/>
+    <cellStyle name="Millares 3 98 2" xfId="922"/>
+    <cellStyle name="Millares 3 99" xfId="235"/>
+    <cellStyle name="Millares 3 99 2" xfId="923"/>
+    <cellStyle name="Millares 4" xfId="236"/>
+    <cellStyle name="Millares 4 2" xfId="237"/>
+    <cellStyle name="Millares 4 2 2" xfId="925"/>
+    <cellStyle name="Millares 4 3" xfId="924"/>
+    <cellStyle name="Millares 5" xfId="238"/>
+    <cellStyle name="Millares 5 2" xfId="239"/>
+    <cellStyle name="Millares 5 2 2" xfId="927"/>
+    <cellStyle name="Millares 5 3" xfId="240"/>
+    <cellStyle name="Millares 5 3 2" xfId="928"/>
+    <cellStyle name="Millares 5 4" xfId="926"/>
+    <cellStyle name="Millares 6" xfId="241"/>
+    <cellStyle name="Millares 6 2" xfId="242"/>
+    <cellStyle name="Millares 6 2 2" xfId="929"/>
+    <cellStyle name="Millares 6 3" xfId="243"/>
+    <cellStyle name="Millares 7" xfId="244"/>
+    <cellStyle name="Millares 7 2" xfId="930"/>
+    <cellStyle name="Millares 8" xfId="245"/>
+    <cellStyle name="Millares 8 2" xfId="246"/>
+    <cellStyle name="Millares 8 2 2" xfId="932"/>
+    <cellStyle name="Millares 8 3" xfId="931"/>
+    <cellStyle name="Millares 9" xfId="247"/>
+    <cellStyle name="Millares 9 2" xfId="933"/>
+    <cellStyle name="Neutral 2" xfId="249"/>
+    <cellStyle name="Neutral 3" xfId="250"/>
+    <cellStyle name="Neutral 4" xfId="251"/>
+    <cellStyle name="Neutral 5" xfId="248"/>
+    <cellStyle name="NivelFila_3 2" xfId="809"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="252" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="Normal 10 2" xfId="253" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="Normal 10 3" xfId="254" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="Normal 10 4" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="Normal 100" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="Normal 100 2" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="Normal 101" xfId="258" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="Normal 101 2" xfId="259" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="Normal 102" xfId="260" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="Normal 102 2" xfId="261" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="Normal 103" xfId="262" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="Normal 103 2" xfId="263" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="Normal 104" xfId="264" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="Normal 104 2" xfId="265" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="Normal 104 3" xfId="266" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="Normal 105" xfId="267" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="Normal 106" xfId="268" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="Normal 106 2" xfId="269" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="Normal 106 3" xfId="270" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="Normal 107" xfId="271" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="Normal 107 2" xfId="272" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="Normal 108" xfId="273" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="Normal 109" xfId="274" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="Normal 11" xfId="275" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="Normal 11 2" xfId="276" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="Normal 11 3" xfId="277" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="Normal 11 4" xfId="278" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="Normal 110" xfId="279" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="Normal 111" xfId="280" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="Normal 112" xfId="281" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="Normal 112 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="Normal 113" xfId="283" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="Normal 113 2" xfId="284" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="Normal 114" xfId="285" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="Normal 114 2" xfId="286" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="Normal 115" xfId="287" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="Normal 115 2" xfId="288" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="Normal 116" xfId="289" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="Normal 116 2" xfId="290" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="Normal 116 3" xfId="291" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="Normal 117" xfId="292" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="Normal 117 2" xfId="293" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="Normal 118" xfId="294" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="Normal 118 2" xfId="295" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="Normal 118 3" xfId="296" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="Normal 119" xfId="297" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="Normal 119 2" xfId="298" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="Normal 119 3" xfId="299" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="Normal 12" xfId="300" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="Normal 12 2" xfId="301" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="Normal 12 3" xfId="302" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="Normal 12 4" xfId="303" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="Normal 120" xfId="304" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="Normal 120 2" xfId="305" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="Normal 121" xfId="306" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="Normal 121 2" xfId="307" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="Normal 122" xfId="308" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="Normal 122 2" xfId="309" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="Normal 123" xfId="310" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
-    <cellStyle name="Normal 124" xfId="311" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
-    <cellStyle name="Normal 124 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="Normal 125" xfId="313" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="Normal 125 2" xfId="314" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="Normal 126" xfId="315" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="Normal 127" xfId="316" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="Normal 127 2" xfId="317" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="Normal 128" xfId="318" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="Normal 129" xfId="319" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="Normal 13" xfId="320" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="Normal 13 2" xfId="321" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="Normal 13 3" xfId="322" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="Normal 13 4" xfId="323" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="Normal 130" xfId="324" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="Normal 130 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="Normal 131" xfId="326" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="Normal 131 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="Normal 132" xfId="328" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="Normal 132 2" xfId="329" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="Normal 133" xfId="330" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="Normal 133 2" xfId="331" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="Normal 134" xfId="332" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="Normal 135" xfId="333" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="Normal 135 2" xfId="334" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="Normal 136" xfId="335" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="Normal 136 2" xfId="336" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="Normal 137" xfId="337" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="Normal 137 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="Normal 138" xfId="339" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="Normal 138 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="Normal 139" xfId="341" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="Normal 139 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="Normal 14" xfId="343" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="Normal 14 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="Normal 14 3" xfId="345" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="Normal 14 4" xfId="346" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="Normal 140" xfId="347" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="Normal 140 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="Normal 141" xfId="349" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="Normal 142" xfId="350" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="Normal 142 2" xfId="351" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="Normal 143" xfId="352" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="Normal 143 2" xfId="353" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="Normal 143 3" xfId="354" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="Normal 144" xfId="355" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="Normal 144 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="Normal 145" xfId="357" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="Normal 145 2" xfId="358" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="Normal 146" xfId="359" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="Normal 147" xfId="360" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="Normal 15" xfId="361" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="Normal 15 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="Normal 15 3" xfId="363" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="Normal 15 4" xfId="364" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="Normal 16" xfId="365" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="Normal 16 2" xfId="366" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="Normal 16 3" xfId="367" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="Normal 16 4" xfId="368" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="Normal 17" xfId="369" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="Normal 17 2" xfId="370" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="Normal 17 3" xfId="371" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="Normal 17 4" xfId="372" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="Normal 18" xfId="373" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="Normal 18 2" xfId="374" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="Normal 18 3" xfId="375" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="Normal 18 4" xfId="376" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="Normal 19" xfId="377" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="Normal 19 2" xfId="378" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="Normal 19 3" xfId="379" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="Normal 19 4" xfId="380" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="Normal 2" xfId="381" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="Normal 2 10" xfId="382" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="Normal 2 100" xfId="383" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="Normal 2 101" xfId="384" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="Normal 2 102" xfId="385" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="Normal 2 103" xfId="386" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="Normal 2 103 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="Normal 2 103 2 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="Normal 2 104" xfId="389" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="Normal 2 104 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="Normal 2 105" xfId="391" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="Normal 2 105 2" xfId="392" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="Normal 2 106" xfId="393" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="Normal 2 106 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="Normal 2 106 3" xfId="395" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="Normal 2 107" xfId="396" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="Normal 2 107 2" xfId="397" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="Normal 2 108" xfId="398" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="Normal 2 108 2" xfId="399" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="Normal 2 109" xfId="400" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="Normal 2 109 2" xfId="401" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="Normal 2 11" xfId="402" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="Normal 2 110" xfId="403" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="Normal 2 111" xfId="404" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="Normal 2 112" xfId="405" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="Normal 2 113" xfId="406" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="Normal 2 114" xfId="407" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="Normal 2 115" xfId="408" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="Normal 2 12" xfId="409" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="Normal 2 13" xfId="410" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="Normal 2 14" xfId="411" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="Normal 2 15" xfId="412" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="Normal 2 16" xfId="413" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
-    <cellStyle name="Normal 2 17" xfId="414" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
-    <cellStyle name="Normal 2 18" xfId="415" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="Normal 2 19" xfId="416" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="Normal 2 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="418" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="Normal 2 2 2 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="Normal 2 2 3" xfId="420" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="Normal 2 2 4" xfId="421" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="Normal 2 20" xfId="422" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="Normal 2 21" xfId="423" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="Normal 2 22" xfId="424" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="Normal 2 23" xfId="425" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="Normal 2 24" xfId="426" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="Normal 2 25" xfId="427" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="Normal 2 26" xfId="428" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="Normal 2 27" xfId="429" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="Normal 2 28" xfId="430" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="Normal 2 29" xfId="431" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="Normal 2 3" xfId="432" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="Normal 2 3 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="Normal 2 3 3" xfId="434" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="Normal 2 30" xfId="435" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="Normal 2 31" xfId="436" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="Normal 2 32" xfId="437" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="Normal 2 33" xfId="438" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="Normal 2 34" xfId="439" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="Normal 2 35" xfId="440" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="Normal 2 36" xfId="441" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="Normal 2 37" xfId="442" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="Normal 2 38" xfId="443" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="Normal 2 39" xfId="444" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="Normal 2 4" xfId="445" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="Normal 2 4 2" xfId="446" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="Normal 2 4 3" xfId="447" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="Normal 2 4 4" xfId="448" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="Normal 2 40" xfId="449" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="Normal 2 41" xfId="450" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="Normal 2 42" xfId="451" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="Normal 2 43" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="Normal 2 44" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="Normal 2 45" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="Normal 2 45 10" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="Normal 2 45 11" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="Normal 2 45 12" xfId="457" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="Normal 2 45 13" xfId="458" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="Normal 2 45 14" xfId="459" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="Normal 2 45 15" xfId="460" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="Normal 2 45 16" xfId="461" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="Normal 2 45 17" xfId="462" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="Normal 2 45 18" xfId="463" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="Normal 2 45 19" xfId="464" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="Normal 2 45 2" xfId="465" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="Normal 2 45 20" xfId="466" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="Normal 2 45 21" xfId="467" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="Normal 2 45 22" xfId="468" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="Normal 2 45 23" xfId="469" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="Normal 2 45 24" xfId="470" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="Normal 2 45 25" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="Normal 2 45 26" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="Normal 2 45 27" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="Normal 2 45 28" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="Normal 2 45 29" xfId="475" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="Normal 2 45 3" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="Normal 2 45 30" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="Normal 2 45 31" xfId="478" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="Normal 2 45 32" xfId="479" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="Normal 2 45 33" xfId="480" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="Normal 2 45 34" xfId="481" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="Normal 2 45 35" xfId="482" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="Normal 2 45 36" xfId="483" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="Normal 2 45 37" xfId="484" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="Normal 2 45 38" xfId="485" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="Normal 2 45 39" xfId="486" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="Normal 2 45 4" xfId="487" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="Normal 2 45 40" xfId="488" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="Normal 2 45 41" xfId="489" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="Normal 2 45 42" xfId="490" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="Normal 2 45 43" xfId="491" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="Normal 2 45 44" xfId="492" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="Normal 2 45 45" xfId="493" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="Normal 2 45 46" xfId="494" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="Normal 2 45 47" xfId="495" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="Normal 2 45 48" xfId="496" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="Normal 2 45 49" xfId="497" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="Normal 2 45 5" xfId="498" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="Normal 2 45 50" xfId="499" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="Normal 2 45 51" xfId="500" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="Normal 2 45 52" xfId="501" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="Normal 2 45 53" xfId="502" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="Normal 2 45 54" xfId="503" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="Normal 2 45 55" xfId="504" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="Normal 2 45 56" xfId="505" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="Normal 2 45 57" xfId="506" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="Normal 2 45 58" xfId="507" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="Normal 2 45 59" xfId="508" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="Normal 2 45 6" xfId="509" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="Normal 2 45 7" xfId="510" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="Normal 2 45 8" xfId="511" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="Normal 2 45 9" xfId="512" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="Normal 2 46" xfId="513" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="Normal 2 47" xfId="514" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="Normal 2 48" xfId="515" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="Normal 2 49" xfId="516" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
-    <cellStyle name="Normal 2 5" xfId="517" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
-    <cellStyle name="Normal 2 5 2" xfId="518" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="Normal 2 5 3" xfId="519" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="Normal 2 5 3 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="Normal 2 5 4" xfId="521" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="Normal 2 50" xfId="522" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="Normal 2 51" xfId="523" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="Normal 2 52" xfId="524" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="Normal 2 53" xfId="525" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="Normal 2 54" xfId="526" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="Normal 2 55" xfId="527" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="Normal 2 56" xfId="528" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="Normal 2 57" xfId="529" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="Normal 2 58" xfId="530" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="Normal 2 59" xfId="531" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="Normal 2 6" xfId="532" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="Normal 2 6 2" xfId="533" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="Normal 2 60" xfId="534" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="Normal 2 61" xfId="535" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="Normal 2 62" xfId="536" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="Normal 2 63" xfId="537" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="Normal 2 64" xfId="538" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="Normal 2 65" xfId="539" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="Normal 2 66" xfId="540" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="Normal 2 67" xfId="541" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="Normal 2 68" xfId="542" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="Normal 2 69" xfId="543" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Normal 2 7" xfId="544" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Normal 2 70" xfId="545" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Normal 2 71" xfId="546" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Normal 2 72" xfId="547" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Normal 2 73" xfId="548" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Normal 2 74" xfId="549" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Normal 2 75" xfId="550" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Normal 2 76" xfId="551" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Normal 2 77" xfId="552" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Normal 2 78" xfId="553" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Normal 2 79" xfId="554" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Normal 2 8" xfId="555" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Normal 2 80" xfId="556" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Normal 2 81" xfId="557" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Normal 2 82" xfId="558" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Normal 2 83" xfId="559" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Normal 2 84" xfId="560" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Normal 2 85" xfId="561" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Normal 2 86" xfId="562" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Normal 2 87" xfId="563" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Normal 2 88" xfId="564" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Normal 2 89" xfId="565" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Normal 2 9" xfId="566" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Normal 2 90" xfId="567" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Normal 2 91" xfId="568" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Normal 2 92" xfId="569" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Normal 2 93" xfId="570" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Normal 2 94" xfId="571" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Normal 2 95" xfId="572" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Normal 2 96" xfId="573" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Normal 2 97" xfId="574" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Normal 2 98" xfId="575" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Normal 2 99" xfId="576" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Normal 20" xfId="577" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Normal 20 2" xfId="578" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Normal 20 3" xfId="579" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Normal 20 4" xfId="580" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Normal 21" xfId="581" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Normal 21 2" xfId="582" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Normal 21 3" xfId="583" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Normal 21 4" xfId="584" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Normal 22" xfId="585" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Normal 22 2" xfId="586" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Normal 22 3" xfId="587" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Normal 22 4" xfId="588" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Normal 23" xfId="589" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Normal 23 2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Normal 23 3" xfId="591" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Normal 24" xfId="592" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Normal 24 2" xfId="593" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Normal 24 3" xfId="594" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Normal 25" xfId="595" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Normal 26" xfId="596" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Normal 27" xfId="597" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Normal 28" xfId="598" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Normal 29" xfId="599" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Normal 3" xfId="600" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Normal 3 2" xfId="601" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="602" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Normal 3 3" xfId="603" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Normal 3 3 2" xfId="604" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Normal 3 3 3" xfId="605" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Normal 3 4" xfId="606" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Normal 3 5" xfId="607" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Normal 30" xfId="608" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Normal 31" xfId="609" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Normal 32" xfId="610" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Normal 33" xfId="611" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Normal 34" xfId="612" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Normal 35" xfId="613" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Normal 36" xfId="614" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Normal 37" xfId="615" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Normal 38" xfId="616" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Normal 39" xfId="617" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Normal 4" xfId="618" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Normal 4 2" xfId="619" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="620" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Normal 4 3" xfId="621" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="Normal 4 4" xfId="622" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="Normal 40" xfId="623" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Normal 41" xfId="624" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Normal 42" xfId="625" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Normal 43" xfId="626" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Normal 44" xfId="627" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Normal 45" xfId="628" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Normal 46" xfId="629" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Normal 47" xfId="630" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="Normal 48" xfId="631" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Normal 49" xfId="632" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Normal 5" xfId="633" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Normal 5 10" xfId="634" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Normal 5 11" xfId="635" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Normal 5 12" xfId="636" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Normal 5 13" xfId="637" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="Normal 5 14" xfId="638" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Normal 5 15" xfId="639" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Normal 5 16" xfId="640" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Normal 5 17" xfId="641" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="Normal 5 18" xfId="642" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Normal 5 19" xfId="643" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Normal 5 2" xfId="644" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Normal 5 20" xfId="645" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Normal 5 21" xfId="646" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Normal 5 22" xfId="647" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Normal 5 23" xfId="648" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="Normal 5 24" xfId="649" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Normal 5 25" xfId="650" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Normal 5 26" xfId="651" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="Normal 5 27" xfId="652" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="Normal 5 28" xfId="653" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="Normal 5 28 10" xfId="654" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="Normal 5 28 11" xfId="655" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="Normal 5 28 12" xfId="656" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="Normal 5 28 13" xfId="657" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="Normal 5 28 14" xfId="658" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="Normal 5 28 15" xfId="659" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="Normal 5 28 16" xfId="660" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="Normal 5 28 17" xfId="661" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="Normal 5 28 18" xfId="662" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="Normal 5 28 19" xfId="663" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="Normal 5 28 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="Normal 5 28 20" xfId="665" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="Normal 5 28 21" xfId="666" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="Normal 5 28 22" xfId="667" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="Normal 5 28 23" xfId="668" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="Normal 5 28 24" xfId="669" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="Normal 5 28 25" xfId="670" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="Normal 5 28 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="Normal 5 28 4" xfId="672" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="Normal 5 28 5" xfId="673" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="Normal 5 28 6" xfId="674" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="Normal 5 28 7" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="Normal 5 28 8" xfId="676" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="Normal 5 28 9" xfId="677" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="Normal 5 29" xfId="678" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="Normal 5 3" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="Normal 5 4" xfId="680" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="Normal 5 5" xfId="681" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="Normal 5 6" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="Normal 5 7" xfId="683" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="Normal 5 8" xfId="684" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="Normal 5 9" xfId="685" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="Normal 50" xfId="686" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="Normal 51" xfId="687" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="Normal 52" xfId="688" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="Normal 53" xfId="689" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="Normal 54" xfId="690" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="Normal 55" xfId="691" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="Normal 56" xfId="2" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="Normal 56 2" xfId="692" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="Normal 57" xfId="693" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="Normal 58" xfId="694" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="Normal 59" xfId="695" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="Normal 6" xfId="696" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="Normal 6 2" xfId="697" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="Normal 6 2 2" xfId="698" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="Normal 6 2 3" xfId="699" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="Normal 6 3" xfId="700" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="Normal 6 4" xfId="701" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="Normal 60" xfId="702" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="Normal 61" xfId="703" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="Normal 62" xfId="704" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="Normal 63" xfId="705" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="Normal 64" xfId="706" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="Normal 65" xfId="707" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="Normal 66" xfId="708" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="Normal 67" xfId="709" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="Normal 68" xfId="710" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="Normal 69" xfId="711" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="Normal 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="Normal 7 2" xfId="713" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="Normal 7 3" xfId="714" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="Normal 7 4" xfId="715" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="Normal 70" xfId="716" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="Normal 71" xfId="717" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="Normal 72" xfId="718" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="Normal 73" xfId="719" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="Normal 74" xfId="720" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="Normal 75" xfId="721" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
-    <cellStyle name="Normal 76" xfId="722" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
-    <cellStyle name="Normal 77" xfId="723" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="Normal 78" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="Normal 79" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="Normal 79 2" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="Normal 79 3" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="Normal 8" xfId="728" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="Normal 8 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="Normal 8 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="Normal 8 4" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="Normal 80" xfId="732" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="Normal 80 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="Normal 81" xfId="734" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="Normal 81 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="Normal 82" xfId="736" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="Normal 82 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="Normal 82 2 2" xfId="738" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="Normal 83" xfId="739" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="Normal 83 2" xfId="740" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="Normal 83 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="Normal 84" xfId="742" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="Normal 84 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="Normal 84 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="Normal 85" xfId="745" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="Normal 85 2" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="Normal 85 3" xfId="747" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="Normal 86" xfId="748" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="Normal 86 2" xfId="749" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="Normal 86 3" xfId="750" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="Normal 87" xfId="751" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="Normal 87 2" xfId="752" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="Normal 87 3" xfId="753" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="Normal 88" xfId="754" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="Normal 88 2" xfId="755" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="Normal 88 3" xfId="756" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="Normal 88 4" xfId="757" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="Normal 89" xfId="758" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="Normal 9" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="Normal 9 2" xfId="760" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="Normal 9 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="Normal 9 4" xfId="762" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="Normal 90" xfId="763" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="Normal 91" xfId="764" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="Normal 92" xfId="765" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="Normal 93" xfId="766" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="Normal 94" xfId="767" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="Normal 94 2" xfId="768" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="Normal 95" xfId="769" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="Normal 95 2" xfId="770" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="Normal 95 3" xfId="771" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="Normal 96" xfId="772" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="Normal 97" xfId="773" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="Normal 97 2" xfId="774" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="Normal 98" xfId="775" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="Normal 98 2" xfId="776" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="Normal 99" xfId="777" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="Normal 99 2" xfId="778" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="Normal_7 DIAS" xfId="3" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="Notas 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="Notas 2 2" xfId="780" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="Notas 2 3" xfId="781" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="Notas 3" xfId="782" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
-    <cellStyle name="Notas 4" xfId="783" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="784" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="Porcentaje 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="Salida 2" xfId="786" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="Salida 3" xfId="787" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="Salida 4" xfId="788" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="Texto de advertencia 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="Texto de advertencia 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="Texto de advertencia 4" xfId="791" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="Texto explicativo 2" xfId="792" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="Texto explicativo 3" xfId="793" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="Texto explicativo 4" xfId="794" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="Título 1 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="Título 2 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="Título 2 3" xfId="797" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="Título 2 4" xfId="798" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="Título 3 2" xfId="799" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="Título 3 3" xfId="800" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="Título 3 4" xfId="801" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="Título 4" xfId="802" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="Título 5" xfId="803" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="Título 6" xfId="804" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="Total 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="Total 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="Total 4" xfId="808" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="Total 5" xfId="805" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Normal 10" xfId="252"/>
+    <cellStyle name="Normal 10 2" xfId="253"/>
+    <cellStyle name="Normal 10 3" xfId="254"/>
+    <cellStyle name="Normal 10 4" xfId="255"/>
+    <cellStyle name="Normal 100" xfId="256"/>
+    <cellStyle name="Normal 100 2" xfId="257"/>
+    <cellStyle name="Normal 101" xfId="258"/>
+    <cellStyle name="Normal 101 2" xfId="259"/>
+    <cellStyle name="Normal 102" xfId="260"/>
+    <cellStyle name="Normal 102 2" xfId="261"/>
+    <cellStyle name="Normal 103" xfId="262"/>
+    <cellStyle name="Normal 103 2" xfId="263"/>
+    <cellStyle name="Normal 104" xfId="264"/>
+    <cellStyle name="Normal 104 2" xfId="265"/>
+    <cellStyle name="Normal 104 3" xfId="266"/>
+    <cellStyle name="Normal 105" xfId="267"/>
+    <cellStyle name="Normal 106" xfId="268"/>
+    <cellStyle name="Normal 106 2" xfId="269"/>
+    <cellStyle name="Normal 106 3" xfId="270"/>
+    <cellStyle name="Normal 107" xfId="271"/>
+    <cellStyle name="Normal 107 2" xfId="272"/>
+    <cellStyle name="Normal 108" xfId="273"/>
+    <cellStyle name="Normal 109" xfId="274"/>
+    <cellStyle name="Normal 11" xfId="275"/>
+    <cellStyle name="Normal 11 2" xfId="276"/>
+    <cellStyle name="Normal 11 3" xfId="277"/>
+    <cellStyle name="Normal 11 4" xfId="278"/>
+    <cellStyle name="Normal 110" xfId="279"/>
+    <cellStyle name="Normal 111" xfId="280"/>
+    <cellStyle name="Normal 112" xfId="281"/>
+    <cellStyle name="Normal 112 2" xfId="282"/>
+    <cellStyle name="Normal 113" xfId="283"/>
+    <cellStyle name="Normal 113 2" xfId="284"/>
+    <cellStyle name="Normal 114" xfId="285"/>
+    <cellStyle name="Normal 114 2" xfId="286"/>
+    <cellStyle name="Normal 115" xfId="287"/>
+    <cellStyle name="Normal 115 2" xfId="288"/>
+    <cellStyle name="Normal 116" xfId="289"/>
+    <cellStyle name="Normal 116 2" xfId="290"/>
+    <cellStyle name="Normal 116 3" xfId="291"/>
+    <cellStyle name="Normal 117" xfId="292"/>
+    <cellStyle name="Normal 117 2" xfId="293"/>
+    <cellStyle name="Normal 118" xfId="294"/>
+    <cellStyle name="Normal 118 2" xfId="295"/>
+    <cellStyle name="Normal 118 3" xfId="296"/>
+    <cellStyle name="Normal 119" xfId="297"/>
+    <cellStyle name="Normal 119 2" xfId="298"/>
+    <cellStyle name="Normal 119 3" xfId="299"/>
+    <cellStyle name="Normal 12" xfId="300"/>
+    <cellStyle name="Normal 12 2" xfId="301"/>
+    <cellStyle name="Normal 12 3" xfId="302"/>
+    <cellStyle name="Normal 12 4" xfId="303"/>
+    <cellStyle name="Normal 120" xfId="304"/>
+    <cellStyle name="Normal 120 2" xfId="305"/>
+    <cellStyle name="Normal 121" xfId="306"/>
+    <cellStyle name="Normal 121 2" xfId="307"/>
+    <cellStyle name="Normal 122" xfId="308"/>
+    <cellStyle name="Normal 122 2" xfId="309"/>
+    <cellStyle name="Normal 123" xfId="310"/>
+    <cellStyle name="Normal 124" xfId="311"/>
+    <cellStyle name="Normal 124 2" xfId="312"/>
+    <cellStyle name="Normal 125" xfId="313"/>
+    <cellStyle name="Normal 125 2" xfId="314"/>
+    <cellStyle name="Normal 126" xfId="315"/>
+    <cellStyle name="Normal 127" xfId="316"/>
+    <cellStyle name="Normal 127 2" xfId="317"/>
+    <cellStyle name="Normal 128" xfId="318"/>
+    <cellStyle name="Normal 129" xfId="319"/>
+    <cellStyle name="Normal 13" xfId="320"/>
+    <cellStyle name="Normal 13 2" xfId="321"/>
+    <cellStyle name="Normal 13 3" xfId="322"/>
+    <cellStyle name="Normal 13 4" xfId="323"/>
+    <cellStyle name="Normal 130" xfId="324"/>
+    <cellStyle name="Normal 130 2" xfId="325"/>
+    <cellStyle name="Normal 131" xfId="326"/>
+    <cellStyle name="Normal 131 2" xfId="327"/>
+    <cellStyle name="Normal 132" xfId="328"/>
+    <cellStyle name="Normal 132 2" xfId="329"/>
+    <cellStyle name="Normal 133" xfId="330"/>
+    <cellStyle name="Normal 133 2" xfId="331"/>
+    <cellStyle name="Normal 134" xfId="332"/>
+    <cellStyle name="Normal 135" xfId="333"/>
+    <cellStyle name="Normal 135 2" xfId="334"/>
+    <cellStyle name="Normal 136" xfId="335"/>
+    <cellStyle name="Normal 136 2" xfId="336"/>
+    <cellStyle name="Normal 137" xfId="337"/>
+    <cellStyle name="Normal 137 2" xfId="338"/>
+    <cellStyle name="Normal 138" xfId="339"/>
+    <cellStyle name="Normal 138 2" xfId="340"/>
+    <cellStyle name="Normal 139" xfId="341"/>
+    <cellStyle name="Normal 139 2" xfId="342"/>
+    <cellStyle name="Normal 14" xfId="343"/>
+    <cellStyle name="Normal 14 2" xfId="344"/>
+    <cellStyle name="Normal 14 3" xfId="345"/>
+    <cellStyle name="Normal 14 4" xfId="346"/>
+    <cellStyle name="Normal 140" xfId="347"/>
+    <cellStyle name="Normal 140 2" xfId="348"/>
+    <cellStyle name="Normal 141" xfId="349"/>
+    <cellStyle name="Normal 142" xfId="350"/>
+    <cellStyle name="Normal 142 2" xfId="351"/>
+    <cellStyle name="Normal 143" xfId="352"/>
+    <cellStyle name="Normal 143 2" xfId="353"/>
+    <cellStyle name="Normal 143 3" xfId="354"/>
+    <cellStyle name="Normal 144" xfId="355"/>
+    <cellStyle name="Normal 144 2" xfId="356"/>
+    <cellStyle name="Normal 145" xfId="357"/>
+    <cellStyle name="Normal 145 2" xfId="358"/>
+    <cellStyle name="Normal 146" xfId="359"/>
+    <cellStyle name="Normal 147" xfId="360"/>
+    <cellStyle name="Normal 15" xfId="361"/>
+    <cellStyle name="Normal 15 2" xfId="362"/>
+    <cellStyle name="Normal 15 3" xfId="363"/>
+    <cellStyle name="Normal 15 4" xfId="364"/>
+    <cellStyle name="Normal 16" xfId="365"/>
+    <cellStyle name="Normal 16 2" xfId="366"/>
+    <cellStyle name="Normal 16 3" xfId="367"/>
+    <cellStyle name="Normal 16 4" xfId="368"/>
+    <cellStyle name="Normal 17" xfId="369"/>
+    <cellStyle name="Normal 17 2" xfId="370"/>
+    <cellStyle name="Normal 17 3" xfId="371"/>
+    <cellStyle name="Normal 17 4" xfId="372"/>
+    <cellStyle name="Normal 18" xfId="373"/>
+    <cellStyle name="Normal 18 2" xfId="374"/>
+    <cellStyle name="Normal 18 3" xfId="375"/>
+    <cellStyle name="Normal 18 4" xfId="376"/>
+    <cellStyle name="Normal 19" xfId="377"/>
+    <cellStyle name="Normal 19 2" xfId="378"/>
+    <cellStyle name="Normal 19 3" xfId="379"/>
+    <cellStyle name="Normal 19 4" xfId="380"/>
+    <cellStyle name="Normal 2" xfId="381"/>
+    <cellStyle name="Normal 2 10" xfId="382"/>
+    <cellStyle name="Normal 2 100" xfId="383"/>
+    <cellStyle name="Normal 2 101" xfId="384"/>
+    <cellStyle name="Normal 2 102" xfId="385"/>
+    <cellStyle name="Normal 2 103" xfId="386"/>
+    <cellStyle name="Normal 2 103 2" xfId="387"/>
+    <cellStyle name="Normal 2 103 2 2" xfId="388"/>
+    <cellStyle name="Normal 2 104" xfId="389"/>
+    <cellStyle name="Normal 2 104 2" xfId="390"/>
+    <cellStyle name="Normal 2 105" xfId="391"/>
+    <cellStyle name="Normal 2 105 2" xfId="392"/>
+    <cellStyle name="Normal 2 106" xfId="393"/>
+    <cellStyle name="Normal 2 106 2" xfId="394"/>
+    <cellStyle name="Normal 2 106 3" xfId="395"/>
+    <cellStyle name="Normal 2 107" xfId="396"/>
+    <cellStyle name="Normal 2 107 2" xfId="397"/>
+    <cellStyle name="Normal 2 108" xfId="398"/>
+    <cellStyle name="Normal 2 108 2" xfId="399"/>
+    <cellStyle name="Normal 2 109" xfId="400"/>
+    <cellStyle name="Normal 2 109 2" xfId="401"/>
+    <cellStyle name="Normal 2 11" xfId="402"/>
+    <cellStyle name="Normal 2 110" xfId="403"/>
+    <cellStyle name="Normal 2 111" xfId="404"/>
+    <cellStyle name="Normal 2 112" xfId="405"/>
+    <cellStyle name="Normal 2 113" xfId="406"/>
+    <cellStyle name="Normal 2 114" xfId="407"/>
+    <cellStyle name="Normal 2 115" xfId="408"/>
+    <cellStyle name="Normal 2 12" xfId="409"/>
+    <cellStyle name="Normal 2 13" xfId="410"/>
+    <cellStyle name="Normal 2 14" xfId="411"/>
+    <cellStyle name="Normal 2 15" xfId="412"/>
+    <cellStyle name="Normal 2 16" xfId="413"/>
+    <cellStyle name="Normal 2 17" xfId="414"/>
+    <cellStyle name="Normal 2 18" xfId="415"/>
+    <cellStyle name="Normal 2 19" xfId="416"/>
+    <cellStyle name="Normal 2 2" xfId="417"/>
+    <cellStyle name="Normal 2 2 2" xfId="418"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="419"/>
+    <cellStyle name="Normal 2 2 3" xfId="420"/>
+    <cellStyle name="Normal 2 2 4" xfId="421"/>
+    <cellStyle name="Normal 2 20" xfId="422"/>
+    <cellStyle name="Normal 2 21" xfId="423"/>
+    <cellStyle name="Normal 2 22" xfId="424"/>
+    <cellStyle name="Normal 2 23" xfId="425"/>
+    <cellStyle name="Normal 2 24" xfId="426"/>
+    <cellStyle name="Normal 2 25" xfId="427"/>
+    <cellStyle name="Normal 2 26" xfId="428"/>
+    <cellStyle name="Normal 2 27" xfId="429"/>
+    <cellStyle name="Normal 2 28" xfId="430"/>
+    <cellStyle name="Normal 2 29" xfId="431"/>
+    <cellStyle name="Normal 2 3" xfId="432"/>
+    <cellStyle name="Normal 2 3 2" xfId="433"/>
+    <cellStyle name="Normal 2 3 3" xfId="434"/>
+    <cellStyle name="Normal 2 30" xfId="435"/>
+    <cellStyle name="Normal 2 31" xfId="436"/>
+    <cellStyle name="Normal 2 32" xfId="437"/>
+    <cellStyle name="Normal 2 33" xfId="438"/>
+    <cellStyle name="Normal 2 34" xfId="439"/>
+    <cellStyle name="Normal 2 35" xfId="440"/>
+    <cellStyle name="Normal 2 36" xfId="441"/>
+    <cellStyle name="Normal 2 37" xfId="442"/>
+    <cellStyle name="Normal 2 38" xfId="443"/>
+    <cellStyle name="Normal 2 39" xfId="444"/>
+    <cellStyle name="Normal 2 4" xfId="445"/>
+    <cellStyle name="Normal 2 4 2" xfId="446"/>
+    <cellStyle name="Normal 2 4 3" xfId="447"/>
+    <cellStyle name="Normal 2 4 4" xfId="448"/>
+    <cellStyle name="Normal 2 40" xfId="449"/>
+    <cellStyle name="Normal 2 41" xfId="450"/>
+    <cellStyle name="Normal 2 42" xfId="451"/>
+    <cellStyle name="Normal 2 43" xfId="452"/>
+    <cellStyle name="Normal 2 44" xfId="453"/>
+    <cellStyle name="Normal 2 45" xfId="454"/>
+    <cellStyle name="Normal 2 45 10" xfId="455"/>
+    <cellStyle name="Normal 2 45 11" xfId="456"/>
+    <cellStyle name="Normal 2 45 12" xfId="457"/>
+    <cellStyle name="Normal 2 45 13" xfId="458"/>
+    <cellStyle name="Normal 2 45 14" xfId="459"/>
+    <cellStyle name="Normal 2 45 15" xfId="460"/>
+    <cellStyle name="Normal 2 45 16" xfId="461"/>
+    <cellStyle name="Normal 2 45 17" xfId="462"/>
+    <cellStyle name="Normal 2 45 18" xfId="463"/>
+    <cellStyle name="Normal 2 45 19" xfId="464"/>
+    <cellStyle name="Normal 2 45 2" xfId="465"/>
+    <cellStyle name="Normal 2 45 20" xfId="466"/>
+    <cellStyle name="Normal 2 45 21" xfId="467"/>
+    <cellStyle name="Normal 2 45 22" xfId="468"/>
+    <cellStyle name="Normal 2 45 23" xfId="469"/>
+    <cellStyle name="Normal 2 45 24" xfId="470"/>
+    <cellStyle name="Normal 2 45 25" xfId="471"/>
+    <cellStyle name="Normal 2 45 26" xfId="472"/>
+    <cellStyle name="Normal 2 45 27" xfId="473"/>
+    <cellStyle name="Normal 2 45 28" xfId="474"/>
+    <cellStyle name="Normal 2 45 29" xfId="475"/>
+    <cellStyle name="Normal 2 45 3" xfId="476"/>
+    <cellStyle name="Normal 2 45 30" xfId="477"/>
+    <cellStyle name="Normal 2 45 31" xfId="478"/>
+    <cellStyle name="Normal 2 45 32" xfId="479"/>
+    <cellStyle name="Normal 2 45 33" xfId="480"/>
+    <cellStyle name="Normal 2 45 34" xfId="481"/>
+    <cellStyle name="Normal 2 45 35" xfId="482"/>
+    <cellStyle name="Normal 2 45 36" xfId="483"/>
+    <cellStyle name="Normal 2 45 37" xfId="484"/>
+    <cellStyle name="Normal 2 45 38" xfId="485"/>
+    <cellStyle name="Normal 2 45 39" xfId="486"/>
+    <cellStyle name="Normal 2 45 4" xfId="487"/>
+    <cellStyle name="Normal 2 45 40" xfId="488"/>
+    <cellStyle name="Normal 2 45 41" xfId="489"/>
+    <cellStyle name="Normal 2 45 42" xfId="490"/>
+    <cellStyle name="Normal 2 45 43" xfId="491"/>
+    <cellStyle name="Normal 2 45 44" xfId="492"/>
+    <cellStyle name="Normal 2 45 45" xfId="493"/>
+    <cellStyle name="Normal 2 45 46" xfId="494"/>
+    <cellStyle name="Normal 2 45 47" xfId="495"/>
+    <cellStyle name="Normal 2 45 48" xfId="496"/>
+    <cellStyle name="Normal 2 45 49" xfId="497"/>
+    <cellStyle name="Normal 2 45 5" xfId="498"/>
+    <cellStyle name="Normal 2 45 50" xfId="499"/>
+    <cellStyle name="Normal 2 45 51" xfId="500"/>
+    <cellStyle name="Normal 2 45 52" xfId="501"/>
+    <cellStyle name="Normal 2 45 53" xfId="502"/>
+    <cellStyle name="Normal 2 45 54" xfId="503"/>
+    <cellStyle name="Normal 2 45 55" xfId="504"/>
+    <cellStyle name="Normal 2 45 56" xfId="505"/>
+    <cellStyle name="Normal 2 45 57" xfId="506"/>
+    <cellStyle name="Normal 2 45 58" xfId="507"/>
+    <cellStyle name="Normal 2 45 59" xfId="508"/>
+    <cellStyle name="Normal 2 45 6" xfId="509"/>
+    <cellStyle name="Normal 2 45 7" xfId="510"/>
+    <cellStyle name="Normal 2 45 8" xfId="511"/>
+    <cellStyle name="Normal 2 45 9" xfId="512"/>
+    <cellStyle name="Normal 2 46" xfId="513"/>
+    <cellStyle name="Normal 2 47" xfId="514"/>
+    <cellStyle name="Normal 2 48" xfId="515"/>
+    <cellStyle name="Normal 2 49" xfId="516"/>
+    <cellStyle name="Normal 2 5" xfId="517"/>
+    <cellStyle name="Normal 2 5 2" xfId="518"/>
+    <cellStyle name="Normal 2 5 3" xfId="519"/>
+    <cellStyle name="Normal 2 5 3 2" xfId="520"/>
+    <cellStyle name="Normal 2 5 4" xfId="521"/>
+    <cellStyle name="Normal 2 50" xfId="522"/>
+    <cellStyle name="Normal 2 51" xfId="523"/>
+    <cellStyle name="Normal 2 52" xfId="524"/>
+    <cellStyle name="Normal 2 53" xfId="525"/>
+    <cellStyle name="Normal 2 54" xfId="526"/>
+    <cellStyle name="Normal 2 55" xfId="527"/>
+    <cellStyle name="Normal 2 56" xfId="528"/>
+    <cellStyle name="Normal 2 57" xfId="529"/>
+    <cellStyle name="Normal 2 58" xfId="530"/>
+    <cellStyle name="Normal 2 59" xfId="531"/>
+    <cellStyle name="Normal 2 6" xfId="532"/>
+    <cellStyle name="Normal 2 6 2" xfId="533"/>
+    <cellStyle name="Normal 2 60" xfId="534"/>
+    <cellStyle name="Normal 2 61" xfId="535"/>
+    <cellStyle name="Normal 2 62" xfId="536"/>
+    <cellStyle name="Normal 2 63" xfId="537"/>
+    <cellStyle name="Normal 2 64" xfId="538"/>
+    <cellStyle name="Normal 2 65" xfId="539"/>
+    <cellStyle name="Normal 2 66" xfId="540"/>
+    <cellStyle name="Normal 2 67" xfId="541"/>
+    <cellStyle name="Normal 2 68" xfId="542"/>
+    <cellStyle name="Normal 2 69" xfId="543"/>
+    <cellStyle name="Normal 2 7" xfId="544"/>
+    <cellStyle name="Normal 2 70" xfId="545"/>
+    <cellStyle name="Normal 2 71" xfId="546"/>
+    <cellStyle name="Normal 2 72" xfId="547"/>
+    <cellStyle name="Normal 2 73" xfId="548"/>
+    <cellStyle name="Normal 2 74" xfId="549"/>
+    <cellStyle name="Normal 2 75" xfId="550"/>
+    <cellStyle name="Normal 2 76" xfId="551"/>
+    <cellStyle name="Normal 2 77" xfId="552"/>
+    <cellStyle name="Normal 2 78" xfId="553"/>
+    <cellStyle name="Normal 2 79" xfId="554"/>
+    <cellStyle name="Normal 2 8" xfId="555"/>
+    <cellStyle name="Normal 2 80" xfId="556"/>
+    <cellStyle name="Normal 2 81" xfId="557"/>
+    <cellStyle name="Normal 2 82" xfId="558"/>
+    <cellStyle name="Normal 2 83" xfId="559"/>
+    <cellStyle name="Normal 2 84" xfId="560"/>
+    <cellStyle name="Normal 2 85" xfId="561"/>
+    <cellStyle name="Normal 2 86" xfId="562"/>
+    <cellStyle name="Normal 2 87" xfId="563"/>
+    <cellStyle name="Normal 2 88" xfId="564"/>
+    <cellStyle name="Normal 2 89" xfId="565"/>
+    <cellStyle name="Normal 2 9" xfId="566"/>
+    <cellStyle name="Normal 2 90" xfId="567"/>
+    <cellStyle name="Normal 2 91" xfId="568"/>
+    <cellStyle name="Normal 2 92" xfId="569"/>
+    <cellStyle name="Normal 2 93" xfId="570"/>
+    <cellStyle name="Normal 2 94" xfId="571"/>
+    <cellStyle name="Normal 2 95" xfId="572"/>
+    <cellStyle name="Normal 2 96" xfId="573"/>
+    <cellStyle name="Normal 2 97" xfId="574"/>
+    <cellStyle name="Normal 2 98" xfId="575"/>
+    <cellStyle name="Normal 2 99" xfId="576"/>
+    <cellStyle name="Normal 20" xfId="577"/>
+    <cellStyle name="Normal 20 2" xfId="578"/>
+    <cellStyle name="Normal 20 3" xfId="579"/>
+    <cellStyle name="Normal 20 4" xfId="580"/>
+    <cellStyle name="Normal 21" xfId="581"/>
+    <cellStyle name="Normal 21 2" xfId="582"/>
+    <cellStyle name="Normal 21 3" xfId="583"/>
+    <cellStyle name="Normal 21 4" xfId="584"/>
+    <cellStyle name="Normal 22" xfId="585"/>
+    <cellStyle name="Normal 22 2" xfId="586"/>
+    <cellStyle name="Normal 22 3" xfId="587"/>
+    <cellStyle name="Normal 22 4" xfId="588"/>
+    <cellStyle name="Normal 23" xfId="589"/>
+    <cellStyle name="Normal 23 2" xfId="590"/>
+    <cellStyle name="Normal 23 3" xfId="591"/>
+    <cellStyle name="Normal 24" xfId="592"/>
+    <cellStyle name="Normal 24 2" xfId="593"/>
+    <cellStyle name="Normal 24 3" xfId="594"/>
+    <cellStyle name="Normal 25" xfId="595"/>
+    <cellStyle name="Normal 26" xfId="596"/>
+    <cellStyle name="Normal 27" xfId="597"/>
+    <cellStyle name="Normal 28" xfId="598"/>
+    <cellStyle name="Normal 29" xfId="599"/>
+    <cellStyle name="Normal 3" xfId="600"/>
+    <cellStyle name="Normal 3 2" xfId="601"/>
+    <cellStyle name="Normal 3 2 2" xfId="602"/>
+    <cellStyle name="Normal 3 3" xfId="603"/>
+    <cellStyle name="Normal 3 3 2" xfId="604"/>
+    <cellStyle name="Normal 3 3 3" xfId="605"/>
+    <cellStyle name="Normal 3 4" xfId="606"/>
+    <cellStyle name="Normal 3 5" xfId="607"/>
+    <cellStyle name="Normal 30" xfId="608"/>
+    <cellStyle name="Normal 31" xfId="609"/>
+    <cellStyle name="Normal 32" xfId="610"/>
+    <cellStyle name="Normal 33" xfId="611"/>
+    <cellStyle name="Normal 34" xfId="612"/>
+    <cellStyle name="Normal 35" xfId="613"/>
+    <cellStyle name="Normal 36" xfId="614"/>
+    <cellStyle name="Normal 37" xfId="615"/>
+    <cellStyle name="Normal 38" xfId="616"/>
+    <cellStyle name="Normal 39" xfId="617"/>
+    <cellStyle name="Normal 4" xfId="618"/>
+    <cellStyle name="Normal 4 2" xfId="619"/>
+    <cellStyle name="Normal 4 2 2" xfId="620"/>
+    <cellStyle name="Normal 4 3" xfId="621"/>
+    <cellStyle name="Normal 4 4" xfId="622"/>
+    <cellStyle name="Normal 40" xfId="623"/>
+    <cellStyle name="Normal 41" xfId="624"/>
+    <cellStyle name="Normal 42" xfId="625"/>
+    <cellStyle name="Normal 43" xfId="626"/>
+    <cellStyle name="Normal 44" xfId="627"/>
+    <cellStyle name="Normal 45" xfId="628"/>
+    <cellStyle name="Normal 46" xfId="629"/>
+    <cellStyle name="Normal 47" xfId="630"/>
+    <cellStyle name="Normal 48" xfId="631"/>
+    <cellStyle name="Normal 49" xfId="632"/>
+    <cellStyle name="Normal 5" xfId="633"/>
+    <cellStyle name="Normal 5 10" xfId="634"/>
+    <cellStyle name="Normal 5 11" xfId="635"/>
+    <cellStyle name="Normal 5 12" xfId="636"/>
+    <cellStyle name="Normal 5 13" xfId="637"/>
+    <cellStyle name="Normal 5 14" xfId="638"/>
+    <cellStyle name="Normal 5 15" xfId="639"/>
+    <cellStyle name="Normal 5 16" xfId="640"/>
+    <cellStyle name="Normal 5 17" xfId="641"/>
+    <cellStyle name="Normal 5 18" xfId="642"/>
+    <cellStyle name="Normal 5 19" xfId="643"/>
+    <cellStyle name="Normal 5 2" xfId="644"/>
+    <cellStyle name="Normal 5 20" xfId="645"/>
+    <cellStyle name="Normal 5 21" xfId="646"/>
+    <cellStyle name="Normal 5 22" xfId="647"/>
+    <cellStyle name="Normal 5 23" xfId="648"/>
+    <cellStyle name="Normal 5 24" xfId="649"/>
+    <cellStyle name="Normal 5 25" xfId="650"/>
+    <cellStyle name="Normal 5 26" xfId="651"/>
+    <cellStyle name="Normal 5 27" xfId="652"/>
+    <cellStyle name="Normal 5 28" xfId="653"/>
+    <cellStyle name="Normal 5 28 10" xfId="654"/>
+    <cellStyle name="Normal 5 28 11" xfId="655"/>
+    <cellStyle name="Normal 5 28 12" xfId="656"/>
+    <cellStyle name="Normal 5 28 13" xfId="657"/>
+    <cellStyle name="Normal 5 28 14" xfId="658"/>
+    <cellStyle name="Normal 5 28 15" xfId="659"/>
+    <cellStyle name="Normal 5 28 16" xfId="660"/>
+    <cellStyle name="Normal 5 28 17" xfId="661"/>
+    <cellStyle name="Normal 5 28 18" xfId="662"/>
+    <cellStyle name="Normal 5 28 19" xfId="663"/>
+    <cellStyle name="Normal 5 28 2" xfId="664"/>
+    <cellStyle name="Normal 5 28 20" xfId="665"/>
+    <cellStyle name="Normal 5 28 21" xfId="666"/>
+    <cellStyle name="Normal 5 28 22" xfId="667"/>
+    <cellStyle name="Normal 5 28 23" xfId="668"/>
+    <cellStyle name="Normal 5 28 24" xfId="669"/>
+    <cellStyle name="Normal 5 28 25" xfId="670"/>
+    <cellStyle name="Normal 5 28 3" xfId="671"/>
+    <cellStyle name="Normal 5 28 4" xfId="672"/>
+    <cellStyle name="Normal 5 28 5" xfId="673"/>
+    <cellStyle name="Normal 5 28 6" xfId="674"/>
+    <cellStyle name="Normal 5 28 7" xfId="675"/>
+    <cellStyle name="Normal 5 28 8" xfId="676"/>
+    <cellStyle name="Normal 5 28 9" xfId="677"/>
+    <cellStyle name="Normal 5 29" xfId="678"/>
+    <cellStyle name="Normal 5 3" xfId="679"/>
+    <cellStyle name="Normal 5 4" xfId="680"/>
+    <cellStyle name="Normal 5 5" xfId="681"/>
+    <cellStyle name="Normal 5 6" xfId="682"/>
+    <cellStyle name="Normal 5 7" xfId="683"/>
+    <cellStyle name="Normal 5 8" xfId="684"/>
+    <cellStyle name="Normal 5 9" xfId="685"/>
+    <cellStyle name="Normal 50" xfId="686"/>
+    <cellStyle name="Normal 51" xfId="687"/>
+    <cellStyle name="Normal 52" xfId="688"/>
+    <cellStyle name="Normal 53" xfId="689"/>
+    <cellStyle name="Normal 54" xfId="690"/>
+    <cellStyle name="Normal 55" xfId="691"/>
+    <cellStyle name="Normal 56" xfId="2"/>
+    <cellStyle name="Normal 56 2" xfId="692"/>
+    <cellStyle name="Normal 57" xfId="693"/>
+    <cellStyle name="Normal 58" xfId="694"/>
+    <cellStyle name="Normal 59" xfId="695"/>
+    <cellStyle name="Normal 6" xfId="696"/>
+    <cellStyle name="Normal 6 2" xfId="697"/>
+    <cellStyle name="Normal 6 2 2" xfId="698"/>
+    <cellStyle name="Normal 6 2 3" xfId="699"/>
+    <cellStyle name="Normal 6 3" xfId="700"/>
+    <cellStyle name="Normal 6 4" xfId="701"/>
+    <cellStyle name="Normal 60" xfId="702"/>
+    <cellStyle name="Normal 61" xfId="703"/>
+    <cellStyle name="Normal 62" xfId="704"/>
+    <cellStyle name="Normal 63" xfId="705"/>
+    <cellStyle name="Normal 64" xfId="706"/>
+    <cellStyle name="Normal 65" xfId="707"/>
+    <cellStyle name="Normal 66" xfId="708"/>
+    <cellStyle name="Normal 67" xfId="709"/>
+    <cellStyle name="Normal 68" xfId="710"/>
+    <cellStyle name="Normal 69" xfId="711"/>
+    <cellStyle name="Normal 7" xfId="712"/>
+    <cellStyle name="Normal 7 2" xfId="713"/>
+    <cellStyle name="Normal 7 3" xfId="714"/>
+    <cellStyle name="Normal 7 4" xfId="715"/>
+    <cellStyle name="Normal 70" xfId="716"/>
+    <cellStyle name="Normal 71" xfId="717"/>
+    <cellStyle name="Normal 72" xfId="718"/>
+    <cellStyle name="Normal 73" xfId="719"/>
+    <cellStyle name="Normal 74" xfId="720"/>
+    <cellStyle name="Normal 75" xfId="721"/>
+    <cellStyle name="Normal 76" xfId="722"/>
+    <cellStyle name="Normal 77" xfId="723"/>
+    <cellStyle name="Normal 78" xfId="724"/>
+    <cellStyle name="Normal 79" xfId="725"/>
+    <cellStyle name="Normal 79 2" xfId="726"/>
+    <cellStyle name="Normal 79 3" xfId="727"/>
+    <cellStyle name="Normal 8" xfId="728"/>
+    <cellStyle name="Normal 8 2" xfId="729"/>
+    <cellStyle name="Normal 8 3" xfId="730"/>
+    <cellStyle name="Normal 8 4" xfId="731"/>
+    <cellStyle name="Normal 80" xfId="732"/>
+    <cellStyle name="Normal 80 2" xfId="733"/>
+    <cellStyle name="Normal 81" xfId="734"/>
+    <cellStyle name="Normal 81 2" xfId="735"/>
+    <cellStyle name="Normal 82" xfId="736"/>
+    <cellStyle name="Normal 82 2" xfId="737"/>
+    <cellStyle name="Normal 82 2 2" xfId="738"/>
+    <cellStyle name="Normal 83" xfId="739"/>
+    <cellStyle name="Normal 83 2" xfId="740"/>
+    <cellStyle name="Normal 83 2 2" xfId="741"/>
+    <cellStyle name="Normal 84" xfId="742"/>
+    <cellStyle name="Normal 84 2" xfId="743"/>
+    <cellStyle name="Normal 84 3" xfId="744"/>
+    <cellStyle name="Normal 85" xfId="745"/>
+    <cellStyle name="Normal 85 2" xfId="746"/>
+    <cellStyle name="Normal 85 3" xfId="747"/>
+    <cellStyle name="Normal 86" xfId="748"/>
+    <cellStyle name="Normal 86 2" xfId="749"/>
+    <cellStyle name="Normal 86 3" xfId="750"/>
+    <cellStyle name="Normal 87" xfId="751"/>
+    <cellStyle name="Normal 87 2" xfId="752"/>
+    <cellStyle name="Normal 87 3" xfId="753"/>
+    <cellStyle name="Normal 88" xfId="754"/>
+    <cellStyle name="Normal 88 2" xfId="755"/>
+    <cellStyle name="Normal 88 3" xfId="756"/>
+    <cellStyle name="Normal 88 4" xfId="757"/>
+    <cellStyle name="Normal 89" xfId="758"/>
+    <cellStyle name="Normal 9" xfId="759"/>
+    <cellStyle name="Normal 9 2" xfId="760"/>
+    <cellStyle name="Normal 9 3" xfId="761"/>
+    <cellStyle name="Normal 9 4" xfId="762"/>
+    <cellStyle name="Normal 90" xfId="763"/>
+    <cellStyle name="Normal 91" xfId="764"/>
+    <cellStyle name="Normal 92" xfId="765"/>
+    <cellStyle name="Normal 93" xfId="766"/>
+    <cellStyle name="Normal 94" xfId="767"/>
+    <cellStyle name="Normal 94 2" xfId="768"/>
+    <cellStyle name="Normal 95" xfId="769"/>
+    <cellStyle name="Normal 95 2" xfId="770"/>
+    <cellStyle name="Normal 95 3" xfId="771"/>
+    <cellStyle name="Normal 96" xfId="772"/>
+    <cellStyle name="Normal 97" xfId="773"/>
+    <cellStyle name="Normal 97 2" xfId="774"/>
+    <cellStyle name="Normal 98" xfId="775"/>
+    <cellStyle name="Normal 98 2" xfId="776"/>
+    <cellStyle name="Normal 99" xfId="777"/>
+    <cellStyle name="Normal 99 2" xfId="778"/>
+    <cellStyle name="Normal_7 DIAS" xfId="3"/>
+    <cellStyle name="Notas 2" xfId="779"/>
+    <cellStyle name="Notas 2 2" xfId="780"/>
+    <cellStyle name="Notas 2 3" xfId="781"/>
+    <cellStyle name="Notas 3" xfId="782"/>
+    <cellStyle name="Notas 4" xfId="783"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje 2" xfId="784"/>
+    <cellStyle name="Porcentaje 2 2" xfId="785"/>
+    <cellStyle name="Salida 2" xfId="786"/>
+    <cellStyle name="Salida 3" xfId="787"/>
+    <cellStyle name="Salida 4" xfId="788"/>
+    <cellStyle name="Texto de advertencia 2" xfId="789"/>
+    <cellStyle name="Texto de advertencia 3" xfId="790"/>
+    <cellStyle name="Texto de advertencia 4" xfId="791"/>
+    <cellStyle name="Texto explicativo 2" xfId="792"/>
+    <cellStyle name="Texto explicativo 3" xfId="793"/>
+    <cellStyle name="Texto explicativo 4" xfId="794"/>
+    <cellStyle name="Título 1 2" xfId="795"/>
+    <cellStyle name="Título 2 2" xfId="796"/>
+    <cellStyle name="Título 2 3" xfId="797"/>
+    <cellStyle name="Título 2 4" xfId="798"/>
+    <cellStyle name="Título 3 2" xfId="799"/>
+    <cellStyle name="Título 3 3" xfId="800"/>
+    <cellStyle name="Título 3 4" xfId="801"/>
+    <cellStyle name="Título 4" xfId="802"/>
+    <cellStyle name="Título 5" xfId="803"/>
+    <cellStyle name="Título 6" xfId="804"/>
+    <cellStyle name="Total 2" xfId="806"/>
+    <cellStyle name="Total 3" xfId="807"/>
+    <cellStyle name="Total 4" xfId="808"/>
+    <cellStyle name="Total 5" xfId="805"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2859,25 +2855,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2894,7 +2890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="11">
         <v>46101</v>
       </c>
@@ -2911,7 +2907,7 @@
         <v>4.8399999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="11">
         <v>46104</v>
       </c>
@@ -2928,7 +2924,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="11">
         <v>46105</v>
       </c>
@@ -2945,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="11">
         <v>46106</v>
       </c>
@@ -2962,7 +2958,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="11">
         <v>46107</v>
       </c>
@@ -2979,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="11">
         <v>46108</v>
       </c>
@@ -2996,7 +2992,7 @@
         <v>5.8799999999999998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="11">
         <v>46111</v>
       </c>
@@ -3013,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="11">
         <v>46112</v>
       </c>
@@ -3030,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="11">
         <v>46113</v>
       </c>
@@ -3047,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="11">
         <v>46118</v>
       </c>
@@ -3064,7 +3060,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="11">
         <v>46119</v>
       </c>
@@ -3081,7 +3077,7 @@
         <v>1.0046999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="11">
         <v>46120</v>
       </c>
@@ -3098,7 +3094,7 @@
         <v>1.0604</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="11">
         <v>46121</v>
       </c>
@@ -3115,7 +3111,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="11">
         <v>46122</v>
       </c>
@@ -3132,7 +3128,7 @@
         <v>0.35270000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="11">
         <v>46125</v>
       </c>
@@ -3149,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="11">
         <v>46126</v>
       </c>
@@ -3166,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="11">
         <v>46127</v>
       </c>
@@ -3183,7 +3179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="11">
         <v>46128</v>
       </c>
@@ -3200,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="11">
         <v>46129</v>
       </c>
@@ -3217,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="11">
         <v>46132</v>
       </c>
@@ -3234,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="11">
         <v>46133</v>
       </c>
@@ -3251,7 +3247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="11">
         <v>46134</v>
       </c>
@@ -3268,7 +3264,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="11">
         <v>46135</v>
       </c>
@@ -3285,7 +3281,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="11">
         <v>46136</v>
       </c>
@@ -3302,7 +3298,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="11">
         <v>46139</v>
       </c>
@@ -3319,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" s="11">
         <v>46140</v>
       </c>
@@ -3336,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="11">
         <v>46141</v>
       </c>
@@ -3353,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" s="11">
         <v>46142</v>
       </c>
@@ -3373,7 +3369,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" s="11">
         <v>46146</v>
       </c>
@@ -3393,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="A31" s="11">
         <v>46147</v>
       </c>
@@ -3413,7 +3409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="11">
         <v>46148</v>
       </c>
@@ -3433,7 +3429,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="24">
         <v>46149</v>
       </c>
@@ -3453,17 +3449,27 @@
         <v>243.9</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
+      <c r="A34" s="24">
+        <v>46150</v>
+      </c>
+      <c r="B34" s="20">
+        <v>8103.3360000000002</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="20">
+        <v>100</v>
+      </c>
+      <c r="E34" s="23"/>
+      <c r="F34" s="20">
+        <v>100</v>
+      </c>
+      <c r="G34" s="23"/>
+      <c r="H34" s="20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="13"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -3473,7 +3479,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8">
       <c r="A36" s="11"/>
       <c r="B36" s="1"/>
       <c r="C36" s="10"/>
@@ -3490,18 +3496,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
     <col min="3" max="3" width="14" style="15" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3518,15 +3524,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
-        <v>46149</v>
-      </c>
-      <c r="B2" s="25">
-        <v>131.99794839</v>
+    <row r="2" spans="1:5">
+      <c r="A2" s="28">
+        <v>46150</v>
+      </c>
+      <c r="B2" s="27">
+        <v>23652.710333340001</v>
       </c>
       <c r="C2" s="18">
-        <f>+((B2-B3)/B3)*100</f>
+        <f>+((B3-B4)/B4)*100</f>
         <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
@@ -3536,15 +3542,15 @@
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="21">
-        <v>46148</v>
-      </c>
-      <c r="B3" s="19">
-        <v>745.52443231999996</v>
+    <row r="3" spans="1:5">
+      <c r="A3" s="26">
+        <v>46149</v>
+      </c>
+      <c r="B3" s="25">
+        <v>131.99794839</v>
       </c>
       <c r="C3" s="18">
-        <f>+((B3-B4)/B4)*100</f>
+        <f>+((B4-B5)/B5)*100</f>
         <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
@@ -3554,15 +3560,15 @@
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="21">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B4" s="19">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C4" s="18">
-        <f t="shared" ref="C4:C27" si="0">+((B4-B5)/B5)*100</f>
+        <f t="shared" ref="C4:C26" si="0">+((B5-B6)/B6)*100</f>
         <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
@@ -3572,12 +3578,12 @@
         <v>85928.931135131905</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="21">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B5" s="19">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C5" s="18">
         <f t="shared" si="0"/>
@@ -3590,267 +3596,275 @@
         <v>22227.4775024345</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
-        <v>46142</v>
+    <row r="6" spans="1:5">
+      <c r="A6" s="21">
+        <v>46146</v>
       </c>
       <c r="B6" s="19">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C6" s="18">
         <f t="shared" si="0"/>
         <v>207.73664296544806</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="22">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B7" s="19">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C7" s="18">
         <f t="shared" si="0"/>
         <v>-59.636256133262869</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="22">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B8" s="19">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C8" s="18">
         <f t="shared" si="0"/>
         <v>74.333012643706198</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="22">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B9" s="19">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C9" s="18">
         <f t="shared" si="0"/>
         <v>-33.842006324553125</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="22">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B10" s="19">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C10" s="18">
         <f t="shared" si="0"/>
         <v>1210.6463903543759</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="22">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B11" s="19">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C11" s="18">
         <f t="shared" si="0"/>
         <v>-73.032401489373797</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="22">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B12" s="19">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C12" s="18">
         <f t="shared" si="0"/>
         <v>-64.046760511667529</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="22">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B13" s="19">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C13" s="18">
         <f t="shared" si="0"/>
         <v>-6.5402088492716128</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="22">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B14" s="19">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C14" s="18">
         <f t="shared" si="0"/>
         <v>198.19948129202027</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="22">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B15" s="19">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C15" s="18">
         <f t="shared" si="0"/>
         <v>91040.237411852577</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="22">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B16" s="19">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C16" s="18">
         <f t="shared" si="0"/>
         <v>19.572063797541304</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="22">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B17" s="19">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C17" s="18">
         <f t="shared" si="0"/>
         <v>-2.5764893835585476</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="22">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B18" s="19">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C18" s="18">
         <f t="shared" si="0"/>
         <v>-99.344926580920657</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="22">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B19" s="19">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C19" s="18">
         <f t="shared" si="0"/>
         <v>-68.887087467151304</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="22">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B20" s="19">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C20" s="18">
         <f t="shared" si="0"/>
         <v>19054.886991293832</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="22">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B21" s="19">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C21" s="18">
         <f t="shared" si="0"/>
         <v>-92.845434694034026</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="22">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B22" s="19">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C22" s="18">
         <f t="shared" si="0"/>
         <v>396.32497533121034</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="22">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B23" s="19">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C23" s="18">
         <f t="shared" si="0"/>
         <v>-98.322351149824243</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="22">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B24" s="19">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C24" s="18">
         <f t="shared" si="0"/>
         <v>1191.1589836815915</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="22">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B25" s="19">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
       <c r="C25" s="18">
         <f t="shared" si="0"/>
         <v>-89.738241267184833</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="22">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B26" s="19">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
       <c r="C26" s="18">
         <f t="shared" si="0"/>
         <v>-77.08997404756451</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="22">
+        <v>46112</v>
+      </c>
+      <c r="B27" s="19">
+        <v>5262.3389565099997</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="22">
         <v>46111</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B28" s="19">
         <v>22969.58967849</v>
-      </c>
-      <c r="C27" s="18">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3860,17 +3874,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3884,7 +3898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3898,7 +3912,7 @@
         <v>317.51</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3912,7 +3926,7 @@
         <v>45.32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3926,7 +3940,7 @@
         <v>43.04</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3947,16 +3961,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3967,7 +3981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>46024</v>
       </c>
@@ -3976,7 +3990,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="2">
         <v>46031</v>
       </c>
@@ -3987,7 +4001,7 @@
         <v>-7.2050081634151582</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15" thickBot="1">
       <c r="A4" s="2">
         <v>46038</v>
       </c>
@@ -3998,7 +4012,7 @@
         <v>8.9822186264706527</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="2">
         <v>46045</v>
       </c>
@@ -4009,7 +4023,7 @@
         <v>5.9816162411350033</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" s="2">
         <v>46052</v>
       </c>
@@ -4020,7 +4034,7 @@
         <v>15.197009063882785</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" s="2">
         <v>46059</v>
       </c>
@@ -4031,7 +4045,7 @@
         <v>-2.5449418495950149</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="2">
         <v>46066</v>
       </c>
@@ -4042,7 +4056,7 @@
         <v>-2.0123569142568702</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="A9" s="2">
         <v>46073</v>
       </c>
@@ -4053,7 +4067,7 @@
         <v>10.56785858540723</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
       <c r="A10" s="2">
         <v>46080</v>
       </c>
@@ -4064,7 +4078,7 @@
         <v>5.8663015109889649</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11" s="2">
         <v>46087</v>
       </c>
@@ -4075,7 +4089,7 @@
         <v>-7.2971926029340803</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15" thickBot="1">
       <c r="A12" s="2">
         <v>46094</v>
       </c>
@@ -4086,7 +4100,7 @@
         <v>10.290725762048252</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="2">
         <v>46101</v>
       </c>
@@ -4097,7 +4111,7 @@
         <v>18.425106797854955</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="2">
         <v>46108</v>
       </c>
@@ -4109,7 +4123,7 @@
         <v>-2.1851046806061447</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="2">
         <v>46129</v>
       </c>
@@ -4119,6 +4133,18 @@
       <c r="C15" s="4">
         <f>+((B15-B14)/B14)*100</f>
         <v>-3.6019979820194892</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1">
+      <c r="A16" s="28">
+        <v>46136</v>
+      </c>
+      <c r="B16" s="20">
+        <v>1206629034.17156</v>
+      </c>
+      <c r="C16" s="4">
+        <f>+((B16-B15)/B15)*100</f>
+        <v>12.607640378286277</v>
       </c>
     </row>
   </sheetData>
@@ -4127,21 +4153,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.75" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="5" max="5" width="21.375" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -4167,7 +4193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -4193,7 +4219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>46115</v>
       </c>
@@ -4220,7 +4246,7 @@
         <v>-1.4067445693212368</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -4247,7 +4273,7 @@
         <v>0.9756937784346702</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -4274,7 +4300,7 @@
         <v>3.4749018512476764</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4299,6 +4325,32 @@
       <c r="H6" s="17">
         <f>+((G6-G5)/G5)*100</f>
         <v>3.0146874710954426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="28">
+        <v>46143</v>
+      </c>
+      <c r="B7" s="20">
+        <v>56289349.634710021</v>
+      </c>
+      <c r="C7" s="20">
+        <v>1572208957.4513197</v>
+      </c>
+      <c r="D7" s="20">
+        <v>131632832.49728999</v>
+      </c>
+      <c r="E7" s="20">
+        <v>1760131139.5833197</v>
+      </c>
+      <c r="F7" s="20">
+        <v>1480052.1803799996</v>
+      </c>
+      <c r="G7" s="20">
+        <v>1761611191.7636998</v>
+      </c>
+      <c r="H7" s="31">
+        <v>9.2253839605925378</v>
       </c>
     </row>
   </sheetData>
@@ -4307,19 +4359,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -4339,7 +4391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>46108</v>
       </c>
@@ -4359,7 +4411,7 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>46113</v>
       </c>
@@ -4373,14 +4425,14 @@
         <v>13741</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E13" si="0">+((D3-D2)/D2)*100</f>
+        <f t="shared" ref="E3:E14" si="0">+((D3-D2)/D2)*100</f>
         <v>4.8691139433717465</v>
       </c>
       <c r="F3" s="5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>46122</v>
       </c>
@@ -4401,7 +4453,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>46129</v>
       </c>
@@ -4422,7 +4474,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>46136</v>
       </c>
@@ -4443,7 +4495,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>46139</v>
       </c>
@@ -4464,7 +4516,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>46140</v>
       </c>
@@ -4485,7 +4537,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>46141</v>
       </c>
@@ -4506,7 +4558,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>46142</v>
       </c>
@@ -4528,7 +4580,7 @@
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>46146</v>
       </c>
@@ -4549,7 +4601,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>46147</v>
       </c>
@@ -4570,7 +4622,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="28">
         <v>46148</v>
       </c>
@@ -4588,6 +4640,27 @@
         <v>-3.3016147635524797</v>
       </c>
       <c r="F13" s="29">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="28">
+        <v>46149</v>
+      </c>
+      <c r="B14" s="30">
+        <v>13460</v>
+      </c>
+      <c r="C14" s="27">
+        <v>3</v>
+      </c>
+      <c r="D14" s="30">
+        <v>13463</v>
+      </c>
+      <c r="E14" s="29">
+        <f t="shared" si="0"/>
+        <v>0.36528999552706126</v>
+      </c>
+      <c r="F14" s="29">
         <v>0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -1533,7 +1533,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1557,9 +1557,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2855,7 +2852,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3430,57 +3427,67 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="24">
+      <c r="A33" s="23">
         <v>46149</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="19">
         <v>32505.648000000001</v>
       </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="20">
+      <c r="C33" s="22"/>
+      <c r="D33" s="19">
         <v>150</v>
       </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="20">
+      <c r="E33" s="22"/>
+      <c r="F33" s="19">
         <v>300</v>
       </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="20">
+      <c r="G33" s="22"/>
+      <c r="H33" s="19">
         <v>243.9</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="24">
+      <c r="A34" s="23">
         <v>46150</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="19">
         <v>8103.3360000000002</v>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="20">
+      <c r="C34" s="22"/>
+      <c r="D34" s="19">
         <v>100</v>
       </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="20">
+      <c r="E34" s="22"/>
+      <c r="F34" s="19">
         <v>100</v>
       </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="20">
+      <c r="G34" s="22"/>
+      <c r="H34" s="19">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="13"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="A35" s="23">
+        <v>46153</v>
+      </c>
+      <c r="B35" s="19">
+        <v>30219.955319000001</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="19">
+        <v>100</v>
+      </c>
+      <c r="E35" s="22"/>
+      <c r="F35" s="19">
+        <v>110.06</v>
+      </c>
+      <c r="G35" s="22"/>
+      <c r="H35" s="19">
+        <v>109.71</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="11"/>
+      <c r="A36" s="23"/>
       <c r="B36" s="1"/>
       <c r="C36" s="10"/>
       <c r="D36" s="1"/>
@@ -3497,12 +3504,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="14" style="15" customWidth="1"/>
+    <col min="3" max="3" width="14" style="14" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -3514,7 +3521,7 @@
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
@@ -3525,14 +3532,14 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="28">
-        <v>46150</v>
-      </c>
-      <c r="B2" s="27">
-        <v>23652.710333340001</v>
-      </c>
-      <c r="C2" s="18">
-        <f>+((B3-B4)/B4)*100</f>
+      <c r="A2" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B2" s="26">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C2" s="17">
+        <f>+((B4-B5)/B5)*100</f>
         <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
@@ -3543,14 +3550,14 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="26">
-        <v>46149</v>
-      </c>
-      <c r="B3" s="25">
-        <v>131.99794839</v>
-      </c>
-      <c r="C3" s="18">
-        <f>+((B4-B5)/B5)*100</f>
+      <c r="A3" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B3" s="26">
+        <v>23652.710333340001</v>
+      </c>
+      <c r="C3" s="17">
+        <f>+((B5-B6)/B6)*100</f>
         <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
@@ -3561,14 +3568,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21">
-        <v>46148</v>
-      </c>
-      <c r="B4" s="19">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C4" s="18">
-        <f t="shared" ref="C4:C26" si="0">+((B5-B6)/B6)*100</f>
+      <c r="A4" s="25">
+        <v>46149</v>
+      </c>
+      <c r="B4" s="24">
+        <v>131.99794839</v>
+      </c>
+      <c r="C4" s="17">
+        <f t="shared" ref="C4:C26" si="0">+((B6-B7)/B7)*100</f>
         <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
@@ -3579,13 +3586,13 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="21">
-        <v>46147</v>
-      </c>
-      <c r="B5" s="19">
-        <v>84317.802960360001</v>
-      </c>
-      <c r="C5" s="18">
+      <c r="A5" s="20">
+        <v>46148</v>
+      </c>
+      <c r="B5" s="18">
+        <v>745.52443231999996</v>
+      </c>
+      <c r="C5" s="17">
         <f t="shared" si="0"/>
         <v>-43.255825515735765</v>
       </c>
@@ -3597,273 +3604,281 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="21">
-        <v>46146</v>
-      </c>
-      <c r="B6" s="19">
-        <v>49567.396050169998</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="A6" s="20">
+        <v>46147</v>
+      </c>
+      <c r="B6" s="18">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C6" s="17">
         <f t="shared" si="0"/>
         <v>207.73664296544806</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="22">
-        <v>46142</v>
-      </c>
-      <c r="B7" s="19">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="A7" s="20">
+        <v>46146</v>
+      </c>
+      <c r="B7" s="18">
+        <v>49567.396050169998</v>
+      </c>
+      <c r="C7" s="17">
         <f t="shared" si="0"/>
         <v>-59.636256133262869</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="22">
-        <v>46141</v>
-      </c>
-      <c r="B8" s="19">
-        <v>28385.438679769999</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="A8" s="21">
+        <v>46142</v>
+      </c>
+      <c r="B8" s="18">
+        <v>87352.396084139997</v>
+      </c>
+      <c r="C8" s="17">
         <f t="shared" si="0"/>
         <v>74.333012643706198</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="22">
-        <v>46140</v>
-      </c>
-      <c r="B9" s="19">
-        <v>70324.097718699995</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="A9" s="21">
+        <v>46141</v>
+      </c>
+      <c r="B9" s="18">
+        <v>28385.438679769999</v>
+      </c>
+      <c r="C9" s="17">
         <f t="shared" si="0"/>
         <v>-33.842006324553125</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="22">
-        <v>46139</v>
-      </c>
-      <c r="B10" s="19">
-        <v>40338.944788629997</v>
-      </c>
-      <c r="C10" s="18">
+      <c r="A10" s="21">
+        <v>46140</v>
+      </c>
+      <c r="B10" s="18">
+        <v>70324.097718699995</v>
+      </c>
+      <c r="C10" s="17">
         <f t="shared" si="0"/>
         <v>1210.6463903543759</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="22">
-        <v>46136</v>
-      </c>
-      <c r="B11" s="19">
-        <v>60973.651931649998</v>
-      </c>
-      <c r="C11" s="18">
+      <c r="A11" s="21">
+        <v>46139</v>
+      </c>
+      <c r="B11" s="18">
+        <v>40338.944788629997</v>
+      </c>
+      <c r="C11" s="17">
         <f t="shared" si="0"/>
         <v>-73.032401489373797</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="22">
-        <v>46135</v>
-      </c>
-      <c r="B12" s="19">
-        <v>4652.1817311200002</v>
-      </c>
-      <c r="C12" s="18">
+      <c r="A12" s="21">
+        <v>46136</v>
+      </c>
+      <c r="B12" s="18">
+        <v>60973.651931649998</v>
+      </c>
+      <c r="C12" s="17">
         <f t="shared" si="0"/>
         <v>-64.046760511667529</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="22">
-        <v>46134</v>
-      </c>
-      <c r="B13" s="19">
-        <v>17251.00486529</v>
-      </c>
-      <c r="C13" s="18">
+      <c r="A13" s="21">
+        <v>46135</v>
+      </c>
+      <c r="B13" s="18">
+        <v>4652.1817311200002</v>
+      </c>
+      <c r="C13" s="17">
         <f t="shared" si="0"/>
         <v>-6.5402088492716128</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="22">
-        <v>46133</v>
-      </c>
-      <c r="B14" s="19">
-        <v>47981.781644150004</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="A14" s="21">
+        <v>46134</v>
+      </c>
+      <c r="B14" s="18">
+        <v>17251.00486529</v>
+      </c>
+      <c r="C14" s="17">
         <f t="shared" si="0"/>
         <v>198.19948129202027</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="22">
-        <v>46132</v>
-      </c>
-      <c r="B15" s="19">
-        <v>51339.49161813</v>
-      </c>
-      <c r="C15" s="18">
+      <c r="A15" s="21">
+        <v>46133</v>
+      </c>
+      <c r="B15" s="18">
+        <v>47981.781644150004</v>
+      </c>
+      <c r="C15" s="17">
         <f t="shared" si="0"/>
         <v>91040.237411852577</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="22">
-        <v>46129</v>
-      </c>
-      <c r="B16" s="19">
-        <v>17216.492596060001</v>
-      </c>
-      <c r="C16" s="18">
+      <c r="A16" s="21">
+        <v>46132</v>
+      </c>
+      <c r="B16" s="18">
+        <v>51339.49161813</v>
+      </c>
+      <c r="C16" s="17">
         <f t="shared" si="0"/>
         <v>19.572063797541304</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="22">
-        <v>46128</v>
-      </c>
-      <c r="B17" s="19">
-        <v>18.890111640000001</v>
-      </c>
-      <c r="C17" s="18">
+      <c r="A17" s="21">
+        <v>46129</v>
+      </c>
+      <c r="B17" s="18">
+        <v>17216.492596060001</v>
+      </c>
+      <c r="C17" s="17">
         <f t="shared" si="0"/>
         <v>-2.5764893835585476</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="22">
-        <v>46127</v>
-      </c>
-      <c r="B18" s="19">
-        <v>15.79809785</v>
-      </c>
-      <c r="C18" s="18">
+      <c r="A18" s="21">
+        <v>46128</v>
+      </c>
+      <c r="B18" s="18">
+        <v>18.890111640000001</v>
+      </c>
+      <c r="C18" s="17">
         <f t="shared" si="0"/>
         <v>-99.344926580920657</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="22">
-        <v>46126</v>
-      </c>
-      <c r="B19" s="19">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C19" s="18">
+      <c r="A19" s="21">
+        <v>46127</v>
+      </c>
+      <c r="B19" s="18">
+        <v>15.79809785</v>
+      </c>
+      <c r="C19" s="17">
         <f t="shared" si="0"/>
         <v>-68.887087467151304</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="22">
-        <v>46125</v>
-      </c>
-      <c r="B20" s="19">
-        <v>2475.4322626600001</v>
-      </c>
-      <c r="C20" s="18">
+      <c r="A20" s="21">
+        <v>46126</v>
+      </c>
+      <c r="B20" s="18">
+        <v>16.215898760000002</v>
+      </c>
+      <c r="C20" s="17">
         <f t="shared" si="0"/>
         <v>19054.886991293832</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="22">
-        <v>46122</v>
-      </c>
-      <c r="B21" s="19">
-        <v>7956.2858669899997</v>
-      </c>
-      <c r="C21" s="18">
+      <c r="A21" s="21">
+        <v>46125</v>
+      </c>
+      <c r="B21" s="18">
+        <v>2475.4322626600001</v>
+      </c>
+      <c r="C21" s="17">
         <f t="shared" si="0"/>
         <v>-92.845434694034026</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="22">
-        <v>46121</v>
-      </c>
-      <c r="B22" s="19">
-        <v>41.536584740000002</v>
-      </c>
-      <c r="C22" s="18">
+      <c r="A22" s="21">
+        <v>46122</v>
+      </c>
+      <c r="B22" s="18">
+        <v>7956.2858669899997</v>
+      </c>
+      <c r="C22" s="17">
         <f t="shared" si="0"/>
         <v>396.32497533121034</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="22">
-        <v>46120</v>
-      </c>
-      <c r="B23" s="19">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C23" s="18">
+      <c r="A23" s="21">
+        <v>46121</v>
+      </c>
+      <c r="B23" s="18">
+        <v>41.536584740000002</v>
+      </c>
+      <c r="C23" s="17">
         <f t="shared" si="0"/>
         <v>-98.322351149824243</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="22">
-        <v>46119</v>
-      </c>
-      <c r="B24" s="19">
-        <v>116.97186189</v>
-      </c>
-      <c r="C24" s="18">
+      <c r="A24" s="21">
+        <v>46120</v>
+      </c>
+      <c r="B24" s="18">
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C24" s="17">
         <f t="shared" si="0"/>
         <v>1191.1589836815915</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="22">
-        <v>46118</v>
-      </c>
-      <c r="B25" s="19">
-        <v>6972.36861443</v>
-      </c>
-      <c r="C25" s="18">
+      <c r="A25" s="21">
+        <v>46119</v>
+      </c>
+      <c r="B25" s="18">
+        <v>116.97186189</v>
+      </c>
+      <c r="C25" s="17">
         <f t="shared" si="0"/>
         <v>-89.738241267184833</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="22">
-        <v>46113</v>
-      </c>
-      <c r="B26" s="19">
-        <v>540.00852741999995</v>
-      </c>
-      <c r="C26" s="18">
+      <c r="A26" s="21">
+        <v>46118</v>
+      </c>
+      <c r="B26" s="18">
+        <v>6972.36861443</v>
+      </c>
+      <c r="C26" s="17">
         <f t="shared" si="0"/>
         <v>-77.08997404756451</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="22">
+      <c r="A27" s="21">
+        <v>46113</v>
+      </c>
+      <c r="B27" s="18">
+        <v>540.00852741999995</v>
+      </c>
+      <c r="C27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="21">
         <v>46112</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B28" s="18">
         <v>5262.3389565099997</v>
       </c>
-      <c r="C27" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="22">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="21">
         <v>46111</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B29" s="18">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4136,10 +4151,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>46136</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="19">
         <v>1206629034.17156</v>
       </c>
       <c r="C16" s="4">
@@ -4215,7 +4230,7 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="16">
         <v>0</v>
       </c>
     </row>
@@ -4241,7 +4256,7 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="16">
         <f>+((G3-G2)/G2)*100</f>
         <v>-1.4067445693212368</v>
       </c>
@@ -4268,7 +4283,7 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <f>+((G4-G3)/G3)*100</f>
         <v>0.9756937784346702</v>
       </c>
@@ -4295,7 +4310,7 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <f>+((G5-G4)/G4)*100</f>
         <v>3.4749018512476764</v>
       </c>
@@ -4322,34 +4337,34 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="16">
         <f>+((G6-G5)/G5)*100</f>
         <v>3.0146874710954426</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>46143</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>56289349.634710021</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <v>1572208957.4513197</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>131632832.49728999</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>1760131139.5833197</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>1480052.1803799996</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <v>1761611191.7636998</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>9.2253839605925378</v>
       </c>
     </row>
@@ -4360,14 +4375,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="7.375" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4384,7 +4399,7 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
@@ -4425,7 +4440,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E14" si="0">+((D3-D2)/D2)*100</f>
+        <f t="shared" ref="E3:E15" si="0">+((D3-D2)/D2)*100</f>
         <v>4.8691139433717465</v>
       </c>
       <c r="F3" s="5">
@@ -4605,13 +4620,13 @@
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>13872</v>
       </c>
       <c r="E12" s="5">
@@ -4623,45 +4638,66 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>46148</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>13411</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>3</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>13414</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="28">
         <f t="shared" si="0"/>
         <v>-3.3016147635524797</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>46149</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>13460</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>3</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>13463</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="28">
         <f t="shared" si="0"/>
         <v>0.36528999552706126</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B15" s="29">
+        <v>13398</v>
+      </c>
+      <c r="C15" s="26">
+        <v>3</v>
+      </c>
+      <c r="D15" s="29">
+        <v>13401</v>
+      </c>
+      <c r="E15" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.46052142910198324</v>
+      </c>
+      <c r="F15" s="28">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2852,7 +2852,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3487,14 +3487,24 @@
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="23"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="1"/>
+      <c r="A36" s="23">
+        <v>46154</v>
+      </c>
+      <c r="B36" s="19">
+        <v>0</v>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="19">
+        <v>0</v>
+      </c>
+      <c r="E36" s="22"/>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="H36" s="19">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3504,7 +3514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3533,13 +3543,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="27">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B2" s="26">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C2" s="17">
-        <f>+((B4-B5)/B5)*100</f>
+        <f>+((B5-B6)/B6)*100</f>
         <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
@@ -3551,13 +3561,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="27">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B3" s="26">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C3" s="17">
-        <f>+((B5-B6)/B6)*100</f>
+        <f>+((B6-B7)/B7)*100</f>
         <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
@@ -3568,14 +3578,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25">
-        <v>46149</v>
-      </c>
-      <c r="B4" s="24">
-        <v>131.99794839</v>
+      <c r="A4" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B4" s="26">
+        <v>23652.710333340001</v>
       </c>
       <c r="C4" s="17">
-        <f t="shared" ref="C4:C26" si="0">+((B6-B7)/B7)*100</f>
+        <f t="shared" ref="C4:C26" si="0">+((B7-B8)/B8)*100</f>
         <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
@@ -3586,11 +3596,11 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="20">
-        <v>46148</v>
-      </c>
-      <c r="B5" s="18">
-        <v>745.52443231999996</v>
+      <c r="A5" s="25">
+        <v>46149</v>
+      </c>
+      <c r="B5" s="24">
+        <v>131.99794839</v>
       </c>
       <c r="C5" s="17">
         <f t="shared" si="0"/>
@@ -3605,10 +3615,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="20">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B6" s="18">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C6" s="17">
         <f t="shared" si="0"/>
@@ -3617,10 +3627,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="20">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B7" s="18">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C7" s="17">
         <f t="shared" si="0"/>
@@ -3628,11 +3638,11 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="21">
-        <v>46142</v>
+      <c r="A8" s="20">
+        <v>46146</v>
       </c>
       <c r="B8" s="18">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C8" s="17">
         <f t="shared" si="0"/>
@@ -3641,10 +3651,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="21">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B9" s="18">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C9" s="17">
         <f t="shared" si="0"/>
@@ -3653,10 +3663,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="21">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B10" s="18">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C10" s="17">
         <f t="shared" si="0"/>
@@ -3665,10 +3675,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="21">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B11" s="18">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C11" s="17">
         <f t="shared" si="0"/>
@@ -3677,10 +3687,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="21">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B12" s="18">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C12" s="17">
         <f t="shared" si="0"/>
@@ -3689,10 +3699,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="21">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B13" s="18">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C13" s="17">
         <f t="shared" si="0"/>
@@ -3701,10 +3711,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="21">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B14" s="18">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C14" s="17">
         <f t="shared" si="0"/>
@@ -3713,10 +3723,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="21">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B15" s="18">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C15" s="17">
         <f t="shared" si="0"/>
@@ -3725,10 +3735,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="21">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B16" s="18">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C16" s="17">
         <f t="shared" si="0"/>
@@ -3737,10 +3747,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="21">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B17" s="18">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C17" s="17">
         <f t="shared" si="0"/>
@@ -3749,10 +3759,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="21">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B18" s="18">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C18" s="17">
         <f t="shared" si="0"/>
@@ -3761,10 +3771,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="21">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B19" s="18">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" si="0"/>
@@ -3773,10 +3783,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="21">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B20" s="18">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C20" s="17">
         <f t="shared" si="0"/>
@@ -3785,10 +3795,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="21">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B21" s="18">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C21" s="17">
         <f t="shared" si="0"/>
@@ -3797,10 +3807,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="21">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B22" s="18">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C22" s="17">
         <f t="shared" si="0"/>
@@ -3809,10 +3819,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="21">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B23" s="18">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C23" s="17">
         <f t="shared" si="0"/>
@@ -3821,10 +3831,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="21">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B24" s="18">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C24" s="17">
         <f t="shared" si="0"/>
@@ -3833,10 +3843,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="21">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B25" s="18">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C25" s="17">
         <f t="shared" si="0"/>
@@ -3845,10 +3855,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="21">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B26" s="18">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C26" s="17">
         <f t="shared" si="0"/>
@@ -3857,10 +3867,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="21">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B27" s="18">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
       <c r="C27" s="17">
         <v>0</v>
@@ -3868,17 +3878,25 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="21">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B28" s="18">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="21">
+        <v>46112</v>
+      </c>
+      <c r="B29" s="18">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="21">
         <v>46111</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B30" s="18">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4375,7 +4393,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4440,7 +4458,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E15" si="0">+((D3-D2)/D2)*100</f>
+        <f t="shared" ref="E3:E16" si="0">+((D3-D2)/D2)*100</f>
         <v>4.8691139433717465</v>
       </c>
       <c r="F3" s="5">
@@ -4697,6 +4715,27 @@
         <v>-0.46052142910198324</v>
       </c>
       <c r="F15" s="28">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="27">
+        <v>46153</v>
+      </c>
+      <c r="B16" s="29">
+        <v>13309</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" s="29">
+        <v>13312</v>
+      </c>
+      <c r="E16" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.66412954257144985</v>
+      </c>
+      <c r="F16" s="28">
         <v>-0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2852,7 +2852,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2860,7 +2860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="12" customWidth="1"/>
@@ -3506,6 +3506,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="23">
+        <v>46155</v>
+      </c>
+      <c r="B37" s="19">
+        <v>200</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="19">
+        <v>100</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="19">
+        <v>100</v>
+      </c>
+      <c r="G37" s="22"/>
+      <c r="H37" s="19">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3514,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3543,13 +3563,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="27">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B2" s="26">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C2" s="17">
-        <f>+((B5-B6)/B6)*100</f>
+        <f>+((B6-B7)/B7)*100</f>
         <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
@@ -3561,13 +3581,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="27">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B3" s="26">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C3" s="17">
-        <f>+((B6-B7)/B7)*100</f>
+        <f>+((B7-B8)/B8)*100</f>
         <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
@@ -3579,13 +3599,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="27">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B4" s="26">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C4" s="17">
-        <f t="shared" ref="C4:C26" si="0">+((B7-B8)/B8)*100</f>
+        <f t="shared" ref="C4:C26" si="0">+((B8-B9)/B9)*100</f>
         <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
@@ -3596,11 +3616,11 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="25">
-        <v>46149</v>
-      </c>
-      <c r="B5" s="24">
-        <v>131.99794839</v>
+      <c r="A5" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B5" s="26">
+        <v>23652.710333340001</v>
       </c>
       <c r="C5" s="17">
         <f t="shared" si="0"/>
@@ -3614,11 +3634,11 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="20">
-        <v>46148</v>
-      </c>
-      <c r="B6" s="18">
-        <v>745.52443231999996</v>
+      <c r="A6" s="25">
+        <v>46149</v>
+      </c>
+      <c r="B6" s="24">
+        <v>131.99794839</v>
       </c>
       <c r="C6" s="17">
         <f t="shared" si="0"/>
@@ -3627,10 +3647,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="20">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B7" s="18">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C7" s="17">
         <f t="shared" si="0"/>
@@ -3639,10 +3659,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="20">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B8" s="18">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C8" s="17">
         <f t="shared" si="0"/>
@@ -3650,11 +3670,11 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="21">
-        <v>46142</v>
+      <c r="A9" s="20">
+        <v>46146</v>
       </c>
       <c r="B9" s="18">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C9" s="17">
         <f t="shared" si="0"/>
@@ -3663,10 +3683,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="21">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B10" s="18">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C10" s="17">
         <f t="shared" si="0"/>
@@ -3675,10 +3695,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="21">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B11" s="18">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C11" s="17">
         <f t="shared" si="0"/>
@@ -3687,10 +3707,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="21">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B12" s="18">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C12" s="17">
         <f t="shared" si="0"/>
@@ -3699,10 +3719,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="21">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B13" s="18">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C13" s="17">
         <f t="shared" si="0"/>
@@ -3711,10 +3731,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="21">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B14" s="18">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C14" s="17">
         <f t="shared" si="0"/>
@@ -3723,10 +3743,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="21">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B15" s="18">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C15" s="17">
         <f t="shared" si="0"/>
@@ -3735,10 +3755,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="21">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B16" s="18">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C16" s="17">
         <f t="shared" si="0"/>
@@ -3747,10 +3767,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="21">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B17" s="18">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C17" s="17">
         <f t="shared" si="0"/>
@@ -3759,10 +3779,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="21">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B18" s="18">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C18" s="17">
         <f t="shared" si="0"/>
@@ -3771,10 +3791,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="21">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B19" s="18">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" si="0"/>
@@ -3783,10 +3803,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="21">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B20" s="18">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C20" s="17">
         <f t="shared" si="0"/>
@@ -3795,10 +3815,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="21">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B21" s="18">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C21" s="17">
         <f t="shared" si="0"/>
@@ -3807,10 +3827,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="21">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B22" s="18">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C22" s="17">
         <f t="shared" si="0"/>
@@ -3819,10 +3839,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="21">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B23" s="18">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C23" s="17">
         <f t="shared" si="0"/>
@@ -3831,10 +3851,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="21">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B24" s="18">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C24" s="17">
         <f t="shared" si="0"/>
@@ -3843,10 +3863,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="21">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B25" s="18">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C25" s="17">
         <f t="shared" si="0"/>
@@ -3855,10 +3875,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="21">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B26" s="18">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C26" s="17">
         <f t="shared" si="0"/>
@@ -3867,10 +3887,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="21">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B27" s="18">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C27" s="17">
         <v>0</v>
@@ -3878,25 +3898,33 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="21">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B28" s="18">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="21">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B29" s="18">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="21">
+        <v>46112</v>
+      </c>
+      <c r="B30" s="18">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="21">
         <v>46111</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B31" s="18">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4393,7 +4421,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4458,7 +4486,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E16" si="0">+((D3-D2)/D2)*100</f>
+        <f t="shared" ref="E3:E17" si="0">+((D3-D2)/D2)*100</f>
         <v>4.8691139433717465</v>
       </c>
       <c r="F3" s="5">
@@ -4736,6 +4764,27 @@
         <v>-0.66412954257144985</v>
       </c>
       <c r="F16" s="28">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="27">
+        <v>46154</v>
+      </c>
+      <c r="B17" s="29">
+        <v>13300</v>
+      </c>
+      <c r="C17" s="26">
+        <v>3</v>
+      </c>
+      <c r="D17" s="29">
+        <v>13303</v>
+      </c>
+      <c r="E17" s="28">
+        <f t="shared" si="0"/>
+        <v>-6.7608173076923073E-2</v>
+      </c>
+      <c r="F17" s="28">
         <v>-0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2852,7 +2852,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2860,7 +2860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="12" customWidth="1"/>
@@ -3526,6 +3526,26 @@
         <v>100</v>
       </c>
     </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="23">
+        <v>46156</v>
+      </c>
+      <c r="B38" s="19">
+        <v>0</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="19">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="19">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3534,7 +3554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3563,13 +3583,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="27">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2" s="26">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C2" s="17">
-        <f>+((B6-B7)/B7)*100</f>
+        <f>+((B7-B8)/B8)*100</f>
         <v>-82.294618034282905</v>
       </c>
       <c r="D2" t="s">
@@ -3581,13 +3601,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="27">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B3" s="26">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C3" s="17">
-        <f>+((B7-B8)/B8)*100</f>
+        <f>+((B8-B9)/B9)*100</f>
         <v>-99.115816107458954</v>
       </c>
       <c r="D3" t="s">
@@ -3599,13 +3619,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="27">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B4" s="26">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C4" s="17">
-        <f t="shared" ref="C4:C26" si="0">+((B8-B9)/B9)*100</f>
+        <f t="shared" ref="C4:C26" si="0">+((B9-B10)/B10)*100</f>
         <v>70.107388483787062</v>
       </c>
       <c r="D4" t="s">
@@ -3617,10 +3637,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="27">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B5" s="26">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C5" s="17">
         <f t="shared" si="0"/>
@@ -3634,11 +3654,11 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25">
-        <v>46149</v>
-      </c>
-      <c r="B6" s="24">
-        <v>131.99794839</v>
+      <c r="A6" s="27">
+        <v>46150</v>
+      </c>
+      <c r="B6" s="26">
+        <v>23652.710333340001</v>
       </c>
       <c r="C6" s="17">
         <f t="shared" si="0"/>
@@ -3646,11 +3666,11 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="20">
-        <v>46148</v>
-      </c>
-      <c r="B7" s="18">
-        <v>745.52443231999996</v>
+      <c r="A7" s="25">
+        <v>46149</v>
+      </c>
+      <c r="B7" s="24">
+        <v>131.99794839</v>
       </c>
       <c r="C7" s="17">
         <f t="shared" si="0"/>
@@ -3659,10 +3679,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="20">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B8" s="18">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C8" s="17">
         <f t="shared" si="0"/>
@@ -3671,10 +3691,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="20">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B9" s="18">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C9" s="17">
         <f t="shared" si="0"/>
@@ -3682,11 +3702,11 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="21">
-        <v>46142</v>
+      <c r="A10" s="20">
+        <v>46146</v>
       </c>
       <c r="B10" s="18">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C10" s="17">
         <f t="shared" si="0"/>
@@ -3695,10 +3715,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="21">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B11" s="18">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C11" s="17">
         <f t="shared" si="0"/>
@@ -3707,10 +3727,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="21">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B12" s="18">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C12" s="17">
         <f t="shared" si="0"/>
@@ -3719,10 +3739,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="21">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B13" s="18">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C13" s="17">
         <f t="shared" si="0"/>
@@ -3731,10 +3751,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="21">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B14" s="18">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C14" s="17">
         <f t="shared" si="0"/>
@@ -3743,10 +3763,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="21">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B15" s="18">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C15" s="17">
         <f t="shared" si="0"/>
@@ -3755,10 +3775,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="21">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B16" s="18">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C16" s="17">
         <f t="shared" si="0"/>
@@ -3767,10 +3787,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="21">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B17" s="18">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C17" s="17">
         <f t="shared" si="0"/>
@@ -3779,10 +3799,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="21">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B18" s="18">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C18" s="17">
         <f t="shared" si="0"/>
@@ -3791,10 +3811,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="21">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B19" s="18">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" si="0"/>
@@ -3803,10 +3823,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="21">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B20" s="18">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C20" s="17">
         <f t="shared" si="0"/>
@@ -3815,10 +3835,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="21">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B21" s="18">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C21" s="17">
         <f t="shared" si="0"/>
@@ -3827,10 +3847,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="21">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B22" s="18">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C22" s="17">
         <f t="shared" si="0"/>
@@ -3839,10 +3859,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="21">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B23" s="18">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C23" s="17">
         <f t="shared" si="0"/>
@@ -3851,10 +3871,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="21">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B24" s="18">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C24" s="17">
         <f t="shared" si="0"/>
@@ -3863,10 +3883,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="21">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B25" s="18">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C25" s="17">
         <f t="shared" si="0"/>
@@ -3875,10 +3895,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="21">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B26" s="18">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C26" s="17">
         <f t="shared" si="0"/>
@@ -3887,10 +3907,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="21">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B27" s="18">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C27" s="17">
         <v>0</v>
@@ -3898,33 +3918,41 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="21">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B28" s="18">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="21">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B29" s="18">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="21">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B30" s="18">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="21">
+        <v>46112</v>
+      </c>
+      <c r="B31" s="18">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="21">
         <v>46111</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B32" s="18">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4421,7 +4449,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4486,7 +4514,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E17" si="0">+((D3-D2)/D2)*100</f>
+        <f t="shared" ref="E3:E18" si="0">+((D3-D2)/D2)*100</f>
         <v>4.8691139433717465</v>
       </c>
       <c r="F3" s="5">
@@ -4785,6 +4813,27 @@
         <v>-6.7608173076923073E-2</v>
       </c>
       <c r="F17" s="28">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="27">
+        <v>46155</v>
+      </c>
+      <c r="B18" s="29">
+        <v>13277</v>
+      </c>
+      <c r="C18" s="26">
+        <v>3</v>
+      </c>
+      <c r="D18" s="29">
+        <v>13280</v>
+      </c>
+      <c r="E18" s="28">
+        <f t="shared" si="0"/>
+        <v>-0.17289333233105317</v>
+      </c>
+      <c r="F18" s="28">
         <v>-0.01</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
@@ -145,6 +145,7 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -289,7 +290,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +434,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1533,7 +1540,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1541,9 +1548,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1586,11 +1590,23 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2860,10 +2876,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
     <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
@@ -2871,7 +2887,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2888,7 +2904,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -2905,7 +2921,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="11">
+      <c r="A3" s="10">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -2922,7 +2938,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -2939,7 +2955,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -2956,7 +2972,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -2973,7 +2989,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -2990,7 +3006,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -3007,7 +3023,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -3024,7 +3040,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="11">
+      <c r="A10" s="10">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -3041,7 +3057,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -3058,7 +3074,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -3075,7 +3091,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -3092,7 +3108,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="11">
+      <c r="A14" s="10">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -3109,7 +3125,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="11">
+      <c r="A15" s="10">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -3126,7 +3142,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -3143,7 +3159,7 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="11">
+      <c r="A17" s="10">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -3160,7 +3176,7 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -3177,7 +3193,7 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -3194,7 +3210,7 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -3211,7 +3227,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -3228,7 +3244,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -3245,7 +3261,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3262,7 +3278,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3279,7 +3295,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3296,7 +3312,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="11">
+      <c r="A26" s="10">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3313,7 +3329,7 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3330,7 +3346,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="11">
+      <c r="A28" s="10">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3347,202 +3363,222 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="11">
+      <c r="A29" s="10">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
         <v>37961.673699999999</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="1">
         <v>15</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="7"/>
       <c r="F29" s="1">
         <v>25</v>
       </c>
-      <c r="G29" s="8"/>
+      <c r="G29" s="7"/>
       <c r="H29" s="1">
         <v>18.43</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="11">
+      <c r="A30" s="10">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="10"/>
+      <c r="G30" s="9"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="11">
+      <c r="A31" s="10">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="10"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="10"/>
+      <c r="G31" s="9"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="11">
+      <c r="A32" s="10">
         <v>46148</v>
       </c>
       <c r="B32" s="1">
         <v>1200</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="1">
         <v>100</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="10"/>
+      <c r="G32" s="9"/>
       <c r="H32" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="23">
+      <c r="A33" s="22">
         <v>46149</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="18">
         <v>32505.648000000001</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="19">
+      <c r="C33" s="21"/>
+      <c r="D33" s="18">
         <v>150</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="19">
+      <c r="E33" s="21"/>
+      <c r="F33" s="18">
         <v>300</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="19">
+      <c r="G33" s="21"/>
+      <c r="H33" s="18">
         <v>243.9</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="23">
+      <c r="A34" s="22">
         <v>46150</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="18">
         <v>8103.3360000000002</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="19">
+      <c r="C34" s="21"/>
+      <c r="D34" s="18">
         <v>100</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="19">
+      <c r="E34" s="21"/>
+      <c r="F34" s="18">
         <v>100</v>
       </c>
-      <c r="G34" s="22"/>
-      <c r="H34" s="19">
+      <c r="G34" s="21"/>
+      <c r="H34" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="23">
+      <c r="A35" s="22">
         <v>46153</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="18">
         <v>30219.955319000001</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="19">
+      <c r="C35" s="21"/>
+      <c r="D35" s="18">
         <v>100</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="19">
+      <c r="E35" s="21"/>
+      <c r="F35" s="18">
         <v>110.06</v>
       </c>
-      <c r="G35" s="22"/>
-      <c r="H35" s="19">
+      <c r="G35" s="21"/>
+      <c r="H35" s="18">
         <v>109.71</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="23">
+      <c r="A36" s="22">
         <v>46154</v>
       </c>
-      <c r="B36" s="19">
-        <v>0</v>
-      </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="19">
-        <v>0</v>
-      </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="19">
-        <v>0</v>
-      </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="19">
+      <c r="B36" s="18">
+        <v>0</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="18">
+        <v>0</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="18">
+        <v>0</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="23">
+      <c r="A37" s="22">
         <v>46155</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="18">
         <v>200</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="19">
+      <c r="C37" s="21"/>
+      <c r="D37" s="18">
         <v>100</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="19">
+      <c r="E37" s="21"/>
+      <c r="F37" s="18">
         <v>100</v>
       </c>
-      <c r="G37" s="22"/>
-      <c r="H37" s="19">
+      <c r="G37" s="21"/>
+      <c r="H37" s="18">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="23">
+      <c r="A38" s="22">
         <v>46156</v>
       </c>
-      <c r="B38" s="19">
-        <v>0</v>
-      </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="19">
-        <v>0</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="19">
-        <v>0</v>
-      </c>
-      <c r="G38" s="22"/>
-      <c r="H38" s="19">
+      <c r="B38" s="18">
+        <v>0</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="22">
+        <v>46157</v>
+      </c>
+      <c r="B39" s="18">
+        <v>0</v>
+      </c>
+      <c r="C39" s="29"/>
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="30"/>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="30"/>
+      <c r="H39" s="18">
         <v>0</v>
       </c>
     </row>
@@ -3554,24 +3590,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="14" style="14" customWidth="1"/>
+    <col min="3" max="3" width="14" style="13" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
@@ -3581,379 +3617,407 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="27">
+    <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="26">
+        <v>46157</v>
+      </c>
+      <c r="B2" s="25">
+        <v>74209.813271849998</v>
+      </c>
+      <c r="C2" s="31">
+        <f>+((B2-B3)/B3)</f>
+        <v>35.243819791014161</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5">
+        <v>42155.425069182624</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" customHeight="1">
+      <c r="A3" s="26">
         <v>46156</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B3" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C2" s="17">
-        <f>+((B7-B8)/B8)*100</f>
-        <v>-82.294618034282905</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="6">
-        <v>42155.425069182624</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="27">
+      <c r="C3" s="31">
+        <f>+((B3-B4)/B4)</f>
+        <v>82.182099964255912</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>68497.757342013356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="26">
         <v>46155</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B4" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C3" s="17">
-        <f>+((B8-B9)/B9)*100</f>
-        <v>-99.115816107458954</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="6">
-        <v>68497.757342013356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="27">
+      <c r="C4" s="31">
+        <f t="shared" ref="C4:C27" si="0">+((B4-B5)/B5)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>85928.931135131905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="26">
         <v>46154</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B5" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C4" s="17">
-        <f t="shared" ref="C4:C26" si="0">+((B9-B10)/B10)*100</f>
-        <v>70.107388483787062</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="7">
-        <v>85928.931135131905</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="27">
+      <c r="C5" s="31">
+        <f t="shared" si="0"/>
+        <v>-0.95811572537747924</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="26">
         <v>46153</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B6" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>-43.255825515735765</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="7">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="27">
+        <v>-0.32064889280191988</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="26">
         <v>46150</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B7" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>207.73664296544806</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25">
+        <v>178.18998455533497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46149</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C8" s="31">
         <f t="shared" si="0"/>
-        <v>-59.636256133262869</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="20">
+        <v>-0.82294618034282907</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="19">
         <v>46148</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B9" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C9" s="31">
         <f t="shared" si="0"/>
-        <v>74.333012643706198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="20">
+        <v>-0.99115816107458954</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="19">
         <v>46147</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B10" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C10" s="31">
         <f t="shared" si="0"/>
-        <v>-33.842006324553125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="20">
+        <v>0.70107388483787059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="19">
         <v>46146</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B11" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C11" s="31">
         <f t="shared" si="0"/>
-        <v>1210.6463903543759</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="21">
+        <v>-0.43255825515735763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="20">
         <v>46142</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B12" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C12" s="31">
         <f t="shared" si="0"/>
-        <v>-73.032401489373797</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="21">
+        <v>2.0773664296544805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="20">
         <v>46141</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B13" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C13" s="31">
         <f t="shared" si="0"/>
-        <v>-64.046760511667529</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="21">
+        <v>-0.59636256133262866</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="20">
         <v>46140</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B14" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C14" s="31">
         <f t="shared" si="0"/>
-        <v>-6.5402088492716128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="21">
+        <v>0.74333012643706198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="20">
         <v>46139</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B15" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C15" s="31">
         <f t="shared" si="0"/>
-        <v>198.19948129202027</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="21">
+        <v>-0.33842006324553126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="20">
         <v>46136</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B16" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C16" s="31">
         <f t="shared" si="0"/>
-        <v>91040.237411852577</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="21">
+        <v>12.106463903543759</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="20">
         <v>46135</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B17" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C17" s="31">
         <f t="shared" si="0"/>
-        <v>19.572063797541304</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="21">
+        <v>-0.73032401489373799</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="20">
         <v>46134</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B18" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C18" s="31">
         <f t="shared" si="0"/>
-        <v>-2.5764893835585476</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="21">
+        <v>-0.64046760511667533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="20">
         <v>46133</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B19" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C19" s="31">
         <f t="shared" si="0"/>
-        <v>-99.344926580920657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="21">
+        <v>-6.5402088492716129E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="20">
         <v>46132</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B20" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C20" s="31">
         <f t="shared" si="0"/>
-        <v>-68.887087467151304</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="21">
+        <v>1.9819948129202027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="20">
         <v>46129</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B21" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C21" s="31">
         <f t="shared" si="0"/>
-        <v>19054.886991293832</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="21">
+        <v>910.40237411852581</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46128</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B22" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C22" s="31">
         <f t="shared" si="0"/>
-        <v>-92.845434694034026</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="21">
+        <v>0.19572063797541306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46127</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B23" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C23" s="31">
         <f t="shared" si="0"/>
-        <v>396.32497533121034</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="21">
+        <v>-2.5764893835585476E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46126</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B24" s="17">
         <v>16.215898760000002</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C24" s="31">
         <f t="shared" si="0"/>
-        <v>-98.322351149824243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="21">
+        <v>-0.99344926580920656</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46125</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B25" s="17">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C25" s="31">
         <f t="shared" si="0"/>
-        <v>1191.1589836815915</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="21">
+        <v>-0.68887087467151309</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46122</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B26" s="17">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C26" s="31">
         <f t="shared" si="0"/>
-        <v>-89.738241267184833</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="21">
+        <v>190.54886991293833</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46121</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B27" s="17">
         <v>41.536584740000002</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C27" s="31">
         <f t="shared" si="0"/>
-        <v>-77.08997404756451</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="21">
+        <v>-0.92845434694034024</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46120</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B28" s="17">
         <v>580.56056466999996</v>
       </c>
-      <c r="C27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="21">
+      <c r="C28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46119</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B29" s="17">
         <v>116.97186189</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="21">
+      <c r="C29" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46118</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B30" s="17">
         <v>6972.36861443</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="21">
+      <c r="C30" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46113</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B31" s="17">
         <v>540.00852741999995</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="21">
+      <c r="C31" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46112</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B32" s="17">
         <v>5262.3389565099997</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="21">
+      <c r="C32" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46111</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B33" s="17">
         <v>22969.58967849</v>
+      </c>
+      <c r="C33" s="16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4039,7 +4103,7 @@
       <c r="C5" s="1">
         <v>4946.5745432999993</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>64.09</v>
       </c>
     </row>
@@ -4225,10 +4289,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="27">
+      <c r="A16" s="26">
         <v>46136</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>1206629034.17156</v>
       </c>
       <c r="C16" s="4">
@@ -4243,7 +4307,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4304,7 +4368,7 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>0</v>
       </c>
     </row>
@@ -4330,7 +4394,7 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <f>+((G3-G2)/G2)*100</f>
         <v>-1.4067445693212368</v>
       </c>
@@ -4357,7 +4421,7 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="15">
         <f>+((G4-G3)/G3)*100</f>
         <v>0.9756937784346702</v>
       </c>
@@ -4384,7 +4448,7 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <f>+((G5-G4)/G4)*100</f>
         <v>3.4749018512476764</v>
       </c>
@@ -4411,35 +4475,61 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <f>+((G6-G5)/G5)*100</f>
         <v>3.0146874710954426</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="27">
+      <c r="A7" s="26">
         <v>46143</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>56289349.634710021</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>1572208957.4513197</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <v>131632832.49728999</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>1760131139.5833197</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="18">
         <v>1480052.1803799996</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="18">
         <v>1761611191.7636998</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="28">
         <v>9.2253839605925378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="26">
+        <v>46150</v>
+      </c>
+      <c r="B8" s="18">
+        <v>56976115.061530016</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1583444536.3055906</v>
+      </c>
+      <c r="D8" s="18">
+        <v>120943453.33754002</v>
+      </c>
+      <c r="E8" s="18">
+        <v>1761364104.7046607</v>
+      </c>
+      <c r="F8" s="18">
+        <v>1443633.0552200002</v>
+      </c>
+      <c r="G8" s="18">
+        <v>1762807737.7598805</v>
+      </c>
+      <c r="H8" s="28">
+        <v>6.7923387508850297E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4449,14 +4539,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="7.375" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.875" style="14" customWidth="1"/>
     <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4473,7 +4563,7 @@
       <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
@@ -4493,10 +4583,11 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="32" t="e">
+        <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F2" s="33">
         <v>-0.03</v>
       </c>
     </row>
@@ -4513,12 +4604,12 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3" s="5">
-        <f t="shared" ref="E3:E18" si="0">+((D3-D2)/D2)*100</f>
-        <v>4.8691139433717465</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.05</v>
+      <c r="E3" s="32">
+        <f t="shared" si="0"/>
+        <v>4.8691139433717466E-2</v>
+      </c>
+      <c r="F3" s="33">
+        <v>4.8691139433717466E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4534,12 +4625,12 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="32">
         <f t="shared" si="0"/>
-        <v>-1.1061785896222982</v>
-      </c>
-      <c r="F4" s="5">
-        <v>-0.01</v>
+        <v>-1.1061785896222982E-2</v>
+      </c>
+      <c r="F4" s="33">
+        <v>-1.1061785896222982E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4555,12 +4646,12 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="32">
         <f t="shared" si="0"/>
-        <v>0.62550592390904403</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.01</v>
+        <v>6.2550592390904405E-3</v>
+      </c>
+      <c r="F5" s="33">
+        <v>6.2550592390904405E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4576,12 +4667,12 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="32">
         <f t="shared" si="0"/>
-        <v>-1.3894983179757203</v>
-      </c>
-      <c r="F6" s="5">
-        <v>-0.01</v>
+        <v>-1.3894983179757204E-2</v>
+      </c>
+      <c r="F6" s="33">
+        <v>-1.3894983179757204E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4597,12 +4688,12 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="32">
         <f t="shared" si="0"/>
-        <v>-0.17798872738059923</v>
-      </c>
-      <c r="F7" s="5">
-        <v>-0.01</v>
+        <v>-1.7798872738059924E-3</v>
+      </c>
+      <c r="F7" s="33">
+        <v>-1.7798872738059924E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4618,12 +4709,12 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="32">
         <f t="shared" si="0"/>
-        <v>-1.5378900445765229</v>
-      </c>
-      <c r="F8" s="5">
-        <v>-0.01</v>
+        <v>-1.5378900445765229E-2</v>
+      </c>
+      <c r="F8" s="33">
+        <v>-1.5378900445765229E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4639,12 +4730,12 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="32">
         <f t="shared" si="0"/>
-        <v>-0.49800045272768434</v>
-      </c>
-      <c r="F9" s="5">
-        <v>-0.01</v>
+        <v>-4.9800045272768434E-3</v>
+      </c>
+      <c r="F9" s="33">
+        <v>-4.9800045272768434E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4660,14 +4751,14 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="32">
         <f t="shared" si="0"/>
-        <v>0.70524000909987106</v>
-      </c>
-      <c r="F10" s="5">
-        <v>-0.01</v>
-      </c>
-      <c r="G10" s="8"/>
+        <v>7.0524000909987106E-3</v>
+      </c>
+      <c r="F10" s="33">
+        <v>7.0524000909987106E-3</v>
+      </c>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
@@ -4682,159 +4773,181 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="32">
         <f t="shared" si="0"/>
-        <v>5.8810240963855422</v>
-      </c>
-      <c r="F11" s="5">
-        <v>-0.01</v>
+        <v>5.8810240963855419E-2</v>
+      </c>
+      <c r="F11" s="33">
+        <v>5.8810240963855419E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>13872</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="32">
         <f t="shared" si="0"/>
-        <v>-1.3441433752933647</v>
-      </c>
-      <c r="F12" s="5">
-        <v>-0.01</v>
+        <v>-1.3441433752933647E-2</v>
+      </c>
+      <c r="F12" s="33">
+        <v>-1.3441433752933647E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="27">
+      <c r="A13" s="26">
         <v>46148</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="27">
         <v>13411</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>3</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="27">
         <v>13414</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="32">
         <f t="shared" si="0"/>
-        <v>-3.3016147635524797</v>
-      </c>
-      <c r="F13" s="28">
-        <v>0.01</v>
+        <v>-3.3016147635524795E-2</v>
+      </c>
+      <c r="F13" s="33">
+        <v>-3.3016147635524795E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27">
+      <c r="A14" s="26">
         <v>46149</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="27">
         <v>13460</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>3</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="27">
         <v>13463</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="32">
         <f t="shared" si="0"/>
-        <v>0.36528999552706126</v>
-      </c>
-      <c r="F14" s="28">
-        <v>0.01</v>
+        <v>3.6528999552706129E-3</v>
+      </c>
+      <c r="F14" s="33">
+        <v>3.6528999552706129E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27">
+      <c r="A15" s="26">
         <v>46150</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="27">
         <v>13398</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>3</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="27">
         <v>13401</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="32">
         <f t="shared" si="0"/>
-        <v>-0.46052142910198324</v>
-      </c>
-      <c r="F15" s="28">
-        <v>-0.01</v>
+        <v>-4.6052142910198322E-3</v>
+      </c>
+      <c r="F15" s="33">
+        <v>-4.6052142910198322E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="27">
+      <c r="A16" s="26">
         <v>46153</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="27">
         <v>13309</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="27">
         <v>13312</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="32">
         <f t="shared" si="0"/>
-        <v>-0.66412954257144985</v>
-      </c>
-      <c r="F16" s="28">
-        <v>-0.01</v>
+        <v>-6.6412954257144986E-3</v>
+      </c>
+      <c r="F16" s="33">
+        <v>-6.6412954257144986E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="27">
+      <c r="A17" s="26">
         <v>46154</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="27">
         <v>13300</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>3</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="27">
         <v>13303</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="32">
         <f t="shared" si="0"/>
-        <v>-6.7608173076923073E-2</v>
-      </c>
-      <c r="F17" s="28">
-        <v>-0.01</v>
+        <v>-6.7608173076923075E-4</v>
+      </c>
+      <c r="F17" s="33">
+        <v>-6.7608173076923075E-4</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="27">
+      <c r="A18" s="26">
         <v>46155</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="27">
         <v>13277</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>3</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="27">
         <v>13280</v>
       </c>
-      <c r="E18" s="28">
-        <f t="shared" si="0"/>
-        <v>-0.17289333233105317</v>
-      </c>
-      <c r="F18" s="28">
-        <v>-0.01</v>
+      <c r="E18" s="32">
+        <f>+((D18-D17)/D17)</f>
+        <v>-1.7289333233105315E-3</v>
+      </c>
+      <c r="F18" s="33">
+        <v>-1.7289333233105315E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="26">
+        <v>46157</v>
+      </c>
+      <c r="B19" s="27">
+        <v>13282</v>
+      </c>
+      <c r="C19" s="25">
+        <v>3</v>
+      </c>
+      <c r="D19" s="27">
+        <f t="shared" ref="D19" si="1">SUM(B19+C19)</f>
+        <v>13285</v>
+      </c>
+      <c r="E19" s="32">
+        <f>+((D19-D18)/D18)</f>
+        <v>3.7650602409638556E-4</v>
+      </c>
+      <c r="F19" s="33">
+        <v>3.7650602409638556E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="2"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2868,7 +2868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2876,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3582,6 +3582,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="22">
+        <v>46161</v>
+      </c>
+      <c r="B40" s="18">
+        <v>0</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="18">
+        <v>0</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="18">
+        <v>0</v>
+      </c>
+      <c r="G40" s="30"/>
+      <c r="H40" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3590,7 +3610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3619,13 +3639,13 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B2" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B2-B3)/B3)</f>
+        <f>+((B3-B4)/B4)</f>
         <v>35.243819791014161</v>
       </c>
       <c r="D2" s="25" t="s">
@@ -3637,13 +3657,13 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B3" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B3-B4)/B4)</f>
+        <f>+((B4-B5)/B5)</f>
         <v>82.182099964255912</v>
       </c>
       <c r="D3" s="25" t="s">
@@ -3655,13 +3675,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B4" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C4" s="31">
-        <f t="shared" ref="C4:C27" si="0">+((B4-B5)/B5)</f>
+        <f t="shared" ref="C4:C27" si="0">+((B5-B6)/B6)</f>
         <v>-0.96342609797465562</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -3673,10 +3693,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B5" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
@@ -3691,10 +3711,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B6" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
@@ -3704,10 +3724,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B7" s="25">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
@@ -3715,11 +3735,11 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B8" s="23">
-        <v>131.99794839</v>
+      <c r="A8" s="26">
+        <v>46150</v>
+      </c>
+      <c r="B8" s="25">
+        <v>23652.710333340001</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
@@ -3727,11 +3747,11 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B9" s="17">
-        <v>745.52443231999996</v>
+      <c r="A9" s="24">
+        <v>46149</v>
+      </c>
+      <c r="B9" s="23">
+        <v>131.99794839</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
@@ -3740,10 +3760,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B10" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
@@ -3752,10 +3772,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="19">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B11" s="17">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
@@ -3763,11 +3783,11 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="20">
-        <v>46142</v>
+      <c r="A12" s="19">
+        <v>46146</v>
       </c>
       <c r="B12" s="17">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
@@ -3776,10 +3796,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B13" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
@@ -3788,10 +3808,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B14" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
@@ -3800,10 +3820,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B15" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
@@ -3812,10 +3832,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B16" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
@@ -3824,10 +3844,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B17" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
@@ -3836,10 +3856,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B18" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
@@ -3848,10 +3868,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B19" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
@@ -3860,10 +3880,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B20" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
@@ -3872,10 +3892,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B21" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
@@ -3884,10 +3904,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B22" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
@@ -3896,10 +3916,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B23" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
@@ -3908,10 +3928,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B24" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
@@ -3920,10 +3940,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B25" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
@@ -3932,10 +3952,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B26" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
@@ -3944,10 +3964,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B27" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
@@ -3956,10 +3976,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B28" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -3967,10 +3987,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B29" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -3978,10 +3998,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B30" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -3989,10 +4009,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B31" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4000,10 +4020,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B32" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4011,13 +4031,21 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B33" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+      <c r="C33" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46111</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>22969.58967849</v>
-      </c>
-      <c r="C33" s="16">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4539,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4930,7 +4958,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="26">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B19" s="27">
         <v>13282</v>
@@ -4947,6 +4975,27 @@
         <v>3.7650602409638556E-4</v>
       </c>
       <c r="F19" s="33">
+        <v>3.7650602409638556E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="26">
+        <v>46157</v>
+      </c>
+      <c r="B20" s="27">
+        <v>13015</v>
+      </c>
+      <c r="C20" s="25">
+        <v>3</v>
+      </c>
+      <c r="D20" s="27">
+        <v>13018</v>
+      </c>
+      <c r="E20" s="32">
+        <f>+((D20-D19)/D19)</f>
+        <v>-2.0097854723372225E-2</v>
+      </c>
+      <c r="F20" s="33">
         <v>3.7650602409638556E-4</v>
       </c>
     </row>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2868,7 +2868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2876,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3589,7 +3589,6 @@
       <c r="B40" s="18">
         <v>0</v>
       </c>
-      <c r="C40" s="29"/>
       <c r="D40" s="18">
         <v>0</v>
       </c>
@@ -3599,6 +3598,26 @@
       </c>
       <c r="G40" s="30"/>
       <c r="H40" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="22">
+        <v>46162</v>
+      </c>
+      <c r="B41" s="18">
+        <v>0</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="18">
+        <v>0</v>
+      </c>
+      <c r="E41" s="25"/>
+      <c r="F41" s="18">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25"/>
+      <c r="H41" s="18">
         <v>0</v>
       </c>
     </row>
@@ -3610,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3639,13 +3658,13 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B2" s="25">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B3-B4)/B4)</f>
+        <f>+((B4-B5)/B5)</f>
         <v>35.243819791014161</v>
       </c>
       <c r="D2" s="25" t="s">
@@ -3657,13 +3676,13 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B3" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B4-B5)/B5)</f>
+        <f>+((B5-B6)/B6)</f>
         <v>82.182099964255912</v>
       </c>
       <c r="D3" s="25" t="s">
@@ -3675,13 +3694,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B4" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C4" s="31">
-        <f t="shared" ref="C4:C27" si="0">+((B5-B6)/B6)</f>
+        <f t="shared" ref="C4:C27" si="0">+((B6-B7)/B7)</f>
         <v>-0.96342609797465562</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -3693,10 +3712,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B5" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
@@ -3711,10 +3730,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B6" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
@@ -3724,10 +3743,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B7" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
@@ -3736,10 +3755,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B8" s="25">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
@@ -3747,11 +3766,11 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B9" s="23">
-        <v>131.99794839</v>
+      <c r="A9" s="26">
+        <v>46150</v>
+      </c>
+      <c r="B9" s="25">
+        <v>23652.710333340001</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
@@ -3759,11 +3778,11 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B10" s="17">
-        <v>745.52443231999996</v>
+      <c r="A10" s="24">
+        <v>46149</v>
+      </c>
+      <c r="B10" s="23">
+        <v>131.99794839</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
@@ -3772,10 +3791,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B11" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
@@ -3784,10 +3803,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="19">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B12" s="17">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
@@ -3795,11 +3814,11 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="20">
-        <v>46142</v>
+      <c r="A13" s="19">
+        <v>46146</v>
       </c>
       <c r="B13" s="17">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
@@ -3808,10 +3827,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B14" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
@@ -3820,10 +3839,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B15" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
@@ -3832,10 +3851,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B16" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
@@ -3844,10 +3863,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B17" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
@@ -3856,10 +3875,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B18" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
@@ -3868,10 +3887,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B19" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
@@ -3880,10 +3899,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B20" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
@@ -3892,10 +3911,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B21" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
@@ -3904,10 +3923,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B22" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
@@ -3916,10 +3935,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B23" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
@@ -3928,10 +3947,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B24" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
@@ -3940,10 +3959,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B25" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
@@ -3952,10 +3971,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B26" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
@@ -3964,10 +3983,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B27" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
@@ -3976,10 +3995,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B28" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -3987,10 +4006,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B29" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -3998,10 +4017,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B30" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4009,10 +4028,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B31" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4020,10 +4039,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B32" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4031,10 +4050,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B33" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4042,9 +4061,17 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B34" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="20">
         <v>46111</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B35" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4567,7 +4594,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4999,6 +5026,27 @@
         <v>3.7650602409638556E-4</v>
       </c>
     </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="26">
+        <v>46161</v>
+      </c>
+      <c r="B21" s="27">
+        <v>12992</v>
+      </c>
+      <c r="C21" s="25">
+        <v>3</v>
+      </c>
+      <c r="D21" s="27">
+        <v>12995</v>
+      </c>
+      <c r="E21" s="32">
+        <f>+((D21-D20)/D20)</f>
+        <v>-1.7667844522968198E-3</v>
+      </c>
+      <c r="F21" s="33">
+        <v>-6.7608173076923075E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2868,7 +2868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2876,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3621,6 +3621,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="22">
+        <v>46163</v>
+      </c>
+      <c r="B42" s="18">
+        <v>5006.6000000000004</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="18">
+        <v>120</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="18">
+        <v>120</v>
+      </c>
+      <c r="G42" s="21"/>
+      <c r="H42" s="18">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3629,7 +3649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3658,13 +3678,13 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B4-B5)/B5)</f>
+        <f>+((B5-B6)/B6)</f>
         <v>35.243819791014161</v>
       </c>
       <c r="D2" s="25" t="s">
@@ -3676,13 +3696,13 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B3" s="25">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B5-B6)/B6)</f>
+        <f>+((B6-B7)/B7)</f>
         <v>82.182099964255912</v>
       </c>
       <c r="D3" s="25" t="s">
@@ -3694,13 +3714,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B4" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C4" s="31">
-        <f t="shared" ref="C4:C27" si="0">+((B6-B7)/B7)</f>
+        <f t="shared" ref="C4:C27" si="0">+((B7-B8)/B8)</f>
         <v>-0.96342609797465562</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -3712,10 +3732,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B5" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
@@ -3730,10 +3750,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B6" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
@@ -3743,10 +3763,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B7" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
@@ -3755,10 +3775,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B8" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
@@ -3767,10 +3787,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B9" s="25">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
@@ -3778,11 +3798,11 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B10" s="23">
-        <v>131.99794839</v>
+      <c r="A10" s="26">
+        <v>46150</v>
+      </c>
+      <c r="B10" s="25">
+        <v>23652.710333340001</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
@@ -3790,11 +3810,11 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B11" s="17">
-        <v>745.52443231999996</v>
+      <c r="A11" s="24">
+        <v>46149</v>
+      </c>
+      <c r="B11" s="23">
+        <v>131.99794839</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
@@ -3803,10 +3823,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B12" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
@@ -3815,10 +3835,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="19">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B13" s="17">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
@@ -3826,11 +3846,11 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="20">
-        <v>46142</v>
+      <c r="A14" s="19">
+        <v>46146</v>
       </c>
       <c r="B14" s="17">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
@@ -3839,10 +3859,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B15" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
@@ -3851,10 +3871,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B16" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
@@ -3863,10 +3883,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B17" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
@@ -3875,10 +3895,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B18" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
@@ -3887,10 +3907,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B19" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
@@ -3899,10 +3919,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B20" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
@@ -3911,10 +3931,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B21" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
@@ -3923,10 +3943,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B22" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
@@ -3935,10 +3955,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B23" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
@@ -3947,10 +3967,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B24" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
@@ -3959,10 +3979,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B25" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
@@ -3971,10 +3991,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B26" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
@@ -3983,10 +4003,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B27" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
@@ -3995,10 +4015,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B28" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -4006,10 +4026,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B29" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -4017,10 +4037,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B30" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4028,10 +4048,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B31" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4039,10 +4059,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B32" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4050,10 +4070,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B33" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4061,17 +4081,25 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B34" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B35" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="20">
         <v>46111</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B36" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4594,7 +4622,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5047,6 +5075,27 @@
         <v>-6.7608173076923075E-4</v>
       </c>
     </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B22" s="27">
+        <v>12888</v>
+      </c>
+      <c r="C22" s="25">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27">
+        <v>12891</v>
+      </c>
+      <c r="E22" s="32">
+        <f>+((D22-D21)/D21)</f>
+        <v>-8.0030781069642173E-3</v>
+      </c>
+      <c r="F22" s="33">
+        <v>-1.1061785896222982E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1540,7 +1540,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1607,6 +1607,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2868,7 +2871,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2876,7 +2879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3641,6 +3644,26 @@
         <v>120</v>
       </c>
     </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="22">
+        <v>46164</v>
+      </c>
+      <c r="B43" s="18">
+        <v>0</v>
+      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="18">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="18">
+        <v>0</v>
+      </c>
+      <c r="G43" s="21"/>
+      <c r="H43" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3649,7 +3672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3678,13 +3701,13 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B5-B6)/B6)</f>
+        <f>+((B6-B7)/B7)</f>
         <v>35.243819791014161</v>
       </c>
       <c r="D2" s="25" t="s">
@@ -3696,13 +3719,13 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B3" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B6-B7)/B7)</f>
+        <f>+((B7-B8)/B8)</f>
         <v>82.182099964255912</v>
       </c>
       <c r="D3" s="25" t="s">
@@ -3714,13 +3737,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B4" s="25">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C4" s="31">
-        <f t="shared" ref="C4:C27" si="0">+((B7-B8)/B8)</f>
+        <f t="shared" ref="C4:C27" si="0">+((B8-B9)/B9)</f>
         <v>-0.96342609797465562</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -3732,10 +3755,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B5" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
@@ -3750,10 +3773,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B6" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
@@ -3763,10 +3786,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B7" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
@@ -3775,10 +3798,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B8" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
@@ -3787,10 +3810,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B9" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
@@ -3799,10 +3822,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B10" s="25">
-        <v>23652.710333340001</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
@@ -3810,11 +3833,11 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B11" s="23">
-        <v>131.99794839</v>
+      <c r="A11" s="26">
+        <v>46150</v>
+      </c>
+      <c r="B11" s="25">
+        <v>23652.710333340001</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
@@ -3822,11 +3845,11 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B12" s="17">
-        <v>745.52443231999996</v>
+      <c r="A12" s="24">
+        <v>46149</v>
+      </c>
+      <c r="B12" s="23">
+        <v>131.99794839</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
@@ -3835,10 +3858,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B13" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
@@ -3847,10 +3870,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="19">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B14" s="17">
-        <v>49567.396050169998</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
@@ -3858,11 +3881,11 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="20">
-        <v>46142</v>
+      <c r="A15" s="19">
+        <v>46146</v>
       </c>
       <c r="B15" s="17">
-        <v>87352.396084139997</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
@@ -3871,10 +3894,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B16" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
@@ -3883,10 +3906,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B17" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
@@ -3895,10 +3918,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B18" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
@@ -3907,10 +3930,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B19" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
@@ -3919,10 +3942,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B20" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
@@ -3931,10 +3954,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B21" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
@@ -3943,10 +3966,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B22" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
@@ -3955,10 +3978,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B23" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
@@ -3967,10 +3990,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B24" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
@@ -3979,10 +4002,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B25" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
@@ -3991,10 +4014,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B26" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
@@ -4003,10 +4026,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B27" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
@@ -4015,10 +4038,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B28" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -4026,10 +4049,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B29" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -4037,10 +4060,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B30" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4048,10 +4071,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B31" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4059,10 +4082,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B32" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4070,10 +4093,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B33" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4081,25 +4104,33 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B34" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B35" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="20">
         <v>46111</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B37" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4198,7 +4229,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4383,6 +4414,9 @@
         <v>12.607640378286277</v>
       </c>
     </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="26"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4390,7 +4424,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4615,6 +4649,32 @@
         <v>6.7923387508850297E-2</v>
       </c>
     </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="26">
+        <v>46157</v>
+      </c>
+      <c r="B9" s="18">
+        <v>57191389.678870022</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1736713788.0136802</v>
+      </c>
+      <c r="D9" s="18">
+        <v>154232219.13352999</v>
+      </c>
+      <c r="E9" s="18">
+        <v>1948137396.8260801</v>
+      </c>
+      <c r="F9" s="18">
+        <v>1517284.0840200002</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1949654680.9101</v>
+      </c>
+      <c r="H9" s="28">
+        <v>10.599394315551303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4622,7 +4682,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5096,6 +5156,26 @@
         <v>-1.1061785896222982E-2</v>
       </c>
     </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="26">
+        <v>46163</v>
+      </c>
+      <c r="B23" s="27">
+        <v>14686</v>
+      </c>
+      <c r="C23" s="25">
+        <v>3</v>
+      </c>
+      <c r="D23" s="27">
+        <v>14689</v>
+      </c>
+      <c r="E23" s="34">
+        <v>12622</v>
+      </c>
+      <c r="F23" s="33">
+        <v>5.8810240963855419E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2871,7 +2871,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3707,8 +3707,8 @@
         <v>58837.242479</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B6-B7)/B7)</f>
-        <v>35.243819791014161</v>
+        <f>+((B2-B3)/B3)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2871,7 +2871,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2879,7 +2879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3664,6 +3664,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="22">
+        <v>46167</v>
+      </c>
+      <c r="B44" s="18">
+        <v>0</v>
+      </c>
+      <c r="C44" s="21"/>
+      <c r="D44" s="18">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="18">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21"/>
+      <c r="H44" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3672,7 +3692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3701,14 +3721,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B2" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C2" s="31">
         <f>+((B2-B3)/B3)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3719,14 +3739,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B3" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B7-B8)/B8)</f>
-        <v>82.182099964255912</v>
+        <f>+((B3-B4)/B4)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3737,14 +3757,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B4" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C4" s="31">
-        <f t="shared" ref="C4:C27" si="0">+((B8-B9)/B9)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B8-B9)/B9)</f>
+        <v>82.182099964255912</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3755,304 +3775,305 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B5" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C5" s="31">
+        <f t="shared" ref="C5:C28" si="0">+((B9-B10)/B10)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="26">
         <v>46161</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B6" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C6" s="31">
         <f t="shared" si="0"/>
         <v>-0.95811572537747924</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="26">
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="26">
         <v>46157</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B7" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C7" s="31">
         <f t="shared" si="0"/>
         <v>-0.32064889280191988</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="26">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="26">
         <v>46156</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B8" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C8" s="31">
         <f t="shared" si="0"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="26">
+    <row r="9" spans="1:5">
+      <c r="A9" s="26">
         <v>46155</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B9" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C9" s="31">
         <f t="shared" si="0"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="26">
+    <row r="10" spans="1:5">
+      <c r="A10" s="26">
         <v>46154</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B10" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <f t="shared" si="0"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="26">
+    <row r="11" spans="1:5">
+      <c r="A11" s="26">
         <v>46153</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B11" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C11" s="31">
         <f t="shared" si="0"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46150</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="0"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46149</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="0"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="19">
+    <row r="14" spans="1:5">
+      <c r="A14" s="19">
         <v>46148</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B14" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="0"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19">
+    <row r="15" spans="1:5">
+      <c r="A15" s="19">
         <v>46147</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B15" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="0"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19">
+    <row r="16" spans="1:5">
+      <c r="A16" s="19">
         <v>46146</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B16" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="0"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="20">
+    <row r="17" spans="1:3">
+      <c r="A17" s="20">
         <v>46142</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B17" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="0"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="20">
+    <row r="18" spans="1:3">
+      <c r="A18" s="20">
         <v>46141</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B18" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="0"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="20">
+    <row r="19" spans="1:3">
+      <c r="A19" s="20">
         <v>46140</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="0"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20">
+    <row r="20" spans="1:3">
+      <c r="A20" s="20">
         <v>46139</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="0"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="20">
+    <row r="21" spans="1:3">
+      <c r="A21" s="20">
         <v>46136</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="0"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="20">
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46135</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="0"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46134</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="0"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46133</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="0"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46132</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="0"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46129</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="0"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46128</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="0"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46127</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="0"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B28" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C28" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B29" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -4060,10 +4081,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B30" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4071,10 +4092,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B31" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4082,10 +4103,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B32" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4093,10 +4114,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B33" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4104,33 +4125,44 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B34" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C34" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B35" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B36" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B37" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="20">
         <v>46111</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B38" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4682,7 +4714,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5176,6 +5208,26 @@
         <v>5.8810240963855419E-2</v>
       </c>
     </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="26">
+        <v>46164</v>
+      </c>
+      <c r="B24" s="27">
+        <v>14649</v>
+      </c>
+      <c r="C24" s="25">
+        <v>3</v>
+      </c>
+      <c r="D24" s="27">
+        <v>14652</v>
+      </c>
+      <c r="E24" s="34">
+        <v>12645</v>
+      </c>
+      <c r="F24" s="33">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1540,7 +1540,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1607,9 +1607,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2871,7 +2868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2879,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3684,6 +3681,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="22">
+        <v>46168</v>
+      </c>
+      <c r="B45" s="18">
+        <v>0</v>
+      </c>
+      <c r="C45" s="21"/>
+      <c r="D45" s="18">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21"/>
+      <c r="F45" s="18">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21"/>
+      <c r="H45" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3692,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3721,14 +3738,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C2" s="31">
         <f>+((B2-B3)/B3)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3739,14 +3756,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B3" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C3" s="31">
         <f>+((B3-B4)/B4)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3757,14 +3774,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B4" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C4" s="31">
-        <f>+((B8-B9)/B9)</f>
-        <v>82.182099964255912</v>
+        <f>+((B4-B5)/B5)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3775,14 +3792,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B5" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C5" s="31">
-        <f t="shared" ref="C5:C28" si="0">+((B9-B10)/B10)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B9-B10)/B10)</f>
+        <v>82.182099964255912</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3793,298 +3810,299 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B6" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C6" s="31">
+        <f t="shared" ref="C6:C29" si="0">+((B10-B11)/B11)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="26">
         <v>46161</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B7" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C7" s="31">
         <f t="shared" si="0"/>
         <v>-0.95811572537747924</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="26">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="26">
         <v>46157</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B8" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C8" s="31">
         <f t="shared" si="0"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="26">
+    <row r="9" spans="1:5">
+      <c r="A9" s="26">
         <v>46156</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B9" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C9" s="31">
         <f t="shared" si="0"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="26">
+    <row r="10" spans="1:5">
+      <c r="A10" s="26">
         <v>46155</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B10" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <f t="shared" si="0"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="26">
+    <row r="11" spans="1:5">
+      <c r="A11" s="26">
         <v>46154</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B11" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C11" s="31">
         <f t="shared" si="0"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46153</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="0"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46150</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="0"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46149</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="0"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19">
+    <row r="15" spans="1:5">
+      <c r="A15" s="19">
         <v>46148</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B15" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="0"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19">
+    <row r="16" spans="1:5">
+      <c r="A16" s="19">
         <v>46147</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B16" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="0"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19">
+    <row r="17" spans="1:3">
+      <c r="A17" s="19">
         <v>46146</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B17" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="0"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="20">
+    <row r="18" spans="1:3">
+      <c r="A18" s="20">
         <v>46142</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B18" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="0"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="20">
+    <row r="19" spans="1:3">
+      <c r="A19" s="20">
         <v>46141</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="0"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20">
+    <row r="20" spans="1:3">
+      <c r="A20" s="20">
         <v>46140</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="0"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="20">
+    <row r="21" spans="1:3">
+      <c r="A21" s="20">
         <v>46139</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="0"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="20">
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46136</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="0"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46135</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="0"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46134</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="0"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46133</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="0"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46132</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="0"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46129</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="0"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46128</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="0"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46127</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="0"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B29" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C29" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B30" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4092,10 +4110,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B31" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4103,10 +4121,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B32" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4114,10 +4132,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B33" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4125,10 +4143,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B34" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4136,33 +4154,44 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B35" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B36" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B37" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B38" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="20">
         <v>46111</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B39" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4714,7 +4743,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5121,9 +5150,7 @@
         <f>+((D19-D18)/D18)</f>
         <v>3.7650602409638556E-4</v>
       </c>
-      <c r="F19" s="33">
-        <v>3.7650602409638556E-4</v>
-      </c>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="26">
@@ -5142,9 +5169,7 @@
         <f>+((D20-D19)/D19)</f>
         <v>-2.0097854723372225E-2</v>
       </c>
-      <c r="F20" s="33">
-        <v>3.7650602409638556E-4</v>
-      </c>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="26">
@@ -5163,9 +5188,7 @@
         <f>+((D21-D20)/D20)</f>
         <v>-1.7667844522968198E-3</v>
       </c>
-      <c r="F21" s="33">
-        <v>-6.7608173076923075E-4</v>
-      </c>
+      <c r="F21" s="33"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="26">
@@ -5184,9 +5207,7 @@
         <f>+((D22-D21)/D21)</f>
         <v>-8.0030781069642173E-3</v>
       </c>
-      <c r="F22" s="33">
-        <v>-1.1061785896222982E-2</v>
-      </c>
+      <c r="F22" s="33"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="26">
@@ -5201,12 +5222,11 @@
       <c r="D23" s="27">
         <v>14689</v>
       </c>
-      <c r="E23" s="34">
-        <v>12622</v>
-      </c>
-      <c r="F23" s="33">
-        <v>5.8810240963855419E-2</v>
-      </c>
+      <c r="E23" s="32">
+        <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
+        <v>0.13947715460398727</v>
+      </c>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="26">
@@ -5221,11 +5241,28 @@
       <c r="D24" s="27">
         <v>14652</v>
       </c>
-      <c r="E24" s="34">
-        <v>12645</v>
-      </c>
-      <c r="F24" s="33">
-        <v>2.9999999999999997E-4</v>
+      <c r="E24" s="32">
+        <f t="shared" si="2"/>
+        <v>-2.5188916876574307E-3</v>
+      </c>
+      <c r="F24" s="33"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="26">
+        <v>46167</v>
+      </c>
+      <c r="B25" s="27">
+        <v>12949</v>
+      </c>
+      <c r="C25" s="25">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27">
+        <v>12952</v>
+      </c>
+      <c r="E25" s="32">
+        <f>+((D25-D24)/D24)</f>
+        <v>-0.11602511602511603</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2868,7 +2868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4960,7 +4960,7 @@
         <v>7.0524000909987106E-3</v>
       </c>
       <c r="F10" s="33">
-        <v>7.0524000909987106E-3</v>
+        <v>-1.7798872738059924E-3</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -5150,7 +5150,9 @@
         <f>+((D19-D18)/D18)</f>
         <v>3.7650602409638556E-4</v>
       </c>
-      <c r="F19" s="33"/>
+      <c r="F19" s="33">
+        <v>3.6528999552700001E-3</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="26">
@@ -5169,7 +5171,9 @@
         <f>+((D20-D19)/D19)</f>
         <v>-2.0097854723372225E-2</v>
       </c>
-      <c r="F20" s="33"/>
+      <c r="F20" s="33">
+        <v>-6.7608173076923075E-4</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="26">
@@ -5188,7 +5192,9 @@
         <f>+((D21-D20)/D20)</f>
         <v>-1.7667844522968198E-3</v>
       </c>
-      <c r="F21" s="33"/>
+      <c r="F21" s="33">
+        <v>-1.7798872738059924E-3</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="26">
@@ -5207,7 +5213,9 @@
         <f>+((D22-D21)/D21)</f>
         <v>-8.0030781069642173E-3</v>
       </c>
-      <c r="F22" s="33"/>
+      <c r="F22" s="33">
+        <v>-1.11988711380599E-3</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="26">
@@ -5226,7 +5234,9 @@
         <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
         <v>0.13947715460398727</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="33">
+        <v>3.11289991117061E-3</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="26">
@@ -5245,7 +5255,9 @@
         <f t="shared" si="2"/>
         <v>-2.5188916876574307E-3</v>
       </c>
-      <c r="F24" s="33"/>
+      <c r="F24" s="33">
+        <v>-2.2052142910198298E-3</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="26">
@@ -5263,6 +5275,9 @@
       <c r="E25" s="32">
         <f>+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
+      </c>
+      <c r="F25" s="33">
+        <v>-1.1061785896222982E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -137,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
@@ -145,7 +145,6 @@
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1606,7 +1605,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2868,7 +2867,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4743,7 +4742,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -4788,11 +4787,11 @@
         <v>13103</v>
       </c>
       <c r="E2" s="32" t="e">
-        <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
+        <f t="shared" ref="E2:F17" si="0">+((D2-D1)/D1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F2" s="33">
-        <v>-0.03</v>
+      <c r="F2" s="33" t="e">
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4960,7 +4959,7 @@
         <v>7.0524000909987106E-3</v>
       </c>
       <c r="F10" s="33">
-        <v>-1.7798872738059924E-3</v>
+        <v>7.0524000909987106E-3</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -5151,7 +5150,7 @@
         <v>3.7650602409638556E-4</v>
       </c>
       <c r="F19" s="33">
-        <v>3.6528999552700001E-3</v>
+        <v>3.7650602409638556E-4</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5172,7 +5171,7 @@
         <v>-2.0097854723372225E-2</v>
       </c>
       <c r="F20" s="33">
-        <v>-6.7608173076923075E-4</v>
+        <v>-2.0097854723372225E-2</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5193,7 +5192,7 @@
         <v>-1.7667844522968198E-3</v>
       </c>
       <c r="F21" s="33">
-        <v>-1.7798872738059924E-3</v>
+        <v>-1.7667844522968198E-3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5214,7 +5213,7 @@
         <v>-8.0030781069642173E-3</v>
       </c>
       <c r="F22" s="33">
-        <v>-1.11988711380599E-3</v>
+        <v>-8.0030781069642173E-3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5231,11 +5230,11 @@
         <v>14689</v>
       </c>
       <c r="E23" s="32">
-        <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
+        <f t="shared" ref="E23:F24" si="2">+((D23-D22)/D22)</f>
         <v>0.13947715460398727</v>
       </c>
       <c r="F23" s="33">
-        <v>3.11289991117061E-3</v>
+        <v>0.13947715460398727</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5256,7 +5255,7 @@
         <v>-2.5188916876574307E-3</v>
       </c>
       <c r="F24" s="33">
-        <v>-2.2052142910198298E-3</v>
+        <v>-2.5188916876574307E-3</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5277,8 +5276,11 @@
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
-        <v>-1.1061785896222982E-2</v>
-      </c>
+        <v>-0.11602511602511603</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2867,7 +2867,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4787,7 +4787,7 @@
         <v>13103</v>
       </c>
       <c r="E2" s="32" t="e">
-        <f t="shared" ref="E2:F17" si="0">+((D2-D1)/D1)</f>
+        <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F2" s="33" t="e">
@@ -5213,7 +5213,7 @@
         <v>-8.0030781069642173E-3</v>
       </c>
       <c r="F22" s="33">
-        <v>-8.0030781069642173E-3</v>
+        <v>-9.9930781069642195E-3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5230,11 +5230,11 @@
         <v>14689</v>
       </c>
       <c r="E23" s="32">
-        <f t="shared" ref="E23:F24" si="2">+((D23-D22)/D22)</f>
+        <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
         <v>0.13947715460398727</v>
       </c>
       <c r="F23" s="33">
-        <v>0.13947715460398727</v>
+        <v>0.13999715460398701</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5255,7 +5255,7 @@
         <v>-2.5188916876574307E-3</v>
       </c>
       <c r="F24" s="33">
-        <v>-2.5188916876574307E-3</v>
+        <v>-9.9988916876574303E-3</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5276,7 +5276,7 @@
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
-        <v>-0.11602511602511603</v>
+        <v>-0.99602511602511601</v>
       </c>
     </row>
     <row r="26" spans="1:6">

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1605,7 +1605,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2867,7 +2867,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4790,8 +4790,8 @@
         <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F2" s="33" t="e">
-        <v>#VALUE!</v>
+      <c r="F2" s="33">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4812,7 +4812,7 @@
         <v>4.8691139433717466E-2</v>
       </c>
       <c r="F3" s="33">
-        <v>4.8691139433717466E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4833,7 +4833,7 @@
         <v>-1.1061785896222982E-2</v>
       </c>
       <c r="F4" s="33">
-        <v>-1.1061785896222982E-2</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4854,7 +4854,7 @@
         <v>6.2550592390904405E-3</v>
       </c>
       <c r="F5" s="33">
-        <v>6.2550592390904405E-3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4875,7 +4875,7 @@
         <v>-1.3894983179757204E-2</v>
       </c>
       <c r="F6" s="33">
-        <v>-1.3894983179757204E-2</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4896,7 +4896,7 @@
         <v>-1.7798872738059924E-3</v>
       </c>
       <c r="F7" s="33">
-        <v>-1.7798872738059924E-3</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4917,7 +4917,7 @@
         <v>-1.5378900445765229E-2</v>
       </c>
       <c r="F8" s="33">
-        <v>-1.5378900445765229E-2</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4938,7 +4938,7 @@
         <v>-4.9800045272768434E-3</v>
       </c>
       <c r="F9" s="33">
-        <v>-4.9800045272768434E-3</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4959,7 +4959,7 @@
         <v>7.0524000909987106E-3</v>
       </c>
       <c r="F10" s="33">
-        <v>7.0524000909987106E-3</v>
+        <v>-0.01</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -4981,7 +4981,7 @@
         <v>5.8810240963855419E-2</v>
       </c>
       <c r="F11" s="33">
-        <v>5.8810240963855419E-2</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5002,7 +5002,7 @@
         <v>-1.3441433752933647E-2</v>
       </c>
       <c r="F12" s="33">
-        <v>-1.3441433752933647E-2</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5023,7 +5023,7 @@
         <v>-3.3016147635524795E-2</v>
       </c>
       <c r="F13" s="33">
-        <v>-3.3016147635524795E-2</v>
+        <v>-0.123456</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5044,7 +5044,7 @@
         <v>3.6528999552706129E-3</v>
       </c>
       <c r="F14" s="33">
-        <v>3.6528999552706129E-3</v>
+        <v>0.37123455999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5065,7 +5065,7 @@
         <v>-4.6052142910198322E-3</v>
       </c>
       <c r="F15" s="33">
-        <v>-4.6052142910198322E-3</v>
+        <v>-0.46123456000000002</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5086,7 +5086,7 @@
         <v>-6.6412954257144986E-3</v>
       </c>
       <c r="F16" s="33">
-        <v>-6.6412954257144986E-3</v>
+        <v>-0.66123456000000003</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5107,7 +5107,7 @@
         <v>-6.7608173076923075E-4</v>
       </c>
       <c r="F17" s="33">
-        <v>-6.7608173076923075E-4</v>
+        <v>-7.1234560000000002E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5128,7 +5128,7 @@
         <v>-1.7289333233105315E-3</v>
       </c>
       <c r="F18" s="33">
-        <v>-1.7289333233105315E-3</v>
+        <v>-0.17123456000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5150,7 +5150,7 @@
         <v>3.7650602409638556E-4</v>
       </c>
       <c r="F19" s="33">
-        <v>3.7650602409638556E-4</v>
+        <v>4.1234560000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5171,7 +5171,7 @@
         <v>-2.0097854723372225E-2</v>
       </c>
       <c r="F20" s="33">
-        <v>-2.0097854723372225E-2</v>
+        <v>-2.0112345600000001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5192,7 +5192,7 @@
         <v>-1.7667844522968198E-3</v>
       </c>
       <c r="F21" s="33">
-        <v>-1.7667844522968198E-3</v>
+        <v>-0.18123455999999999</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5213,7 +5213,7 @@
         <v>-8.0030781069642173E-3</v>
       </c>
       <c r="F22" s="33">
-        <v>-9.9930781069642195E-3</v>
+        <v>-0.80123456000000004</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5234,7 +5234,7 @@
         <v>0.13947715460398727</v>
       </c>
       <c r="F23" s="33">
-        <v>0.13999715460398701</v>
+        <v>13.95123456</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5255,7 +5255,7 @@
         <v>-2.5188916876574307E-3</v>
       </c>
       <c r="F24" s="33">
-        <v>-9.9988916876574303E-3</v>
+        <v>-0.25123456</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5276,7 +5276,7 @@
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
-        <v>-0.99602511602511601</v>
+        <v>-11.60123456</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5284,5 +5284,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1605,7 +1605,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2867,7 +2867,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>DÍA</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>ABRIL</t>
+  </si>
+  <si>
+    <t>2705/2026</t>
   </si>
 </sst>
 </file>
@@ -603,7 +606,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="934">
+  <cellStyleXfs count="935">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
@@ -1538,6 +1541,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1605,11 +1609,11 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="934" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="934">
+  <cellStyles count="935">
     <cellStyle name="20% - Énfasis1 2" xfId="4"/>
     <cellStyle name="20% - Énfasis1 2 2" xfId="5"/>
     <cellStyle name="20% - Énfasis1 2 3" xfId="6"/>
@@ -1728,6 +1732,7 @@
     <cellStyle name="Incorrecto 2" xfId="118"/>
     <cellStyle name="Incorrecto 3" xfId="119"/>
     <cellStyle name="Incorrecto 4" xfId="120"/>
+    <cellStyle name="Millares" xfId="934" builtinId="3"/>
     <cellStyle name="Millares 10" xfId="122"/>
     <cellStyle name="Millares 10 2" xfId="810"/>
     <cellStyle name="Millares 2" xfId="123"/>
@@ -2875,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3700,6 +3705,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="22">
+        <v>46169</v>
+      </c>
+      <c r="B46" s="18">
+        <v>51256.235569999997</v>
+      </c>
+      <c r="C46" s="21"/>
+      <c r="D46" s="18">
+        <v>250</v>
+      </c>
+      <c r="E46" s="21"/>
+      <c r="F46" s="18">
+        <v>300.02</v>
+      </c>
+      <c r="G46" s="21"/>
+      <c r="H46" s="18">
+        <v>273.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3708,7 +3733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3736,16 +3761,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="26">
-        <v>46168</v>
+      <c r="A2" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="B2" s="25">
-        <v>8513.9651106900001</v>
-      </c>
-      <c r="C2" s="31">
-        <f>+((B2-B3)/B3)</f>
-        <v>-0.31892665326814518</v>
-      </c>
+        <v>21.673895040000001</v>
+      </c>
+      <c r="C2" s="13"/>
       <c r="D2" s="25" t="s">
         <v>8</v>
       </c>
@@ -3755,14 +3777,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B3" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C3" s="31">
         <f>+((B3-B4)/B4)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3773,14 +3795,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B4" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C4" s="31">
         <f>+((B4-B5)/B5)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3791,14 +3813,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B5" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C5" s="31">
-        <f>+((B9-B10)/B10)</f>
-        <v>82.182099964255912</v>
+        <f>+((B5-B6)/B6)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3809,310 +3831,311 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B6" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C6" s="31">
-        <f t="shared" ref="C6:C29" si="0">+((B10-B11)/B11)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B10-B11)/B11)</f>
+        <v>82.182099964255912</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B7" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C7" s="31">
+        <f t="shared" ref="C7:C30" si="0">+((B11-B12)/B12)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="26">
         <v>46161</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B8" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C8" s="31">
         <f t="shared" si="0"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="26">
+    <row r="9" spans="1:5">
+      <c r="A9" s="26">
         <v>46157</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B9" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C9" s="31">
         <f t="shared" si="0"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="26">
+    <row r="10" spans="1:5">
+      <c r="A10" s="26">
         <v>46156</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B10" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <f t="shared" si="0"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="26">
+    <row r="11" spans="1:5">
+      <c r="A11" s="26">
         <v>46155</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B11" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C11" s="31">
         <f t="shared" si="0"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46154</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="0"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46153</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="0"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46150</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="0"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46149</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="0"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19">
+    <row r="16" spans="1:5">
+      <c r="A16" s="19">
         <v>46148</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B16" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="0"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19">
+    <row r="17" spans="1:3">
+      <c r="A17" s="19">
         <v>46147</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B17" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="0"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="19">
+    <row r="18" spans="1:3">
+      <c r="A18" s="19">
         <v>46146</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B18" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="0"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="20">
+    <row r="19" spans="1:3">
+      <c r="A19" s="20">
         <v>46142</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="0"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20">
+    <row r="20" spans="1:3">
+      <c r="A20" s="20">
         <v>46141</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="0"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="20">
+    <row r="21" spans="1:3">
+      <c r="A21" s="20">
         <v>46140</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="0"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="20">
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46139</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="0"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46136</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="0"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46135</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="0"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46134</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="0"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46133</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="0"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46132</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="0"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46129</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="0"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46128</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="0"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46127</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="0"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B30" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C30" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B31" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4120,10 +4143,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B32" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4131,10 +4154,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B33" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4142,10 +4165,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B34" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4153,10 +4176,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B35" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4164,33 +4187,44 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B36" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C36" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B37" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B38" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B39" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="20">
         <v>46111</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B40" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -5280,7 +5314,25 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="F26" s="25"/>
+      <c r="A26" s="26">
+        <v>46168</v>
+      </c>
+      <c r="B26" s="27">
+        <v>12961</v>
+      </c>
+      <c r="C26" s="25">
+        <v>3</v>
+      </c>
+      <c r="D26" s="27">
+        <v>12964</v>
+      </c>
+      <c r="E26" s="32">
+        <f>+((D26-D25)/D25)</f>
+        <v>9.2649783817171094E-4</v>
+      </c>
+      <c r="F26" s="33">
+        <v>9.1234560000000006E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3725,6 +3725,26 @@
         <v>273.24</v>
       </c>
     </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="22">
+        <v>46170</v>
+      </c>
+      <c r="B47" s="18">
+        <v>38032.045118000002</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="18">
+        <v>300</v>
+      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="18">
+        <v>330</v>
+      </c>
+      <c r="G47" s="21"/>
+      <c r="H47" s="18">
+        <v>311.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3733,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3761,13 +3781,16 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="25" t="s">
-        <v>31</v>
+      <c r="A2" s="26">
+        <v>46170</v>
       </c>
       <c r="B2" s="25">
-        <v>21.673895040000001</v>
-      </c>
-      <c r="C2" s="13"/>
+        <v>9253.9873366299998</v>
+      </c>
+      <c r="C2" s="31">
+        <f t="shared" ref="C2:C3" si="0">+((B2-B3)/B3)</f>
+        <v>425.96466507526281</v>
+      </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
       </c>
@@ -3776,15 +3799,15 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A3" s="26">
-        <v>46168</v>
+      <c r="A3" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="B3" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B3-B4)/B4)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3795,14 +3818,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B4" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C4" s="31">
         <f>+((B4-B5)/B5)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3813,14 +3836,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B5" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C5" s="31">
         <f>+((B5-B6)/B6)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3831,322 +3854,323 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B6" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C6" s="31">
-        <f>+((B10-B11)/B11)</f>
-        <v>82.182099964255912</v>
+        <f>+((B6-B7)/B7)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B7" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C7" s="31">
-        <f t="shared" ref="C7:C30" si="0">+((B11-B12)/B12)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B11-B12)/B12)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B8" s="25">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C8" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.95811572537747924</v>
+        <f t="shared" ref="C8:C31" si="1">+((B12-B13)/B13)</f>
+        <v>-0.96342609797465562</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B9" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C9" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.32064889280191988</v>
+        <f t="shared" si="1"/>
+        <v>-0.95811572537747924</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B10" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C10" s="31">
-        <f t="shared" si="0"/>
-        <v>178.18998455533497</v>
+        <f t="shared" si="1"/>
+        <v>-0.32064889280191988</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B11" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C11" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.82294618034282907</v>
+        <f t="shared" si="1"/>
+        <v>178.18998455533497</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B12" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C12" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99115816107458954</v>
+        <f t="shared" si="1"/>
+        <v>-0.82294618034282907</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B13" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C13" s="31">
-        <f t="shared" si="0"/>
-        <v>0.70107388483787059</v>
+        <f t="shared" si="1"/>
+        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
+        <v>46153</v>
+      </c>
+      <c r="B14" s="25">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C14" s="31">
+        <f t="shared" si="1"/>
+        <v>0.70107388483787059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46150</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C14" s="31">
-        <f t="shared" si="0"/>
+      <c r="C15" s="31">
+        <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46149</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C15" s="31">
-        <f t="shared" si="0"/>
+      <c r="C16" s="31">
+        <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B16" s="17">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C16" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B17" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C17" s="31">
-        <f t="shared" si="0"/>
-        <v>0.74333012643706198</v>
+        <f t="shared" si="1"/>
+        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="19">
+        <v>46147</v>
+      </c>
+      <c r="B18" s="17">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C18" s="31">
+        <f t="shared" si="1"/>
+        <v>0.74333012643706198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="19">
         <v>46146</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C18" s="31">
-        <f t="shared" si="0"/>
+      <c r="C19" s="31">
+        <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20">
-        <v>46142</v>
-      </c>
-      <c r="B19" s="17">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C19" s="31">
-        <f t="shared" si="0"/>
-        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B20" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C20" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.73032401489373799</v>
+        <f t="shared" si="1"/>
+        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B21" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C21" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.64046760511667533</v>
+        <f t="shared" si="1"/>
+        <v>-0.73032401489373799</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B22" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C22" s="31">
-        <f t="shared" si="0"/>
-        <v>-6.5402088492716129E-2</v>
+        <f t="shared" si="1"/>
+        <v>-0.64046760511667533</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B23" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C23" s="31">
-        <f t="shared" si="0"/>
-        <v>1.9819948129202027</v>
+        <f t="shared" si="1"/>
+        <v>-6.5402088492716129E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B24" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C24" s="31">
-        <f t="shared" si="0"/>
-        <v>910.40237411852581</v>
+        <f t="shared" si="1"/>
+        <v>1.9819948129202027</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B25" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C25" s="31">
-        <f t="shared" si="0"/>
-        <v>0.19572063797541306</v>
+        <f t="shared" si="1"/>
+        <v>910.40237411852581</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B26" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C26" s="31">
-        <f t="shared" si="0"/>
-        <v>-2.5764893835585476E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.19572063797541306</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B27" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C27" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99344926580920656</v>
+        <f t="shared" si="1"/>
+        <v>-2.5764893835585476E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B28" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C28" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.68887087467151309</v>
+        <f t="shared" si="1"/>
+        <v>-0.99344926580920656</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B29" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C29" s="31">
-        <f t="shared" si="0"/>
-        <v>190.54886991293833</v>
+        <f t="shared" si="1"/>
+        <v>-0.68887087467151309</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B30" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C30" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.92845434694034024</v>
+        <f t="shared" si="1"/>
+        <v>190.54886991293833</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B31" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C31" s="16">
-        <v>0</v>
+        <v>15.79809785</v>
+      </c>
+      <c r="C31" s="31">
+        <f t="shared" si="1"/>
+        <v>-0.92845434694034024</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B32" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4154,10 +4178,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B33" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4165,10 +4189,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B34" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4176,10 +4200,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B35" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4187,10 +4211,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B36" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4198,33 +4222,44 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B37" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C37" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B38" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B39" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B40" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="20">
         <v>46111</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B41" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4776,7 +4811,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5334,6 +5369,27 @@
         <v>9.1234560000000006E-2</v>
       </c>
     </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="26">
+        <v>46169</v>
+      </c>
+      <c r="B27" s="27">
+        <v>12914</v>
+      </c>
+      <c r="C27" s="25">
+        <v>3</v>
+      </c>
+      <c r="D27" s="27">
+        <v>12917</v>
+      </c>
+      <c r="E27" s="32">
+        <f>+((D27-D26)/D26)</f>
+        <v>-3.625424251774144E-3</v>
+      </c>
+      <c r="F27" s="33">
+        <v>-0.36123455999999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -5387,7 +5387,7 @@
         <v>-3.625424251774144E-3</v>
       </c>
       <c r="F27" s="33">
-        <v>-0.36123455999999998</v>
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46170</v>
+        <v>45074</v>
       </c>
       <c r="B2" s="25">
         <v>9253.9873366299998</v>
@@ -5387,7 +5387,7 @@
         <v>-3.625424251774144E-3</v>
       </c>
       <c r="F27" s="33">
-        <v>-0.36</v>
+        <v>9.1234560000000006E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>DÍA</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>ABRIL</t>
-  </si>
-  <si>
-    <t>2705/2026</t>
   </si>
 </sst>
 </file>
@@ -2872,7 +2869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3799,8 +3796,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A3" s="25" t="s">
-        <v>31</v>
+      <c r="A3" s="26">
+        <v>46169</v>
       </c>
       <c r="B3" s="25">
         <v>21.673895040000001</v>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2869,7 +2869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3723,24 +3723,14 @@
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="22">
-        <v>46170</v>
-      </c>
-      <c r="B47" s="18">
-        <v>38032.045118000002</v>
-      </c>
+      <c r="A47" s="22"/>
+      <c r="B47" s="18"/>
       <c r="C47" s="21"/>
-      <c r="D47" s="18">
-        <v>300</v>
-      </c>
+      <c r="D47" s="18"/>
       <c r="E47" s="21"/>
-      <c r="F47" s="18">
-        <v>330</v>
-      </c>
+      <c r="F47" s="18"/>
       <c r="G47" s="21"/>
-      <c r="H47" s="18">
-        <v>311.49</v>
-      </c>
+      <c r="H47" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3750,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3779,14 +3769,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>45074</v>
+        <v>46169</v>
       </c>
       <c r="B2" s="25">
-        <v>9253.9873366299998</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C3" si="0">+((B2-B3)/B3)</f>
-        <v>425.96466507526281</v>
+        <f>+((B2-B3)/B3)</f>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3797,14 +3787,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B3" s="25">
-        <v>21.673895040000001</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C3" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <f>+((B3-B4)/B4)</f>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3815,14 +3805,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B4" s="25">
-        <v>8513.9651106900001</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C4" s="31">
         <f>+((B4-B5)/B5)</f>
-        <v>-0.31892665326814518</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3833,14 +3823,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B5" s="25">
-        <v>12500.80501835</v>
+        <v>58837.242479</v>
       </c>
       <c r="C5" s="31">
         <f>+((B5-B6)/B6)</f>
-        <v>-0.78753584478722383</v>
+        <v>1063.8095709311931</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3851,323 +3841,322 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B6" s="25">
-        <v>58837.242479</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C6" s="31">
-        <f>+((B6-B7)/B7)</f>
-        <v>1063.8095709311931</v>
+        <f>+((B10-B11)/B11)</f>
+        <v>82.182099964255912</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B7" s="25">
-        <v>55.256117230000001</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C7" s="31">
-        <f>+((B11-B12)/B12)</f>
-        <v>82.182099964255912</v>
+        <f t="shared" ref="C7:C30" si="0">+((B11-B12)/B12)</f>
+        <v>-0.96342609797465562</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B8" s="25">
-        <v>20356.468143580001</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C8" s="31">
-        <f t="shared" ref="C8:C31" si="1">+((B12-B13)/B13)</f>
-        <v>-0.96342609797465562</v>
+        <f t="shared" si="0"/>
+        <v>-0.95811572537747924</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B9" s="25">
-        <v>72301.933723569993</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C9" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.95811572537747924</v>
+        <f t="shared" si="0"/>
+        <v>-0.32064889280191988</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B10" s="25">
-        <v>74209.813271849998</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C10" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.32064889280191988</v>
+        <f t="shared" si="0"/>
+        <v>178.18998455533497</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B11" s="25">
-        <v>2047.5163407099999</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C11" s="31">
-        <f t="shared" si="1"/>
-        <v>178.18998455533497</v>
+        <f t="shared" si="0"/>
+        <v>-0.82294618034282907</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B12" s="25">
-        <v>24.614867159999999</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C12" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.82294618034282907</v>
+        <f t="shared" si="0"/>
+        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B13" s="25">
-        <v>673.01725538999995</v>
+        <v>16068.49495319</v>
       </c>
       <c r="C13" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.99115816107458954</v>
+        <f t="shared" si="0"/>
+        <v>0.70107388483787059</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="B14" s="25">
-        <v>16068.49495319</v>
+        <v>23652.710333340001</v>
       </c>
       <c r="C14" s="31">
-        <f t="shared" si="1"/>
-        <v>0.70107388483787059</v>
+        <f t="shared" si="0"/>
+        <v>-0.43255825515735763</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="26">
-        <v>46150</v>
-      </c>
-      <c r="B15" s="25">
-        <v>23652.710333340001</v>
+      <c r="A15" s="24">
+        <v>46149</v>
+      </c>
+      <c r="B15" s="23">
+        <v>131.99794839</v>
       </c>
       <c r="C15" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.43255825515735763</v>
+        <f t="shared" si="0"/>
+        <v>2.0773664296544805</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B16" s="23">
-        <v>131.99794839</v>
+      <c r="A16" s="19">
+        <v>46148</v>
+      </c>
+      <c r="B16" s="17">
+        <v>745.52443231999996</v>
       </c>
       <c r="C16" s="31">
-        <f t="shared" si="1"/>
-        <v>2.0773664296544805</v>
+        <f t="shared" si="0"/>
+        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="19">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B17" s="17">
-        <v>745.52443231999996</v>
+        <v>84317.802960360001</v>
       </c>
       <c r="C17" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.59636256133262866</v>
+        <f t="shared" si="0"/>
+        <v>0.74333012643706198</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="19">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B18" s="17">
-        <v>84317.802960360001</v>
+        <v>49567.396050169998</v>
       </c>
       <c r="C18" s="31">
-        <f t="shared" si="1"/>
-        <v>0.74333012643706198</v>
+        <f t="shared" si="0"/>
+        <v>-0.33842006324553126</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="19">
-        <v>46146</v>
+      <c r="A19" s="20">
+        <v>46142</v>
       </c>
       <c r="B19" s="17">
-        <v>49567.396050169998</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C19" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.33842006324553126</v>
+        <f t="shared" si="0"/>
+        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="B20" s="17">
-        <v>87352.396084139997</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C20" s="31">
-        <f t="shared" si="1"/>
-        <v>12.106463903543759</v>
+        <f t="shared" si="0"/>
+        <v>-0.73032401489373799</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="B21" s="17">
-        <v>28385.438679769999</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C21" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.73032401489373799</v>
+        <f t="shared" si="0"/>
+        <v>-0.64046760511667533</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="B22" s="17">
-        <v>70324.097718699995</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C22" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.64046760511667533</v>
+        <f t="shared" si="0"/>
+        <v>-6.5402088492716129E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="B23" s="17">
-        <v>40338.944788629997</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C23" s="31">
-        <f t="shared" si="1"/>
-        <v>-6.5402088492716129E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.9819948129202027</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="B24" s="17">
-        <v>60973.651931649998</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C24" s="31">
-        <f t="shared" si="1"/>
-        <v>1.9819948129202027</v>
+        <f t="shared" si="0"/>
+        <v>910.40237411852581</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="B25" s="17">
-        <v>4652.1817311200002</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C25" s="31">
-        <f t="shared" si="1"/>
-        <v>910.40237411852581</v>
+        <f t="shared" si="0"/>
+        <v>0.19572063797541306</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46134</v>
+        <v>46133</v>
       </c>
       <c r="B26" s="17">
-        <v>17251.00486529</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C26" s="31">
-        <f t="shared" si="1"/>
-        <v>0.19572063797541306</v>
+        <f t="shared" si="0"/>
+        <v>-2.5764893835585476E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="B27" s="17">
-        <v>47981.781644150004</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C27" s="31">
-        <f t="shared" si="1"/>
-        <v>-2.5764893835585476E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.99344926580920656</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46132</v>
+        <v>46129</v>
       </c>
       <c r="B28" s="17">
-        <v>51339.49161813</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C28" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.99344926580920656</v>
+        <f t="shared" si="0"/>
+        <v>-0.68887087467151309</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="B29" s="17">
-        <v>17216.492596060001</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C29" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.68887087467151309</v>
+        <f t="shared" si="0"/>
+        <v>190.54886991293833</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="B30" s="17">
-        <v>18.890111640000001</v>
+        <v>15.79809785</v>
       </c>
       <c r="C30" s="31">
-        <f t="shared" si="1"/>
-        <v>190.54886991293833</v>
+        <f t="shared" si="0"/>
+        <v>-0.92845434694034024</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="B31" s="17">
-        <v>15.79809785</v>
-      </c>
-      <c r="C31" s="31">
-        <f t="shared" si="1"/>
-        <v>-0.92845434694034024</v>
+        <v>16.215898760000002</v>
+      </c>
+      <c r="C31" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B32" s="17">
-        <v>16.215898760000002</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4175,10 +4164,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="B33" s="17">
-        <v>2475.4322626600001</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4186,10 +4175,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="B34" s="17">
-        <v>7956.2858669899997</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4197,10 +4186,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="B35" s="17">
-        <v>41.536584740000002</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4208,10 +4197,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="B36" s="17">
-        <v>580.56056466999996</v>
+        <v>116.97186189</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4219,44 +4208,33 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46119</v>
+        <v>46118</v>
       </c>
       <c r="B37" s="17">
-        <v>116.97186189</v>
-      </c>
-      <c r="C37" s="16">
-        <v>0</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46118</v>
+        <v>46113</v>
       </c>
       <c r="B38" s="17">
-        <v>6972.36861443</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B39" s="17">
-        <v>540.00852741999995</v>
+        <v>5262.3389565099997</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B40" s="17">
-        <v>5262.3389565099997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="20">
-        <v>46111</v>
-      </c>
-      <c r="B41" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -5367,25 +5345,12 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="26">
-        <v>46169</v>
-      </c>
-      <c r="B27" s="27">
-        <v>12914</v>
-      </c>
-      <c r="C27" s="25">
-        <v>3</v>
-      </c>
-      <c r="D27" s="27">
-        <v>12917</v>
-      </c>
-      <c r="E27" s="32">
-        <f>+((D27-D26)/D26)</f>
-        <v>-3.625424251774144E-3</v>
-      </c>
-      <c r="F27" s="33">
-        <v>9.1234560000000006E-2</v>
-      </c>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2869,7 +2869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3723,14 +3723,24 @@
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="22"/>
-      <c r="B47" s="18"/>
+      <c r="A47" s="22">
+        <v>46170</v>
+      </c>
+      <c r="B47" s="18">
+        <v>38032.045118000002</v>
+      </c>
       <c r="C47" s="21"/>
-      <c r="D47" s="18"/>
+      <c r="D47" s="18">
+        <v>300</v>
+      </c>
       <c r="E47" s="21"/>
-      <c r="F47" s="18"/>
+      <c r="F47" s="18">
+        <v>330</v>
+      </c>
       <c r="G47" s="21"/>
-      <c r="H47" s="18"/>
+      <c r="H47" s="18">
+        <v>311.49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3740,7 +3750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3769,14 +3779,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B2" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C2" s="31">
-        <f>+((B2-B3)/B3)</f>
-        <v>-0.99745431244335425</v>
+        <f t="shared" ref="C2:C3" si="0">+((B2-B3)/B3)</f>
+        <v>425.96466507526281</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3787,14 +3797,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B3" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C3" s="31">
-        <f>+((B3-B4)/B4)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3805,14 +3815,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B4" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C4" s="31">
         <f>+((B4-B5)/B5)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3823,14 +3833,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B5" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C5" s="31">
         <f>+((B5-B6)/B6)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3841,322 +3851,323 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B6" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C6" s="31">
-        <f>+((B10-B11)/B11)</f>
-        <v>82.182099964255912</v>
+        <f>+((B6-B7)/B7)</f>
+        <v>1063.8095709311931</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B7" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C7" s="31">
-        <f t="shared" ref="C7:C30" si="0">+((B11-B12)/B12)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B11-B12)/B12)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B8" s="25">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C8" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.95811572537747924</v>
+        <f t="shared" ref="C8:C31" si="1">+((B12-B13)/B13)</f>
+        <v>-0.96342609797465562</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B9" s="25">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C9" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.32064889280191988</v>
+        <f t="shared" si="1"/>
+        <v>-0.95811572537747924</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B10" s="25">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C10" s="31">
-        <f t="shared" si="0"/>
-        <v>178.18998455533497</v>
+        <f t="shared" si="1"/>
+        <v>-0.32064889280191988</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B11" s="25">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C11" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.82294618034282907</v>
+        <f t="shared" si="1"/>
+        <v>178.18998455533497</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B12" s="25">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C12" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99115816107458954</v>
+        <f t="shared" si="1"/>
+        <v>-0.82294618034282907</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B13" s="25">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C13" s="31">
-        <f t="shared" si="0"/>
-        <v>0.70107388483787059</v>
+        <f t="shared" si="1"/>
+        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
+        <v>46153</v>
+      </c>
+      <c r="B14" s="25">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C14" s="31">
+        <f t="shared" si="1"/>
+        <v>0.70107388483787059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46150</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C14" s="31">
-        <f t="shared" si="0"/>
+      <c r="C15" s="31">
+        <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46149</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C15" s="31">
-        <f t="shared" si="0"/>
+      <c r="C16" s="31">
+        <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B16" s="17">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C16" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="19">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B17" s="17">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C17" s="31">
-        <f t="shared" si="0"/>
-        <v>0.74333012643706198</v>
+        <f t="shared" si="1"/>
+        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="19">
+        <v>46147</v>
+      </c>
+      <c r="B18" s="17">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C18" s="31">
+        <f t="shared" si="1"/>
+        <v>0.74333012643706198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="19">
         <v>46146</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C18" s="31">
-        <f t="shared" si="0"/>
+      <c r="C19" s="31">
+        <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="20">
-        <v>46142</v>
-      </c>
-      <c r="B19" s="17">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C19" s="31">
-        <f t="shared" si="0"/>
-        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="20">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B20" s="17">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C20" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.73032401489373799</v>
+        <f t="shared" si="1"/>
+        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="20">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B21" s="17">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C21" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.64046760511667533</v>
+        <f t="shared" si="1"/>
+        <v>-0.73032401489373799</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="20">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B22" s="17">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C22" s="31">
-        <f t="shared" si="0"/>
-        <v>-6.5402088492716129E-2</v>
+        <f t="shared" si="1"/>
+        <v>-0.64046760511667533</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="20">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B23" s="17">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C23" s="31">
-        <f t="shared" si="0"/>
-        <v>1.9819948129202027</v>
+        <f t="shared" si="1"/>
+        <v>-6.5402088492716129E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="20">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B24" s="17">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C24" s="31">
-        <f t="shared" si="0"/>
-        <v>910.40237411852581</v>
+        <f t="shared" si="1"/>
+        <v>1.9819948129202027</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="20">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B25" s="17">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C25" s="31">
-        <f t="shared" si="0"/>
-        <v>0.19572063797541306</v>
+        <f t="shared" si="1"/>
+        <v>910.40237411852581</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="20">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B26" s="17">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C26" s="31">
-        <f t="shared" si="0"/>
-        <v>-2.5764893835585476E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.19572063797541306</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="20">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B27" s="17">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C27" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99344926580920656</v>
+        <f t="shared" si="1"/>
+        <v>-2.5764893835585476E-2</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="20">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B28" s="17">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C28" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.68887087467151309</v>
+        <f t="shared" si="1"/>
+        <v>-0.99344926580920656</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="20">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B29" s="17">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C29" s="31">
-        <f t="shared" si="0"/>
-        <v>190.54886991293833</v>
+        <f t="shared" si="1"/>
+        <v>-0.68887087467151309</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="20">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B30" s="17">
-        <v>15.79809785</v>
+        <v>18.890111640000001</v>
       </c>
       <c r="C30" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.92845434694034024</v>
+        <f t="shared" si="1"/>
+        <v>190.54886991293833</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B31" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C31" s="16">
-        <v>0</v>
+        <v>15.79809785</v>
+      </c>
+      <c r="C31" s="31">
+        <f t="shared" si="1"/>
+        <v>-0.92845434694034024</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B32" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4164,10 +4175,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B33" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4175,10 +4186,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B34" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4186,10 +4197,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B35" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4197,10 +4208,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B36" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4208,33 +4219,44 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B37" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C37" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B38" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B39" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B40" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="20">
         <v>46111</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B41" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -5345,12 +5367,25 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33"/>
+      <c r="A27" s="26">
+        <v>46169</v>
+      </c>
+      <c r="B27" s="27">
+        <v>12914</v>
+      </c>
+      <c r="C27" s="25">
+        <v>3</v>
+      </c>
+      <c r="D27" s="27">
+        <v>12917</v>
+      </c>
+      <c r="E27" s="32">
+        <f>+((D27-D26)/D26)</f>
+        <v>-3.625424251774144E-3</v>
+      </c>
+      <c r="F27" s="33">
+        <v>-0.36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2869,7 +2869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2877,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3742,6 +3742,26 @@
         <v>311.49</v>
       </c>
     </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="22">
+        <v>46171</v>
+      </c>
+      <c r="B48" s="18">
+        <v>45546.404509</v>
+      </c>
+      <c r="C48" s="21"/>
+      <c r="D48" s="18">
+        <v>100</v>
+      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="18">
+        <v>120</v>
+      </c>
+      <c r="G48" s="21"/>
+      <c r="H48" s="18">
+        <v>107.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3750,7 +3770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3779,14 +3799,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B2" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C3" si="0">+((B2-B3)/B3)</f>
-        <v>425.96466507526281</v>
+        <f t="shared" ref="C2:C4" si="0">+((B2-B3)/B3)</f>
+        <v>2.616728100871637</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3797,14 +3817,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B3" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3815,14 +3835,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B4" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C4" s="31">
-        <f>+((B4-B5)/B5)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3833,14 +3853,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B5" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C5" s="31">
         <f>+((B5-B6)/B6)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3851,334 +3871,335 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B6" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C6" s="31">
         <f>+((B6-B7)/B7)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B7" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C7" s="31">
-        <f>+((B11-B12)/B12)</f>
-        <v>82.182099964255912</v>
+        <f>+((B7-B8)/B8)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B8" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C8" s="31">
-        <f t="shared" ref="C8:C31" si="1">+((B12-B13)/B13)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B12-B13)/B13)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B9" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C9" s="31">
+        <f t="shared" ref="C9:C32" si="1">+((B13-B14)/B14)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="26">
         <v>46161</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B10" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="26">
+    <row r="11" spans="1:5">
+      <c r="A11" s="26">
         <v>46157</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B11" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C11" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46156</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46155</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46154</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46153</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46150</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    <row r="17" spans="1:3">
+      <c r="A17" s="24">
         <v>46149</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="19">
+    <row r="18" spans="1:3">
+      <c r="A18" s="19">
         <v>46148</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B18" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="19">
+    <row r="19" spans="1:3">
+      <c r="A19" s="19">
         <v>46147</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="19">
+    <row r="20" spans="1:3">
+      <c r="A20" s="19">
         <v>46146</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="20">
+    <row r="21" spans="1:3">
+      <c r="A21" s="20">
         <v>46142</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="20">
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46141</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46140</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46139</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46136</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46135</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46134</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46133</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46132</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46129</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46128</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46127</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B32" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C32" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="33" spans="1:3">
       <c r="A33" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B33" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4186,10 +4207,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B34" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4197,10 +4218,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B35" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4208,10 +4229,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B36" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4219,10 +4240,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B37" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4230,33 +4251,44 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B38" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C38" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B39" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B40" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B41" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="20">
         <v>46111</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B42" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4540,8 +4572,17 @@
         <v>12.607640378286277</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="26"/>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="26">
+        <v>46164</v>
+      </c>
+      <c r="B17" s="18">
+        <v>1440966613.4014599</v>
+      </c>
+      <c r="C17" s="4">
+        <f>+((B17-B16)/B16)*100</f>
+        <v>19.42084705352627</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4550,7 +4591,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -4801,6 +4842,32 @@
         <v>10.599394315551303</v>
       </c>
     </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="26">
+        <v>46164</v>
+      </c>
+      <c r="B10" s="18">
+        <v>59297253.722750016</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1756395281.4472902</v>
+      </c>
+      <c r="D10" s="18">
+        <v>146574089.18363994</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1962266624.3536801</v>
+      </c>
+      <c r="F10" s="18">
+        <v>1598030.6558000003</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1963864655.0094802</v>
+      </c>
+      <c r="H10" s="28">
+        <v>0.72884568936828487</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4808,7 +4875,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5387,6 +5454,27 @@
         <v>-0.36</v>
       </c>
     </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="26">
+        <v>46170</v>
+      </c>
+      <c r="B28" s="27">
+        <v>12758</v>
+      </c>
+      <c r="C28" s="25">
+        <v>3</v>
+      </c>
+      <c r="D28" s="27">
+        <v>12761</v>
+      </c>
+      <c r="E28" s="32">
+        <f>+((D28-D27)/D27)</f>
+        <v>-1.2077107687543547E-2</v>
+      </c>
+      <c r="F28" s="33">
+        <v>-1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>DÍA</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAYO</t>
   </si>
 </sst>
 </file>
@@ -2869,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4300,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -4377,6 +4380,20 @@
       </c>
       <c r="D5" s="8">
         <v>64.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="18">
+        <v>251306.31</v>
+      </c>
+      <c r="C6" s="18">
+        <v>13226.65</v>
+      </c>
+      <c r="D6">
+        <v>188.96</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="2"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3765,6 +3765,26 @@
         <v>107.95</v>
       </c>
     </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="22">
+        <v>46174</v>
+      </c>
+      <c r="B49" s="18">
+        <v>0</v>
+      </c>
+      <c r="C49" s="21"/>
+      <c r="D49" s="18">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="18">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21"/>
+      <c r="H49" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3773,7 +3793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3802,14 +3822,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C4" si="0">+((B2-B3)/B3)</f>
-        <v>2.616728100871637</v>
+        <f t="shared" ref="C2:C5" si="0">+((B2-B3)/B3)</f>
+        <v>-0.99834811895033015</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3820,14 +3840,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B3" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3838,14 +3858,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B4" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3856,14 +3876,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B5" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C5" s="31">
-        <f>+((B5-B6)/B6)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3874,346 +3894,347 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B6" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C6" s="31">
         <f>+((B6-B7)/B7)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B7" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C7" s="31">
         <f>+((B7-B8)/B8)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B8" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C8" s="31">
-        <f>+((B12-B13)/B13)</f>
-        <v>82.182099964255912</v>
+        <f>+((B8-B9)/B9)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B9" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C9" s="31">
-        <f t="shared" ref="C9:C32" si="1">+((B13-B14)/B14)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B13-B14)/B14)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B10" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C10" s="31">
+        <f t="shared" ref="C10:C33" si="1">+((B14-B15)/B15)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="26">
         <v>46161</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B11" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C11" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46157</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46156</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46155</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46154</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46153</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46150</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="24">
+    <row r="18" spans="1:3">
+      <c r="A18" s="24">
         <v>46149</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="19">
+    <row r="19" spans="1:3">
+      <c r="A19" s="19">
         <v>46148</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B19" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="19">
+    <row r="20" spans="1:3">
+      <c r="A20" s="19">
         <v>46147</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="19">
+    <row r="21" spans="1:3">
+      <c r="A21" s="19">
         <v>46146</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="20">
+    <row r="22" spans="1:3">
+      <c r="A22" s="20">
         <v>46142</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46141</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46140</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46139</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46136</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46135</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46134</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46133</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46132</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46129</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46128</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46127</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B33" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C33" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="34" spans="1:3">
       <c r="A34" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B34" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4221,10 +4242,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B35" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4232,10 +4253,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B36" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4243,10 +4264,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B37" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4254,10 +4275,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B38" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -4265,33 +4286,44 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B39" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C39" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B40" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B41" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B42" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="20">
         <v>46111</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B43" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4892,7 +4924,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5492,6 +5524,27 @@
         <v>-1.21</v>
       </c>
     </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="26">
+        <v>46171</v>
+      </c>
+      <c r="B29" s="27">
+        <v>12968</v>
+      </c>
+      <c r="C29" s="25">
+        <v>3</v>
+      </c>
+      <c r="D29" s="27">
+        <v>12971</v>
+      </c>
+      <c r="E29" s="32">
+        <f>+((D29-D28)/D28)</f>
+        <v>1.6456390565002744E-2</v>
+      </c>
+      <c r="F29" s="33">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3785,6 +3785,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="22">
+        <v>46175</v>
+      </c>
+      <c r="B50" s="18">
+        <v>0</v>
+      </c>
+      <c r="C50" s="21"/>
+      <c r="D50" s="18">
+        <v>0</v>
+      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="18">
+        <v>0</v>
+      </c>
+      <c r="G50" s="21"/>
+      <c r="H50" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3793,7 +3813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3822,14 +3842,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B2" s="25">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C5" si="0">+((B2-B3)/B3)</f>
-        <v>-0.99834811895033015</v>
+        <f t="shared" ref="C2:C6" si="0">+((B2-B3)/B3)</f>
+        <v>539.15459406063144</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3840,14 +3860,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>2.616728100871637</v>
+        <v>-0.99834811895033015</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3858,14 +3878,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B4" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3876,14 +3896,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B5" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3894,358 +3914,359 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B6" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C6" s="31">
-        <f>+((B6-B7)/B7)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B7" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C7" s="31">
         <f>+((B7-B8)/B8)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B8" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C8" s="31">
         <f>+((B8-B9)/B9)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B9" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C9" s="31">
-        <f>+((B13-B14)/B14)</f>
-        <v>82.182099964255912</v>
+        <f>+((B9-B10)/B10)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B10" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C10" s="31">
-        <f t="shared" ref="C10:C33" si="1">+((B14-B15)/B15)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B14-B15)/B15)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B11" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C11" s="31">
+        <f t="shared" ref="C11:C34" si="1">+((B15-B16)/B16)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="26">
         <v>46161</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C12" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46157</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46156</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46155</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46154</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46153</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
+    <row r="18" spans="1:3">
+      <c r="A18" s="26">
         <v>46150</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B18" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="24">
+    <row r="19" spans="1:3">
+      <c r="A19" s="24">
         <v>46149</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="19">
+    <row r="20" spans="1:3">
+      <c r="A20" s="19">
         <v>46148</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B20" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="19">
+    <row r="21" spans="1:3">
+      <c r="A21" s="19">
         <v>46147</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="19">
+    <row r="22" spans="1:3">
+      <c r="A22" s="19">
         <v>46146</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="20">
+    <row r="23" spans="1:3">
+      <c r="A23" s="20">
         <v>46142</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46141</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46140</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46139</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46136</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46135</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46134</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46133</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46132</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46129</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46128</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46127</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B34" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C34" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="35" spans="1:3">
       <c r="A35" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B35" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C35" s="16">
         <v>0</v>
@@ -4253,10 +4274,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B36" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4264,10 +4285,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B37" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4275,10 +4296,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B38" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -4286,10 +4307,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B39" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4297,33 +4318,44 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B40" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C40" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B41" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B42" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B43" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="20">
         <v>46111</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B44" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4924,7 +4956,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5545,6 +5577,27 @@
         <v>1.65</v>
       </c>
     </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="26">
+        <v>46174</v>
+      </c>
+      <c r="B30" s="27">
+        <v>12916</v>
+      </c>
+      <c r="C30" s="25">
+        <v>3</v>
+      </c>
+      <c r="D30" s="27">
+        <v>12919</v>
+      </c>
+      <c r="E30" s="32">
+        <f>+((D30-D29)/D29)</f>
+        <v>-4.0089430267519852E-3</v>
+      </c>
+      <c r="F30" s="33">
+        <v>-0.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3805,6 +3805,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="22">
+        <v>46176</v>
+      </c>
+      <c r="B51" s="18">
+        <v>0</v>
+      </c>
+      <c r="C51" s="21"/>
+      <c r="D51" s="18">
+        <v>0</v>
+      </c>
+      <c r="E51" s="21"/>
+      <c r="F51" s="18">
+        <v>0</v>
+      </c>
+      <c r="G51" s="21"/>
+      <c r="H51" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3813,7 +3833,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3842,14 +3862,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B2" s="25">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C6" si="0">+((B2-B3)/B3)</f>
-        <v>539.15459406063144</v>
+        <f t="shared" ref="C2:C7" si="0">+((B2-B3)/B3)</f>
+        <v>-0.88947445735006914</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3860,14 +3880,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B3" s="25">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99834811895033015</v>
+        <v>539.15459406063144</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3878,14 +3898,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>2.616728100871637</v>
+        <v>-0.99834811895033015</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3896,14 +3916,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B5" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3914,370 +3934,371 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B6" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B7" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C7" s="31">
-        <f>+((B7-B8)/B8)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B8" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C8" s="31">
         <f>+((B8-B9)/B9)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B9" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C9" s="31">
         <f>+((B9-B10)/B10)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B10" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C10" s="31">
-        <f>+((B14-B15)/B15)</f>
-        <v>82.182099964255912</v>
+        <f>+((B10-B11)/B11)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B11" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C11" s="31">
-        <f t="shared" ref="C11:C34" si="1">+((B15-B16)/B16)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B15-B16)/B16)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B12" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C12" s="31">
+        <f t="shared" ref="C12:C35" si="1">+((B16-B17)/B17)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="26">
         <v>46161</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B13" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C13" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46157</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46156</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46155</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46154</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
+    <row r="18" spans="1:3">
+      <c r="A18" s="26">
         <v>46153</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B18" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26">
+    <row r="19" spans="1:3">
+      <c r="A19" s="26">
         <v>46150</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B19" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="24">
+    <row r="20" spans="1:3">
+      <c r="A20" s="24">
         <v>46149</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="19">
+    <row r="21" spans="1:3">
+      <c r="A21" s="19">
         <v>46148</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B21" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="19">
+    <row r="22" spans="1:3">
+      <c r="A22" s="19">
         <v>46147</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="19">
+    <row r="23" spans="1:3">
+      <c r="A23" s="19">
         <v>46146</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="20">
+    <row r="24" spans="1:3">
+      <c r="A24" s="20">
         <v>46142</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46141</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46140</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46139</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46136</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46135</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46134</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46133</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46132</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46129</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46128</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="20">
+    <row r="35" spans="1:3">
+      <c r="A35" s="20">
         <v>46127</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B35" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B35" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C35" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="36" spans="1:3">
       <c r="A36" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B36" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4285,10 +4306,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B37" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4296,10 +4317,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B38" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -4307,10 +4328,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B39" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4318,10 +4339,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B40" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -4329,33 +4350,44 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B41" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C41" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B42" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B43" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B44" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="20">
         <v>46111</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B45" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4956,7 +4988,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5486,7 +5518,7 @@
         <v>12952</v>
       </c>
       <c r="E25" s="32">
-        <f>+((D25-D24)/D24)</f>
+        <f t="shared" ref="E25:E31" si="3">+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
@@ -5507,7 +5539,7 @@
         <v>12964</v>
       </c>
       <c r="E26" s="32">
-        <f>+((D26-D25)/D25)</f>
+        <f t="shared" si="3"/>
         <v>9.2649783817171094E-4</v>
       </c>
       <c r="F26" s="33">
@@ -5528,7 +5560,7 @@
         <v>12917</v>
       </c>
       <c r="E27" s="32">
-        <f>+((D27-D26)/D26)</f>
+        <f t="shared" si="3"/>
         <v>-3.625424251774144E-3</v>
       </c>
       <c r="F27" s="33">
@@ -5549,7 +5581,7 @@
         <v>12761</v>
       </c>
       <c r="E28" s="32">
-        <f>+((D28-D27)/D27)</f>
+        <f t="shared" si="3"/>
         <v>-1.2077107687543547E-2</v>
       </c>
       <c r="F28" s="33">
@@ -5570,7 +5602,7 @@
         <v>12971</v>
       </c>
       <c r="E29" s="32">
-        <f>+((D29-D28)/D28)</f>
+        <f t="shared" si="3"/>
         <v>1.6456390565002744E-2</v>
       </c>
       <c r="F29" s="33">
@@ -5591,11 +5623,32 @@
         <v>12919</v>
       </c>
       <c r="E30" s="32">
-        <f>+((D30-D29)/D29)</f>
+        <f t="shared" si="3"/>
         <v>-4.0089430267519852E-3</v>
       </c>
       <c r="F30" s="33">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="26">
+        <v>46175</v>
+      </c>
+      <c r="B31" s="27">
+        <v>12982</v>
+      </c>
+      <c r="C31" s="25">
+        <v>3</v>
+      </c>
+      <c r="D31" s="27">
+        <v>12985</v>
+      </c>
+      <c r="E31" s="32">
+        <f t="shared" si="3"/>
+        <v>5.1087545475656014E-3</v>
+      </c>
+      <c r="F31" s="33">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="1"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3825,6 +3825,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="22">
+        <v>46177</v>
+      </c>
+      <c r="B52" s="18">
+        <v>200</v>
+      </c>
+      <c r="C52" s="21"/>
+      <c r="D52" s="18">
+        <v>150</v>
+      </c>
+      <c r="E52" s="21"/>
+      <c r="F52" s="18">
+        <v>150</v>
+      </c>
+      <c r="G52" s="21"/>
+      <c r="H52" s="18">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3833,7 +3853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3862,14 +3882,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B2" s="25">
-        <v>3300.6863896099999</v>
+        <v>9350.0363108799993</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C7" si="0">+((B2-B3)/B3)</f>
-        <v>-0.88947445735006914</v>
+        <f t="shared" ref="C2:C8" si="0">+((B2-B3)/B3)</f>
+        <v>1.8327551324816331</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3880,14 +3900,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B3" s="25">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>539.15459406063144</v>
+        <v>-0.88947445735006914</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3898,14 +3918,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B4" s="25">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99834811895033015</v>
+        <v>539.15459406063144</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3916,14 +3936,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>2.616728100871637</v>
+        <v>-0.99834811895033015</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3934,382 +3954,383 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B6" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B7" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B8" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C8" s="31">
-        <f>+((B8-B9)/B9)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B9" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C9" s="31">
         <f>+((B9-B10)/B10)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B10" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C10" s="31">
         <f>+((B10-B11)/B11)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B11" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C11" s="31">
-        <f>+((B15-B16)/B16)</f>
-        <v>82.182099964255912</v>
+        <f>+((B11-B12)/B12)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B12" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C12" s="31">
-        <f t="shared" ref="C12:C35" si="1">+((B16-B17)/B17)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B16-B17)/B17)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B13" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C13" s="31">
+        <f t="shared" ref="C13:C36" si="1">+((B17-B18)/B18)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="26">
         <v>46161</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B14" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46157</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46156</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46155</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
+    <row r="18" spans="1:3">
+      <c r="A18" s="26">
         <v>46154</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B18" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26">
+    <row r="19" spans="1:3">
+      <c r="A19" s="26">
         <v>46153</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B19" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="26">
+    <row r="20" spans="1:3">
+      <c r="A20" s="26">
         <v>46150</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B20" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="24">
+    <row r="21" spans="1:3">
+      <c r="A21" s="24">
         <v>46149</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="19">
+    <row r="22" spans="1:3">
+      <c r="A22" s="19">
         <v>46148</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B22" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="19">
+    <row r="23" spans="1:3">
+      <c r="A23" s="19">
         <v>46147</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="19">
+    <row r="24" spans="1:3">
+      <c r="A24" s="19">
         <v>46146</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="20">
+    <row r="25" spans="1:3">
+      <c r="A25" s="20">
         <v>46142</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46141</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46140</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46139</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46136</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46135</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46134</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46133</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46132</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46129</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="20">
+    <row r="35" spans="1:3">
+      <c r="A35" s="20">
         <v>46128</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B35" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="20">
+    <row r="36" spans="1:3">
+      <c r="A36" s="20">
         <v>46127</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B36" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B36" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C36" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="37" spans="1:3">
       <c r="A37" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B37" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4317,10 +4338,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B38" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -4328,10 +4349,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B39" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4339,10 +4360,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B40" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -4350,10 +4371,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B41" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -4361,33 +4382,44 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B42" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C42" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B43" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B44" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B45" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="20">
         <v>46111</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B46" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4988,7 +5020,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5518,7 +5550,7 @@
         <v>12952</v>
       </c>
       <c r="E25" s="32">
-        <f t="shared" ref="E25:E31" si="3">+((D25-D24)/D24)</f>
+        <f t="shared" ref="E25:E32" si="3">+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
@@ -5649,6 +5681,27 @@
       </c>
       <c r="F31" s="33">
         <v>0.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="26">
+        <v>46176</v>
+      </c>
+      <c r="B32" s="27">
+        <v>12852</v>
+      </c>
+      <c r="C32" s="25">
+        <v>3</v>
+      </c>
+      <c r="D32" s="27">
+        <v>12855</v>
+      </c>
+      <c r="E32" s="32">
+        <f t="shared" si="3"/>
+        <v>-1.0011551790527531E-2</v>
+      </c>
+      <c r="F32" s="33">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3845,6 +3845,26 @@
         <v>150</v>
       </c>
     </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="22">
+        <v>46178</v>
+      </c>
+      <c r="B53" s="18">
+        <v>10878.022664</v>
+      </c>
+      <c r="C53" s="21"/>
+      <c r="D53" s="18">
+        <v>50</v>
+      </c>
+      <c r="E53" s="21"/>
+      <c r="F53" s="18">
+        <v>50</v>
+      </c>
+      <c r="G53" s="21"/>
+      <c r="H53" s="18">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3853,7 +3873,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3882,14 +3902,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B2" s="25">
-        <v>9350.0363108799993</v>
+        <v>58292.928576159997</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C8" si="0">+((B2-B3)/B3)</f>
-        <v>1.8327551324816331</v>
+        <f t="shared" ref="C2:C9" si="0">+((B2-B3)/B3)</f>
+        <v>5.2345136037951523</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3900,14 +3920,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B3" s="25">
-        <v>3300.6863896099999</v>
+        <v>9350.0363108799993</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>-0.88947445735006914</v>
+        <v>1.8327551324816331</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3918,14 +3938,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B4" s="25">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>539.15459406063144</v>
+        <v>-0.88947445735006914</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3936,14 +3956,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B5" s="25">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99834811895033015</v>
+        <v>539.15459406063144</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3954,394 +3974,395 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B6" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>2.616728100871637</v>
+        <v>-0.99834811895033015</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B7" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B8" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B9" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C9" s="31">
-        <f>+((B9-B10)/B10)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B10" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C10" s="31">
         <f>+((B10-B11)/B11)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B11" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C11" s="31">
         <f>+((B11-B12)/B12)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B12" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C12" s="31">
-        <f>+((B16-B17)/B17)</f>
-        <v>82.182099964255912</v>
+        <f>+((B12-B13)/B13)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B13" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C13" s="31">
-        <f t="shared" ref="C13:C36" si="1">+((B17-B18)/B18)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B17-B18)/B18)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B14" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C14" s="31">
+        <f t="shared" ref="C14:C37" si="1">+((B18-B19)/B19)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="26">
         <v>46161</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B15" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C15" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46157</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46156</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
+    <row r="18" spans="1:3">
+      <c r="A18" s="26">
         <v>46155</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B18" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26">
+    <row r="19" spans="1:3">
+      <c r="A19" s="26">
         <v>46154</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B19" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="26">
+    <row r="20" spans="1:3">
+      <c r="A20" s="26">
         <v>46153</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B20" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="26">
+    <row r="21" spans="1:3">
+      <c r="A21" s="26">
         <v>46150</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B21" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="24">
+    <row r="22" spans="1:3">
+      <c r="A22" s="24">
         <v>46149</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="19">
+    <row r="23" spans="1:3">
+      <c r="A23" s="19">
         <v>46148</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B23" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="19">
+    <row r="24" spans="1:3">
+      <c r="A24" s="19">
         <v>46147</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="19">
+    <row r="25" spans="1:3">
+      <c r="A25" s="19">
         <v>46146</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="20">
+    <row r="26" spans="1:3">
+      <c r="A26" s="20">
         <v>46142</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46141</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46140</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46139</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46136</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46135</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46134</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46133</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46132</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="20">
+    <row r="35" spans="1:3">
+      <c r="A35" s="20">
         <v>46129</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B35" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="20">
+    <row r="36" spans="1:3">
+      <c r="A36" s="20">
         <v>46128</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B36" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="20">
+    <row r="37" spans="1:3">
+      <c r="A37" s="20">
         <v>46127</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B37" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C37" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B37" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C37" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="38" spans="1:3">
       <c r="A38" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B38" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C38" s="16">
         <v>0</v>
@@ -4349,10 +4370,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B39" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4360,10 +4381,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B40" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -4371,10 +4392,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B41" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -4382,10 +4403,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B42" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C42" s="16">
         <v>0</v>
@@ -4393,33 +4414,44 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B43" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C43" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B44" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B45" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B46" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="20">
         <v>46111</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B47" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -4736,7 +4768,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5013,6 +5045,32 @@
         <v>0.72884568936828487</v>
       </c>
     </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="26">
+        <v>46202</v>
+      </c>
+      <c r="B11" s="18">
+        <v>61835356.210640013</v>
+      </c>
+      <c r="C11" s="18">
+        <v>1886607672.3299406</v>
+      </c>
+      <c r="D11" s="18">
+        <v>163572012.59929004</v>
+      </c>
+      <c r="E11" s="18">
+        <v>2112015041.1398706</v>
+      </c>
+      <c r="F11" s="18">
+        <v>1706770.0237499999</v>
+      </c>
+      <c r="G11" s="18">
+        <v>2113721811.1636207</v>
+      </c>
+      <c r="H11" s="28">
+        <v>7.6307272892701832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5020,7 +5078,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -5550,7 +5608,7 @@
         <v>12952</v>
       </c>
       <c r="E25" s="32">
-        <f t="shared" ref="E25:E32" si="3">+((D25-D24)/D24)</f>
+        <f t="shared" ref="E25:E33" si="3">+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
       </c>
       <c r="F25" s="33">
@@ -5702,6 +5760,27 @@
       </c>
       <c r="F32" s="33">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="26">
+        <v>46177</v>
+      </c>
+      <c r="B33" s="27">
+        <v>12861</v>
+      </c>
+      <c r="C33" s="25">
+        <v>3</v>
+      </c>
+      <c r="D33" s="27">
+        <v>12864</v>
+      </c>
+      <c r="E33" s="32">
+        <f t="shared" si="3"/>
+        <v>7.0011668611435238E-4</v>
+      </c>
+      <c r="F33" s="33">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10440" yWindow="135" windowWidth="8595" windowHeight="10080" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2872,7 +2872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2880,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3865,6 +3865,26 @@
         <v>50</v>
       </c>
     </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="22">
+        <v>46182</v>
+      </c>
+      <c r="B54" s="18">
+        <v>0</v>
+      </c>
+      <c r="C54" s="21"/>
+      <c r="D54" s="18">
+        <v>0</v>
+      </c>
+      <c r="E54" s="21"/>
+      <c r="F54" s="18">
+        <v>0</v>
+      </c>
+      <c r="G54" s="21"/>
+      <c r="H54" s="18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3873,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3902,14 +3922,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B2" s="25">
-        <v>58292.928576159997</v>
+        <v>3601.9386242999999</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C9" si="0">+((B2-B3)/B3)</f>
-        <v>5.2345136037951523</v>
+        <f t="shared" ref="C2:C10" si="0">+((B2-B3)/B3)</f>
+        <v>-0.93820968147801931</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -3920,14 +3940,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B3" s="25">
-        <v>9350.0363108799993</v>
+        <v>58292.928576159997</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>1.8327551324816331</v>
+        <v>5.2345136037951523</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -3938,14 +3958,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B4" s="25">
-        <v>3300.6863896099999</v>
+        <v>9350.0363108799993</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>-0.88947445735006914</v>
+        <v>1.8327551324816331</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -3956,14 +3976,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B5" s="25">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>539.15459406063144</v>
+        <v>-0.88947445735006914</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -3974,406 +3994,407 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B6" s="25">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99834811895033015</v>
+        <v>539.15459406063144</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B7" s="25">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>2.616728100871637</v>
+        <v>-0.99834811895033015</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B8" s="25">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
-        <v>425.96466507526281</v>
+        <v>2.616728100871637</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B9" s="25">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99745431244335425</v>
+        <v>425.96466507526281</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B10" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C10" s="31">
-        <f>+((B10-B11)/B11)</f>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="0"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B11" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C11" s="31">
         <f>+((B11-B12)/B12)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B12" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C12" s="31">
         <f>+((B12-B13)/B13)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B13" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C13" s="31">
-        <f>+((B17-B18)/B18)</f>
-        <v>82.182099964255912</v>
+        <f>+((B13-B14)/B14)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B14" s="25">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C14" s="31">
-        <f t="shared" ref="C14:C37" si="1">+((B18-B19)/B19)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B18-B19)/B19)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="26">
+        <v>46162</v>
+      </c>
+      <c r="B15" s="25">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C15" s="31">
+        <f t="shared" ref="C15:C38" si="1">+((B19-B20)/B20)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="26">
         <v>46161</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B16" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="31">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
+    <row r="17" spans="1:3">
+      <c r="A17" s="26">
         <v>46157</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B17" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
+    <row r="18" spans="1:3">
+      <c r="A18" s="26">
         <v>46156</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B18" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26">
+    <row r="19" spans="1:3">
+      <c r="A19" s="26">
         <v>46155</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B19" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="26">
+    <row r="20" spans="1:3">
+      <c r="A20" s="26">
         <v>46154</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B20" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C20" s="31">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="26">
+    <row r="21" spans="1:3">
+      <c r="A21" s="26">
         <v>46153</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B21" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="26">
+    <row r="22" spans="1:3">
+      <c r="A22" s="26">
         <v>46150</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B22" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C22" s="31">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="24">
+    <row r="23" spans="1:3">
+      <c r="A23" s="24">
         <v>46149</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="19">
+    <row r="24" spans="1:3">
+      <c r="A24" s="19">
         <v>46148</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B24" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="19">
+    <row r="25" spans="1:3">
+      <c r="A25" s="19">
         <v>46147</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B25" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="19">
+    <row r="26" spans="1:3">
+      <c r="A26" s="19">
         <v>46146</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B26" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C26" s="31">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="20">
+    <row r="27" spans="1:3">
+      <c r="A27" s="20">
         <v>46142</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B27" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="20">
+    <row r="28" spans="1:3">
+      <c r="A28" s="20">
         <v>46141</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B28" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="31">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="20">
+    <row r="29" spans="1:3">
+      <c r="A29" s="20">
         <v>46140</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B29" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="20">
+    <row r="30" spans="1:3">
+      <c r="A30" s="20">
         <v>46139</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B30" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="20">
+    <row r="31" spans="1:3">
+      <c r="A31" s="20">
         <v>46136</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B31" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="20">
+    <row r="32" spans="1:3">
+      <c r="A32" s="20">
         <v>46135</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B32" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="20">
+    <row r="33" spans="1:3">
+      <c r="A33" s="20">
         <v>46134</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B33" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="20">
+    <row r="34" spans="1:3">
+      <c r="A34" s="20">
         <v>46133</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B34" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="20">
+    <row r="35" spans="1:3">
+      <c r="A35" s="20">
         <v>46132</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B35" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="20">
+    <row r="36" spans="1:3">
+      <c r="A36" s="20">
         <v>46129</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B36" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="31">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="20">
+    <row r="37" spans="1:3">
+      <c r="A37" s="20">
         <v>46128</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B37" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C37" s="31">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="20">
+    <row r="38" spans="1:3">
+      <c r="A38" s="20">
         <v>46127</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B38" s="17">
         <v>15.79809785</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C38" s="31">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B38" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C38" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="39" spans="1:3">
       <c r="A39" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B39" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4381,10 +4402,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B40" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -4392,10 +4413,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B41" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -4403,10 +4424,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B42" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C42" s="16">
         <v>0</v>
@@ -4414,10 +4435,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B43" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
       </c>
       <c r="C43" s="16">
         <v>0</v>
@@ -4425,33 +4446,44 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B44" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
+      </c>
+      <c r="C44" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B45" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B46" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B47" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="20">
  